--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -3775,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3975,9 +3975,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4005,9 +4002,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4035,9 +4029,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4065,9 +4056,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4095,9 +4083,6 @@
           <t>New 8-K filed 2026-05-08 (accession 0001594805-26-000022)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4125,9 +4110,6 @@
           <t>New 144 filed 2026-05-05 (accession 0001950047-26-004066)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4155,9 +4137,6 @@
           <t>New S-8 POS filed 2026-05-05 (accession 0001594805-26-000020)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4185,9 +4164,6 @@
           <t>New 10-Q filed 2026-05-05 (accession 0001594805-26-000019)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4215,9 +4191,6 @@
           <t>New 8-K filed 2026-05-05 (accession 0001594805-26-000018)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4245,9 +4218,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4275,9 +4245,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4305,9 +4272,6 @@
           <t>New 4 filed 2026-05-19 (accession 0001731746-26-000002)</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4335,9 +4299,6 @@
           <t>New 144 filed 2026-05-15 (accession 0001969223-26-000559)</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4365,9 +4326,6 @@
           <t>New 4 filed 2026-05-05 (accession 0002068229-26-000009)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4395,9 +4353,6 @@
           <t>New 4 filed 2026-05-05 (accession 0001525358-26-000012)</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4425,9 +4380,6 @@
           <t>New 4 filed 2026-05-05 (accession 0002047113-26-000006)</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4455,9 +4407,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4485,9 +4434,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4515,9 +4461,6 @@
           <t>New SCHEDULE 13G/A filed 2026-05-15 (accession 0000905148-26-002425)</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4545,9 +4488,6 @@
           <t>New SCHEDULE 13G filed 2026-05-14 (accession 0001167557-26-000087)</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4575,9 +4515,6 @@
           <t>New 4 filed 2026-05-05 (accession 0001766502-26-000048)</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4605,9 +4542,6 @@
           <t>New 4 filed 2026-05-05 (accession 0001766502-26-000047)</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4635,9 +4569,6 @@
           <t>New 4 filed 2026-05-05 (accession 0001766502-26-000046)</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4665,9 +4596,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4695,9 +4623,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4725,9 +4650,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4755,9 +4677,6 @@
           <t>New 4 filed 2026-05-19 (accession 0001628280-26-036519)</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4785,9 +4704,6 @@
           <t>New 4 filed 2026-05-19 (accession 0001628280-26-036518)</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4815,9 +4731,6 @@
           <t>New 4 filed 2026-05-19 (accession 0001628280-26-036517)</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4845,9 +4758,6 @@
           <t>New 144 filed 2026-05-18 (accession 0001950047-26-004684)</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4875,9 +4785,6 @@
           <t>New 144 filed 2026-05-18 (accession 0001950047-26-004683)</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4905,9 +4812,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4935,9 +4839,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4965,9 +4866,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4995,9 +4893,6 @@
           <t>New 10-Q filed 2026-05-08 (accession 0001628280-26-032387)</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5025,9 +4920,6 @@
           <t>New 8-K filed 2026-05-07 (accession 0001628280-26-032064)</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5055,9 +4947,6 @@
           <t>New SCHEDULE 13G filed 2026-04-29 (accession 0002100121-26-000146)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5085,9 +4974,6 @@
           <t>New SCHEDULE 13G/A filed 2026-03-27 (accession 0000102909-26-001417)</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5115,9 +5001,6 @@
           <t>New 8-K filed 2026-03-16 (accession 0001628280-26-018149)</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5145,9 +5028,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5175,9 +5055,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5205,9 +5082,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5235,9 +5109,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5265,9 +5136,6 @@
           <t>New SD filed 2026-05-19 (accession 0001650164-26-000119)</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5295,9 +5163,6 @@
           <t>New SCHEDULE 13G/A filed 2026-05-15 (accession 0001193125-26-227328)</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5325,9 +5190,6 @@
           <t>New SCHEDULE 13G/A filed 2026-05-14 (accession 0001562230-26-000100)</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5355,9 +5217,6 @@
           <t>New S-8 filed 2026-05-08 (accession 0001650164-26-000116)</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5385,9 +5244,6 @@
           <t>New 10-Q filed 2026-05-08 (accession 0001650164-26-000114)</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5415,9 +5271,6 @@
           <t>New 144 filed 2026-05-20 (accession 0001950047-26-004850)</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5445,9 +5298,6 @@
           <t>New 4 filed 2026-05-19 (accession 0002108589-26-000012)</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5475,9 +5325,6 @@
           <t>New SCHEDULE 13G filed 2026-05-18 (accession 0000950103-26-007332)</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5505,9 +5352,6 @@
           <t>New 8-K filed 2026-05-08 (accession 0001783879-26-000065)</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5535,9 +5379,36 @@
           <t>New 4 filed 2026-05-06 (accession 0001705560-26-000011)</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://blog.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -3775,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5406,9 +5406,36 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -3775,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5433,9 +5433,96 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CHWY</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Chewy Inc.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1766502/000114036126022531/ny20064174x3_ars.pdf</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>New ARS filed 2026-05-22 (accession 0001140361-26-022531)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CHWY</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Chewy Inc.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1766502/000114036126022530/ny20064174x2_defa14a.htm</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>New DEFA14A filed 2026-05-22 (accession 0001140361-26-022530)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CHWY</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Chewy Inc.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1766502/000114036126022529/ny20064174x1_def14a.htm</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>New DEF 14A filed 2026-05-22 (accession 0001140361-26-022529)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -3775,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5460,9 +5460,6 @@
           <t>New ARS filed 2026-05-22 (accession 0001140361-26-022531)</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5490,9 +5487,6 @@
           <t>New DEFA14A filed 2026-05-22 (accession 0001140361-26-022530)</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5520,9 +5514,36 @@
           <t>New DEF 14A filed 2026-05-22 (accession 0001140361-26-022529)</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -3775,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5541,9 +5541,36 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1370637/000195004726004998/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-22 (accession 0001950047-26-004998)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -3775,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5568,9 +5568,36 @@
           <t>New 144 filed 2026-05-22 (accession 0001950047-26-004998)</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000187091426000011/xslF345X06/wk-form4_1779483458.xml</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-22 (accession 0001870914-26-000011)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -3775,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5595,9 +5595,36 @@
           <t>New 4 filed 2026-05-22 (accession 0001870914-26-000011)</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.bill.com/legal/terms-of-service</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -3775,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5622,9 +5622,96 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://investors.shopify.com</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://blog.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -3775,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5649,9 +5649,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5679,9 +5676,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5709,9 +5703,66 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1370637/000122768826000004/xslF345X06/form4-05262026_040501.xml</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-26 (accession 0001227688-26-000004)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000119312526239245/d931634d8k.htm</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>New 8-K filed 2026-05-26 (accession 0001193125-26-239245)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -670,7 +670,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>https://investors.shopify.com/corporate-governance/board-of-directors-and-management/default.aspx</t>
+          <t>https://www.shopify.com/investors/board-of-directors</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>https://www.wix.com/blog/news</t>
+          <t>https://www.wix.com/press-room/home</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>https://investors.wix.com/corporate-governance/board-and-executives</t>
+          <t>https://investors.wix.com/board-of-directors</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>https://www.global-e.com/blog/</t>
+          <t>https://www.global-e.com/media-centre/</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -840,12 +840,12 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://www.global-e.com/solutions/</t>
+          <t>https://www.global-e.com/platform/</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>https://www.global-e.com/legal/terms-of-service/</t>
+          <t>https://www.global-e.com/terms/</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>https://newsroom.godaddy.com/about-godaddy/executive-team/</t>
+          <t>https://aboutus.godaddy.net/about-us/team/default.aspx</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>https://investors.ebayinc.com/leadership/default.aspx</t>
+          <t>https://investors.ebayinc.com/corporate-governance/board-of-directors/default.aspx</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://www.ebay.com/sellercenter/resources/selling-fees</t>
+          <t>https://www.ebay.com/sellercenter/selling/start-selling-on-ebay/seller-fees</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>https://investor.wayfair.com/leadership/default.aspx</t>
+          <t>https://www.aboutwayfair.com/leadership</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>https://investors.etsy.com/leadership/default.aspx</t>
+          <t>https://investors.etsy.com/company-information/executive-team</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>https://investor.chewy.com/news-releases</t>
+          <t>https://investor.chewy.com/news-and-events/news/default.aspx</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>https://investor.chewy.com/leadership/default.aspx</t>
+          <t>https://investor.chewy.com/governance/executive-management/default.aspx</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>https://ir.doordash.com/leadership/default.aspx</t>
+          <t>https://ir.doordash.com/governance/management/default.aspx</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://get.doordash.com/en-us/products/merchant-pricing</t>
+          <t>https://merchants.doordash.com/en-us/products/merchant-pricing</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>https://www.instacart.com/company/news/</t>
+          <t>https://www.instacart.com/company/newsroom</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>https://www.instacart.com/plans</t>
+          <t>https://www.instacart.com/instacart-plus</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>https://ir.mtch.com/news-releases</t>
+          <t>https://ir.mtch.com/investor-relations/news-events/news-events/default.aspx</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>https://investors.zillowgroup.com/board-and-management/leadership</t>
+          <t>https://www.zillowgroup.com/about-us/our-leaders/</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>https://www.zillowgroup.com/zg-terms-of-use/</t>
+          <t>https://www.zillow.com/z/corp/terms/</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>https://ir.rocketcompanies.com/leadership/default.aspx</t>
+          <t>https://www.rocketcompanies.com/our-team/leadership/</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>https://investors.compass.com/leadership/default.aspx</t>
+          <t>https://investors.compass.com/governance/management/default.aspx</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>https://www.compass.com/terms/</t>
+          <t>https://www.compass.com/legal/terms-of-service/</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>https://www.appfolio.com/careers/</t>
+          <t>https://www.appfolio.com/company/careers</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://www.appfolio.com/property-manager/pricing/</t>
+          <t>https://www.appfolio.com/pricing</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>https://block.xyz/about</t>
+          <t>https://investors.block.xyz/governance/leadership/default.aspx</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>https://squareup.com/us/en/payments/our-rates</t>
+          <t>https://squareup.com/us/en/payments/our-fees</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>https://www.bill.com/resource/press-releases</t>
+          <t>https://www.bill.com/press-release</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>https://investor.bill.com/leadership/default.aspx</t>
+          <t>https://www.bill.com/leadership</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>https://investor.pypl.com/leadership/default.aspx</t>
+          <t>https://about.pypl.com/who-we-are/executive-leadership/default.aspx</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>https://www.paypal.com/us/legalhub/paypal-user-agreement-full</t>
+          <t>https://www.paypal.com/us/legalhub/paypal/useragreement-full</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>https://investors.toasttab.com/leadership/default.aspx</t>
+          <t>https://pos.toasttab.com/leadership</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>https://www.adyen.com/news</t>
+          <t>https://www.adyen.com/press-and-media</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>https://investors.adyen.com/about-adyen/management-board</t>
+          <t>https://www.adyen.com/about/team</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>https://investors.adyen.com/financial-results</t>
+          <t>https://investors.adyen.com/financials</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>https://www.sezzle.com/</t>
+          <t>https://sezzle.com/premium/</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>https://dave.com/</t>
+          <t>https://dave.com/extra-cash-account</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>https://dave.com/legal/terms-of-service</t>
+          <t>https://dave.com/terms/</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>https://zip.co/media</t>
+          <t>https://zip.co/investors/news</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>https://help.zip.co/hc/en-us/articles/360000750996-Terms-of-Use</t>
+          <t>https://zip.co/au/page/important-information</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>https://www.asx.com.au/asx/share-price-research/company/ZIP</t>
+          <t>https://zip.co/investors/asx-announcements</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>https://www.klarna.com/international/about-klarna/leadership/</t>
+          <t>https://investors.klarna.com/governance/leadership/default.aspx</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>https://www.klarna.com/us/legal/terms-of-use/</t>
+          <t>https://www.klarna.com/us/terms-of-use/</t>
         </is>
       </c>
       <c r="J28" s="10" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>https://robinhood.com/us/en/support/articles/fees-and-charges/</t>
+          <t>https://robinhood.com/us/en/support/articles/trading-fees-on-robinhood/</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>https://robinhood.com/us/en/support/articles/customer-agreement/</t>
+          <t>https://cdn.robinhood.com/assets/robinhood/legal/Robinhood-Customer-Agreement.pdf</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>https://www.upstart.com/legal/terms-of-use</t>
+          <t>https://www.upstart.com/terms</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>https://ir.rh.com/leadership/default.aspx</t>
+          <t>https://ir.rh.com/corporate-governance/leadership</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>https://www.williams-sonoma.com/customer-service/terms-of-use.html</t>
+          <t>https://www.williams-sonoma.com/m/customer-service/terms.html</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>https://www.tempurpedic.com/mattresses/</t>
+          <t>https://www.tempurpedic.com/shop-mattresses/</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>https://ir.enova.com/news-releases</t>
+          <t>https://ir.enova.com/news-events/news-releases/default.aspx</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>https://ir.enova.com/leadership/default.aspx</t>
+          <t>https://ir.enova.com/corporate-governance/leadership-team/default.aspx</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -3180,12 +3180,12 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://www.enova.com/products/</t>
+          <t>https://www.enova.com/brands/</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>https://www.enova.com/legal/terms-of-use/</t>
+          <t>https://www.enova.com/terms-conditions/</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>https://investors.on.com/corporate-governance/board-of-directors</t>
+          <t>https://investors.on-running.com/governance/default.aspx</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -3775,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H143"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5730,9 +5730,6 @@
           <t>New 4 filed 2026-05-26 (accession 0001227688-26-000004)</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5760,9 +5757,1953 @@
           <t>New 8-K filed 2026-05-26 (accession 0001193125-26-239245)</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/legal/terms</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://news.shopify.com</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://investors.shopify.com</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000159480526000022/shop-20260508.htm</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>New 8-K filed 2026-05-08 (accession 0001594805-26-000022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000195004726004066/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-05 (accession 0001950047-26-004066)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000159480526000020/forms-8postxeffectiveamend.htm</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>New S-8 POS filed 2026-05-05 (accession 0001594805-26-000020)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000159480526000019/shop-20260331.htm</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>New 10-Q filed 2026-05-05 (accession 0001594805-26-000019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000159480526000018/shop-20260505.htm</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>New 8-K filed 2026-05-05 (accession 0001594805-26-000018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://support.wix.com/en/article/terms-of-use</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/upgrade/website</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://investors.wix.com</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000119312526225926/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>New SCHEDULE 13G/A filed 2026-05-15 (accession 0001193125-26-225926)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000090266426002441/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>New SCHEDULE 13G/A filed 2026-05-14 (accession 0000902664-26-002441)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000117266126001868/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>New SCHEDULE 13G filed 2026-05-14 (accession 0001172661-26-001868)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000117891326002642/zk2635313.htm</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>New S-8 filed 2026-05-13 (accession 0001178913-26-002642)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000117891326002640/zk2635312.htm</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>New S-8 filed 2026-05-13 (accession 0001178913-26-002640)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://help.doordash.com/consumers/s/terms-of-service</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://ir.doordash.com</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726005086/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-26 (accession 0001950047-26-005086)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726005081/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-26 (accession 0001950047-26-005081)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726004985/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-22 (accession 0001950047-26-004985)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726004984/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-22 (accession 0001950047-26-004984)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183239026000011/xslF345X06/form4-05222026_040501.xml</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-22 (accession 0001832390-26-000011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/terms</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000165168726000009/xslF345X06/wk-form4_1779221300.xml</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-19 (accession 0001651687-26-000009)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000202205026000007/xslF345X06/wk-form4_1779221163.xml</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-19 (accession 0002022050-26-000007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000199010626000014/xslF345X06/wk-form4_1779221074.xml</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-19 (accession 0001990106-26-000014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000208293026000008/xslF345X06/wk-form4_1779220992.xml</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-19 (accession 0002082930-26-000008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000192109426000512/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-18 (accession 0001921094-26-000512)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/legal/terms</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/investors/board-of-directors</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://news.shopify.com</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://investors.shopify.com</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000159480526000022/shop-20260508.htm</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>New 8-K filed 2026-05-08 (accession 0001594805-26-000022)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000195004726004066/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-05 (accession 0001950047-26-004066)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000159480526000020/forms-8postxeffectiveamend.htm</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>New S-8 POS filed 2026-05-05 (accession 0001594805-26-000020)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000159480526000019/shop-20260331.htm</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>New 10-Q filed 2026-05-05 (accession 0001594805-26-000019)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000159480526000018/shop-20260505.htm</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>New 8-K filed 2026-05-05 (accession 0001594805-26-000018)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://support.wix.com/en/article/terms-of-use</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://investors.wix.com/board-of-directors</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/upgrade/website</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/press-room/home</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://investors.wix.com</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000119312526225926/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>New SCHEDULE 13G/A filed 2026-05-15 (accession 0001193125-26-225926)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000090266426002441/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>New SCHEDULE 13G/A filed 2026-05-14 (accession 0000902664-26-002441)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000117266126001868/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>New SCHEDULE 13G filed 2026-05-14 (accession 0001172661-26-001868)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000117891326002642/zk2635313.htm</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>New S-8 filed 2026-05-13 (accession 0001178913-26-002642)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000117891326002640/zk2635312.htm</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>New S-8 filed 2026-05-13 (accession 0001178913-26-002640)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://help.doordash.com/consumers/s/terms-of-service</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://ir.doordash.com/governance/management/default.aspx</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://ir.doordash.com</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726005086/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-26 (accession 0001950047-26-005086)</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726005081/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-26 (accession 0001950047-26-005081)</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726004985/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-22 (accession 0001950047-26-004985)</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726004984/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-22 (accession 0001950047-26-004984)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183239026000011/xslF345X06/form4-05222026_040501.xml</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-22 (accession 0001832390-26-000011)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/terms</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/company/newsroom</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000165168726000009/xslF345X06/wk-form4_1779221300.xml</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-19 (accession 0001651687-26-000009)</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000202205026000007/xslF345X06/wk-form4_1779221163.xml</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-19 (accession 0002022050-26-000007)</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000199010626000014/xslF345X06/wk-form4_1779221074.xml</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-19 (accession 0001990106-26-000014)</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000208293026000008/xslF345X06/wk-form4_1779220992.xml</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-19 (accession 0002082930-26-000008)</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000192109426000512/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-18 (accession 0001921094-26-000512)</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,6 +68,9 @@
       <name val="Calibri"/>
       <family val="2"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -136,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -178,6 +181,7 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -543,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,6 +645,21 @@
           <t>Monitoring Notes</t>
         </is>
       </c>
+      <c r="Q1" s="15" t="inlineStr">
+        <is>
+          <t>Priority Tier</t>
+        </is>
+      </c>
+      <c r="R1" s="15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="S1" s="15" t="inlineStr">
+        <is>
+          <t>Newsroom RSS</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -723,6 +742,14 @@
           <t>Monitor changelog.shopify.com; App Store changes signal platform strategy</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -801,6 +828,19 @@
           <t>Israeli co; files 20-F; monitor Studio AI website builder product</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R3" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/press-room/home/blog-feed.xml</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -879,6 +919,14 @@
           <t>Israeli co; files 20-F; watch Shopify partnership; merchant wins are leading indicator</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -957,6 +1005,14 @@
           <t>Monitor Airo AI product and domain pricing; SMB pricing changes are material</t>
         </is>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1035,6 +1091,14 @@
           <t>Seller fee changes are key signal; also watch eBay Seller Hub announcements</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" ht="52" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -1113,6 +1177,14 @@
           <t>Monitor supplier portal for supplier terms; tech/engineering headcount is leading indicator</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1191,6 +1263,14 @@
           <t>Also monitor r/EtsySellers — seller sentiment is material; transaction fee changes cause seller exodus</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" ht="52" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -1269,6 +1349,14 @@
           <t>Autoship pricing and Chewy Vet telehealth are key monitoring targets</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1347,6 +1435,14 @@
           <t>Monitor DashPass pricing and merchant commission; also r/doordash_drivers for gig sentiment</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R10" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -1425,6 +1521,14 @@
           <t>Instacart+ subscription pricing; Carrot Ads advertising product is key growth vector</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1503,6 +1607,14 @@
           <t>Super/Max subscription pricing is key; AI feature rollouts have been material catalysts</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -1581,6 +1693,14 @@
           <t>Monitor Tinder Gold/Platinum and Hinge subscription pricing separately; track Hinge product blog</t>
         </is>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R13" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1659,6 +1779,14 @@
           <t>Agent pricing (Premier Agent) is key; also monitor ShowingTime and Follow Up Boss products</t>
         </is>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R14" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1737,6 +1865,14 @@
           <t>Monitor Homes.com product page separately; aggressively investing in residential — track agent sign-up terms</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R15" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1815,6 +1951,14 @@
           <t>Mortgage rate page is real-time signal; monitor Rocket Money product pages for cross-sell</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R16" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -1893,6 +2037,14 @@
           <t>Agent commission splits and technology platform terms are key; agent count and retention are leading indicators</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R17" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1971,6 +2123,14 @@
           <t>Pricing page changes (per-unit pricing) are highly material; AppFolio Intelligence AI is key</t>
         </is>
       </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R18" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
@@ -2049,6 +2209,14 @@
           <t>⚠️ VERIFY TICKER: Block typically trades as SQ — confirm XYZ. TWO product/pricing pages to monitor: Square rates (squareup.com/us/en/payments/our-rates) AND Cash App (cash.app). Square T&amp;C: squareup.com/us/en/legal/general/ua. Cash App T&amp;C: cash.app/legal/us/en/tos.</t>
         </is>
       </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -2127,6 +2295,14 @@
           <t>Pricing page is key — tier structure for AP/AR automation; also track Divvy spend management product</t>
         </is>
       </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R20" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -2205,6 +2381,14 @@
           <t>Merchant fee changes are highly material; also monitor Venmo monetisation and PayPal Everywhere</t>
         </is>
       </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R21" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -2283,6 +2467,14 @@
           <t>Pricing page (processing rate + SaaS fee) is highly material; also track Toast Capital lending product</t>
         </is>
       </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R22" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -2361,6 +2553,14 @@
           <t>Dutch co; H1/H2 reporting only (not quarterly); pricing page is particularly informative on take-rate trends</t>
         </is>
       </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="R23" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -2439,6 +2639,14 @@
           <t>Small-cap BNPL; monitor merchant partner announcements and Sezzle Premium subscription terms</t>
         </is>
       </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R24" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -2517,6 +2725,14 @@
           <t>ExtraCash advance limits and fee structure are key monitoring targets; also track Dave Banking product</t>
         </is>
       </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R25" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -2595,6 +2811,14 @@
           <t>ASX-listed; H1/FY reports only; merchant fee changes are key</t>
         </is>
       </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="R26" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
@@ -2673,6 +2897,14 @@
           <t>Monitor merchant partner page for new integrations; Affirm Card (Debit+) is key growth vector</t>
         </is>
       </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R27" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" ht="52" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
@@ -2751,6 +2983,14 @@
           <t>⚠️ VERIFY: Recently IPO'd on NYSE — confirm IR URL and SEC filings link. Monitor AI shopping assistant product closely.</t>
         </is>
       </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="R28" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" ht="52" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
@@ -2829,6 +3069,14 @@
           <t>Monitor Robinhood Gold pricing and Legend desktop platform; international expansion is key signal</t>
         </is>
       </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="R29" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" ht="52" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -2907,6 +3155,14 @@
           <t>Bank/CU partnership announcements are key leading indicators; monitor auto loan and HELOC product expansion</t>
         </is>
       </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R30" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" ht="52" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
@@ -2985,6 +3241,14 @@
           <t>RH Membership pricing is key; monitor RH Hospitality expansion; Gary Friedman letters to shareholders are essential reading</t>
         </is>
       </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R31" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" ht="52" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -3063,6 +3327,14 @@
           <t>Monitor all brands: West Elm, Pottery Barn, Rejuvenation; B2B contract business is underappreciated</t>
         </is>
       </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R32" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" ht="52" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -3141,6 +3413,14 @@
           <t>Fmr. Tempur Sealy (TPX); renamed + rebranded Feb 2025. Owns Tempur-Pedic, Sealy, Stearns &amp; Foster brands + Mattress Firm retail chain. Monitor all three brand sites separately: tempurpedic.com, sealy.com, mattressfirm.com.</t>
         </is>
       </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R33" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" ht="52" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -3219,6 +3499,14 @@
           <t>Regulatory news (CFPB rules on installment lending) is major risk signal; monitor NetCredit and CashNetUSA</t>
         </is>
       </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R34" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" ht="52" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
@@ -3297,6 +3585,14 @@
           <t>Swiss co; files 20-F; monitor DTC expansion and Loewe collaboration; trail/Cloudmonster launches signal brand trajectory</t>
         </is>
       </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="R35" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" ht="52" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -3374,6 +3670,14 @@
         <is>
           <t>Japanese character IP co (Hello Kitty, My Melody, Cinnamoroll etc.); TSE 8136; monitor global licensing deal announcements, theme park updates (Sanrio Puroland), and US/Americas expansion (Craig Takiguchi named CEO Americas Jan 2026).</t>
         </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="R36" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3775,7 +4079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6621,9 +6925,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6651,9 +6952,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6681,9 +6979,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6711,9 +7006,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6741,9 +7033,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6771,9 +7060,6 @@
           <t>New 8-K filed 2026-05-08 (accession 0001594805-26-000022)</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6801,9 +7087,6 @@
           <t>New 144 filed 2026-05-05 (accession 0001950047-26-004066)</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6831,9 +7114,6 @@
           <t>New S-8 POS filed 2026-05-05 (accession 0001594805-26-000020)</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6861,9 +7141,6 @@
           <t>New 10-Q filed 2026-05-05 (accession 0001594805-26-000019)</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6891,9 +7168,6 @@
           <t>New 8-K filed 2026-05-05 (accession 0001594805-26-000018)</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6921,9 +7195,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6951,9 +7222,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6981,9 +7249,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7011,9 +7276,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7041,9 +7303,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7071,9 +7330,6 @@
           <t>New SCHEDULE 13G/A filed 2026-05-15 (accession 0001193125-26-225926)</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7101,9 +7357,6 @@
           <t>New SCHEDULE 13G/A filed 2026-05-14 (accession 0000902664-26-002441)</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7131,9 +7384,6 @@
           <t>New SCHEDULE 13G filed 2026-05-14 (accession 0001172661-26-001868)</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7161,9 +7411,6 @@
           <t>New S-8 filed 2026-05-13 (accession 0001178913-26-002642)</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7191,9 +7438,6 @@
           <t>New S-8 filed 2026-05-13 (accession 0001178913-26-002640)</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7221,9 +7465,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7251,9 +7492,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7281,9 +7519,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7311,9 +7546,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7341,9 +7573,6 @@
           <t>New 144 filed 2026-05-26 (accession 0001950047-26-005086)</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7371,9 +7600,6 @@
           <t>New 144 filed 2026-05-26 (accession 0001950047-26-005081)</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7401,9 +7627,6 @@
           <t>New 144 filed 2026-05-22 (accession 0001950047-26-004985)</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7431,9 +7654,6 @@
           <t>New 144 filed 2026-05-22 (accession 0001950047-26-004984)</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7461,9 +7681,6 @@
           <t>New 4 filed 2026-05-22 (accession 0001832390-26-000011)</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7491,9 +7708,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7521,9 +7735,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7551,9 +7762,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7581,9 +7789,6 @@
           <t>New 4 filed 2026-05-19 (accession 0001651687-26-000009)</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7611,9 +7816,6 @@
           <t>New 4 filed 2026-05-19 (accession 0002022050-26-000007)</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7641,9 +7843,6 @@
           <t>New 4 filed 2026-05-19 (accession 0001990106-26-000014)</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7671,9 +7870,6 @@
           <t>New 4 filed 2026-05-19 (accession 0002082930-26-000008)</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7701,9 +7897,1236 @@
           <t>New 144 filed 2026-05-18 (accession 0001921094-26-000512)</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/legal/terms</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/investors/board-of-directors</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>https://news.shopify.com</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>https://investors.shopify.com</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000159480526000022/shop-20260508.htm</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>New 8-K filed 2026-05-08 (accession 0001594805-26-000022)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000195004726004066/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-05 (accession 0001950047-26-004066)</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000159480526000020/forms-8postxeffectiveamend.htm</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>New S-8 POS filed 2026-05-05 (accession 0001594805-26-000020)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000159480526000019/shop-20260331.htm</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>New 10-Q filed 2026-05-05 (accession 0001594805-26-000019)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000159480526000018/shop-20260505.htm</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>New 8-K filed 2026-05-05 (accession 0001594805-26-000018)</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/press-room/home/post/wix-reports-first-quarter-2026-results</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>newsroom: Wix Reports First Quarter 2026 Results</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/press-room/home/post/wix-to-participate-in-fireside-chat-at-the-2026-jefferies-software-internet-and-ai-conference</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>newsroom: Wix to Participate in Fireside Chat at the 2026 Jefferies Software, Internet, and AI Conference</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/press-room/home/post/wix-to-announce-first-quarter-2026-results-on-may-13-2026</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>newsroom: Wix to Announce First Quarter 2026 Results on May 13, 2026</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/press-room/home/post/wix-launches-hipaa-compliance-solution-expanding-support-for-health-service-providers-in-the-u-s</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>newsroom: Wix Launches HIPAA Compliance Solution Expanding Support for Health Service Providers in the U.S.</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/press-room/home/post/wix-announces-final-results-of-modified-dutch-auction-tender-offer</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>newsroom: Wix Announces Final Results of Modified Dutch Auction Tender Offer</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>https://support.wix.com/en/article/terms-of-use</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>https://investors.wix.com/board-of-directors</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/upgrade/website</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>https://investors.wix.com</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000119312526225926/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>New SCHEDULE 13G/A filed 2026-05-15 (accession 0001193125-26-225926)</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000090266426002441/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>New SCHEDULE 13G/A filed 2026-05-14 (accession 0000902664-26-002441)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000117266126001868/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>New SCHEDULE 13G filed 2026-05-14 (accession 0001172661-26-001868)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000117891326002642/zk2635313.htm</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>New S-8 filed 2026-05-13 (accession 0001178913-26-002642)</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000117891326002640/zk2635312.htm</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>New S-8 filed 2026-05-13 (accession 0001178913-26-002640)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>https://help.doordash.com/consumers/s/terms-of-service</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>https://ir.doordash.com/governance/management/default.aspx</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>https://ir.doordash.com</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726005086/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-26 (accession 0001950047-26-005086)</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726005081/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-26 (accession 0001950047-26-005081)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726004985/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-22 (accession 0001950047-26-004985)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726004984/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-22 (accession 0001950047-26-004984)</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183239026000011/xslF345X06/form4-05222026_040501.xml</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-22 (accession 0001832390-26-000011)</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/terms</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/company/newsroom</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000165168726000009/xslF345X06/wk-form4_1779221300.xml</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-19 (accession 0001651687-26-000009)</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000202205026000007/xslF345X06/wk-form4_1779221163.xml</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-19 (accession 0002022050-26-000007)</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000199010626000014/xslF345X06/wk-form4_1779221074.xml</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-19 (accession 0001990106-26-000014)</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000208293026000008/xslF345X06/wk-form4_1779220992.xml</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-19 (accession 0002082930-26-000008)</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000192109426000512/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-18 (accession 0001921094-26-000512)</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4079,7 +4079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H225"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -7924,9 +7924,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7954,9 +7951,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7984,9 +7978,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8014,9 +8005,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8044,9 +8032,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8074,9 +8059,6 @@
           <t>New 8-K filed 2026-05-08 (accession 0001594805-26-000022)</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8104,9 +8086,6 @@
           <t>New 144 filed 2026-05-05 (accession 0001950047-26-004066)</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8134,9 +8113,6 @@
           <t>New S-8 POS filed 2026-05-05 (accession 0001594805-26-000020)</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8164,9 +8140,6 @@
           <t>New 10-Q filed 2026-05-05 (accession 0001594805-26-000019)</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8194,9 +8167,6 @@
           <t>New 8-K filed 2026-05-05 (accession 0001594805-26-000018)</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8224,9 +8194,6 @@
           <t>newsroom: Wix Reports First Quarter 2026 Results</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8254,9 +8221,6 @@
           <t>newsroom: Wix to Participate in Fireside Chat at the 2026 Jefferies Software, Internet, and AI Conference</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8284,9 +8248,6 @@
           <t>newsroom: Wix to Announce First Quarter 2026 Results on May 13, 2026</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8314,9 +8275,6 @@
           <t>newsroom: Wix Launches HIPAA Compliance Solution Expanding Support for Health Service Providers in the U.S.</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8344,9 +8302,6 @@
           <t>newsroom: Wix Announces Final Results of Modified Dutch Auction Tender Offer</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8374,9 +8329,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8404,9 +8356,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8434,9 +8383,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8464,9 +8410,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8494,9 +8437,6 @@
           <t>New SCHEDULE 13G/A filed 2026-05-15 (accession 0001193125-26-225926)</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8524,9 +8464,6 @@
           <t>New SCHEDULE 13G/A filed 2026-05-14 (accession 0000902664-26-002441)</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8554,9 +8491,6 @@
           <t>New SCHEDULE 13G filed 2026-05-14 (accession 0001172661-26-001868)</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8584,9 +8518,6 @@
           <t>New S-8 filed 2026-05-13 (accession 0001178913-26-002642)</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8614,9 +8545,6 @@
           <t>New S-8 filed 2026-05-13 (accession 0001178913-26-002640)</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8644,9 +8572,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8674,9 +8599,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8704,9 +8626,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8734,9 +8653,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8764,9 +8680,6 @@
           <t>New 144 filed 2026-05-26 (accession 0001950047-26-005086)</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8794,9 +8707,6 @@
           <t>New 144 filed 2026-05-26 (accession 0001950047-26-005081)</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8824,9 +8734,6 @@
           <t>New 144 filed 2026-05-22 (accession 0001950047-26-004985)</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8854,9 +8761,6 @@
           <t>New 144 filed 2026-05-22 (accession 0001950047-26-004984)</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8884,9 +8788,6 @@
           <t>New 4 filed 2026-05-22 (accession 0001832390-26-000011)</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8914,9 +8815,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8944,9 +8842,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8974,9 +8869,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9004,9 +8896,6 @@
           <t>New 4 filed 2026-05-19 (accession 0001651687-26-000009)</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9034,9 +8923,6 @@
           <t>New 4 filed 2026-05-19 (accession 0002022050-26-000007)</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9064,9 +8950,6 @@
           <t>New 4 filed 2026-05-19 (accession 0001990106-26-000014)</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9094,9 +8977,6 @@
           <t>New 4 filed 2026-05-19 (accession 0002082930-26-000008)</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9124,9 +9004,1236 @@
           <t>New 144 filed 2026-05-18 (accession 0001921094-26-000512)</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/legal/terms</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/investors/board-of-directors</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>https://news.shopify.com</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>https://investors.shopify.com</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000159480526000022/shop-20260508.htm</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>New 8-K filed 2026-05-08 (accession 0001594805-26-000022)</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000195004726004066/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-05 (accession 0001950047-26-004066)</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000159480526000020/forms-8postxeffectiveamend.htm</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>New S-8 POS filed 2026-05-05 (accession 0001594805-26-000020)</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000159480526000019/shop-20260331.htm</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>New 10-Q filed 2026-05-05 (accession 0001594805-26-000019)</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000159480526000018/shop-20260505.htm</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>New 8-K filed 2026-05-05 (accession 0001594805-26-000018)</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/press-room/home/post/wix-reports-first-quarter-2026-results</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>newsroom: Wix Reports First Quarter 2026 Results</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/press-room/home/post/wix-to-participate-in-fireside-chat-at-the-2026-jefferies-software-internet-and-ai-conference</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>newsroom: Wix to Participate in Fireside Chat at the 2026 Jefferies Software, Internet, and AI Conference</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/press-room/home/post/wix-to-announce-first-quarter-2026-results-on-may-13-2026</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>newsroom: Wix to Announce First Quarter 2026 Results on May 13, 2026</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/press-room/home/post/wix-launches-hipaa-compliance-solution-expanding-support-for-health-service-providers-in-the-u-s</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>newsroom: Wix Launches HIPAA Compliance Solution Expanding Support for Health Service Providers in the U.S.</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/press-room/home/post/wix-announces-final-results-of-modified-dutch-auction-tender-offer</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>newsroom: Wix Announces Final Results of Modified Dutch Auction Tender Offer</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>https://support.wix.com/en/article/terms-of-use</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>https://investors.wix.com/board-of-directors</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/upgrade/website</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>https://investors.wix.com</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000119312526225926/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>New SCHEDULE 13G/A filed 2026-05-15 (accession 0001193125-26-225926)</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000090266426002441/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>New SCHEDULE 13G/A filed 2026-05-14 (accession 0000902664-26-002441)</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000117266126001868/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>New SCHEDULE 13G filed 2026-05-14 (accession 0001172661-26-001868)</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000117891326002642/zk2635313.htm</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>New S-8 filed 2026-05-13 (accession 0001178913-26-002642)</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000117891326002640/zk2635312.htm</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>New S-8 filed 2026-05-13 (accession 0001178913-26-002640)</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>https://help.doordash.com/consumers/s/terms-of-service</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>https://ir.doordash.com/governance/management/default.aspx</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>https://ir.doordash.com</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726005086/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-26 (accession 0001950047-26-005086)</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726005081/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-26 (accession 0001950047-26-005081)</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726004985/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-22 (accession 0001950047-26-004985)</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726004984/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-22 (accession 0001950047-26-004984)</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183239026000011/xslF345X06/form4-05222026_040501.xml</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-22 (accession 0001832390-26-000011)</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/terms</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/company/newsroom</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000165168726000009/xslF345X06/wk-form4_1779221300.xml</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-19 (accession 0001651687-26-000009)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000202205026000007/xslF345X06/wk-form4_1779221163.xml</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-19 (accession 0002022050-26-000007)</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000199010626000014/xslF345X06/wk-form4_1779221074.xml</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-19 (accession 0001990106-26-000014)</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000208293026000008/xslF345X06/wk-form4_1779220992.xml</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-19 (accession 0002082930-26-000008)</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000192109426000512/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-18 (accession 0001921094-26-000512)</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4079,7 +4079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H225"/>
+  <dimension ref="A1:H236"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -9031,9 +9031,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9061,9 +9058,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9091,9 +9085,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9121,9 +9112,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9151,9 +9139,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9181,9 +9166,6 @@
           <t>New 8-K filed 2026-05-08 (accession 0001594805-26-000022)</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9211,9 +9193,6 @@
           <t>New 144 filed 2026-05-05 (accession 0001950047-26-004066)</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9241,9 +9220,6 @@
           <t>New S-8 POS filed 2026-05-05 (accession 0001594805-26-000020)</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9271,9 +9247,6 @@
           <t>New 10-Q filed 2026-05-05 (accession 0001594805-26-000019)</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9301,9 +9274,6 @@
           <t>New 8-K filed 2026-05-05 (accession 0001594805-26-000018)</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9331,9 +9301,6 @@
           <t>newsroom: Wix Reports First Quarter 2026 Results</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9361,9 +9328,6 @@
           <t>newsroom: Wix to Participate in Fireside Chat at the 2026 Jefferies Software, Internet, and AI Conference</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9391,9 +9355,6 @@
           <t>newsroom: Wix to Announce First Quarter 2026 Results on May 13, 2026</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
-      <c r="H197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9421,9 +9382,6 @@
           <t>newsroom: Wix Launches HIPAA Compliance Solution Expanding Support for Health Service Providers in the U.S.</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9451,9 +9409,6 @@
           <t>newsroom: Wix Announces Final Results of Modified Dutch Auction Tender Offer</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9481,9 +9436,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9511,9 +9463,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9541,9 +9490,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9571,9 +9517,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -9601,9 +9544,6 @@
           <t>New SCHEDULE 13G/A filed 2026-05-15 (accession 0001193125-26-225926)</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9631,9 +9571,6 @@
           <t>New SCHEDULE 13G/A filed 2026-05-14 (accession 0000902664-26-002441)</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -9661,9 +9598,6 @@
           <t>New SCHEDULE 13G filed 2026-05-14 (accession 0001172661-26-001868)</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9691,9 +9625,6 @@
           <t>New S-8 filed 2026-05-13 (accession 0001178913-26-002642)</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr"/>
-      <c r="H207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -9721,9 +9652,6 @@
           <t>New S-8 filed 2026-05-13 (accession 0001178913-26-002640)</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -9751,9 +9679,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr"/>
-      <c r="H209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -9781,9 +9706,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr"/>
-      <c r="H210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -9811,9 +9733,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
-      <c r="H211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -9841,9 +9760,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -9871,9 +9787,6 @@
           <t>New 144 filed 2026-05-26 (accession 0001950047-26-005086)</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -9901,9 +9814,6 @@
           <t>New 144 filed 2026-05-26 (accession 0001950047-26-005081)</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr"/>
-      <c r="H214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -9931,9 +9841,6 @@
           <t>New 144 filed 2026-05-22 (accession 0001950047-26-004985)</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr"/>
-      <c r="H215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -9961,9 +9868,6 @@
           <t>New 144 filed 2026-05-22 (accession 0001950047-26-004984)</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -9991,9 +9895,6 @@
           <t>New 4 filed 2026-05-22 (accession 0001832390-26-000011)</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
-      <c r="H217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -10021,9 +9922,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10051,9 +9949,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10081,9 +9976,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr"/>
-      <c r="H220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -10111,9 +10003,6 @@
           <t>New 4 filed 2026-05-19 (accession 0001651687-26-000009)</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -10141,9 +10030,6 @@
           <t>New 4 filed 2026-05-19 (accession 0002022050-26-000007)</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr"/>
-      <c r="H222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -10171,9 +10057,6 @@
           <t>New 4 filed 2026-05-19 (accession 0001990106-26-000014)</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr"/>
-      <c r="H223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -10201,9 +10084,6 @@
           <t>New 4 filed 2026-05-19 (accession 0002082930-26-000008)</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -10231,9 +10111,336 @@
           <t>New 144 filed 2026-05-18 (accession 0001921094-26-000512)</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr"/>
-      <c r="H225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726005086/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-26 (accession 0001950047-26-005086)</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726005081/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-26 (accession 0001950047-26-005081)</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726004985/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-22 (accession 0001950047-26-004985)</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726004984/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>New 144 filed 2026-05-22 (accession 0001950047-26-004984)</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183239026000011/xslF345X06/form4-05222026_040501.xml</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-22 (accession 0001832390-26-000011)</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183261426000017/xslF345X06/form4-05222026_040512.xml</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-22 (accession 0001832614-26-000017)</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000189968826000010/xslF345X06/form4-05222026_040510.xml</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-22 (accession 0001899688-26-000010)</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000184970926000012/xslF345X06/form4-05222026_040508.xml</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-22 (accession 0001849709-26-000012)</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183261226000012/xslF345X06/form4-05222026_040507.xml</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-22 (accession 0001832612-26-000012)</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183355226000008/xslF345X06/form4-05222026_040505.xml</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-22 (accession 0001833552-26-000008)</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000163564826000008/xslF345X06/form4-05222026_040503.xml</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>New 4 filed 2026-05-22 (accession 0001635648-26-000008)</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4079,7 +4079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H236"/>
+  <dimension ref="A1:H237"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10138,9 +10138,6 @@
           <t>New 144 filed 2026-05-26 (accession 0001950047-26-005086)</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
-      <c r="H226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -10168,9 +10165,6 @@
           <t>New 144 filed 2026-05-26 (accession 0001950047-26-005081)</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -10198,9 +10192,6 @@
           <t>New 144 filed 2026-05-22 (accession 0001950047-26-004985)</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -10228,9 +10219,6 @@
           <t>New 144 filed 2026-05-22 (accession 0001950047-26-004984)</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -10258,9 +10246,6 @@
           <t>New 4 filed 2026-05-22 (accession 0001832390-26-000011)</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -10288,9 +10273,6 @@
           <t>New 4 filed 2026-05-22 (accession 0001832614-26-000017)</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
-      <c r="H231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -10318,9 +10300,6 @@
           <t>New 4 filed 2026-05-22 (accession 0001899688-26-000010)</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr"/>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -10348,9 +10327,6 @@
           <t>New 4 filed 2026-05-22 (accession 0001849709-26-000012)</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr"/>
-      <c r="G233" t="inlineStr"/>
-      <c r="H233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -10378,9 +10354,6 @@
           <t>New 4 filed 2026-05-22 (accession 0001832612-26-000012)</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr"/>
-      <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -10408,9 +10381,6 @@
           <t>New 4 filed 2026-05-22 (accession 0001833552-26-000008)</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr"/>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -10438,9 +10408,36 @@
           <t>New 4 filed 2026-05-22 (accession 0001635648-26-000008)</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4079,7 +4079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H237"/>
+  <dimension ref="A1:H249"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10435,9 +10435,366 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr"/>
-      <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726005086/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Yandell Keith (Officer) plans to sell 2,643 shares (~$423.5K) on/after 05/26/2026</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726005081/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Adarkar Prabir (Officer) plans to sell 11,739 shares (~$1.88M) on/after 05/26/2026</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726004985/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Sherringham Tia (Officer) plans to sell 2,743 shares (~$436.9K) on/after 05/22/2026</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726004984/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Lee Gordon (Officer) plans to sell 2,204 shares (~$351.0K) on/after 05/22/2026</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183239026000011/xslF345X06/form4-05222026_040501.xml</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Fang Andy (Director) sold 1,164 shares @ $155.59 ($181.1K) on 2026-05-20</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183261426000017/xslF345X06/form4-05222026_040512.xml</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Tang Stanley (Director) sold 1,592 shares @ $155.59 ($247.7K) on 2026-05-20</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000189968826000010/xslF345X06/form4-05222026_040510.xml</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sherringham Tia (GENERAL COUNSEL AND SECRETARY) sold 7,690 shares @ $155.59 ($1.20M) on 2026-05-20</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000184970926000012/xslF345X06/form4-05222026_040508.xml</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Inukonda Ravi (CHIEF FINANCIAL OFFICER) sold 19,505 shares @ $155.59 ($3.03M) on 2026-05-20</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183261226000012/xslF345X06/form4-05222026_040507.xml</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Adarkar Prabir (PRESIDENT AND COO) sold 17,126 shares @ $155.59 ($2.66M) on 2026-05-20</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183355226000008/xslF345X06/form4-05222026_040505.xml</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Yandell Keith (CHIEF BUSINESS OFFICER) sold 4,227 shares @ $155.59 ($657.7K) on 2026-05-20</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000163564826000008/xslF345X06/form4-05222026_040503.xml</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lee Gordon S (CHIEF ACCOUNTING OFFICER) sold 2,910 shares @ $155.59 ($452.8K) on 2026-05-20</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -660,6 +660,11 @@
           <t>Newsroom RSS</t>
         </is>
       </c>
+      <c r="T1" s="15" t="inlineStr">
+        <is>
+          <t>Pricing Selector</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -750,6 +755,11 @@
       <c r="R2" t="b">
         <v>1</v>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -841,6 +851,11 @@
           <t>https://www.wix.com/press-room/home/blog-feed.xml</t>
         </is>
       </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,6 +1543,11 @@
       </c>
       <c r="R11" t="b">
         <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
@@ -10462,9 +10482,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Yandell Keith (Officer) plans to sell 2,643 shares (~$423.5K) on/after 05/26/2026</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -10492,9 +10509,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Adarkar Prabir (Officer) plans to sell 11,739 shares (~$1.88M) on/after 05/26/2026</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr"/>
-      <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -10522,9 +10536,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Sherringham Tia (Officer) plans to sell 2,743 shares (~$436.9K) on/after 05/22/2026</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -10552,9 +10563,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Lee Gordon (Officer) plans to sell 2,204 shares (~$351.0K) on/after 05/22/2026</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr"/>
-      <c r="H241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -10582,9 +10590,6 @@
           <t>[ROUTINE] Insider trade — Fang Andy (Director) sold 1,164 shares @ $155.59 ($181.1K) on 2026-05-20</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr"/>
-      <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -10612,9 +10617,6 @@
           <t>[ROUTINE] Insider trade — Tang Stanley (Director) sold 1,592 shares @ $155.59 ($247.7K) on 2026-05-20</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr"/>
-      <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -10642,9 +10644,6 @@
           <t>[ROUTINE] Insider trade — Sherringham Tia (GENERAL COUNSEL AND SECRETARY) sold 7,690 shares @ $155.59 ($1.20M) on 2026-05-20</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr"/>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -10672,9 +10671,6 @@
           <t>[ROUTINE] Insider trade — Inukonda Ravi (CHIEF FINANCIAL OFFICER) sold 19,505 shares @ $155.59 ($3.03M) on 2026-05-20</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr"/>
-      <c r="G245" t="inlineStr"/>
-      <c r="H245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -10702,9 +10698,6 @@
           <t>[ROUTINE] Insider trade — Adarkar Prabir (PRESIDENT AND COO) sold 17,126 shares @ $155.59 ($2.66M) on 2026-05-20</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr"/>
-      <c r="G246" t="inlineStr"/>
-      <c r="H246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -10732,9 +10725,6 @@
           <t>[ROUTINE] Insider trade — Yandell Keith (CHIEF BUSINESS OFFICER) sold 4,227 shares @ $155.59 ($657.7K) on 2026-05-20</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr"/>
-      <c r="G247" t="inlineStr"/>
-      <c r="H247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -10762,9 +10752,6 @@
           <t>[ROUTINE] Insider trade — Lee Gordon S (CHIEF ACCOUNTING OFFICER) sold 2,910 shares @ $155.59 ($452.8K) on 2026-05-20</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr"/>
-      <c r="G248" t="inlineStr"/>
-      <c r="H248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -10792,9 +10779,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr"/>
-      <c r="H249" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4099,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H249"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10779,6 +10779,96 @@
           <t>pricing: change detected</t>
         </is>
       </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/upgrade/website</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4099,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H252"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10806,9 +10806,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr"/>
-      <c r="G250" t="inlineStr"/>
-      <c r="H250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -10836,9 +10833,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
-      <c r="H251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -10866,9 +10860,36 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
-      <c r="H252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>https://investors.wix.com</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4099,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H254"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10887,9 +10887,36 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr"/>
-      <c r="H253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4099,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H254"/>
+  <dimension ref="A1:H255"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10914,9 +10914,36 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr"/>
-      <c r="H254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>https://investors.etsy.com</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4099,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H255"/>
+  <dimension ref="A1:H257"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10941,9 +10941,66 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr"/>
-      <c r="H255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>CHWY</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Chewy Inc.</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>https://investor.chewy.com</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>https://cdn.robinhood.com/assets/robinhood/legal/Robinhood-Customer-Agreement.pdf</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4099,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H257"/>
+  <dimension ref="A1:H258"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10968,9 +10968,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr"/>
-      <c r="G256" t="inlineStr"/>
-      <c r="H256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -10998,9 +10995,36 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000110465926067045/xslF345X06/tm2615788-1_4seq1.xml</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4099,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H258"/>
+  <dimension ref="A1:H260"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11022,9 +11022,66 @@
           <t>[ROUTINE] Insider trade</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
-      <c r="H258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>https://robinhood.com/us/en/support/articles/trading-fees-on-robinhood/</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4099,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H260"/>
+  <dimension ref="A1:H272"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11049,9 +11049,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -11079,9 +11076,366 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000189968826000012/xslF345X06/form4-05272026_040509.xml</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sherringham Tia (GENERAL COUNSEL AND SECRETARY) sold 2,743 shares @ $160.79 ($441.0K) on 2026-05-22</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000163564826000010/xslF345X06/form4-05272026_040507.xml</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lee Gordon S (CHIEF ACCOUNTING OFFICER) sold 2,204 shares @ $160.79 ($354.4K) on 2026-05-22</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000091957426003716/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sundheim Daniel S. (Director) RSU/grant of 6,048 shares on 2026-05-22</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000198846026000002/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Gupta Ravi (Director) RSU/grant of 6,048 shares on 2026-05-22</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000164007526000011/xslF345X06/wk-form4_1779913021.xml</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Levien Meredith A. Kopit (Director) RSU/grant of 6,048 shares on 2026-05-22</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000173634126000005/xslF345X06/wk-form4_1779912973.xml</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sarafan Lily (Director) RSU/grant of 6,048 shares on 2026-05-22</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000151113426000002/xslF345X06/wk-form4_1779912918.xml</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Dolan Victoria L (Director) RSU/grant of 6,048 shares on 2026-05-22</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000152535826000016/xslF345X06/wk-form4_1779912875.xml</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Silverman Josh (Director) RSU/grant of 6,048 shares on 2026-05-22</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000189467426000002/xslF345X06/wk-form4_1779912813.xml</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Laughton Mary Beth (Director) RSU/grant of 6,048 shares on 2026-05-22</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4099,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H272"/>
+  <dimension ref="A1:H273"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11103,9 +11103,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -11133,9 +11130,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr"/>
-      <c r="G262" t="inlineStr"/>
-      <c r="H262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -11163,9 +11157,6 @@
           <t>[ROUTINE] Insider trade — Sherringham Tia (GENERAL COUNSEL AND SECRETARY) sold 2,743 shares @ $160.79 ($441.0K) on 2026-05-22</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr"/>
-      <c r="H263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -11193,9 +11184,6 @@
           <t>[ROUTINE] Insider trade — Lee Gordon S (CHIEF ACCOUNTING OFFICER) sold 2,204 shares @ $160.79 ($354.4K) on 2026-05-22</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr"/>
-      <c r="H264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -11223,9 +11211,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr"/>
-      <c r="H265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -11253,9 +11238,6 @@
           <t>[ROUTINE] Insider trade — Sundheim Daniel S. (Director) RSU/grant of 6,048 shares on 2026-05-22</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
-      <c r="H266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -11283,9 +11265,6 @@
           <t>[ROUTINE] Insider trade — Gupta Ravi (Director) RSU/grant of 6,048 shares on 2026-05-22</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr"/>
-      <c r="G267" t="inlineStr"/>
-      <c r="H267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -11313,9 +11292,6 @@
           <t>[ROUTINE] Insider trade — Levien Meredith A. Kopit (Director) RSU/grant of 6,048 shares on 2026-05-22</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr"/>
-      <c r="H268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -11343,9 +11319,6 @@
           <t>[ROUTINE] Insider trade — Sarafan Lily (Director) RSU/grant of 6,048 shares on 2026-05-22</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr"/>
-      <c r="H269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -11373,9 +11346,6 @@
           <t>[ROUTINE] Insider trade — Dolan Victoria L (Director) RSU/grant of 6,048 shares on 2026-05-22</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
-      <c r="H270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -11403,9 +11373,6 @@
           <t>[ROUTINE] Insider trade — Silverman Josh (Director) RSU/grant of 6,048 shares on 2026-05-22</t>
         </is>
       </c>
-      <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
-      <c r="H271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -11433,9 +11400,36 @@
           <t>[ROUTINE] Insider trade — Laughton Mary Beth (Director) RSU/grant of 6,048 shares on 2026-05-22</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr"/>
-      <c r="H272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4099,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H273"/>
+  <dimension ref="A1:H276"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11427,9 +11427,96 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>https://news.shopify.com</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4099,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H276"/>
+  <dimension ref="A1:H278"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11454,9 +11454,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr"/>
-      <c r="G274" t="inlineStr"/>
-      <c r="H274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -11484,9 +11481,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -11514,9 +11508,66 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F276" t="inlineStr"/>
-      <c r="G276" t="inlineStr"/>
-      <c r="H276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>https://investors.wix.com/board-of-directors</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/terms</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4099,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H278"/>
+  <dimension ref="A1:H279"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11535,9 +11535,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F277" t="inlineStr"/>
-      <c r="G277" t="inlineStr"/>
-      <c r="H277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -11565,9 +11562,36 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr"/>
-      <c r="H278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4099,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H279"/>
+  <dimension ref="A1:H300"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11589,9 +11589,636 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F279" t="inlineStr"/>
-      <c r="G279" t="inlineStr"/>
-      <c r="H279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/shopify/comments/1ttn8xs/custom_feature_for_shopify_quick_question/</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>reddit: Custom feature for Shopify.. quick question</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/shopify/comments/1ttmcp1/ai_referrals_may_turn_product_pages_into_the_new/</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>reddit: AI referrals may turn product pages into the new homepage.</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/shopify/comments/1ttlejz/how_to_add_card_processing_fees_in_checkout_uk/</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>reddit: How to add card processing fees in checkout - UK store</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/shopify/comments/1ttoli5/currency_display_issue/</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>reddit: Currency Display Issue</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/shopify/comments/1ttokfy/how_do_i_create_a_collapsible_row_with_both/</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>reddit: How do i create a collapsible row with both images and table and text?</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/WIX/comments/1ttm2wp/server_not_found_error_when_trying_to_embed_a_map/</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>reddit: Server Not Found error when trying to embed a map from google - help?</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr"/>
+      <c r="H285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/WIX/comments/1ttkdf3/what_the_layoff_round_at_wix_might_tell_us_about/</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>reddit: What the layoff round at Wix might tell us about the future of Israel (and its tech industry)</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/WIX/comments/1ttcvhf/all_elements_on_wix_website_have_enlarged_help/</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>reddit: ALL ELEMENTS ON WIX WEBSITE HAVE ENLARGED!!! HELP PLEASE</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/WIX/comments/1tsp1ms/help_me_i_am_so_pissed/</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>reddit: HELP ME I AM SO PISSED</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/WIX/comments/1tsgmjv/transferring_from_wix_classic_to_wix_studio_can/</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>reddit: Transferring from Wix Classic to Wix Studio - Can this hurt SEO?</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/doordash/comments/1ttdxn4/by_far_the_worst_order_ive_done/</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>reddit: By far the worst order I’ve done</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/doordash/comments/1ttdxhy/last_time_i_dont_check_items_for_grocery/</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>reddit: Last time I don’t check items for grocery.</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr"/>
+      <c r="H291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/doordash/comments/1ttiqhx/dasher_fent_folded_in_front_of_me/</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>reddit: dasher fent folded in front of me</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/doordash/comments/1ttjalz/doordash_has_ruined_take_out/</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>reddit: Doordash has ruined Take Out.</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr"/>
+      <c r="H293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/doordash/comments/1ttjj3c/what_does_this_mean_if_anything/</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>reddit: what does this mean, if anything?</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr"/>
+      <c r="H294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/InstacartShoppers/comments/1ttkzlb/this_is_new_maybe_everyone_will_get_it/</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>reddit: This is new maybe everyone will get it.</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr"/>
+      <c r="H295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/InstacartShoppers/comments/1ttkahc/not_sure_if_i_can_call_it_a_unicorn_but_this_is/</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>reddit: Not sure if I can call it a unicorn but this is the biggest tip that I ever got.</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr"/>
+      <c r="H296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/InstacartShoppers/comments/1tt2aza/new_method_after_7_years/</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>reddit: New method after 7 years</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr"/>
+      <c r="H297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/InstacartShoppers/comments/1tt6f3z/if_you_lost_your_card_in_ga_dm_me/</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>reddit: If you lost your card in GA dm me.</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/InstacartShoppers/comments/1tt7h64/customers_asking_to_enter_home_in_delivery_note/</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>reddit: Customers asking to enter home in delivery note</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4099,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H300"/>
+  <dimension ref="A1:H310"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11616,9 +11616,6 @@
           <t>reddit: Custom feature for Shopify.. quick question</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr"/>
-      <c r="G280" t="inlineStr"/>
-      <c r="H280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -11646,9 +11643,6 @@
           <t>reddit: AI referrals may turn product pages into the new homepage.</t>
         </is>
       </c>
-      <c r="F281" t="inlineStr"/>
-      <c r="G281" t="inlineStr"/>
-      <c r="H281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -11676,9 +11670,6 @@
           <t>reddit: How to add card processing fees in checkout - UK store</t>
         </is>
       </c>
-      <c r="F282" t="inlineStr"/>
-      <c r="G282" t="inlineStr"/>
-      <c r="H282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -11706,9 +11697,6 @@
           <t>reddit: Currency Display Issue</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr"/>
-      <c r="G283" t="inlineStr"/>
-      <c r="H283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -11736,9 +11724,6 @@
           <t>reddit: How do i create a collapsible row with both images and table and text?</t>
         </is>
       </c>
-      <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr"/>
-      <c r="H284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -11766,9 +11751,6 @@
           <t>reddit: Server Not Found error when trying to embed a map from google - help?</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr"/>
-      <c r="G285" t="inlineStr"/>
-      <c r="H285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -11796,9 +11778,6 @@
           <t>reddit: What the layoff round at Wix might tell us about the future of Israel (and its tech industry)</t>
         </is>
       </c>
-      <c r="F286" t="inlineStr"/>
-      <c r="G286" t="inlineStr"/>
-      <c r="H286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -11826,9 +11805,6 @@
           <t>reddit: ALL ELEMENTS ON WIX WEBSITE HAVE ENLARGED!!! HELP PLEASE</t>
         </is>
       </c>
-      <c r="F287" t="inlineStr"/>
-      <c r="G287" t="inlineStr"/>
-      <c r="H287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -11856,9 +11832,6 @@
           <t>reddit: HELP ME I AM SO PISSED</t>
         </is>
       </c>
-      <c r="F288" t="inlineStr"/>
-      <c r="G288" t="inlineStr"/>
-      <c r="H288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -11886,9 +11859,6 @@
           <t>reddit: Transferring from Wix Classic to Wix Studio - Can this hurt SEO?</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr"/>
-      <c r="G289" t="inlineStr"/>
-      <c r="H289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -11916,9 +11886,6 @@
           <t>reddit: By far the worst order I’ve done</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr"/>
-      <c r="H290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -11946,9 +11913,6 @@
           <t>reddit: Last time I don’t check items for grocery.</t>
         </is>
       </c>
-      <c r="F291" t="inlineStr"/>
-      <c r="G291" t="inlineStr"/>
-      <c r="H291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -11976,9 +11940,6 @@
           <t>reddit: dasher fent folded in front of me</t>
         </is>
       </c>
-      <c r="F292" t="inlineStr"/>
-      <c r="G292" t="inlineStr"/>
-      <c r="H292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -12006,9 +11967,6 @@
           <t>reddit: Doordash has ruined Take Out.</t>
         </is>
       </c>
-      <c r="F293" t="inlineStr"/>
-      <c r="G293" t="inlineStr"/>
-      <c r="H293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -12036,9 +11994,6 @@
           <t>reddit: what does this mean, if anything?</t>
         </is>
       </c>
-      <c r="F294" t="inlineStr"/>
-      <c r="G294" t="inlineStr"/>
-      <c r="H294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -12066,9 +12021,6 @@
           <t>reddit: This is new maybe everyone will get it.</t>
         </is>
       </c>
-      <c r="F295" t="inlineStr"/>
-      <c r="G295" t="inlineStr"/>
-      <c r="H295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -12096,9 +12048,6 @@
           <t>reddit: Not sure if I can call it a unicorn but this is the biggest tip that I ever got.</t>
         </is>
       </c>
-      <c r="F296" t="inlineStr"/>
-      <c r="G296" t="inlineStr"/>
-      <c r="H296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -12126,9 +12075,6 @@
           <t>reddit: New method after 7 years</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr"/>
-      <c r="G297" t="inlineStr"/>
-      <c r="H297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -12156,9 +12102,6 @@
           <t>reddit: If you lost your card in GA dm me.</t>
         </is>
       </c>
-      <c r="F298" t="inlineStr"/>
-      <c r="G298" t="inlineStr"/>
-      <c r="H298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -12186,9 +12129,6 @@
           <t>reddit: Customers asking to enter home in delivery note</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr"/>
-      <c r="G299" t="inlineStr"/>
-      <c r="H299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -12216,9 +12156,306 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr"/>
-      <c r="G300" t="inlineStr"/>
-      <c r="H300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/shopify/comments/1tttupa/customer_waits_15_months_to_reach_out_about_an/</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>reddit: Customer waits 15 MONTHS to reach out about an order they never received; wwyd?</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr"/>
+      <c r="H301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/shopify/comments/1ttw705/your_shopify_speed_score_isnt_your_themes_fault/</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>reddit: Your Shopify speed score isn't your theme's fault (usually). Here's what actually kills it.</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr"/>
+      <c r="H302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/WIX/comments/1ttunyg/how_to_align_heights_for_each_card_in_repeaters/</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>reddit: How to align heights for each card in repeaters</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr"/>
+      <c r="H303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/doordash/comments/1tttduq/can_you_make_this_weekly_dd/</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>reddit: Can you make this weekly DD</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr"/>
+      <c r="H304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/doordash/comments/1ttuq9r/do_you_take_this_i_wanna_know/</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>reddit: Do you TAKE THIS??? 😮‍💨😩 i wanna know</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr"/>
+      <c r="H305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/InstacartShoppers/comments/1ttvyy4/going_online_after_3_years_hiatus/</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>reddit: Going online after 3 years hiatus</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr"/>
+      <c r="H306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/InstacartShoppers/comments/1ttvoln/taxes_for_instacart/</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>reddit: taxes for instacart</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/InstacartShoppers/comments/1ttw7h1/i_wish_instacart_would_add_this/</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>reddit: I wish Instacart would add this!</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr"/>
+      <c r="H308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/InstacartShoppers/comments/1ttw2sp/how_do_yall_make_so_much_money_in_a_week/</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>reddit: how do y'all make so much money in a week??</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr"/>
+      <c r="H309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/InstacartShoppers/comments/1ttw27w/better_to_wait_or_move_stores/</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>reddit: Better to wait or move stores?</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr"/>
+      <c r="H310" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4099,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H310"/>
+  <dimension ref="A1:H312"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12183,9 +12183,6 @@
           <t>reddit: Customer waits 15 MONTHS to reach out about an order they never received; wwyd?</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr"/>
-      <c r="G301" t="inlineStr"/>
-      <c r="H301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -12213,9 +12210,6 @@
           <t>reddit: Your Shopify speed score isn't your theme's fault (usually). Here's what actually kills it.</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr"/>
-      <c r="G302" t="inlineStr"/>
-      <c r="H302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -12243,9 +12237,6 @@
           <t>reddit: How to align heights for each card in repeaters</t>
         </is>
       </c>
-      <c r="F303" t="inlineStr"/>
-      <c r="G303" t="inlineStr"/>
-      <c r="H303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -12273,9 +12264,6 @@
           <t>reddit: Can you make this weekly DD</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr"/>
-      <c r="H304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -12303,9 +12291,6 @@
           <t>reddit: Do you TAKE THIS??? 😮‍💨😩 i wanna know</t>
         </is>
       </c>
-      <c r="F305" t="inlineStr"/>
-      <c r="G305" t="inlineStr"/>
-      <c r="H305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -12333,9 +12318,6 @@
           <t>reddit: Going online after 3 years hiatus</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr"/>
-      <c r="G306" t="inlineStr"/>
-      <c r="H306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -12363,9 +12345,6 @@
           <t>reddit: taxes for instacart</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr"/>
-      <c r="G307" t="inlineStr"/>
-      <c r="H307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -12393,9 +12372,6 @@
           <t>reddit: I wish Instacart would add this!</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr"/>
-      <c r="G308" t="inlineStr"/>
-      <c r="H308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -12423,9 +12399,6 @@
           <t>reddit: how do y'all make so much money in a week??</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr"/>
-      <c r="G309" t="inlineStr"/>
-      <c r="H309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -12453,9 +12426,66 @@
           <t>reddit: Better to wait or move stores?</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr"/>
-      <c r="G310" t="inlineStr"/>
-      <c r="H310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr"/>
+      <c r="H311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr"/>
+      <c r="H312" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4099,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H312"/>
+  <dimension ref="A1:H318"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12453,9 +12453,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F311" t="inlineStr"/>
-      <c r="G311" t="inlineStr"/>
-      <c r="H311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -12483,9 +12480,186 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F312" t="inlineStr"/>
-      <c r="G312" t="inlineStr"/>
-      <c r="H312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr"/>
+      <c r="H313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>CHWY</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Chewy Inc.</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>https://www.chewy.com/app/content/terms</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr"/>
+      <c r="H314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>https://blog.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr"/>
+      <c r="H315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>https://www.bill.com/product/pricing</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr"/>
+      <c r="H316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>https://pos.toasttab.com/terms-of-service</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr"/>
+      <c r="H317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>https://pos.toasttab.com/pricing</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr"/>
+      <c r="H318" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -3035,7 +3035,7 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>https://newsroom.robinhood.com</t>
+          <t>https://newsroom.aboutrobinhood.com</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -12507,9 +12507,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F313" t="inlineStr"/>
-      <c r="G313" t="inlineStr"/>
-      <c r="H313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -12537,9 +12534,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F314" t="inlineStr"/>
-      <c r="G314" t="inlineStr"/>
-      <c r="H314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -12567,9 +12561,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr"/>
-      <c r="G315" t="inlineStr"/>
-      <c r="H315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -12597,9 +12588,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr"/>
-      <c r="G316" t="inlineStr"/>
-      <c r="H316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -12627,9 +12615,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr"/>
-      <c r="G317" t="inlineStr"/>
-      <c r="H317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -12657,9 +12642,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr"/>
-      <c r="G318" t="inlineStr"/>
-      <c r="H318" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4099,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H318"/>
+  <dimension ref="A1:H319"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12642,6 +12642,36 @@
           <t>pricing: change detected</t>
         </is>
       </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr"/>
+      <c r="H319" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4099,7 +4099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H319"/>
+  <dimension ref="A1:H332"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12669,9 +12669,396 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr"/>
-      <c r="G319" t="inlineStr"/>
-      <c r="H319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>https://news.shopify.com</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr"/>
+      <c r="H320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr"/>
+      <c r="H321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1370637/000196922326000610/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Silverman Josh (Officer) plans to sell 134,730 shares (~$9.28M) on/after 06/01/2026</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr"/>
+      <c r="H322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>https://blog.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr"/>
+      <c r="H323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000206742526000001/xslF345X06/form4-06012026_040616.xml</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Cieri Michael (Chief Product Officer) sold 32,875 shares @ $36.64 ($1.20M) on 2026-05-29</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr"/>
+      <c r="H324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000179549726000002/xslF345X06/form4-06012026_040610.xml</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lacerte Rene A. (CEO) 15,922 shares withheld for taxes (vest event) on 2026-05-28</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr"/>
+      <c r="H325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000161395526000002/xslF345X06/form4-06012026_040614.xml</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Moss Kenneth A (Chief Technology Officer) 13,031 shares withheld for taxes (vest event) on 2026-05-28</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr"/>
+      <c r="H326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000203968326000002/xslF345X06/form4-06012026_040612.xml</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Bowman Mary Kay (See Remarks) 6,976 shares withheld for taxes (vest event) on 2026-05-28</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr"/>
+      <c r="H327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr"/>
+      <c r="H328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>https://pos.toasttab.com/pricing</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr"/>
+      <c r="H329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr"/>
+      <c r="H330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>https://newsroom.aboutrobinhood.com</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr"/>
+      <c r="H331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000110465926068980/xslF345X06/tm2616557-1_4seq1.xml</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Malka Meyer (Director) BOUGHT 249,000 shares @ $80.39 ($20.02M) on 2026-05-28</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr"/>
+      <c r="H332" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T36"/>
+  <dimension ref="A1:T45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3697,6 +3697,604 @@
         </is>
       </c>
       <c r="R36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://ir.logitech.com</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.logitech.com/en-us/about/newsroom.html</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://ir.logitech.com/corporate-governance/leadership-team</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://jobs.logitech.com</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://www.logitech.com/en-us/legal/terms-of-use.html</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=LOGI</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Consumer hardware (mice, keyboards, webcams); watch G PRO gaming and Streamlabs ecosystem</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="R37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Garmin Ltd.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.garmin.com/en-US/company/investors/</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://newsroom.garmin.com</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.garmin.com/en-US/company/leadership/</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://careers.garmin.com</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://www.garmin.com/en-US/legal/terms-of-use/</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=GRMN</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/Garmin/</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>GPS, wearables, marine, aviation; watch fitness wearable segment vs Apple Watch</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="R38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://ir.tesla.com</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.tesla.com/blog</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://ir.tesla.com/corporate/leadership</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.tesla.com/careers</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.tesla.com/inventory/new/m3</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://www.tesla.com/about/legal</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=TSLA</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/teslamotors/</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Watch FSD pricing, vehicle MSRP changes, energy storage deployments, Cybertruck/Semi shipments</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="R39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://investor.lyft.com</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://investor.lyft.com/corporate-governance/leadership</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/careers</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/pricing</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/terms</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=LYFT</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/lyftdrivers/</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Watch Lyft Pink subscription, driver pay, ride pricing; r/lyftdrivers leads on policy changes</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="R40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://investor.uber.com</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://www.uber.com/newsroom/</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://investor.uber.com/governance/leadership</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.uber.com/global/en/careers/</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.uber.com/us/en/ride/uberone/</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://www.uber.com/legal/terms/</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=UBER</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/uberdrivers/</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Watch Uber One subscription, freight segment, autonomous vehicle partnerships, delivery commission</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="R41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.expediagroup.com/investors/</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://newsroom.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://www.expediagroup.com/about/leadership/default.aspx</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://www.expedia.com/legal</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=EXPE</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/expedia/</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Owns Vrbo, Hotels.com; watch ADR, room nights, take-rate changes, AI search rollout</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="R42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.bookingholdings.com/investors/</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://www.bookingholdings.com/news/</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://www.bookingholdings.com/about/leadership/</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://careers.bookingholdings.com</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=BKNG</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Booking.com, Priceline, Agoda, Kayak; watch room-night growth, alternative-accommodations mix, Genius loyalty tier expansion</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="R43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://investors.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://news.airbnb.com</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://investors.airbnb.com/leadership/</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://www.airbnb.com/terms</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=ABNB</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/airbnb_hosts/</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Watch host fee changes, Experiences relaunch, regulatory pressure (EU/NYC), Co-Host marketplace</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="R44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SPHR</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sphere Entertainment Co.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.sphereentertainmentco.com/investors/</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://www.sphereentertainmentco.com/newsroom/</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://www.sphereentertainmentco.com/governance/leadership/</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.sphereentertainmentco.com/careers/</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.thesphere.com/upcoming-events</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://www.sphereentertainmentco.com/legal/</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=SPHR</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sphere Las Vegas venue + MSG Networks; watch event bookings, sponsor deals, Abu Dhabi sphere progress</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="R45" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4088,6 +4686,70 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId384"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId385"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId450"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12696,9 +13358,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr"/>
-      <c r="G320" t="inlineStr"/>
-      <c r="H320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -12726,9 +13385,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr"/>
-      <c r="G321" t="inlineStr"/>
-      <c r="H321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -12756,9 +13412,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Silverman Josh (Officer) plans to sell 134,730 shares (~$9.28M) on/after 06/01/2026</t>
         </is>
       </c>
-      <c r="F322" t="inlineStr"/>
-      <c r="G322" t="inlineStr"/>
-      <c r="H322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -12786,9 +13439,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr"/>
-      <c r="G323" t="inlineStr"/>
-      <c r="H323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -12816,9 +13466,6 @@
           <t>[ROUTINE] Insider trade — Cieri Michael (Chief Product Officer) sold 32,875 shares @ $36.64 ($1.20M) on 2026-05-29</t>
         </is>
       </c>
-      <c r="F324" t="inlineStr"/>
-      <c r="G324" t="inlineStr"/>
-      <c r="H324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -12846,9 +13493,6 @@
           <t>[ROUTINE] Insider trade — Lacerte Rene A. (CEO) 15,922 shares withheld for taxes (vest event) on 2026-05-28</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr"/>
-      <c r="G325" t="inlineStr"/>
-      <c r="H325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -12876,9 +13520,6 @@
           <t>[ROUTINE] Insider trade — Moss Kenneth A (Chief Technology Officer) 13,031 shares withheld for taxes (vest event) on 2026-05-28</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr"/>
-      <c r="G326" t="inlineStr"/>
-      <c r="H326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -12906,9 +13547,6 @@
           <t>[ROUTINE] Insider trade — Bowman Mary Kay (See Remarks) 6,976 shares withheld for taxes (vest event) on 2026-05-28</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr"/>
-      <c r="G327" t="inlineStr"/>
-      <c r="H327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -12936,9 +13574,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F328" t="inlineStr"/>
-      <c r="G328" t="inlineStr"/>
-      <c r="H328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -12966,9 +13601,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr"/>
-      <c r="G329" t="inlineStr"/>
-      <c r="H329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -12996,9 +13628,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F330" t="inlineStr"/>
-      <c r="G330" t="inlineStr"/>
-      <c r="H330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -13026,9 +13655,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr"/>
-      <c r="G331" t="inlineStr"/>
-      <c r="H331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -13056,9 +13682,6 @@
           <t>[ROUTINE] Insider trade — Malka Meyer (Director) BOUGHT 249,000 shares @ $80.39 ($20.02M) on 2026-05-28</t>
         </is>
       </c>
-      <c r="F332" t="inlineStr"/>
-      <c r="G332" t="inlineStr"/>
-      <c r="H332" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -3736,7 +3736,6 @@
           <t>https://jobs.logitech.com</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>https://www.logitech.com/en-us/legal/terms-of-use.html</t>
@@ -3747,7 +3746,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=LOGI</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Consumer hardware (mice, keyboards, webcams); watch G PRO gaming and Streamlabs ecosystem</t>
@@ -3798,7 +3796,6 @@
           <t>https://careers.garmin.com</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>https://www.garmin.com/en-US/legal/terms-of-use/</t>
@@ -4074,7 +4071,6 @@
           <t>https://careers.expediagroup.com</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>https://www.expedia.com/legal</t>
@@ -4140,7 +4136,6 @@
           <t>https://careers.bookingholdings.com</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>https://www.booking.com/content/terms.html</t>
@@ -4151,7 +4146,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=BKNG</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Booking.com, Priceline, Agoda, Kayak; watch room-night growth, alternative-accommodations mix, Genius loyalty tier expansion</t>
@@ -4202,7 +4196,6 @@
           <t>https://careers.airbnb.com</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>https://www.airbnb.com/terms</t>
@@ -4283,7 +4276,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=SPHR</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sphere Las Vegas venue + MSG Networks; watch event bookings, sponsor deals, Abu Dhabi sphere progress</t>
@@ -4761,7 +4753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H332"/>
+  <dimension ref="A1:H336"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13682,6 +13674,126 @@
           <t>[ROUTINE] Insider trade — Malka Meyer (Director) BOUGHT 249,000 shares @ $80.39 ($20.02M) on 2026-05-28</t>
         </is>
       </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1759509/000162828026039513/lyft-formsd2026.htm</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form SD</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr"/>
+      <c r="H333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1759509/000192109426000578/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Llewellyn Lindsay Catherine (Officer) plans to sell 11,491 shares (~$172.4K) on/after 06/01/2026</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr"/>
+      <c r="H334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000196858226000514/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Joseph Gebbia (Director) plans to sell 1,855,000 shares (~$247.29M) on/after 06/01/2026</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr"/>
+      <c r="H335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000195917326004228/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Chesky Brian (Officer) plans to sell 257,273 shares (~$35.00M) on/after 06/01/2026</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr"/>
+      <c r="H336" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4753,7 +4753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H336"/>
+  <dimension ref="A1:H347"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13701,9 +13701,6 @@
           <t>[UNKNOWN] Form SD</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr"/>
-      <c r="G333" t="inlineStr"/>
-      <c r="H333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -13731,9 +13728,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Llewellyn Lindsay Catherine (Officer) plans to sell 11,491 shares (~$172.4K) on/after 06/01/2026</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr"/>
-      <c r="G334" t="inlineStr"/>
-      <c r="H334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -13761,9 +13755,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Joseph Gebbia (Director) plans to sell 1,855,000 shares (~$247.29M) on/after 06/01/2026</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr"/>
-      <c r="G335" t="inlineStr"/>
-      <c r="H335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -13791,9 +13782,336 @@
           <t>[ROUTINE] Notice of proposed insider sale — Chesky Brian (Officer) plans to sell 257,273 shares (~$35.00M) on/after 06/01/2026</t>
         </is>
       </c>
-      <c r="F336" t="inlineStr"/>
-      <c r="G336" t="inlineStr"/>
-      <c r="H336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>https://ir.logitech.com</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr"/>
+      <c r="H337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Garmin Ltd.</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>https://newsroom.garmin.com</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr"/>
+      <c r="H338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr"/>
+      <c r="H339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>https://investor.lyft.com</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr"/>
+      <c r="H340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr"/>
+      <c r="H341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1324424/000132442426000042/expe-20260617.htm</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr"/>
+      <c r="H342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>https://www.bookingholdings.com/about/leadership/</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr"/>
+      <c r="H343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>https://www.airbnb.com/terms</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr"/>
+      <c r="H344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>https://news.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr"/>
+      <c r="H345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr"/>
+      <c r="H346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>SPHR</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Sphere Entertainment Co.</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>https://www.sphereentertainmentco.com/careers/</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="inlineStr"/>
+      <c r="H347" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4753,7 +4753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H347"/>
+  <dimension ref="A1:H353"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13809,9 +13809,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr"/>
-      <c r="G337" t="inlineStr"/>
-      <c r="H337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -13839,9 +13836,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F338" t="inlineStr"/>
-      <c r="G338" t="inlineStr"/>
-      <c r="H338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -13869,9 +13863,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F339" t="inlineStr"/>
-      <c r="G339" t="inlineStr"/>
-      <c r="H339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -13899,9 +13890,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F340" t="inlineStr"/>
-      <c r="G340" t="inlineStr"/>
-      <c r="H340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -13929,9 +13917,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F341" t="inlineStr"/>
-      <c r="G341" t="inlineStr"/>
-      <c r="H341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -13959,9 +13944,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F342" t="inlineStr"/>
-      <c r="G342" t="inlineStr"/>
-      <c r="H342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -13989,9 +13971,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F343" t="inlineStr"/>
-      <c r="G343" t="inlineStr"/>
-      <c r="H343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -14019,9 +13998,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F344" t="inlineStr"/>
-      <c r="G344" t="inlineStr"/>
-      <c r="H344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -14049,9 +14025,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F345" t="inlineStr"/>
-      <c r="G345" t="inlineStr"/>
-      <c r="H345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -14079,9 +14052,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F346" t="inlineStr"/>
-      <c r="G346" t="inlineStr"/>
-      <c r="H346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -14109,9 +14079,186 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F347" t="inlineStr"/>
-      <c r="G347" t="inlineStr"/>
-      <c r="H347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Garmin Ltd.</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>https://newsroom.garmin.com</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr"/>
+      <c r="H348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr"/>
+      <c r="H349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr"/>
+      <c r="H350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr"/>
+      <c r="H351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000195917326004865/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Blecharczyk Nathan (Officer) plans to sell 88,366 shares (~$12.88M) on/after 06/24/2026</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr"/>
+      <c r="H352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000195917326004851/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Blecharczyk Nathan (Officer) plans to sell 34,614 shares (~$5.02M) on/after 06/24/2026</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr"/>
+      <c r="H353" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4753,7 +4753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H353"/>
+  <dimension ref="A1:H366"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14106,9 +14106,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F348" t="inlineStr"/>
-      <c r="G348" t="inlineStr"/>
-      <c r="H348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -14136,9 +14133,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F349" t="inlineStr"/>
-      <c r="G349" t="inlineStr"/>
-      <c r="H349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -14166,9 +14160,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F350" t="inlineStr"/>
-      <c r="G350" t="inlineStr"/>
-      <c r="H350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -14196,9 +14187,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F351" t="inlineStr"/>
-      <c r="G351" t="inlineStr"/>
-      <c r="H351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -14226,9 +14214,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Blecharczyk Nathan (Officer) plans to sell 88,366 shares (~$12.88M) on/after 06/24/2026</t>
         </is>
       </c>
-      <c r="F352" t="inlineStr"/>
-      <c r="G352" t="inlineStr"/>
-      <c r="H352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -14256,9 +14241,396 @@
           <t>[ROUTINE] Notice of proposed insider sale — Blecharczyk Nathan (Officer) plans to sell 34,614 shares (~$5.02M) on/after 06/24/2026</t>
         </is>
       </c>
-      <c r="F353" t="inlineStr"/>
-      <c r="G353" t="inlineStr"/>
-      <c r="H353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>https://ir.logitech.com</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr"/>
+      <c r="H354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Garmin Ltd.</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>https://newsroom.garmin.com</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr"/>
+      <c r="H355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Garmin Ltd.</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1121788/000101410826000038/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr"/>
+      <c r="H356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/terms</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr"/>
+      <c r="H357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr"/>
+      <c r="H358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>https://investor.lyft.com</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr"/>
+      <c r="H359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1759509/000119312526298108/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr"/>
+      <c r="H360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000155278126000379/xslSCHEDULE_13D_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ active owner disclosure</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr"/>
+      <c r="H361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr"/>
+      <c r="H362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr"/>
+      <c r="H363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000119312526298928/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Blecharczyk Nathan (Chief Strategy Officer) sold 13,615 shares @ $148.37 ($2.02M) on 2026-07-06</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr"/>
+      <c r="H364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000119312526297868/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Gebbia Joseph (Director) sold 27,733 shares @ $150.01 ($4.16M) on 2026-07-02</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr"/>
+      <c r="H365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000119312526297867/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Mertz Elinor (Chief Financial Officer) sold 3,750 shares @ $148.01 ($555.0K) on 2026-07-02</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr"/>
+      <c r="H366" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4753,7 +4753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H366"/>
+  <dimension ref="A1:H374"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14268,9 +14268,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F354" t="inlineStr"/>
-      <c r="G354" t="inlineStr"/>
-      <c r="H354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -14298,9 +14295,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F355" t="inlineStr"/>
-      <c r="G355" t="inlineStr"/>
-      <c r="H355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -14328,9 +14322,6 @@
           <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr"/>
-      <c r="G356" t="inlineStr"/>
-      <c r="H356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -14358,9 +14349,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr"/>
-      <c r="G357" t="inlineStr"/>
-      <c r="H357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -14388,9 +14376,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F358" t="inlineStr"/>
-      <c r="G358" t="inlineStr"/>
-      <c r="H358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -14418,9 +14403,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F359" t="inlineStr"/>
-      <c r="G359" t="inlineStr"/>
-      <c r="H359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -14448,9 +14430,6 @@
           <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
         </is>
       </c>
-      <c r="F360" t="inlineStr"/>
-      <c r="G360" t="inlineStr"/>
-      <c r="H360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -14478,9 +14457,6 @@
           <t>[MATERIAL] Update to 5%+ active owner disclosure</t>
         </is>
       </c>
-      <c r="F361" t="inlineStr"/>
-      <c r="G361" t="inlineStr"/>
-      <c r="H361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -14508,9 +14484,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F362" t="inlineStr"/>
-      <c r="G362" t="inlineStr"/>
-      <c r="H362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -14538,9 +14511,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F363" t="inlineStr"/>
-      <c r="G363" t="inlineStr"/>
-      <c r="H363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -14568,9 +14538,6 @@
           <t>[ROUTINE] Insider trade — Blecharczyk Nathan (Chief Strategy Officer) sold 13,615 shares @ $148.37 ($2.02M) on 2026-07-06</t>
         </is>
       </c>
-      <c r="F364" t="inlineStr"/>
-      <c r="G364" t="inlineStr"/>
-      <c r="H364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -14598,9 +14565,6 @@
           <t>[ROUTINE] Insider trade — Gebbia Joseph (Director) sold 27,733 shares @ $150.01 ($4.16M) on 2026-07-02</t>
         </is>
       </c>
-      <c r="F365" t="inlineStr"/>
-      <c r="G365" t="inlineStr"/>
-      <c r="H365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -14628,9 +14592,246 @@
           <t>[ROUTINE] Insider trade — Mertz Elinor (Chief Financial Officer) sold 3,750 shares @ $148.01 ($555.0K) on 2026-07-02</t>
         </is>
       </c>
-      <c r="F366" t="inlineStr"/>
-      <c r="G366" t="inlineStr"/>
-      <c r="H366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>CHWY</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Chewy Inc.</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>https://www.chewy.com/app/content/terms</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr"/>
+      <c r="H367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>https://ir.doordash.com/governance/management/default.aspx</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr"/>
+      <c r="H368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr"/>
+      <c r="H369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>https://ir.doordash.com</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr"/>
+      <c r="H370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726006964/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Ravi Inukonda (Officer) plans to sell 21,129 shares (~$4.14M) on/after 07/08/2026</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr"/>
+      <c r="H371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183261426000021/xslF345X06/form4-07072026_040701.xml</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Tang Stanley (Director) sold 23,125 shares @ $191.19 ($4.42M) on 2026-07-02</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr"/>
+      <c r="H372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr"/>
+      <c r="H373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/company/newsroom</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr"/>
+      <c r="H374" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4753,7 +4753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H374"/>
+  <dimension ref="A1:H380"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14619,9 +14619,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F367" t="inlineStr"/>
-      <c r="G367" t="inlineStr"/>
-      <c r="H367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -14649,9 +14646,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F368" t="inlineStr"/>
-      <c r="G368" t="inlineStr"/>
-      <c r="H368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -14679,9 +14673,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F369" t="inlineStr"/>
-      <c r="G369" t="inlineStr"/>
-      <c r="H369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -14709,9 +14700,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F370" t="inlineStr"/>
-      <c r="G370" t="inlineStr"/>
-      <c r="H370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -14739,9 +14727,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Ravi Inukonda (Officer) plans to sell 21,129 shares (~$4.14M) on/after 07/08/2026</t>
         </is>
       </c>
-      <c r="F371" t="inlineStr"/>
-      <c r="G371" t="inlineStr"/>
-      <c r="H371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -14769,9 +14754,6 @@
           <t>[ROUTINE] Insider trade — Tang Stanley (Director) sold 23,125 shares @ $191.19 ($4.42M) on 2026-07-02</t>
         </is>
       </c>
-      <c r="F372" t="inlineStr"/>
-      <c r="G372" t="inlineStr"/>
-      <c r="H372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -14799,9 +14781,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr"/>
-      <c r="G373" t="inlineStr"/>
-      <c r="H373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -14829,9 +14808,186 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F374" t="inlineStr"/>
-      <c r="G374" t="inlineStr"/>
-      <c r="H374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/investors/board-of-directors</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr"/>
+      <c r="H375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr"/>
+      <c r="H376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>https://news.shopify.com</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr"/>
+      <c r="H377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>https://investors.shopify.com</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr"/>
+      <c r="H378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/upgrade/website</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="inlineStr"/>
+      <c r="H380" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T45"/>
+  <dimension ref="A1:T49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4287,6 +4287,258 @@
         </is>
       </c>
       <c r="R45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>VRSK</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Verisk Analytics, Inc.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://investor.verisk.com</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://www.verisk.com/newsroom/</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://investor.verisk.com/corporate-governance/leadership</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://careers.verisk.com</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://www.verisk.com/legal/terms-of-use/</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=VRSK</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Insurance analytics + data; watch subscription revenue growth, environmental/climate data expansion, insurance underwriting product launches</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="R46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CVNA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Carvana Co.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://investors.carvana.com</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.carvana.com/blog</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://investors.carvana.com/corporate-governance/management</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.carvana.com/careers</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://www.carvana.com/terms</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=CVNA</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/carvana/</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Online used-car retailer; watch GPU (gross profit per unit), ADESA integration, retail unit growth vs guidance, auto finance spread</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="R47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>HQY</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HealthEquity, Inc.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://ir.healthequity.com</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://ir.healthequity.com/news-events/press-releases</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://ir.healthequity.com/corporate-governance/leadership</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://careers.healthequity.com</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://www.healthequity.com/terms/</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=HQY</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>HSA custodian; watch HSA account growth, custodial yield spread, investment AUM balance, HSA-related legislation</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="R48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ARMK</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Aramark</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.aramark.com/about-us/investors</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://www.aramark.com/about-us/news</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://www.aramark.com/about-us/leadership</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://careers.aramark.com</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://www.aramark.com/legal/terms-of-use</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=ARMK</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Food services + uniforms; watch food inflation pass-through, uniform rental growth, education/business/healthcare segment mix</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="R49" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4742,6 +4994,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId448"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId449"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId475"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14835,9 +15112,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F375" t="inlineStr"/>
-      <c r="G375" t="inlineStr"/>
-      <c r="H375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -14865,9 +15139,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F376" t="inlineStr"/>
-      <c r="G376" t="inlineStr"/>
-      <c r="H376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -14895,9 +15166,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr"/>
-      <c r="G377" t="inlineStr"/>
-      <c r="H377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -14925,9 +15193,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F378" t="inlineStr"/>
-      <c r="G378" t="inlineStr"/>
-      <c r="H378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -14955,9 +15220,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F379" t="inlineStr"/>
-      <c r="G379" t="inlineStr"/>
-      <c r="H379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -14985,9 +15247,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr"/>
-      <c r="G380" t="inlineStr"/>
-      <c r="H380" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4326,7 +4326,6 @@
           <t>https://careers.verisk.com</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>https://www.verisk.com/legal/terms-of-use/</t>
@@ -4337,7 +4336,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=VRSK</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Insurance analytics + data; watch subscription revenue growth, environmental/climate data expansion, insurance underwriting product launches</t>
@@ -4388,7 +4386,6 @@
           <t>https://www.carvana.com/careers</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>https://www.carvana.com/terms</t>
@@ -4454,7 +4451,6 @@
           <t>https://careers.healthequity.com</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>https://www.healthequity.com/terms/</t>
@@ -4465,7 +4461,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=HQY</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>HSA custodian; watch HSA account growth, custodial yield spread, investment AUM balance, HSA-related legislation</t>
@@ -4516,7 +4511,6 @@
           <t>https://careers.aramark.com</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>https://www.aramark.com/legal/terms-of-use</t>
@@ -4527,7 +4521,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=ARMK</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Food services + uniforms; watch food inflation pass-through, uniform rental growth, education/business/healthcare segment mix</t>
@@ -5030,7 +5023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H380"/>
+  <dimension ref="A1:H386"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15247,6 +15240,186 @@
           <t>pricing: change detected</t>
         </is>
       </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>VRSK</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Verisk Analytics, Inc.</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1442145/000119312526298574/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Purtill Sabra R. (Director) RSU/grant of 163 shares on 2026-06-30</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="inlineStr"/>
+      <c r="H381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>VRSK</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Verisk Analytics, Inc.</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1442145/000119312526298568/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Christopher John Perry (Director) RSU/grant of 146 shares on 2026-06-30</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr"/>
+      <c r="H382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>VRSK</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Verisk Analytics, Inc.</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1442145/000119312526298564/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hendrick Gregory (Director) RSU/grant of 146 shares on 2026-06-30</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr"/>
+      <c r="G383" t="inlineStr"/>
+      <c r="H383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>VRSK</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Verisk Analytics, Inc.</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1442145/000119312526298561/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Patiath Pradip (Director) RSU/grant of 69 shares on 2026-06-30</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="inlineStr"/>
+      <c r="H384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>VRSK</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Verisk Analytics, Inc.</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1442145/000119312526298556/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Samuel G Liss (Director) RSU/grant of 167 shares on 2026-06-30</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr"/>
+      <c r="G385" t="inlineStr"/>
+      <c r="H385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>HQY</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>HealthEquity, Inc.</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1428336/000201611626000014/xslF345X06/form4-07072026_080705.xml</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Fiore Michael Henry (EVP, CHIEF COMMERCIAL OFFICER) sold 2,470 shares @ $95.00 ($234.7K) on 2026-07-02</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr"/>
+      <c r="H386" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -5023,7 +5023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H386"/>
+  <dimension ref="A1:H389"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15267,9 +15267,6 @@
           <t>[ROUTINE] Insider trade — Purtill Sabra R. (Director) RSU/grant of 163 shares on 2026-06-30</t>
         </is>
       </c>
-      <c r="F381" t="inlineStr"/>
-      <c r="G381" t="inlineStr"/>
-      <c r="H381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -15297,9 +15294,6 @@
           <t>[ROUTINE] Insider trade — Christopher John Perry (Director) RSU/grant of 146 shares on 2026-06-30</t>
         </is>
       </c>
-      <c r="F382" t="inlineStr"/>
-      <c r="G382" t="inlineStr"/>
-      <c r="H382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -15327,9 +15321,6 @@
           <t>[ROUTINE] Insider trade — Hendrick Gregory (Director) RSU/grant of 146 shares on 2026-06-30</t>
         </is>
       </c>
-      <c r="F383" t="inlineStr"/>
-      <c r="G383" t="inlineStr"/>
-      <c r="H383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -15357,9 +15348,6 @@
           <t>[ROUTINE] Insider trade — Patiath Pradip (Director) RSU/grant of 69 shares on 2026-06-30</t>
         </is>
       </c>
-      <c r="F384" t="inlineStr"/>
-      <c r="G384" t="inlineStr"/>
-      <c r="H384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -15387,9 +15375,6 @@
           <t>[ROUTINE] Insider trade — Samuel G Liss (Director) RSU/grant of 167 shares on 2026-06-30</t>
         </is>
       </c>
-      <c r="F385" t="inlineStr"/>
-      <c r="G385" t="inlineStr"/>
-      <c r="H385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -15417,9 +15402,96 @@
           <t>[ROUTINE] Insider trade — Fiore Michael Henry (EVP, CHIEF COMMERCIAL OFFICER) sold 2,470 shares @ $95.00 ($234.7K) on 2026-07-02</t>
         </is>
       </c>
-      <c r="F386" t="inlineStr"/>
-      <c r="G386" t="inlineStr"/>
-      <c r="H386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr"/>
+      <c r="H387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>https://ir.doordash.com/governance/management/default.aspx</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr"/>
+      <c r="H388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>https://ir.doordash.com</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr"/>
+      <c r="H389" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -5023,7 +5023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H389"/>
+  <dimension ref="A1:H394"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15429,9 +15429,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F387" t="inlineStr"/>
-      <c r="G387" t="inlineStr"/>
-      <c r="H387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -15459,9 +15456,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F388" t="inlineStr"/>
-      <c r="G388" t="inlineStr"/>
-      <c r="H388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -15489,9 +15483,156 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F389" t="inlineStr"/>
-      <c r="G389" t="inlineStr"/>
-      <c r="H389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>https://ir.logitech.com</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr"/>
+      <c r="H390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr"/>
+      <c r="H391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr"/>
+      <c r="H392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr"/>
+      <c r="H393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000119312526299741/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Gebbia Joseph (Director) sold 2,460 shares @ $150.00 ($369.0K) on 2026-07-07</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr"/>
+      <c r="H394" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -5023,7 +5023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H394"/>
+  <dimension ref="A1:H395"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15510,9 +15510,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F390" t="inlineStr"/>
-      <c r="G390" t="inlineStr"/>
-      <c r="H390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -15540,9 +15537,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F391" t="inlineStr"/>
-      <c r="G391" t="inlineStr"/>
-      <c r="H391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -15570,9 +15564,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F392" t="inlineStr"/>
-      <c r="G392" t="inlineStr"/>
-      <c r="H392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -15600,9 +15591,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F393" t="inlineStr"/>
-      <c r="G393" t="inlineStr"/>
-      <c r="H393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -15630,9 +15618,36 @@
           <t>[ROUTINE] Insider trade — Gebbia Joseph (Director) sold 2,460 shares @ $150.00 ($369.0K) on 2026-07-07</t>
         </is>
       </c>
-      <c r="F394" t="inlineStr"/>
-      <c r="G394" t="inlineStr"/>
-      <c r="H394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>ARMK</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Aramark</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>https://careers.aramark.com</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr"/>
+      <c r="H395" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T49"/>
+  <dimension ref="A1:T81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4532,6 +4532,1854 @@
         </is>
       </c>
       <c r="R49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>YOU</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Clear Secure, Inc.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://ir.clearme.com</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://ir.clearme.com/news-events</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.clearme.com/careers</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://www.clearme.com/legal</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=YOU</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Biometric identity verification; watch Clear Plus subscription growth, airport partnership expansions, TSA PreCheck competition</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Choice Hotels International, Inc.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://media.choicehotels.com/investors</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://media.choicehotels.com</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://careers.choicehotels.com</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://www.choicehotels.com/legal/terms-of-use</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=CHH</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Franchised hotels (Comfort, Quality, Radisson Americas); watch RevPAR, unit growth, Radisson integration</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://about.fb.com/news/</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://about.meta.com/company-info/</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.metacareers.com</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/legal/terms</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=META</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Watch Reels monetization, Threads growth, Reality Labs spend, AI capex, WhatsApp Business</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://abc.xyz/investor/</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://blog.google</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://abc.xyz/investor/other/management/</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://careers.google.com</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://policies.google.com/terms</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=GOOG</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Watch Search AI overviews impact, Cloud growth vs AWS/Azure, YouTube ad revenue, Waymo scaling, DOJ antitrust remedies</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://investor.snap.com</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://newsroom.snap.com</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://investor.snap.com/corporate-governance/leadership/</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://careers.snap.com</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://snap.com/en-US/terms</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=SNAP</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Watch DAU trend, Snapchat+ subscription, ad revenue vs guidance, AR partnerships</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://investor.pinterestinc.com</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://newsroom.pinterest.com</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://policy.pinterest.com/en/terms-of-service</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=PINS</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Watch MAU trend, ARPU growth, shopping/commerce integrations, Amazon partnership scaling</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://investor.redditinc.com</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/press</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://www.redditinc.com/policies/user-agreement</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=RDDT</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/reddit/</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Watch data licensing deals (Google/OpenAI), ad revenue growth, DAUq trend, Reddit Answers rollout</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>AppLovin Corporation</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://investors.applovin.com</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://www.applovin.com/blog/</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.applovin.com/careers/</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://www.applovin.com/legal/</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=APP</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Ad tech / mobile gaming; watch AXON 2 ML model performance, e-commerce ad expansion, gaming vs non-gaming ad mix</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://investors.unity.com</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://unity.com/company/press</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://unity.com/legal/terms-of-service</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=U</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Watch Runtime Fee resolution/aftermath, Create/Grow segment split, subscription renewals</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://ir.netflix.net</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/en/news</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://jobs.netflix.com</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://help.netflix.com/en/node/24926</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://help.netflix.com/legal/termsofuse</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=NFLX</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Watch subscriber adds, ARM changes, ads-tier growth, content spend, live sports strategy, password-sharing crackdown effect</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://investors.spotify.com</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com/premium</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com/legal/end-user-agreement/</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=SPOT</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Watch MAU/Premium sub growth, gross margin (audiobook/podcast), pricing power, Marketplace ad revenue</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>NYT</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>The New York Times Company</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://investors.nytco.com</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://www.nytco.com/press/</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.nytco.com/careers/</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://help.nytimes.com/hc/en-us/articles/115014893428</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=NYT</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Watch digital subs adds (news, cooking, games, Wirecutter, Athletic), ARPU, bundle attach rate</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>LIF</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>LIF (verify ticker)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=LIF</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Ticker unclear — could be Life Insurance / other. Verify via SEC index.</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BBY</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Best Buy Co., Inc.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://investors.bestbuy.com</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://corporate.bestbuy.com/newsroom/</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://jobs.bestbuy.com</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://www.bestbuy.com/site/help-topics/terms-and-conditions/pcmcat204400050067.c</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=BBY</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Watch comparable sales, membership (My Best Buy Total), TotalTech services attach, gaming/PC upgrade cycle</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/investor-relations/</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/news/</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://disneytermsofuse.com</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=DIS</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Watch DTC (Disney+/Hulu/ESPN+) sub growth + profitability, ESPN direct-to-consumer 2025 launch, Parks OI, streaming ARPU</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://investor.foxcorporation.com</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://www.foxcorporation.com/news/</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>https://www.fox.com/terms-of-use</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=FOXA</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Watch Tubi ad growth, Fox News ratings + political cycle, Sports rights renewals, retransmission fees</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>UMG</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Universal Music Group N.V.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Euronext Amsterdam</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.universalmusic.com/investor-relations/</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://www.universalmusic.com/news/</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.universalmusic.com/careers/</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=UMG</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Non-US listed (Euronext); watch subscription streaming ARPU trends, TikTok deal, artist advance write-downs</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Warner Music Group Corp.</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://investors.wmg.com</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://www.wmg.com/news/</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://careers.wmg.com</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>https://www.wmg.com/terms-of-use</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=WMG</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Watch streaming revenue growth, mechanical royalty rates, artist advances, Live Nation vs. WMG dynamics</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://www.livenationentertainment.com/newsroom/</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://careers.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://help.ticketmaster.com/hc/en-us/articles/10736907984657</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=LYV</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Watch DOJ lawsuit outcomes, ticket AOV, concert attendance, Ticketmaster market share, VIP/premium seat mix</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://investors.stubhub.com</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/press</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/legal/</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=STUB</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Recent 2024/2025 IPO; watch GMV growth, take rate, marketing spend, international expansion</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>LION</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>LION (verify ticker)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=LION</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Ticker unclear — could be Fidelity National Financial or Lions Gate. Verify via SEC index.</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>OUTFRONT Media Inc.</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://investor.outfrontmedia.com</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://www.outfrontmedia.com/newsroom/</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.outfrontmedia.com/careers</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>https://www.outfrontmedia.com/legal/</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=OUT</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Out-of-home advertising (billboards, transit); watch same-store growth, digital conversion, MTA contract</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>LAMR</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Lamar Advertising Company</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://www.lamar.com/investor-relations</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://www.lamar.com/news</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.lamar.com/careers</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://www.lamar.com/terms-of-use</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=LAMR</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Out-of-home advertising REIT; watch same-store growth, digital board conversion, dividend policy</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com/press-releases</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.take2games.com/careers</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=TTWO</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Watch GTA VI launch timing/reception, NBA 2K + Zynga performance, deferred revenue accretion</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://ea.com/careers</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>https://tos.ea.com</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=EA</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Watch EA SPORTS FC engagement, Battlefield launches, live services bookings, mobile gaming</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://ir.roblox.com</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://ir.roblox.com/news-releases</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://careers.roblox.com</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>https://en.help.roblox.com/hc/en-us/articles/115004647846</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=RBLX</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Watch DAU trend (esp older cohorts), bookings/DAU, developer earnings share, advertising rollout, Roblox Studio AI</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://investors.intuit.com</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://www.intuit.com/company/press-room/</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.intuit.com/careers/</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://quickbooks.intuit.com/pricing/</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>https://www.intuit.com/legal/terms-of-service/</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=INTU</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Watch QuickBooks Online growth, TurboTax mix, Credit Karma monetization, Mailchimp cross-sell, AI features</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://investors.adp.com</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://mediacenter.adp.com</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://jobs.adp.com</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>https://www.adp.com/about-adp/privacy.aspx</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=ADP</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Watch pays per control (employment proxy), client fund float, employer services growth, PEO segment</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Paychex, Inc.</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://investor.paychex.com</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://www.paychex.com/newsroom</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.paychex.com/careers</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>https://www.paychex.com/terms-of-use</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=PAYX</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Watch client count, HR services attach rates, retention, float income, PEO expansion</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PAYC</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Paycom Software, Inc.</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://investors.paycom.com</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://www.paycom.com/resources/news/</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://paycom.com/careers</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>https://www.paycom.com/terms-of-use/</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=PAYC</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Watch Beti self-service adoption, revenue per client, sales productivity, competitive pressure vs Rippling/Gusto</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://investors.paylocity.com</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://www.paylocity.com/resources/press-releases/</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.paylocity.com/careers</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>https://www.paylocity.com/terms/</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=PCTY</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Watch mid-market win rate, revenue per client, community features / employee experience adoption</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://investor.cdw.com</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://www.cdw.com/content/cdw/en/about/newsroom.html</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.cdw.com/content/cdw/en/careers.html</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>https://www.cdw.com/content/cdw/en/terms-conditions.html</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=CDW</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>IT reseller; watch corporate/public/small-biz mix, gross margin, hardware refresh cycle, cloud services growth</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="R81" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5012,6 +6860,164 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId473"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId474"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId633"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15645,9 +17651,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F395" t="inlineStr"/>
-      <c r="G395" t="inlineStr"/>
-      <c r="H395" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -4561,13 +4561,11 @@
           <t>https://ir.clearme.com/news-events</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>https://www.clearme.com/careers</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>https://www.clearme.com/legal</t>
@@ -4578,7 +4576,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=YOU</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Biometric identity verification; watch Clear Plus subscription growth, airport partnership expansions, TSA PreCheck competition</t>
@@ -4619,13 +4616,11 @@
           <t>https://media.choicehotels.com</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>https://careers.choicehotels.com</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>https://www.choicehotels.com/legal/terms-of-use</t>
@@ -4636,7 +4631,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=CHH</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Franchised hotels (Comfort, Quality, Radisson Americas); watch RevPAR, unit growth, Radisson integration</t>
@@ -4687,7 +4681,6 @@
           <t>https://www.metacareers.com</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>https://www.facebook.com/legal/terms</t>
@@ -4698,7 +4691,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=META</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Watch Reels monetization, Threads growth, Reality Labs spend, AI capex, WhatsApp Business</t>
@@ -4749,7 +4741,6 @@
           <t>https://careers.google.com</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>https://policies.google.com/terms</t>
@@ -4760,7 +4751,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=GOOG</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Watch Search AI overviews impact, Cloud growth vs AWS/Azure, YouTube ad revenue, Waymo scaling, DOJ antitrust remedies</t>
@@ -4811,7 +4801,6 @@
           <t>https://careers.snap.com</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>https://snap.com/en-US/terms</t>
@@ -4822,7 +4811,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=SNAP</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Watch DAU trend, Snapchat+ subscription, ad revenue vs guidance, AR partnerships</t>
@@ -4863,13 +4851,11 @@
           <t>https://newsroom.pinterest.com</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>https://www.pinterestcareers.com</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>https://policy.pinterest.com/en/terms-of-service</t>
@@ -4880,7 +4866,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=PINS</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Watch MAU trend, ARPU growth, shopping/commerce integrations, Amazon partnership scaling</t>
@@ -4921,13 +4906,11 @@
           <t>https://redditinc.com/press</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>https://redditinc.com/careers</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>https://www.redditinc.com/policies/user-agreement</t>
@@ -4983,13 +4966,11 @@
           <t>https://www.applovin.com/blog/</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>https://www.applovin.com/careers/</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>https://www.applovin.com/legal/</t>
@@ -5000,7 +4981,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=APP</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ad tech / mobile gaming; watch AXON 2 ML model performance, e-commerce ad expansion, gaming vs non-gaming ad mix</t>
@@ -5041,13 +5021,11 @@
           <t>https://unity.com/company/press</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>https://careers.unity.com</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>https://unity.com/legal/terms-of-service</t>
@@ -5058,7 +5036,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=U</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Watch Runtime Fee resolution/aftermath, Create/Grow segment split, subscription renewals</t>
@@ -5099,7 +5076,6 @@
           <t>https://about.netflix.com/en/news</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>https://jobs.netflix.com</t>
@@ -5120,7 +5096,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=NFLX</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Watch subscriber adds, ARM changes, ads-tier growth, content spend, live sports strategy, password-sharing crackdown effect</t>
@@ -5161,7 +5136,6 @@
           <t>https://newsroom.spotify.com</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>https://www.lifeatspotify.com</t>
@@ -5182,7 +5156,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=SPOT</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Watch MAU/Premium sub growth, gross margin (audiobook/podcast), pricing power, Marketplace ad revenue</t>
@@ -5223,13 +5196,11 @@
           <t>https://www.nytco.com/press/</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>https://www.nytco.com/careers/</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>https://help.nytimes.com/hc/en-us/articles/115014893428</t>
@@ -5240,7 +5211,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=NYT</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Watch digital subs adds (news, cooking, games, Wirecutter, Athletic), ARPU, bundle attach rate</t>
@@ -5271,18 +5241,11 @@
           <t>?</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=LIF</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ticker unclear — could be Life Insurance / other. Verify via SEC index.</t>
@@ -5323,13 +5286,11 @@
           <t>https://corporate.bestbuy.com/newsroom/</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>https://jobs.bestbuy.com</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>https://www.bestbuy.com/site/help-topics/terms-and-conditions/pcmcat204400050067.c</t>
@@ -5340,7 +5301,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=BBY</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Watch comparable sales, membership (My Best Buy Total), TotalTech services attach, gaming/PC upgrade cycle</t>
@@ -5381,7 +5341,6 @@
           <t>https://thewaltdisneycompany.com/news/</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>https://jobs.disneycareers.com</t>
@@ -5402,7 +5361,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=DIS</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Watch DTC (Disney+/Hulu/ESPN+) sub growth + profitability, ESPN direct-to-consumer 2025 launch, Parks OI, streaming ARPU</t>
@@ -5443,13 +5401,11 @@
           <t>https://www.foxcorporation.com/news/</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>https://foxcareers.com</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>https://www.fox.com/terms-of-use</t>
@@ -5460,7 +5416,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=FOXA</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Watch Tubi ad growth, Fox News ratings + political cycle, Sports rights renewals, retransmission fees</t>
@@ -5501,20 +5456,16 @@
           <t>https://www.universalmusic.com/news/</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>https://www.universalmusic.com/careers/</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=UMG</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Non-US listed (Euronext); watch subscription streaming ARPU trends, TikTok deal, artist advance write-downs</t>
@@ -5555,13 +5506,11 @@
           <t>https://www.wmg.com/news/</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>https://careers.wmg.com</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>https://www.wmg.com/terms-of-use</t>
@@ -5572,7 +5521,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=WMG</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Watch streaming revenue growth, mechanical royalty rates, artist advances, Live Nation vs. WMG dynamics</t>
@@ -5613,13 +5561,11 @@
           <t>https://www.livenationentertainment.com/newsroom/</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>https://careers.livenationentertainment.com</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>https://help.ticketmaster.com/hc/en-us/articles/10736907984657</t>
@@ -5630,7 +5576,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=LYV</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Watch DOJ lawsuit outcomes, ticket AOV, concert attendance, Ticketmaster market share, VIP/premium seat mix</t>
@@ -5671,13 +5616,11 @@
           <t>https://www.stubhub.com/press</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>https://www.stubhub.com/careers/</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>https://www.stubhub.com/legal/</t>
@@ -5688,7 +5631,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=STUB</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Recent 2024/2025 IPO; watch GMV growth, take rate, marketing spend, international expansion</t>
@@ -5719,18 +5661,11 @@
           <t>?</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=LION</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ticker unclear — could be Fidelity National Financial or Lions Gate. Verify via SEC index.</t>
@@ -5771,13 +5706,11 @@
           <t>https://www.outfrontmedia.com/newsroom/</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>https://www.outfrontmedia.com/careers</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>https://www.outfrontmedia.com/legal/</t>
@@ -5788,7 +5721,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=OUT</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Out-of-home advertising (billboards, transit); watch same-store growth, digital conversion, MTA contract</t>
@@ -5829,13 +5761,11 @@
           <t>https://www.lamar.com/news</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>https://www.lamar.com/careers</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>https://www.lamar.com/terms-of-use</t>
@@ -5846,7 +5776,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=LAMR</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Out-of-home advertising REIT; watch same-store growth, digital board conversion, dividend policy</t>
@@ -5887,20 +5816,16 @@
           <t>https://ir.take2games.com/press-releases</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>https://www.take2games.com/careers</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=TTWO</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Watch GTA VI launch timing/reception, NBA 2K + Zynga performance, deferred revenue accretion</t>
@@ -5941,13 +5866,11 @@
           <t>https://www.ea.com/news</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>https://ea.com/careers</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>https://tos.ea.com</t>
@@ -5958,7 +5881,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=EA</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Watch EA SPORTS FC engagement, Battlefield launches, live services bookings, mobile gaming</t>
@@ -5999,13 +5921,11 @@
           <t>https://ir.roblox.com/news-releases</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>https://careers.roblox.com</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>https://en.help.roblox.com/hc/en-us/articles/115004647846</t>
@@ -6016,7 +5936,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=RBLX</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Watch DAU trend (esp older cohorts), bookings/DAU, developer earnings share, advertising rollout, Roblox Studio AI</t>
@@ -6057,7 +5976,6 @@
           <t>https://www.intuit.com/company/press-room/</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>https://www.intuit.com/careers/</t>
@@ -6078,7 +5996,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=INTU</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Watch QuickBooks Online growth, TurboTax mix, Credit Karma monetization, Mailchimp cross-sell, AI features</t>
@@ -6119,13 +6036,11 @@
           <t>https://mediacenter.adp.com</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>https://jobs.adp.com</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>https://www.adp.com/about-adp/privacy.aspx</t>
@@ -6136,7 +6051,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=ADP</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Watch pays per control (employment proxy), client fund float, employer services growth, PEO segment</t>
@@ -6177,13 +6091,11 @@
           <t>https://www.paychex.com/newsroom</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>https://www.paychex.com/careers</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>https://www.paychex.com/terms-of-use</t>
@@ -6194,7 +6106,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=PAYX</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Watch client count, HR services attach rates, retention, float income, PEO expansion</t>
@@ -6235,13 +6146,11 @@
           <t>https://www.paycom.com/resources/news/</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>https://paycom.com/careers</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>https://www.paycom.com/terms-of-use/</t>
@@ -6252,7 +6161,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=PAYC</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Watch Beti self-service adoption, revenue per client, sales productivity, competitive pressure vs Rippling/Gusto</t>
@@ -6293,13 +6201,11 @@
           <t>https://www.paylocity.com/resources/press-releases/</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>https://www.paylocity.com/careers</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>https://www.paylocity.com/terms/</t>
@@ -6310,7 +6216,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=PCTY</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Watch mid-market win rate, revenue per client, community features / employee experience adoption</t>
@@ -6351,13 +6256,11 @@
           <t>https://www.cdw.com/content/cdw/en/about/newsroom.html</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>https://www.cdw.com/content/cdw/en/careers.html</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>https://www.cdw.com/content/cdw/en/terms-conditions.html</t>
@@ -6368,7 +6271,6 @@
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=CDW</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>IT reseller; watch corporate/public/small-biz mix, gross margin, hardware refresh cycle, cloud services growth</t>
@@ -7029,7 +6931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H395"/>
+  <dimension ref="A1:H398"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17651,6 +17553,96 @@
           <t>careers: change detected</t>
         </is>
       </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr"/>
+      <c r="H396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr"/>
+      <c r="H397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>LIF</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>LIF (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1581760/000195917326005204/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Prober Charles J. (Director) plans to sell 7,930 shares (~$420.7K) on/after 07/13/2026</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr"/>
+      <c r="H398" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -3723,12 +3723,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://www.logitech.com/en-us/about/newsroom.html</t>
+          <t>https://www.logitech.com/press</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://ir.logitech.com/corporate-governance/leadership-team</t>
+          <t>https://ir.logitech.com/corporate-governance/leadership</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://www.logitech.com/en-us/legal/terms-of-use.html</t>
+          <t>https://www.logitech.com/terms</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3841,36 +3841,6 @@
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://ir.tesla.com</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://www.tesla.com/blog</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>https://ir.tesla.com/corporate/leadership</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.tesla.com/careers</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>https://www.tesla.com/inventory/new/m3</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>https://www.tesla.com/about/legal</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=TSLA</t>
@@ -3986,29 +3956,9 @@
           <t>https://investor.uber.com</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>https://www.uber.com/newsroom/</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>https://investor.uber.com/governance/leadership</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.uber.com/global/en/careers/</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>https://www.uber.com/us/en/ride/uberone/</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>https://www.uber.com/legal/terms/</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4058,7 +4008,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://newsroom.expediagroup.com</t>
+          <t>https://www.expediagroup.com/media</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4123,7 +4073,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://www.bookingholdings.com/news/</t>
+          <t>https://www.bookingholdings.com/press-releases</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4133,7 +4083,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://careers.bookingholdings.com</t>
+          <t>https://www.bookingholdings.com/careers</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4253,7 +4203,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.sphereentertainmentco.com/governance/leadership/</t>
+          <t>https://www.sphereentertainmentco.com/leadership</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4268,7 +4218,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://www.sphereentertainmentco.com/legal/</t>
+          <t>https://www.sphereentertainmentco.com/terms</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4568,7 +4518,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://www.clearme.com/legal</t>
+          <t>https://www.clearme.com/terms</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4733,7 +4683,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://abc.xyz/investor/other/management/</t>
+          <t>https://abc.xyz/governance/leadership</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4793,7 +4743,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://investor.snap.com/corporate-governance/leadership/</t>
+          <t>https://investor.snap.com/governance/leadership</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5018,7 +4968,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://unity.com/company/press</t>
+          <t>https://unity.com/news</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5073,7 +5023,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://about.netflix.com/en/news</t>
+          <t>https://about.netflix.com/newsroom</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5283,7 +5233,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://corporate.bestbuy.com/newsroom/</t>
+          <t>https://corporate.bestbuy.com/news</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5508,7 +5458,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://careers.wmg.com</t>
+          <t>https://www.wmg.com/careers</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5563,12 +5513,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://careers.livenationentertainment.com</t>
+          <t>https://www.livenationentertainment.com/careers</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://help.ticketmaster.com/hc/en-us/articles/10736907984657</t>
+          <t>https://www.livenationentertainment.com/terms</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5703,7 +5653,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://www.outfrontmedia.com/newsroom/</t>
+          <t>https://www.outfrontmedia.com/media</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5713,7 +5663,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://www.outfrontmedia.com/legal/</t>
+          <t>https://www.outfrontmedia.com/terms-of-use</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5753,7 +5703,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.lamar.com/investor-relations</t>
+          <t>https://www.lamar.com/about/investors</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5763,7 +5713,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.lamar.com/careers</t>
+          <t>https://www.lamar.com/about/careers</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5918,7 +5868,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://ir.roblox.com/news-releases</t>
+          <t>https://ir.roblox.com/news</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6043,7 +5993,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://www.adp.com/about-adp/privacy.aspx</t>
+          <t>https://www.adp.com/legal</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -6098,7 +6048,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://www.paychex.com/terms-of-use</t>
+          <t>https://www.paychex.com/terms</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -6139,21 +6089,6 @@
       <c r="D79" t="inlineStr">
         <is>
           <t>https://investors.paycom.com</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>https://www.paycom.com/resources/news/</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://paycom.com/careers</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>https://www.paycom.com/terms-of-use/</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6686,240 +6621,227 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId397"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId398"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId620"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17580,9 +17502,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F396" t="inlineStr"/>
-      <c r="G396" t="inlineStr"/>
-      <c r="H396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -17610,9 +17529,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F397" t="inlineStr"/>
-      <c r="G397" t="inlineStr"/>
-      <c r="H397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -17640,9 +17556,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Prober Charles J. (Director) plans to sell 7,930 shares (~$420.7K) on/after 07/13/2026</t>
         </is>
       </c>
-      <c r="F398" t="inlineStr"/>
-      <c r="G398" t="inlineStr"/>
-      <c r="H398" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -6853,7 +6853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H398"/>
+  <dimension ref="A1:H418"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17556,6 +17556,606 @@
           <t>[ROUTINE] Notice of proposed insider sale — Prober Charles J. (Director) plans to sell 7,930 shares (~$420.7K) on/after 07/13/2026</t>
         </is>
       </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1032975/000103297526000028/logi-20260713.htm</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form PRE 14A</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr"/>
+      <c r="H399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr"/>
+      <c r="H400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr"/>
+      <c r="H401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr"/>
+      <c r="H402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr"/>
+      <c r="H403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>YOU</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Clear Secure, Inc.</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1856314/000196858226000724/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Alclear Investments LLC (Officer) plans to sell 250,000 shares (~$13.80M) on/after 07/13/2026</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr"/>
+      <c r="H404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr"/>
+      <c r="H405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000192109426000726/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Olivan Javier (Officer) plans to sell 1,466 shares (~$969.2K) on/after 07/13/2026</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr"/>
+      <c r="H406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>https://blog.google</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr"/>
+      <c r="H407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="inlineStr"/>
+      <c r="H408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="inlineStr"/>
+      <c r="H409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com/premium</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="inlineStr"/>
+      <c r="H410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr"/>
+      <c r="H411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr"/>
+      <c r="H412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>BBY</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Best Buy Co., Inc.</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/764478/000196794026000038/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Richard M Schulze (10% Stockholder) plans to sell 900,000 shares (~$74.52M) on/after 07/13/2026</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr"/>
+      <c r="H413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr"/>
+      <c r="H414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr"/>
+      <c r="H415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr"/>
+      <c r="H416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr"/>
+      <c r="H417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>https://mediacenter.adp.com</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr"/>
+      <c r="H418" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -6853,7 +6853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H418"/>
+  <dimension ref="A1:H444"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17583,9 +17583,6 @@
           <t>[UNKNOWN] Form PRE 14A</t>
         </is>
       </c>
-      <c r="F399" t="inlineStr"/>
-      <c r="G399" t="inlineStr"/>
-      <c r="H399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -17613,9 +17610,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F400" t="inlineStr"/>
-      <c r="G400" t="inlineStr"/>
-      <c r="H400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -17643,9 +17637,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F401" t="inlineStr"/>
-      <c r="G401" t="inlineStr"/>
-      <c r="H401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -17673,9 +17664,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F402" t="inlineStr"/>
-      <c r="G402" t="inlineStr"/>
-      <c r="H402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -17703,9 +17691,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F403" t="inlineStr"/>
-      <c r="G403" t="inlineStr"/>
-      <c r="H403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -17733,9 +17718,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Alclear Investments LLC (Officer) plans to sell 250,000 shares (~$13.80M) on/after 07/13/2026</t>
         </is>
       </c>
-      <c r="F404" t="inlineStr"/>
-      <c r="G404" t="inlineStr"/>
-      <c r="H404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -17763,9 +17745,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F405" t="inlineStr"/>
-      <c r="G405" t="inlineStr"/>
-      <c r="H405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -17793,9 +17772,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Olivan Javier (Officer) plans to sell 1,466 shares (~$969.2K) on/after 07/13/2026</t>
         </is>
       </c>
-      <c r="F406" t="inlineStr"/>
-      <c r="G406" t="inlineStr"/>
-      <c r="H406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -17823,9 +17799,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F407" t="inlineStr"/>
-      <c r="G407" t="inlineStr"/>
-      <c r="H407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -17853,9 +17826,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F408" t="inlineStr"/>
-      <c r="G408" t="inlineStr"/>
-      <c r="H408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -17883,9 +17853,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F409" t="inlineStr"/>
-      <c r="G409" t="inlineStr"/>
-      <c r="H409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -17913,9 +17880,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F410" t="inlineStr"/>
-      <c r="G410" t="inlineStr"/>
-      <c r="H410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -17943,9 +17907,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F411" t="inlineStr"/>
-      <c r="G411" t="inlineStr"/>
-      <c r="H411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -17973,9 +17934,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F412" t="inlineStr"/>
-      <c r="G412" t="inlineStr"/>
-      <c r="H412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -18003,9 +17961,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Richard M Schulze (10% Stockholder) plans to sell 900,000 shares (~$74.52M) on/after 07/13/2026</t>
         </is>
       </c>
-      <c r="F413" t="inlineStr"/>
-      <c r="G413" t="inlineStr"/>
-      <c r="H413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -18033,9 +17988,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F414" t="inlineStr"/>
-      <c r="G414" t="inlineStr"/>
-      <c r="H414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -18063,9 +18015,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="inlineStr"/>
-      <c r="H415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -18093,9 +18042,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F416" t="inlineStr"/>
-      <c r="G416" t="inlineStr"/>
-      <c r="H416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -18123,9 +18069,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F417" t="inlineStr"/>
-      <c r="G417" t="inlineStr"/>
-      <c r="H417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -18153,9 +18096,786 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F418" t="inlineStr"/>
-      <c r="G418" t="inlineStr"/>
-      <c r="H418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Garmin Ltd.</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>https://newsroom.garmin.com</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr"/>
+      <c r="H419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr"/>
+      <c r="H420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>https://investor.uber.com/governance/leadership</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr"/>
+      <c r="H421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000146823326000010/xslF345X06/primarydocument.xml</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr"/>
+      <c r="H422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000119069926000004/xslF345X06/primarydocument.xml</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr"/>
+      <c r="H423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000109035526000006/xslF345X06/primarydocument.xml</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr"/>
+      <c r="H424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr"/>
+      <c r="H425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr"/>
+      <c r="H426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000192109426000731/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 144/A</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr"/>
+      <c r="H428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>https://blog.google</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000192109426000728/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Silbermann Benjamin (Director) plans to sell 46,875 shares (~$1.04M) on/after 07/14/2026</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr"/>
+      <c r="H430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr"/>
+      <c r="H431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="inlineStr"/>
+      <c r="H432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr"/>
+      <c r="H433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com/premium</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr"/>
+      <c r="H434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr"/>
+      <c r="H435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr"/>
+      <c r="H436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/news/</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr"/>
+      <c r="H437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr"/>
+      <c r="H438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr"/>
+      <c r="H439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1335258/000187054326000011/xslF345X06/wk-form4_1784061214.xml</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hopmans John (EVP, M&amp;A and Strategic Finance) 6,083 shares withheld for taxes (vest event) on 2026-07-11</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr"/>
+      <c r="H440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr"/>
+      <c r="H441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr"/>
+      <c r="H442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Paychex, Inc.</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>https://www.paychex.com/careers</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr"/>
+      <c r="H443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Paychex, Inc.</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/723531/000195917326005218/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Martin Mucci (Director) plans to sell 25,000 shares (~$2.75M) on/after 07/14/2026</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr"/>
+      <c r="H444" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -6853,7 +6853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H444"/>
+  <dimension ref="A1:H528"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18123,9 +18123,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F419" t="inlineStr"/>
-      <c r="G419" t="inlineStr"/>
-      <c r="H419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -18153,9 +18150,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F420" t="inlineStr"/>
-      <c r="G420" t="inlineStr"/>
-      <c r="H420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -18183,9 +18177,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F421" t="inlineStr"/>
-      <c r="G421" t="inlineStr"/>
-      <c r="H421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -18213,9 +18204,6 @@
           <t>[ROUTINE] Insider trade</t>
         </is>
       </c>
-      <c r="F422" t="inlineStr"/>
-      <c r="G422" t="inlineStr"/>
-      <c r="H422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -18243,9 +18231,6 @@
           <t>[ROUTINE] Insider trade</t>
         </is>
       </c>
-      <c r="F423" t="inlineStr"/>
-      <c r="G423" t="inlineStr"/>
-      <c r="H423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -18273,9 +18258,6 @@
           <t>[ROUTINE] Insider trade</t>
         </is>
       </c>
-      <c r="F424" t="inlineStr"/>
-      <c r="G424" t="inlineStr"/>
-      <c r="H424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -18303,9 +18285,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F425" t="inlineStr"/>
-      <c r="G425" t="inlineStr"/>
-      <c r="H425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -18333,9 +18312,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F426" t="inlineStr"/>
-      <c r="G426" t="inlineStr"/>
-      <c r="H426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -18363,9 +18339,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F427" t="inlineStr"/>
-      <c r="G427" t="inlineStr"/>
-      <c r="H427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -18393,9 +18366,6 @@
           <t>[UNKNOWN] Form 144/A</t>
         </is>
       </c>
-      <c r="F428" t="inlineStr"/>
-      <c r="G428" t="inlineStr"/>
-      <c r="H428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -18423,9 +18393,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F429" t="inlineStr"/>
-      <c r="G429" t="inlineStr"/>
-      <c r="H429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -18453,9 +18420,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Silbermann Benjamin (Director) plans to sell 46,875 shares (~$1.04M) on/after 07/14/2026</t>
         </is>
       </c>
-      <c r="F430" t="inlineStr"/>
-      <c r="G430" t="inlineStr"/>
-      <c r="H430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -18483,9 +18447,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F431" t="inlineStr"/>
-      <c r="G431" t="inlineStr"/>
-      <c r="H431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -18513,9 +18474,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F432" t="inlineStr"/>
-      <c r="G432" t="inlineStr"/>
-      <c r="H432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -18543,9 +18501,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F433" t="inlineStr"/>
-      <c r="G433" t="inlineStr"/>
-      <c r="H433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -18573,9 +18528,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F434" t="inlineStr"/>
-      <c r="G434" t="inlineStr"/>
-      <c r="H434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -18603,9 +18555,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F435" t="inlineStr"/>
-      <c r="G435" t="inlineStr"/>
-      <c r="H435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -18633,9 +18582,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F436" t="inlineStr"/>
-      <c r="G436" t="inlineStr"/>
-      <c r="H436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -18663,9 +18609,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F437" t="inlineStr"/>
-      <c r="G437" t="inlineStr"/>
-      <c r="H437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -18693,9 +18636,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F438" t="inlineStr"/>
-      <c r="G438" t="inlineStr"/>
-      <c r="H438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -18723,9 +18663,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F439" t="inlineStr"/>
-      <c r="G439" t="inlineStr"/>
-      <c r="H439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -18753,9 +18690,6 @@
           <t>[ROUTINE] Insider trade — Hopmans John (EVP, M&amp;A and Strategic Finance) 6,083 shares withheld for taxes (vest event) on 2026-07-11</t>
         </is>
       </c>
-      <c r="F440" t="inlineStr"/>
-      <c r="G440" t="inlineStr"/>
-      <c r="H440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -18783,9 +18717,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F441" t="inlineStr"/>
-      <c r="G441" t="inlineStr"/>
-      <c r="H441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -18813,9 +18744,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F442" t="inlineStr"/>
-      <c r="G442" t="inlineStr"/>
-      <c r="H442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -18843,9 +18771,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F443" t="inlineStr"/>
-      <c r="G443" t="inlineStr"/>
-      <c r="H443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -18873,9 +18798,2526 @@
           <t>[ROUTINE] Notice of proposed insider sale — Martin Mucci (Director) plans to sell 25,000 shares (~$2.75M) on/after 07/14/2026</t>
         </is>
       </c>
-      <c r="F444" t="inlineStr"/>
-      <c r="G444" t="inlineStr"/>
-      <c r="H444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>https://www.logitech.com/press</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="inlineStr"/>
+      <c r="H445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>https://ir.logitech.com</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr"/>
+      <c r="G446" t="inlineStr"/>
+      <c r="H446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Garmin Ltd.</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>https://newsroom.garmin.com</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr"/>
+      <c r="G447" t="inlineStr"/>
+      <c r="H447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Garmin Ltd.</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>https://www.garmin.com/en-US/company/investors/</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr"/>
+      <c r="G448" t="inlineStr"/>
+      <c r="H448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" t="inlineStr"/>
+      <c r="H449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>https://investor.lyft.com</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr"/>
+      <c r="G450" t="inlineStr"/>
+      <c r="H450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>https://investor.uber.com/governance/leadership</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr"/>
+      <c r="G451" t="inlineStr"/>
+      <c r="H451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>https://www.expediagroup.com/media</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr"/>
+      <c r="G452" t="inlineStr"/>
+      <c r="H452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr"/>
+      <c r="G453" t="inlineStr"/>
+      <c r="H453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr"/>
+      <c r="G454" t="inlineStr"/>
+      <c r="H454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>https://www.bookingholdings.com/careers</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr"/>
+      <c r="G455" t="inlineStr"/>
+      <c r="H455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr"/>
+      <c r="G456" t="inlineStr"/>
+      <c r="H456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>YOU</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Clear Secure, Inc.</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>https://www.clearme.com/terms</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr"/>
+      <c r="G457" t="inlineStr"/>
+      <c r="H457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>YOU</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Clear Secure, Inc.</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>https://ir.clearme.com/news-events</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr"/>
+      <c r="G458" t="inlineStr"/>
+      <c r="H458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>YOU</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Clear Secure, Inc.</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>https://ir.clearme.com</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr"/>
+      <c r="G459" t="inlineStr"/>
+      <c r="H459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>YOU</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Clear Secure, Inc.</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>https://www.clearme.com/careers</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr"/>
+      <c r="G460" t="inlineStr"/>
+      <c r="H460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>YOU</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Clear Secure, Inc.</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1856314/000196858226000811/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Warrior Mensch Foundation (Affiliate) plans to sell 196,656 shares (~$10.09M) on/after 08/10/2026</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr"/>
+      <c r="G461" t="inlineStr"/>
+      <c r="H461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Choice Hotels International, Inc.</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>https://media.choicehotels.com</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr"/>
+      <c r="G462" t="inlineStr"/>
+      <c r="H462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr"/>
+      <c r="G463" t="inlineStr"/>
+      <c r="H463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000192109426000824/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Olivan Javier (Officer) plans to sell 1,692 shares (~$1.02M) on/after 08/10/2026</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr"/>
+      <c r="G464" t="inlineStr"/>
+      <c r="H464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>https://policies.google.com/terms</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr"/>
+      <c r="G465" t="inlineStr"/>
+      <c r="H465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>https://blog.google</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr"/>
+      <c r="G466" t="inlineStr"/>
+      <c r="H466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526342390/d171253d8k.htm</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr"/>
+      <c r="G467" t="inlineStr"/>
+      <c r="H467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>https://snap.com/en-US/terms</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr"/>
+      <c r="G468" t="inlineStr"/>
+      <c r="H468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>https://investor.snap.com/governance/leadership</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr"/>
+      <c r="G469" t="inlineStr"/>
+      <c r="H469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>https://newsroom.snap.com</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr"/>
+      <c r="G470" t="inlineStr"/>
+      <c r="H470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>https://investor.snap.com</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr"/>
+      <c r="G471" t="inlineStr"/>
+      <c r="H471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr"/>
+      <c r="G472" t="inlineStr"/>
+      <c r="H472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000088698226000325/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr"/>
+      <c r="G473" t="inlineStr"/>
+      <c r="H473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>https://www.redditinc.com/policies/user-agreement</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr"/>
+      <c r="G474" t="inlineStr"/>
+      <c r="H474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/press</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr"/>
+      <c r="G475" t="inlineStr"/>
+      <c r="H475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr"/>
+      <c r="G476" t="inlineStr"/>
+      <c r="H476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>AppLovin Corporation</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>https://www.applovin.com/legal/</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr"/>
+      <c r="G477" t="inlineStr"/>
+      <c r="H477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>AppLovin Corporation</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>https://www.applovin.com/blog/</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr"/>
+      <c r="G478" t="inlineStr"/>
+      <c r="H478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>AppLovin Corporation</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>https://www.applovin.com/careers/</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr"/>
+      <c r="G479" t="inlineStr"/>
+      <c r="H479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr"/>
+      <c r="G480" t="inlineStr"/>
+      <c r="H480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810806/000122228726000017/xslF345X06/wk-form4_1786405422.xml</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Roelof Botha (Director) other: 461,106 shares on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="inlineStr"/>
+      <c r="H481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr"/>
+      <c r="G482" t="inlineStr"/>
+      <c r="H482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065280/000106528026000249/xslF345X06/wk-form4_1786394054.xml</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Neumann Spencer Adam (Chief Financial Officer) sold 9,248 shares @ $75.79 ($700.9K) on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr"/>
+      <c r="G483" t="inlineStr"/>
+      <c r="H483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065280/000195004726007858/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Neumann Spencer (Officer) plans to sell 9,248 shares (~$700.9K) on/after 08/10/2026</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr"/>
+      <c r="G484" t="inlineStr"/>
+      <c r="H484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com/premium</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr"/>
+      <c r="G485" t="inlineStr"/>
+      <c r="H485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr"/>
+      <c r="G486" t="inlineStr"/>
+      <c r="H486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>https://investors.spotify.com</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr"/>
+      <c r="G487" t="inlineStr"/>
+      <c r="H487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr"/>
+      <c r="G488" t="inlineStr"/>
+      <c r="H488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>NYT</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>The New York Times Company</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>https://help.nytimes.com/hc/en-us/articles/115014893428</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr"/>
+      <c r="G489" t="inlineStr"/>
+      <c r="H489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>LIF</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>LIF (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1581760/000195917326005857/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Morin Brit (Director) plans to sell 15,582 shares (~$1.01M) on/after 08/10/2026</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr"/>
+      <c r="G490" t="inlineStr"/>
+      <c r="H490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>LIF</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>LIF (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1581760/000158176026000142/lifx-20260810.htm</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr"/>
+      <c r="G491" t="inlineStr"/>
+      <c r="H491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>LIF</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>LIF (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1581760/000158176026000141/lifx-20260630.htm</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Quarterly report</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr"/>
+      <c r="G492" t="inlineStr"/>
+      <c r="H492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>BBY</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Best Buy Co., Inc.</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>https://www.bestbuy.com/site/help-topics/terms-and-conditions/pcmcat204400050067.c</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr"/>
+      <c r="G493" t="inlineStr"/>
+      <c r="H493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr"/>
+      <c r="G494" t="inlineStr"/>
+      <c r="H494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/news/</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr"/>
+      <c r="G495" t="inlineStr"/>
+      <c r="H495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/investor-relations/</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr"/>
+      <c r="G496" t="inlineStr"/>
+      <c r="H496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr"/>
+      <c r="G497" t="inlineStr"/>
+      <c r="H497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>https://investor.foxcorporation.com</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr"/>
+      <c r="G498" t="inlineStr"/>
+      <c r="H498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr"/>
+      <c r="G499" t="inlineStr"/>
+      <c r="H499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000162828026055398/xslF345X06/wk-form4_1786398279.xml</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr"/>
+      <c r="G500" t="inlineStr"/>
+      <c r="H500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000162828026055396/xslF345X06/wk-form4_1786398195.xml</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr"/>
+      <c r="G501" t="inlineStr"/>
+      <c r="H501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000162828026055392/xslF345X06/wk-form4_1786398055.xml</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="inlineStr"/>
+      <c r="H502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000162828026055391/xslF345X06/wk-form4_1786398011.xml</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr"/>
+      <c r="G503" t="inlineStr"/>
+      <c r="H503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000119312526341282/d140335ds3asr.htm</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form S-3ASR</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr"/>
+      <c r="G504" t="inlineStr"/>
+      <c r="H504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000119312526341217/d133486d425.htm</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 425</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr"/>
+      <c r="G505" t="inlineStr"/>
+      <c r="H505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000119312526341200/d133486d8ka.htm</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 8-K/A</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr"/>
+      <c r="G506" t="inlineStr"/>
+      <c r="H506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>UMG</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Universal Music Group N.V.</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>https://www.universalmusic.com/news/</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr"/>
+      <c r="G507" t="inlineStr"/>
+      <c r="H507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>UMG</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Universal Music Group N.V.</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>https://www.universalmusic.com/careers/</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr"/>
+      <c r="G508" t="inlineStr"/>
+      <c r="H508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Warner Music Group Corp.</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>https://www.wmg.com/news/</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr"/>
+      <c r="G509" t="inlineStr"/>
+      <c r="H509" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Warner Music Group Corp.</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>https://investors.wmg.com</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr"/>
+      <c r="G510" t="inlineStr"/>
+      <c r="H510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr"/>
+      <c r="G511" t="inlineStr"/>
+      <c r="H511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>https://www.livenationentertainment.com/careers</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr"/>
+      <c r="G512" t="inlineStr"/>
+      <c r="H512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr"/>
+      <c r="G513" t="inlineStr"/>
+      <c r="H513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>OUTFRONT Media Inc.</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>https://investor.outfrontmedia.com</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr"/>
+      <c r="G514" t="inlineStr"/>
+      <c r="H514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr"/>
+      <c r="G515" t="inlineStr"/>
+      <c r="H515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/946581/000195824426000496/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — H. Strauss Zelnick (Officer) plans to sell 40,000 shares (~$10.14M) on/after 08/10/2026</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr"/>
+      <c r="G516" t="inlineStr"/>
+      <c r="H516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr"/>
+      <c r="G517" t="inlineStr"/>
+      <c r="H517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr"/>
+      <c r="G518" t="inlineStr"/>
+      <c r="H518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>https://ea.com/careers</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr"/>
+      <c r="G519" t="inlineStr"/>
+      <c r="H519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>https://quickbooks.intuit.com/pricing/</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr"/>
+      <c r="G520" t="inlineStr"/>
+      <c r="H520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>https://investors.intuit.com</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr"/>
+      <c r="G521" t="inlineStr"/>
+      <c r="H521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>https://mediacenter.adp.com</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr"/>
+      <c r="G522" t="inlineStr"/>
+      <c r="H522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>https://investors.adp.com</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr"/>
+      <c r="G523" t="inlineStr"/>
+      <c r="H523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Paychex, Inc.</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>https://www.paychex.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr"/>
+      <c r="G524" t="inlineStr"/>
+      <c r="H524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Paychex, Inc.</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>https://investor.paychex.com</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr"/>
+      <c r="G525" t="inlineStr"/>
+      <c r="H525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>PAYC</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Paycom Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>https://investors.paycom.com</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr"/>
+      <c r="G526" t="inlineStr"/>
+      <c r="H526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159787026000002/xslF345X06/wk-form4_1786392623.xml</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sarowitz Steven I (Director) sold 11,136 shares @ $150.81 ($1.68M) on 2026-08-06</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr"/>
+      <c r="G527" t="inlineStr"/>
+      <c r="H527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>https://investor.cdw.com</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr"/>
+      <c r="G528" t="inlineStr"/>
+      <c r="H528" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -6853,7 +6853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H528"/>
+  <dimension ref="A1:H575"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18825,9 +18825,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F445" t="inlineStr"/>
-      <c r="G445" t="inlineStr"/>
-      <c r="H445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -18855,9 +18852,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F446" t="inlineStr"/>
-      <c r="G446" t="inlineStr"/>
-      <c r="H446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -18885,9 +18879,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F447" t="inlineStr"/>
-      <c r="G447" t="inlineStr"/>
-      <c r="H447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -18915,9 +18906,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F448" t="inlineStr"/>
-      <c r="G448" t="inlineStr"/>
-      <c r="H448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -18945,9 +18933,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F449" t="inlineStr"/>
-      <c r="G449" t="inlineStr"/>
-      <c r="H449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -18975,9 +18960,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F450" t="inlineStr"/>
-      <c r="G450" t="inlineStr"/>
-      <c r="H450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -19005,9 +18987,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F451" t="inlineStr"/>
-      <c r="G451" t="inlineStr"/>
-      <c r="H451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -19035,9 +19014,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F452" t="inlineStr"/>
-      <c r="G452" t="inlineStr"/>
-      <c r="H452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -19065,9 +19041,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F453" t="inlineStr"/>
-      <c r="G453" t="inlineStr"/>
-      <c r="H453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -19095,9 +19068,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F454" t="inlineStr"/>
-      <c r="G454" t="inlineStr"/>
-      <c r="H454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -19125,9 +19095,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F455" t="inlineStr"/>
-      <c r="G455" t="inlineStr"/>
-      <c r="H455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -19155,9 +19122,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F456" t="inlineStr"/>
-      <c r="G456" t="inlineStr"/>
-      <c r="H456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -19185,9 +19149,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F457" t="inlineStr"/>
-      <c r="G457" t="inlineStr"/>
-      <c r="H457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -19215,9 +19176,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F458" t="inlineStr"/>
-      <c r="G458" t="inlineStr"/>
-      <c r="H458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -19245,9 +19203,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F459" t="inlineStr"/>
-      <c r="G459" t="inlineStr"/>
-      <c r="H459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -19275,9 +19230,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F460" t="inlineStr"/>
-      <c r="G460" t="inlineStr"/>
-      <c r="H460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -19305,9 +19257,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Warrior Mensch Foundation (Affiliate) plans to sell 196,656 shares (~$10.09M) on/after 08/10/2026</t>
         </is>
       </c>
-      <c r="F461" t="inlineStr"/>
-      <c r="G461" t="inlineStr"/>
-      <c r="H461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -19335,9 +19284,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F462" t="inlineStr"/>
-      <c r="G462" t="inlineStr"/>
-      <c r="H462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -19365,9 +19311,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F463" t="inlineStr"/>
-      <c r="G463" t="inlineStr"/>
-      <c r="H463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -19395,9 +19338,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Olivan Javier (Officer) plans to sell 1,692 shares (~$1.02M) on/after 08/10/2026</t>
         </is>
       </c>
-      <c r="F464" t="inlineStr"/>
-      <c r="G464" t="inlineStr"/>
-      <c r="H464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -19425,9 +19365,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F465" t="inlineStr"/>
-      <c r="G465" t="inlineStr"/>
-      <c r="H465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -19455,9 +19392,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F466" t="inlineStr"/>
-      <c r="G466" t="inlineStr"/>
-      <c r="H466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -19485,9 +19419,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F467" t="inlineStr"/>
-      <c r="G467" t="inlineStr"/>
-      <c r="H467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -19515,9 +19446,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F468" t="inlineStr"/>
-      <c r="G468" t="inlineStr"/>
-      <c r="H468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -19545,9 +19473,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F469" t="inlineStr"/>
-      <c r="G469" t="inlineStr"/>
-      <c r="H469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -19575,9 +19500,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F470" t="inlineStr"/>
-      <c r="G470" t="inlineStr"/>
-      <c r="H470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -19605,9 +19527,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F471" t="inlineStr"/>
-      <c r="G471" t="inlineStr"/>
-      <c r="H471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -19635,9 +19554,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F472" t="inlineStr"/>
-      <c r="G472" t="inlineStr"/>
-      <c r="H472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -19665,9 +19581,6 @@
           <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
         </is>
       </c>
-      <c r="F473" t="inlineStr"/>
-      <c r="G473" t="inlineStr"/>
-      <c r="H473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -19695,9 +19608,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F474" t="inlineStr"/>
-      <c r="G474" t="inlineStr"/>
-      <c r="H474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -19725,9 +19635,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F475" t="inlineStr"/>
-      <c r="G475" t="inlineStr"/>
-      <c r="H475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -19755,9 +19662,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F476" t="inlineStr"/>
-      <c r="G476" t="inlineStr"/>
-      <c r="H476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -19785,9 +19689,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F477" t="inlineStr"/>
-      <c r="G477" t="inlineStr"/>
-      <c r="H477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -19815,9 +19716,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F478" t="inlineStr"/>
-      <c r="G478" t="inlineStr"/>
-      <c r="H478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -19845,9 +19743,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F479" t="inlineStr"/>
-      <c r="G479" t="inlineStr"/>
-      <c r="H479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -19875,9 +19770,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F480" t="inlineStr"/>
-      <c r="G480" t="inlineStr"/>
-      <c r="H480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -19905,9 +19797,6 @@
           <t>[ROUTINE] Insider trade — Roelof Botha (Director) other: 461,106 shares on 2026-08-07</t>
         </is>
       </c>
-      <c r="F481" t="inlineStr"/>
-      <c r="G481" t="inlineStr"/>
-      <c r="H481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -19935,9 +19824,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F482" t="inlineStr"/>
-      <c r="G482" t="inlineStr"/>
-      <c r="H482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -19965,9 +19851,6 @@
           <t>[ROUTINE] Insider trade — Neumann Spencer Adam (Chief Financial Officer) sold 9,248 shares @ $75.79 ($700.9K) on 2026-08-10</t>
         </is>
       </c>
-      <c r="F483" t="inlineStr"/>
-      <c r="G483" t="inlineStr"/>
-      <c r="H483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -19995,9 +19878,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Neumann Spencer (Officer) plans to sell 9,248 shares (~$700.9K) on/after 08/10/2026</t>
         </is>
       </c>
-      <c r="F484" t="inlineStr"/>
-      <c r="G484" t="inlineStr"/>
-      <c r="H484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -20025,9 +19905,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F485" t="inlineStr"/>
-      <c r="G485" t="inlineStr"/>
-      <c r="H485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -20055,9 +19932,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F486" t="inlineStr"/>
-      <c r="G486" t="inlineStr"/>
-      <c r="H486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -20085,9 +19959,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F487" t="inlineStr"/>
-      <c r="G487" t="inlineStr"/>
-      <c r="H487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -20115,9 +19986,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F488" t="inlineStr"/>
-      <c r="G488" t="inlineStr"/>
-      <c r="H488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -20145,9 +20013,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F489" t="inlineStr"/>
-      <c r="G489" t="inlineStr"/>
-      <c r="H489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -20175,9 +20040,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Morin Brit (Director) plans to sell 15,582 shares (~$1.01M) on/after 08/10/2026</t>
         </is>
       </c>
-      <c r="F490" t="inlineStr"/>
-      <c r="G490" t="inlineStr"/>
-      <c r="H490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -20205,9 +20067,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F491" t="inlineStr"/>
-      <c r="G491" t="inlineStr"/>
-      <c r="H491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -20235,9 +20094,6 @@
           <t>[MATERIAL] Quarterly report</t>
         </is>
       </c>
-      <c r="F492" t="inlineStr"/>
-      <c r="G492" t="inlineStr"/>
-      <c r="H492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -20265,9 +20121,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F493" t="inlineStr"/>
-      <c r="G493" t="inlineStr"/>
-      <c r="H493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -20295,9 +20148,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F494" t="inlineStr"/>
-      <c r="G494" t="inlineStr"/>
-      <c r="H494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -20325,9 +20175,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F495" t="inlineStr"/>
-      <c r="G495" t="inlineStr"/>
-      <c r="H495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -20355,9 +20202,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F496" t="inlineStr"/>
-      <c r="G496" t="inlineStr"/>
-      <c r="H496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -20385,9 +20229,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F497" t="inlineStr"/>
-      <c r="G497" t="inlineStr"/>
-      <c r="H497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -20415,9 +20256,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F498" t="inlineStr"/>
-      <c r="G498" t="inlineStr"/>
-      <c r="H498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -20445,9 +20283,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F499" t="inlineStr"/>
-      <c r="G499" t="inlineStr"/>
-      <c r="H499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -20475,9 +20310,6 @@
           <t>[ROUTINE] Insider trade</t>
         </is>
       </c>
-      <c r="F500" t="inlineStr"/>
-      <c r="G500" t="inlineStr"/>
-      <c r="H500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -20505,9 +20337,6 @@
           <t>[ROUTINE] Insider trade</t>
         </is>
       </c>
-      <c r="F501" t="inlineStr"/>
-      <c r="G501" t="inlineStr"/>
-      <c r="H501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -20535,9 +20364,6 @@
           <t>[ROUTINE] Insider trade</t>
         </is>
       </c>
-      <c r="F502" t="inlineStr"/>
-      <c r="G502" t="inlineStr"/>
-      <c r="H502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -20565,9 +20391,6 @@
           <t>[ROUTINE] Insider trade</t>
         </is>
       </c>
-      <c r="F503" t="inlineStr"/>
-      <c r="G503" t="inlineStr"/>
-      <c r="H503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -20595,9 +20418,6 @@
           <t>[UNKNOWN] Form S-3ASR</t>
         </is>
       </c>
-      <c r="F504" t="inlineStr"/>
-      <c r="G504" t="inlineStr"/>
-      <c r="H504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -20625,9 +20445,6 @@
           <t>[UNKNOWN] Form 425</t>
         </is>
       </c>
-      <c r="F505" t="inlineStr"/>
-      <c r="G505" t="inlineStr"/>
-      <c r="H505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -20655,9 +20472,6 @@
           <t>[UNKNOWN] Form 8-K/A</t>
         </is>
       </c>
-      <c r="F506" t="inlineStr"/>
-      <c r="G506" t="inlineStr"/>
-      <c r="H506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -20685,9 +20499,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F507" t="inlineStr"/>
-      <c r="G507" t="inlineStr"/>
-      <c r="H507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -20715,9 +20526,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F508" t="inlineStr"/>
-      <c r="G508" t="inlineStr"/>
-      <c r="H508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -20745,9 +20553,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F509" t="inlineStr"/>
-      <c r="G509" t="inlineStr"/>
-      <c r="H509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -20775,9 +20580,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F510" t="inlineStr"/>
-      <c r="G510" t="inlineStr"/>
-      <c r="H510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -20805,9 +20607,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F511" t="inlineStr"/>
-      <c r="G511" t="inlineStr"/>
-      <c r="H511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -20835,9 +20634,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F512" t="inlineStr"/>
-      <c r="G512" t="inlineStr"/>
-      <c r="H512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -20865,9 +20661,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F513" t="inlineStr"/>
-      <c r="G513" t="inlineStr"/>
-      <c r="H513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -20895,9 +20688,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F514" t="inlineStr"/>
-      <c r="G514" t="inlineStr"/>
-      <c r="H514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -20925,9 +20715,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F515" t="inlineStr"/>
-      <c r="G515" t="inlineStr"/>
-      <c r="H515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -20955,9 +20742,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — H. Strauss Zelnick (Officer) plans to sell 40,000 shares (~$10.14M) on/after 08/10/2026</t>
         </is>
       </c>
-      <c r="F516" t="inlineStr"/>
-      <c r="G516" t="inlineStr"/>
-      <c r="H516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -20985,9 +20769,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F517" t="inlineStr"/>
-      <c r="G517" t="inlineStr"/>
-      <c r="H517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -21015,9 +20796,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F518" t="inlineStr"/>
-      <c r="G518" t="inlineStr"/>
-      <c r="H518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -21045,9 +20823,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F519" t="inlineStr"/>
-      <c r="G519" t="inlineStr"/>
-      <c r="H519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -21075,9 +20850,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F520" t="inlineStr"/>
-      <c r="G520" t="inlineStr"/>
-      <c r="H520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -21105,9 +20877,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F521" t="inlineStr"/>
-      <c r="G521" t="inlineStr"/>
-      <c r="H521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -21135,9 +20904,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F522" t="inlineStr"/>
-      <c r="G522" t="inlineStr"/>
-      <c r="H522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -21165,9 +20931,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F523" t="inlineStr"/>
-      <c r="G523" t="inlineStr"/>
-      <c r="H523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -21195,9 +20958,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F524" t="inlineStr"/>
-      <c r="G524" t="inlineStr"/>
-      <c r="H524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -21225,9 +20985,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F525" t="inlineStr"/>
-      <c r="G525" t="inlineStr"/>
-      <c r="H525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -21255,9 +21012,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F526" t="inlineStr"/>
-      <c r="G526" t="inlineStr"/>
-      <c r="H526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -21285,9 +21039,6 @@
           <t>[ROUTINE] Insider trade — Sarowitz Steven I (Director) sold 11,136 shares @ $150.81 ($1.68M) on 2026-08-06</t>
         </is>
       </c>
-      <c r="F527" t="inlineStr"/>
-      <c r="G527" t="inlineStr"/>
-      <c r="H527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -21315,9 +21066,1416 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F528" t="inlineStr"/>
-      <c r="G528" t="inlineStr"/>
-      <c r="H528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Garmin Ltd.</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1121788/000101410826000045/xslF345X06/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Jonathan Burrell (Director) gift: 90,000 Registered Shares on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr"/>
+      <c r="G529" t="inlineStr"/>
+      <c r="H529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr"/>
+      <c r="G530" t="inlineStr"/>
+      <c r="H530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1759509/000197349526000005/xslF345X06/form4-08112026_100831.xml</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Whiteside Janey (Director) sold 14,220 shares @ $17.00 ($241.7K) on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr"/>
+      <c r="G531" t="inlineStr"/>
+      <c r="H531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr"/>
+      <c r="G532" t="inlineStr"/>
+      <c r="H532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr"/>
+      <c r="G533" t="inlineStr"/>
+      <c r="H533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr"/>
+      <c r="G534" t="inlineStr"/>
+      <c r="H534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000119312526345333/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Chesky Brian (CEO and Chairman) sold 20,000 shares @ $173.61 ($3.47M) on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr"/>
+      <c r="G535" t="inlineStr"/>
+      <c r="H535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000119312526345326/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Chesky Brian (CEO and Chairman) sold 200,000 shares @ $174.79 ($34.96M) on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr"/>
+      <c r="G536" t="inlineStr"/>
+      <c r="H536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000119312526345316/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Blecharczyk Nathan (Chief Strategy Officer) sold 531,000 shares @ $174.41 ($92.61M) on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr"/>
+      <c r="G537" t="inlineStr"/>
+      <c r="H537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000119312526345303/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Kenneth I Chenault (Director) sold 8,346 shares @ $170.00 ($1.42M) on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr"/>
+      <c r="G538" t="inlineStr"/>
+      <c r="H538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Choice Hotels International, Inc.</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>https://media.choicehotels.com</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr"/>
+      <c r="G539" t="inlineStr"/>
+      <c r="H539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>https://blog.google</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr"/>
+      <c r="G540" t="inlineStr"/>
+      <c r="H540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526345383/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sergey Brin (Director) C: 673,200 shares on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr"/>
+      <c r="G541" t="inlineStr"/>
+      <c r="H541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000180678426000003/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Coffey Kelly (Director) granted 46,905 shares on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr"/>
+      <c r="G542" t="inlineStr"/>
+      <c r="H542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000187456626000003/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Vargas Fidel (Director) granted 46,905 shares on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr"/>
+      <c r="G543" t="inlineStr"/>
+      <c r="H543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000169932326000002/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Coles Joanna (Director) granted 46,905 shares on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr"/>
+      <c r="G544" t="inlineStr"/>
+      <c r="H544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000175091326000003/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lanzone James (Director) granted 46,905 shares on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr"/>
+      <c r="G545" t="inlineStr"/>
+      <c r="H545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000213702426000012/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Wood Luke (Director) granted 46,905 shares on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr"/>
+      <c r="G546" t="inlineStr"/>
+      <c r="H546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000127335726000003/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Scott D Miller (Director) granted 46,905 shares on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr"/>
+      <c r="G547" t="inlineStr"/>
+      <c r="H547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000174331726000003/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Spence Patrick (Director) granted 46,905 shares on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr"/>
+      <c r="G548" t="inlineStr"/>
+      <c r="H548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000160611526000006/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lynton Michael (Director) granted 46,905 shares on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr"/>
+      <c r="G549" t="inlineStr"/>
+      <c r="H549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000183277826000003/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Jenkins Elizabeth (Director) granted 46,905 shares on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr"/>
+      <c r="G550" t="inlineStr"/>
+      <c r="H550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000174798926000003/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Thorpe Poppy (Director) granted 46,905 shares on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr"/>
+      <c r="G551" t="inlineStr"/>
+      <c r="H551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000172739626000007/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Morrow Rebecca (Chief Accounting Officer) granted 65,081 shares on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr"/>
+      <c r="G552" t="inlineStr"/>
+      <c r="H552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000165473326000010/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Matthew Blake Mcrae (Director) granted 46,905 shares on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr"/>
+      <c r="G553" t="inlineStr"/>
+      <c r="H553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000192109426000830/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Silbermann Benjamin (Director) plans to sell 46,875 shares (~$1.12M) on/after 08/11/2026</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr"/>
+      <c r="G554" t="inlineStr"/>
+      <c r="H554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000192109426000829/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Brown Claude Leonard (Officer) plans to sell 12,240 shares (~$292.3K) on/after 08/11/2026</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr"/>
+      <c r="G555" t="inlineStr"/>
+      <c r="H555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr"/>
+      <c r="G556" t="inlineStr"/>
+      <c r="H556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>AppLovin Corporation</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>https://www.applovin.com/blog/</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr"/>
+      <c r="G557" t="inlineStr"/>
+      <c r="H557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr"/>
+      <c r="G558" t="inlineStr"/>
+      <c r="H558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810806/000197640826000716/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Dovrat Shlomo (Former Director) plans to sell 50,000 shares (~$2.15M) on/after 08/11/2026</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr"/>
+      <c r="G559" t="inlineStr"/>
+      <c r="H559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810806/000119312526344792/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Durban Egon (Director) other: 21,537 shares on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr"/>
+      <c r="G560" t="inlineStr"/>
+      <c r="H560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com/premium</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr"/>
+      <c r="G561" t="inlineStr"/>
+      <c r="H561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr"/>
+      <c r="G562" t="inlineStr"/>
+      <c r="H562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr"/>
+      <c r="G563" t="inlineStr"/>
+      <c r="H563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/news/</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr"/>
+      <c r="G564" t="inlineStr"/>
+      <c r="H564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr"/>
+      <c r="G565" t="inlineStr"/>
+      <c r="H565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr"/>
+      <c r="G566" t="inlineStr"/>
+      <c r="H566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Warner Music Group Corp.</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1319161/000119312526344951/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>[ROUTINE] New insider — initial ownership statement</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr"/>
+      <c r="G567" t="inlineStr"/>
+      <c r="H567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr"/>
+      <c r="G568" t="inlineStr"/>
+      <c r="H568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr"/>
+      <c r="G569" t="inlineStr"/>
+      <c r="H569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/946581/000094658126000069/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Strauss Zelnick (Chairman, CEO) sold 40,000 shares @ $252.64 ($10.11M) on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr"/>
+      <c r="G570" t="inlineStr"/>
+      <c r="H570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000183498826000008/xslF345X06/form4-08112026_080826.xml</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lee Anthony P (Director) gift: 100,000 shares on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr"/>
+      <c r="G571" t="inlineStr"/>
+      <c r="H571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>https://investors.intuit.com</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr"/>
+      <c r="G572" t="inlineStr"/>
+      <c r="H572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>PAYC</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Paycom Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1590955/000119312526345730/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Boelte Craig E. (Director) gift: 1,000 shares on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr"/>
+      <c r="G573" t="inlineStr"/>
+      <c r="H573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159787026000004/xslF345X06/wk-form4_1786478595.xml</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sarowitz Steven I (Director) sold 32,972 shares @ $152.48 ($5.03M) on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr"/>
+      <c r="G574" t="inlineStr"/>
+      <c r="H574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000140205726000068/xslF345X06/wk-form4_1786479982.xml</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Elizabeth H. Connelly (See Remarks) sold 26,695 shares @ $137.62 ($3.67M) on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr"/>
+      <c r="G575" t="inlineStr"/>
+      <c r="H575" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -6853,7 +6853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H575"/>
+  <dimension ref="A1:H581"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21093,9 +21093,6 @@
           <t>[ROUTINE] Insider trade — Jonathan Burrell (Director) gift: 90,000 Registered Shares on 2026-08-10</t>
         </is>
       </c>
-      <c r="F529" t="inlineStr"/>
-      <c r="G529" t="inlineStr"/>
-      <c r="H529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -21123,9 +21120,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F530" t="inlineStr"/>
-      <c r="G530" t="inlineStr"/>
-      <c r="H530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -21153,9 +21147,6 @@
           <t>[ROUTINE] Insider trade — Whiteside Janey (Director) sold 14,220 shares @ $17.00 ($241.7K) on 2026-08-07</t>
         </is>
       </c>
-      <c r="F531" t="inlineStr"/>
-      <c r="G531" t="inlineStr"/>
-      <c r="H531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -21183,9 +21174,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F532" t="inlineStr"/>
-      <c r="G532" t="inlineStr"/>
-      <c r="H532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -21213,9 +21201,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F533" t="inlineStr"/>
-      <c r="G533" t="inlineStr"/>
-      <c r="H533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -21243,9 +21228,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F534" t="inlineStr"/>
-      <c r="G534" t="inlineStr"/>
-      <c r="H534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -21273,9 +21255,6 @@
           <t>[ROUTINE] Insider trade — Chesky Brian (CEO and Chairman) sold 20,000 shares @ $173.61 ($3.47M) on 2026-08-07</t>
         </is>
       </c>
-      <c r="F535" t="inlineStr"/>
-      <c r="G535" t="inlineStr"/>
-      <c r="H535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -21303,9 +21282,6 @@
           <t>[ROUTINE] Insider trade — Chesky Brian (CEO and Chairman) sold 200,000 shares @ $174.79 ($34.96M) on 2026-08-07</t>
         </is>
       </c>
-      <c r="F536" t="inlineStr"/>
-      <c r="G536" t="inlineStr"/>
-      <c r="H536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -21333,9 +21309,6 @@
           <t>[ROUTINE] Insider trade — Blecharczyk Nathan (Chief Strategy Officer) sold 531,000 shares @ $174.41 ($92.61M) on 2026-08-07</t>
         </is>
       </c>
-      <c r="F537" t="inlineStr"/>
-      <c r="G537" t="inlineStr"/>
-      <c r="H537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -21363,9 +21336,6 @@
           <t>[ROUTINE] Insider trade — Kenneth I Chenault (Director) sold 8,346 shares @ $170.00 ($1.42M) on 2026-08-07</t>
         </is>
       </c>
-      <c r="F538" t="inlineStr"/>
-      <c r="G538" t="inlineStr"/>
-      <c r="H538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -21393,9 +21363,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F539" t="inlineStr"/>
-      <c r="G539" t="inlineStr"/>
-      <c r="H539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -21423,9 +21390,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F540" t="inlineStr"/>
-      <c r="G540" t="inlineStr"/>
-      <c r="H540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -21453,9 +21417,6 @@
           <t>[ROUTINE] Insider trade — Sergey Brin (Director) C: 673,200 shares on 2026-08-07</t>
         </is>
       </c>
-      <c r="F541" t="inlineStr"/>
-      <c r="G541" t="inlineStr"/>
-      <c r="H541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -21483,9 +21444,6 @@
           <t>[ROUTINE] Insider trade — Coffey Kelly (Director) granted 46,905 shares on 2026-08-07</t>
         </is>
       </c>
-      <c r="F542" t="inlineStr"/>
-      <c r="G542" t="inlineStr"/>
-      <c r="H542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -21513,9 +21471,6 @@
           <t>[ROUTINE] Insider trade — Vargas Fidel (Director) granted 46,905 shares on 2026-08-07</t>
         </is>
       </c>
-      <c r="F543" t="inlineStr"/>
-      <c r="G543" t="inlineStr"/>
-      <c r="H543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -21543,9 +21498,6 @@
           <t>[ROUTINE] Insider trade — Coles Joanna (Director) granted 46,905 shares on 2026-08-07</t>
         </is>
       </c>
-      <c r="F544" t="inlineStr"/>
-      <c r="G544" t="inlineStr"/>
-      <c r="H544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -21573,9 +21525,6 @@
           <t>[ROUTINE] Insider trade — Lanzone James (Director) granted 46,905 shares on 2026-08-07</t>
         </is>
       </c>
-      <c r="F545" t="inlineStr"/>
-      <c r="G545" t="inlineStr"/>
-      <c r="H545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -21603,9 +21552,6 @@
           <t>[ROUTINE] Insider trade — Wood Luke (Director) granted 46,905 shares on 2026-08-07</t>
         </is>
       </c>
-      <c r="F546" t="inlineStr"/>
-      <c r="G546" t="inlineStr"/>
-      <c r="H546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -21633,9 +21579,6 @@
           <t>[ROUTINE] Insider trade — Scott D Miller (Director) granted 46,905 shares on 2026-08-07</t>
         </is>
       </c>
-      <c r="F547" t="inlineStr"/>
-      <c r="G547" t="inlineStr"/>
-      <c r="H547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -21663,9 +21606,6 @@
           <t>[ROUTINE] Insider trade — Spence Patrick (Director) granted 46,905 shares on 2026-08-07</t>
         </is>
       </c>
-      <c r="F548" t="inlineStr"/>
-      <c r="G548" t="inlineStr"/>
-      <c r="H548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -21693,9 +21633,6 @@
           <t>[ROUTINE] Insider trade — Lynton Michael (Director) granted 46,905 shares on 2026-08-07</t>
         </is>
       </c>
-      <c r="F549" t="inlineStr"/>
-      <c r="G549" t="inlineStr"/>
-      <c r="H549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -21723,9 +21660,6 @@
           <t>[ROUTINE] Insider trade — Jenkins Elizabeth (Director) granted 46,905 shares on 2026-08-07</t>
         </is>
       </c>
-      <c r="F550" t="inlineStr"/>
-      <c r="G550" t="inlineStr"/>
-      <c r="H550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -21753,9 +21687,6 @@
           <t>[ROUTINE] Insider trade — Thorpe Poppy (Director) granted 46,905 shares on 2026-08-07</t>
         </is>
       </c>
-      <c r="F551" t="inlineStr"/>
-      <c r="G551" t="inlineStr"/>
-      <c r="H551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -21783,9 +21714,6 @@
           <t>[ROUTINE] Insider trade — Morrow Rebecca (Chief Accounting Officer) granted 65,081 shares on 2026-08-07</t>
         </is>
       </c>
-      <c r="F552" t="inlineStr"/>
-      <c r="G552" t="inlineStr"/>
-      <c r="H552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -21813,9 +21741,6 @@
           <t>[ROUTINE] Insider trade — Matthew Blake Mcrae (Director) granted 46,905 shares on 2026-08-07</t>
         </is>
       </c>
-      <c r="F553" t="inlineStr"/>
-      <c r="G553" t="inlineStr"/>
-      <c r="H553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -21843,9 +21768,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Silbermann Benjamin (Director) plans to sell 46,875 shares (~$1.12M) on/after 08/11/2026</t>
         </is>
       </c>
-      <c r="F554" t="inlineStr"/>
-      <c r="G554" t="inlineStr"/>
-      <c r="H554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -21873,9 +21795,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Brown Claude Leonard (Officer) plans to sell 12,240 shares (~$292.3K) on/after 08/11/2026</t>
         </is>
       </c>
-      <c r="F555" t="inlineStr"/>
-      <c r="G555" t="inlineStr"/>
-      <c r="H555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -21903,9 +21822,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F556" t="inlineStr"/>
-      <c r="G556" t="inlineStr"/>
-      <c r="H556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -21933,9 +21849,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F557" t="inlineStr"/>
-      <c r="G557" t="inlineStr"/>
-      <c r="H557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -21963,9 +21876,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F558" t="inlineStr"/>
-      <c r="G558" t="inlineStr"/>
-      <c r="H558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -21993,9 +21903,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Dovrat Shlomo (Former Director) plans to sell 50,000 shares (~$2.15M) on/after 08/11/2026</t>
         </is>
       </c>
-      <c r="F559" t="inlineStr"/>
-      <c r="G559" t="inlineStr"/>
-      <c r="H559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -22023,9 +21930,6 @@
           <t>[ROUTINE] Insider trade — Durban Egon (Director) other: 21,537 shares on 2026-08-07</t>
         </is>
       </c>
-      <c r="F560" t="inlineStr"/>
-      <c r="G560" t="inlineStr"/>
-      <c r="H560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -22053,9 +21957,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F561" t="inlineStr"/>
-      <c r="G561" t="inlineStr"/>
-      <c r="H561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -22083,9 +21984,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F562" t="inlineStr"/>
-      <c r="G562" t="inlineStr"/>
-      <c r="H562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -22113,9 +22011,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F563" t="inlineStr"/>
-      <c r="G563" t="inlineStr"/>
-      <c r="H563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -22143,9 +22038,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F564" t="inlineStr"/>
-      <c r="G564" t="inlineStr"/>
-      <c r="H564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -22173,9 +22065,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F565" t="inlineStr"/>
-      <c r="G565" t="inlineStr"/>
-      <c r="H565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -22203,9 +22092,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F566" t="inlineStr"/>
-      <c r="G566" t="inlineStr"/>
-      <c r="H566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -22233,9 +22119,6 @@
           <t>[ROUTINE] New insider — initial ownership statement</t>
         </is>
       </c>
-      <c r="F567" t="inlineStr"/>
-      <c r="G567" t="inlineStr"/>
-      <c r="H567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -22263,9 +22146,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F568" t="inlineStr"/>
-      <c r="G568" t="inlineStr"/>
-      <c r="H568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -22293,9 +22173,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F569" t="inlineStr"/>
-      <c r="G569" t="inlineStr"/>
-      <c r="H569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -22323,9 +22200,6 @@
           <t>[ROUTINE] Insider trade — Strauss Zelnick (Chairman, CEO) sold 40,000 shares @ $252.64 ($10.11M) on 2026-08-10</t>
         </is>
       </c>
-      <c r="F570" t="inlineStr"/>
-      <c r="G570" t="inlineStr"/>
-      <c r="H570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -22353,9 +22227,6 @@
           <t>[ROUTINE] Insider trade — Lee Anthony P (Director) gift: 100,000 shares on 2026-08-10</t>
         </is>
       </c>
-      <c r="F571" t="inlineStr"/>
-      <c r="G571" t="inlineStr"/>
-      <c r="H571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -22383,9 +22254,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F572" t="inlineStr"/>
-      <c r="G572" t="inlineStr"/>
-      <c r="H572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -22413,9 +22281,6 @@
           <t>[ROUTINE] Insider trade — Boelte Craig E. (Director) gift: 1,000 shares on 2026-08-10</t>
         </is>
       </c>
-      <c r="F573" t="inlineStr"/>
-      <c r="G573" t="inlineStr"/>
-      <c r="H573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -22443,9 +22308,6 @@
           <t>[ROUTINE] Insider trade — Sarowitz Steven I (Director) sold 32,972 shares @ $152.48 ($5.03M) on 2026-08-07</t>
         </is>
       </c>
-      <c r="F574" t="inlineStr"/>
-      <c r="G574" t="inlineStr"/>
-      <c r="H574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -22473,9 +22335,186 @@
           <t>[ROUTINE] Insider trade — Elizabeth H. Connelly (See Remarks) sold 26,695 shares @ $137.62 ($3.67M) on 2026-08-07</t>
         </is>
       </c>
-      <c r="F575" t="inlineStr"/>
-      <c r="G575" t="inlineStr"/>
-      <c r="H575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>VRSK</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Verisk Analytics, Inc.</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>https://investor.verisk.com</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr"/>
+      <c r="G576" t="inlineStr"/>
+      <c r="H576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>CVNA</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Carvana Co.</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>https://investors.carvana.com</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr"/>
+      <c r="G577" t="inlineStr"/>
+      <c r="H577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>ARMK</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Aramark</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>https://careers.aramark.com</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr"/>
+      <c r="G578" t="inlineStr"/>
+      <c r="H578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>ARMK</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Aramark</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1584509/000170255126000011/xslF345X06/wk-form3_1786480868.xml</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>[ROUTINE] New insider — initial ownership statement</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr"/>
+      <c r="G579" t="inlineStr"/>
+      <c r="H579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>ARMK</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Aramark</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1584509/000158450926000122/cik0-20260703.htm</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Quarterly report</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr"/>
+      <c r="G580" t="inlineStr"/>
+      <c r="H580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>ARMK</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Aramark</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1584509/000158450926000118/cik0-20260811.htm</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr"/>
+      <c r="G581" t="inlineStr"/>
+      <c r="H581" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -6853,7 +6853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H581"/>
+  <dimension ref="A1:H623"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22362,9 +22362,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F576" t="inlineStr"/>
-      <c r="G576" t="inlineStr"/>
-      <c r="H576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -22392,9 +22389,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F577" t="inlineStr"/>
-      <c r="G577" t="inlineStr"/>
-      <c r="H577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -22422,9 +22416,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F578" t="inlineStr"/>
-      <c r="G578" t="inlineStr"/>
-      <c r="H578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -22452,9 +22443,6 @@
           <t>[ROUTINE] New insider — initial ownership statement</t>
         </is>
       </c>
-      <c r="F579" t="inlineStr"/>
-      <c r="G579" t="inlineStr"/>
-      <c r="H579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -22482,9 +22470,6 @@
           <t>[MATERIAL] Quarterly report</t>
         </is>
       </c>
-      <c r="F580" t="inlineStr"/>
-      <c r="G580" t="inlineStr"/>
-      <c r="H580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -22512,9 +22497,1266 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F581" t="inlineStr"/>
-      <c r="G581" t="inlineStr"/>
-      <c r="H581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/legal/terms</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr"/>
+      <c r="G582" t="inlineStr"/>
+      <c r="H582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr"/>
+      <c r="G583" t="inlineStr"/>
+      <c r="H583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>https://news.shopify.com</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr"/>
+      <c r="G584" t="inlineStr"/>
+      <c r="H584" t="inlineStr"/>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>https://investors.shopify.com</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr"/>
+      <c r="G585" t="inlineStr"/>
+      <c r="H585" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr"/>
+      <c r="G586" t="inlineStr"/>
+      <c r="H586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>https://investors.etsy.com</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr"/>
+      <c r="G587" t="inlineStr"/>
+      <c r="H587" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1370637/000088698226000342/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr"/>
+      <c r="G588" t="inlineStr"/>
+      <c r="H588" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1370637/000196922326000868/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Colburn Richard Edward III (Officer) plans to sell 8,252 shares (~$694.9K) on/after 08/10/2026</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr"/>
+      <c r="G589" t="inlineStr"/>
+      <c r="H589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>https://careers.duolingo.com/jobs/8687677002?gh_jid=8687677002</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>New senior role: Director of Growth Marketing Strategy</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr"/>
+      <c r="G590" t="inlineStr"/>
+      <c r="H590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>https://careers.duolingo.com/jobs/8691257002?gh_jid=8691257002</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>New senior role: Director of Sourcing</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr"/>
+      <c r="G591" t="inlineStr"/>
+      <c r="H591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>https://careers.duolingo.com/jobs/8590178002?gh_jid=8590178002</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>New senior role: Head of Talent Management Programs and PMO</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr"/>
+      <c r="G592" t="inlineStr"/>
+      <c r="H592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>https://careers.duolingo.com/jobs/8616695002?gh_jid=8616695002</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>New senior role: Senior Director of Engineering, Math</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr"/>
+      <c r="G593" t="inlineStr"/>
+      <c r="H593" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>https://careers.duolingo.com/jobs/8584465002?gh_jid=8584465002</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>New senior role: Senior Director of Engineering, New Subjects</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr"/>
+      <c r="G594" t="inlineStr"/>
+      <c r="H594" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/duolingo</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>35 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr"/>
+      <c r="G595" t="inlineStr"/>
+      <c r="H595" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>https://blog.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr"/>
+      <c r="G596" t="inlineStr"/>
+      <c r="H596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000162828026055015/duol-20260810.htm</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr"/>
+      <c r="G597" t="inlineStr"/>
+      <c r="H597" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>https://www.bill.com/leadership</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr"/>
+      <c r="G598" t="inlineStr"/>
+      <c r="H598" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>https://www.bill.com/product/pricing</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr"/>
+      <c r="G599" t="inlineStr"/>
+      <c r="H599" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>https://www.bill.com/press-release</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr"/>
+      <c r="G600" t="inlineStr"/>
+      <c r="H600" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>https://investor.bill.com</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr"/>
+      <c r="G601" t="inlineStr"/>
+      <c r="H601" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>https://www.bill.com/careers</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr"/>
+      <c r="G602" t="inlineStr"/>
+      <c r="H602" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>https://careers.toasttab.com/jobs?gh_jid=7743831</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>New senior role: Director of International Program Management</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr"/>
+      <c r="G603" t="inlineStr"/>
+      <c r="H603" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>https://careers.toasttab.com/jobs?gh_jid=7777850</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>New senior role: Director of International Program Management</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr"/>
+      <c r="G604" t="inlineStr"/>
+      <c r="H604" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>https://careers.toasttab.com/jobs?gh_jid=7996612</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>New senior role: Director of Product Management, Enterprise</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr"/>
+      <c r="G605" t="inlineStr"/>
+      <c r="H605" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>https://careers.toasttab.com/jobs?gh_jid=7838464</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>New senior role: Vice President, Enterprise Sales</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr"/>
+      <c r="G606" t="inlineStr"/>
+      <c r="H606" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>250 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr"/>
+      <c r="G607" t="inlineStr"/>
+      <c r="H607" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>https://pos.toasttab.com/terms-of-service</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr"/>
+      <c r="G608" t="inlineStr"/>
+      <c r="H608" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>https://pos.toasttab.com/pricing</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr"/>
+      <c r="G609" t="inlineStr"/>
+      <c r="H609" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>https://investors.toasttab.com</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr"/>
+      <c r="G610" t="inlineStr"/>
+      <c r="H610" t="inlineStr"/>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1650164/000195917326005905/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Vassil Jonathan (Officer) plans to sell 13,797 shares (~$496.9K) on/after 08/11/2026</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr"/>
+      <c r="G611" t="inlineStr"/>
+      <c r="H611" t="inlineStr"/>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1650164/000165016426000178/xslF345X06/wk-form4_1786480258.xml</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Narang Aman (CEO) sold 161,948 shares @ $35.31 ($5.72M) on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr"/>
+      <c r="G612" t="inlineStr"/>
+      <c r="H612" t="inlineStr"/>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1650164/000165016426000177/xslF345X06/wk-form4_1786480226.xml</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Gomez Elena (President, CFO) sold 7,924 shares @ $35.30 ($279.7K) on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr"/>
+      <c r="G613" t="inlineStr"/>
+      <c r="H613" t="inlineStr"/>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1650164/000195917326005860/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Narang Aman (Officer) plans to sell 119,843 shares (~$4.24M) on/after 08/10/2026</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr"/>
+      <c r="G614" t="inlineStr"/>
+      <c r="H614" t="inlineStr"/>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1650164/000195917326005851/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Gomez Elena (Officer) plans to sell 5,761 shares (~$203.8K) on/after 08/10/2026</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr"/>
+      <c r="G615" t="inlineStr"/>
+      <c r="H615" t="inlineStr"/>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood/jobs/7839130?t=gh_src=&amp;gh_jid=7839130</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>New senior role: Chief of Staff, Brokerage Product</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr"/>
+      <c r="G616" t="inlineStr"/>
+      <c r="H616" t="inlineStr"/>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8088954?t=gh_src=&amp;gh_jid=8088954</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>New senior role: Director of Accounting</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr"/>
+      <c r="G617" t="inlineStr"/>
+      <c r="H617" t="inlineStr"/>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8039695?t=gh_src=&amp;gh_jid=8039695</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>New senior role: Senior Director of Income Tax</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr"/>
+      <c r="G618" t="inlineStr"/>
+      <c r="H618" t="inlineStr"/>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>95 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr"/>
+      <c r="G619" t="inlineStr"/>
+      <c r="H619" t="inlineStr"/>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>https://cdn.robinhood.com/assets/robinhood/legal/Robinhood-Customer-Agreement.pdf</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr"/>
+      <c r="G620" t="inlineStr"/>
+      <c r="H620" t="inlineStr"/>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>https://robinhood.com/us/en/support/articles/trading-fees-on-robinhood/</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr"/>
+      <c r="G621" t="inlineStr"/>
+      <c r="H621" t="inlineStr"/>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>https://newsroom.aboutrobinhood.com</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr"/>
+      <c r="G622" t="inlineStr"/>
+      <c r="H622" t="inlineStr"/>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000178387926000124/xslF345X06/wk-form4_1786481261.xml</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Robinhood Markets, Inc. (10%+ owner) sold 18,365 shares @ $28.10 ($516.1K) on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr"/>
+      <c r="G623" t="inlineStr"/>
+      <c r="H623" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -6853,7 +6853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H623"/>
+  <dimension ref="A1:H639"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22524,9 +22524,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F582" t="inlineStr"/>
-      <c r="G582" t="inlineStr"/>
-      <c r="H582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -22554,9 +22551,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F583" t="inlineStr"/>
-      <c r="G583" t="inlineStr"/>
-      <c r="H583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -22584,9 +22578,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F584" t="inlineStr"/>
-      <c r="G584" t="inlineStr"/>
-      <c r="H584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -22614,9 +22605,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F585" t="inlineStr"/>
-      <c r="G585" t="inlineStr"/>
-      <c r="H585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -22644,9 +22632,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F586" t="inlineStr"/>
-      <c r="G586" t="inlineStr"/>
-      <c r="H586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -22674,9 +22659,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F587" t="inlineStr"/>
-      <c r="G587" t="inlineStr"/>
-      <c r="H587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -22704,9 +22686,6 @@
           <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
         </is>
       </c>
-      <c r="F588" t="inlineStr"/>
-      <c r="G588" t="inlineStr"/>
-      <c r="H588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -22734,9 +22713,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Colburn Richard Edward III (Officer) plans to sell 8,252 shares (~$694.9K) on/after 08/10/2026</t>
         </is>
       </c>
-      <c r="F589" t="inlineStr"/>
-      <c r="G589" t="inlineStr"/>
-      <c r="H589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -22764,9 +22740,6 @@
           <t>New senior role: Director of Growth Marketing Strategy</t>
         </is>
       </c>
-      <c r="F590" t="inlineStr"/>
-      <c r="G590" t="inlineStr"/>
-      <c r="H590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -22794,9 +22767,6 @@
           <t>New senior role: Director of Sourcing</t>
         </is>
       </c>
-      <c r="F591" t="inlineStr"/>
-      <c r="G591" t="inlineStr"/>
-      <c r="H591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -22824,9 +22794,6 @@
           <t>New senior role: Head of Talent Management Programs and PMO</t>
         </is>
       </c>
-      <c r="F592" t="inlineStr"/>
-      <c r="G592" t="inlineStr"/>
-      <c r="H592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -22854,9 +22821,6 @@
           <t>New senior role: Senior Director of Engineering, Math</t>
         </is>
       </c>
-      <c r="F593" t="inlineStr"/>
-      <c r="G593" t="inlineStr"/>
-      <c r="H593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -22884,9 +22848,6 @@
           <t>New senior role: Senior Director of Engineering, New Subjects</t>
         </is>
       </c>
-      <c r="F594" t="inlineStr"/>
-      <c r="G594" t="inlineStr"/>
-      <c r="H594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -22914,9 +22875,6 @@
           <t>35 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F595" t="inlineStr"/>
-      <c r="G595" t="inlineStr"/>
-      <c r="H595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -22944,9 +22902,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F596" t="inlineStr"/>
-      <c r="G596" t="inlineStr"/>
-      <c r="H596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -22974,9 +22929,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F597" t="inlineStr"/>
-      <c r="G597" t="inlineStr"/>
-      <c r="H597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -23004,9 +22956,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F598" t="inlineStr"/>
-      <c r="G598" t="inlineStr"/>
-      <c r="H598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -23034,9 +22983,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F599" t="inlineStr"/>
-      <c r="G599" t="inlineStr"/>
-      <c r="H599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -23064,9 +23010,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F600" t="inlineStr"/>
-      <c r="G600" t="inlineStr"/>
-      <c r="H600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -23094,9 +23037,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F601" t="inlineStr"/>
-      <c r="G601" t="inlineStr"/>
-      <c r="H601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -23124,9 +23064,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F602" t="inlineStr"/>
-      <c r="G602" t="inlineStr"/>
-      <c r="H602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -23154,9 +23091,6 @@
           <t>New senior role: Director of International Program Management</t>
         </is>
       </c>
-      <c r="F603" t="inlineStr"/>
-      <c r="G603" t="inlineStr"/>
-      <c r="H603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -23184,9 +23118,6 @@
           <t>New senior role: Director of International Program Management</t>
         </is>
       </c>
-      <c r="F604" t="inlineStr"/>
-      <c r="G604" t="inlineStr"/>
-      <c r="H604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -23214,9 +23145,6 @@
           <t>New senior role: Director of Product Management, Enterprise</t>
         </is>
       </c>
-      <c r="F605" t="inlineStr"/>
-      <c r="G605" t="inlineStr"/>
-      <c r="H605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -23244,9 +23172,6 @@
           <t>New senior role: Vice President, Enterprise Sales</t>
         </is>
       </c>
-      <c r="F606" t="inlineStr"/>
-      <c r="G606" t="inlineStr"/>
-      <c r="H606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -23274,9 +23199,6 @@
           <t>250 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F607" t="inlineStr"/>
-      <c r="G607" t="inlineStr"/>
-      <c r="H607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -23304,9 +23226,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F608" t="inlineStr"/>
-      <c r="G608" t="inlineStr"/>
-      <c r="H608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -23334,9 +23253,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F609" t="inlineStr"/>
-      <c r="G609" t="inlineStr"/>
-      <c r="H609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -23364,9 +23280,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F610" t="inlineStr"/>
-      <c r="G610" t="inlineStr"/>
-      <c r="H610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -23394,9 +23307,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Vassil Jonathan (Officer) plans to sell 13,797 shares (~$496.9K) on/after 08/11/2026</t>
         </is>
       </c>
-      <c r="F611" t="inlineStr"/>
-      <c r="G611" t="inlineStr"/>
-      <c r="H611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -23424,9 +23334,6 @@
           <t>[ROUTINE] Insider trade — Narang Aman (CEO) sold 161,948 shares @ $35.31 ($5.72M) on 2026-08-07</t>
         </is>
       </c>
-      <c r="F612" t="inlineStr"/>
-      <c r="G612" t="inlineStr"/>
-      <c r="H612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -23454,9 +23361,6 @@
           <t>[ROUTINE] Insider trade — Gomez Elena (President, CFO) sold 7,924 shares @ $35.30 ($279.7K) on 2026-08-07</t>
         </is>
       </c>
-      <c r="F613" t="inlineStr"/>
-      <c r="G613" t="inlineStr"/>
-      <c r="H613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -23484,9 +23388,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Narang Aman (Officer) plans to sell 119,843 shares (~$4.24M) on/after 08/10/2026</t>
         </is>
       </c>
-      <c r="F614" t="inlineStr"/>
-      <c r="G614" t="inlineStr"/>
-      <c r="H614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -23514,9 +23415,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Gomez Elena (Officer) plans to sell 5,761 shares (~$203.8K) on/after 08/10/2026</t>
         </is>
       </c>
-      <c r="F615" t="inlineStr"/>
-      <c r="G615" t="inlineStr"/>
-      <c r="H615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -23544,9 +23442,6 @@
           <t>New senior role: Chief of Staff, Brokerage Product</t>
         </is>
       </c>
-      <c r="F616" t="inlineStr"/>
-      <c r="G616" t="inlineStr"/>
-      <c r="H616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -23574,9 +23469,6 @@
           <t>New senior role: Director of Accounting</t>
         </is>
       </c>
-      <c r="F617" t="inlineStr"/>
-      <c r="G617" t="inlineStr"/>
-      <c r="H617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -23604,9 +23496,6 @@
           <t>New senior role: Senior Director of Income Tax</t>
         </is>
       </c>
-      <c r="F618" t="inlineStr"/>
-      <c r="G618" t="inlineStr"/>
-      <c r="H618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -23634,9 +23523,6 @@
           <t>95 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F619" t="inlineStr"/>
-      <c r="G619" t="inlineStr"/>
-      <c r="H619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -23664,9 +23550,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F620" t="inlineStr"/>
-      <c r="G620" t="inlineStr"/>
-      <c r="H620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -23694,9 +23577,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F621" t="inlineStr"/>
-      <c r="G621" t="inlineStr"/>
-      <c r="H621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -23724,9 +23604,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F622" t="inlineStr"/>
-      <c r="G622" t="inlineStr"/>
-      <c r="H622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -23754,9 +23631,486 @@
           <t>[ROUTINE] Insider trade — Robinhood Markets, Inc. (10%+ owner) sold 18,365 shares @ $28.10 ($516.1K) on 2026-08-07</t>
         </is>
       </c>
-      <c r="F623" t="inlineStr"/>
-      <c r="G623" t="inlineStr"/>
-      <c r="H623" t="inlineStr"/>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>https://help.doordash.com/consumers/s/terms-of-service</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr"/>
+      <c r="G624" t="inlineStr"/>
+      <c r="H624" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>https://ir.doordash.com/governance/management/default.aspx</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr"/>
+      <c r="G625" t="inlineStr"/>
+      <c r="H625" t="inlineStr"/>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr"/>
+      <c r="G626" t="inlineStr"/>
+      <c r="H626" t="inlineStr"/>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>https://ir.doordash.com</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr"/>
+      <c r="G627" t="inlineStr"/>
+      <c r="H627" t="inlineStr"/>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000179033026000005/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lin Alfred (Director) other: 7,030,715 shares on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr"/>
+      <c r="G628" t="inlineStr"/>
+      <c r="H628" t="inlineStr"/>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000114036126032238/ny20079824x1_pre14c.htm</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form PRE 14C</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr"/>
+      <c r="G629" t="inlineStr"/>
+      <c r="H629" t="inlineStr"/>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000114036126032235/ef20079912_8k.htm</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr"/>
+      <c r="G630" t="inlineStr"/>
+      <c r="H630" t="inlineStr"/>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183261426000025/xslF345X06/form4-08112026_040804.xml</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Tang Stanley (Director) other: 10,361 shares on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr"/>
+      <c r="G631" t="inlineStr"/>
+      <c r="H631" t="inlineStr"/>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183261726000007/xslF345X06/form4-08112026_040802.xml</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Xu Tony (CHIEF EXECUTIVE OFFICER) other: 8,159 shares on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr"/>
+      <c r="G632" t="inlineStr"/>
+      <c r="H632" t="inlineStr"/>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183239026000019/xslF345X06/form4-08102026_040802.xml</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Fang Andy (Director) sold 15,000 shares @ $215.00 ($3.23M) on 2026-08-06</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr"/>
+      <c r="G633" t="inlineStr"/>
+      <c r="H633" t="inlineStr"/>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=8112136</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>New senior role: Chief of Staff, Online Grocery</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr"/>
+      <c r="G634" t="inlineStr"/>
+      <c r="H634" t="inlineStr"/>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=8112138</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>New senior role: Chief of Staff, Online Grocery</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr"/>
+      <c r="G635" t="inlineStr"/>
+      <c r="H635" t="inlineStr"/>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=7871823</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>New senior role: Director of Customer Success</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr"/>
+      <c r="G636" t="inlineStr"/>
+      <c r="H636" t="inlineStr"/>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>43 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr"/>
+      <c r="G637" t="inlineStr"/>
+      <c r="H637" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/company/newsroom</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr"/>
+      <c r="G638" t="inlineStr"/>
+      <c r="H638" t="inlineStr"/>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000208293026000012/xslF345X06/wk-form4_1786478742.xml</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Rogers Chris (President and CEO) sold 4,933 shares @ $50.00 ($246.7K) on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr"/>
+      <c r="G639" t="inlineStr"/>
+      <c r="H639" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -6853,7 +6853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H639"/>
+  <dimension ref="A1:H661"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -23658,9 +23658,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F624" t="inlineStr"/>
-      <c r="G624" t="inlineStr"/>
-      <c r="H624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -23688,9 +23685,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F625" t="inlineStr"/>
-      <c r="G625" t="inlineStr"/>
-      <c r="H625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -23718,9 +23712,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F626" t="inlineStr"/>
-      <c r="G626" t="inlineStr"/>
-      <c r="H626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -23748,9 +23739,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F627" t="inlineStr"/>
-      <c r="G627" t="inlineStr"/>
-      <c r="H627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -23778,9 +23766,6 @@
           <t>[ROUTINE] Insider trade — Lin Alfred (Director) other: 7,030,715 shares on 2026-08-07</t>
         </is>
       </c>
-      <c r="F628" t="inlineStr"/>
-      <c r="G628" t="inlineStr"/>
-      <c r="H628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -23808,9 +23793,6 @@
           <t>[UNKNOWN] Form PRE 14C</t>
         </is>
       </c>
-      <c r="F629" t="inlineStr"/>
-      <c r="G629" t="inlineStr"/>
-      <c r="H629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -23838,9 +23820,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F630" t="inlineStr"/>
-      <c r="G630" t="inlineStr"/>
-      <c r="H630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -23868,9 +23847,6 @@
           <t>[ROUTINE] Insider trade — Tang Stanley (Director) other: 10,361 shares on 2026-08-07</t>
         </is>
       </c>
-      <c r="F631" t="inlineStr"/>
-      <c r="G631" t="inlineStr"/>
-      <c r="H631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -23898,9 +23874,6 @@
           <t>[ROUTINE] Insider trade — Xu Tony (CHIEF EXECUTIVE OFFICER) other: 8,159 shares on 2026-08-07</t>
         </is>
       </c>
-      <c r="F632" t="inlineStr"/>
-      <c r="G632" t="inlineStr"/>
-      <c r="H632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -23928,9 +23901,6 @@
           <t>[ROUTINE] Insider trade — Fang Andy (Director) sold 15,000 shares @ $215.00 ($3.23M) on 2026-08-06</t>
         </is>
       </c>
-      <c r="F633" t="inlineStr"/>
-      <c r="G633" t="inlineStr"/>
-      <c r="H633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -23958,9 +23928,6 @@
           <t>New senior role: Chief of Staff, Online Grocery</t>
         </is>
       </c>
-      <c r="F634" t="inlineStr"/>
-      <c r="G634" t="inlineStr"/>
-      <c r="H634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -23988,9 +23955,6 @@
           <t>New senior role: Chief of Staff, Online Grocery</t>
         </is>
       </c>
-      <c r="F635" t="inlineStr"/>
-      <c r="G635" t="inlineStr"/>
-      <c r="H635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -24018,9 +23982,6 @@
           <t>New senior role: Director of Customer Success</t>
         </is>
       </c>
-      <c r="F636" t="inlineStr"/>
-      <c r="G636" t="inlineStr"/>
-      <c r="H636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -24048,9 +24009,6 @@
           <t>43 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F637" t="inlineStr"/>
-      <c r="G637" t="inlineStr"/>
-      <c r="H637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -24078,9 +24036,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F638" t="inlineStr"/>
-      <c r="G638" t="inlineStr"/>
-      <c r="H638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -24108,9 +24063,666 @@
           <t>[ROUTINE] Insider trade — Rogers Chris (President and CEO) sold 4,933 shares @ $50.00 ($246.7K) on 2026-08-07</t>
         </is>
       </c>
-      <c r="F639" t="inlineStr"/>
-      <c r="G639" t="inlineStr"/>
-      <c r="H639" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/press-room/home/post/wix-launches-symphony-by-wix-a-new-standalone-multi-agent-system-built-for-smbs</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>newsroom: Wix Launches Symphony by Wix, a New Standalone Multi-Agent System Built for SMBs</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr"/>
+      <c r="G640" t="inlineStr"/>
+      <c r="H640" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>https://support.wix.com/en/article/terms-of-use</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr"/>
+      <c r="G641" t="inlineStr"/>
+      <c r="H641" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/upgrade/website</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr"/>
+      <c r="G642" t="inlineStr"/>
+      <c r="H642" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>GLBE</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Global-E Online Ltd.</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835963/000117891326004050/zk2635930.htm</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 6-K</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr"/>
+      <c r="G643" t="inlineStr"/>
+      <c r="H643" t="inlineStr"/>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>GLBE</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Global-E Online Ltd.</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835963/000119312526343811/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Schlachet Amir (CEO) sold 322 shares @ $42.07 ($13.5K) on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr"/>
+      <c r="G644" t="inlineStr"/>
+      <c r="H644" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>GLBE</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Global-E Online Ltd.</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835963/000119312526342619/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Schlachet Amir (CEO) sold 100,000 shares @ $42.20 ($4.22M) on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr"/>
+      <c r="G645" t="inlineStr"/>
+      <c r="H645" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065088/000106508826000181/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Rebecca Spencer (VP, Chief Accounting Officer) sold 5,190 shares @ $107.79 ($559.4K) on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr"/>
+      <c r="G646" t="inlineStr"/>
+      <c r="H646" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Wayfair Inc.</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1616707/000195917326005813/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Shah Niraj (Officer) plans to sell 6,000 shares (~$636.0K) on/after 08/10/2026</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr"/>
+      <c r="G647" t="inlineStr"/>
+      <c r="H647" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Wayfair Inc.</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1616707/000195917326005812/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Conine Steven (Officer) plans to sell 6,000 shares (~$636.0K) on/after 08/10/2026</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr"/>
+      <c r="G648" t="inlineStr"/>
+      <c r="H648" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr"/>
+      <c r="G649" t="inlineStr"/>
+      <c r="H649" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000192109426000831/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Cormier Thielke Claire (Director) plans to sell 1,187 shares (~$39.3K) on/after 08/11/2026</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr"/>
+      <c r="G650" t="inlineStr"/>
+      <c r="H650" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>CSGP</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>CoStar Group Inc.</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1057352/000147276226000012/xslF345X06/wk-form4_1786392398.xml</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Cann Cynthia Cammett (Chief Accounting Officer) sold 4,788 shares @ $30.78 ($147.4K) on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr"/>
+      <c r="G651" t="inlineStr"/>
+      <c r="H651" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>CSGP</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>CoStar Group Inc.</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1057352/000135168926000005/xslF345X06/wk-form4_1786392390.xml</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hill John W (Director) sold 3,500 shares @ $30.21 ($105.7K) on 2026-08-05</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr"/>
+      <c r="G652" t="inlineStr"/>
+      <c r="H652" t="inlineStr"/>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000195004726007950/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Pickering Evan (Officer) plans to sell 141 shares (~$28.1K) on/after 08/11/2026</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr"/>
+      <c r="G653" t="inlineStr"/>
+      <c r="H653" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000093833326000012/xslF345X06/form4-08102026_090836.xml</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Maurice J Duca (10%+ owner) sold 5,809 shares @ $198.44 ($1.15M) on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr"/>
+      <c r="G654" t="inlineStr"/>
+      <c r="H654" t="inlineStr"/>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000093833326000011/xslF345X06/form4-08102026_090853.xml</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Maurice J Duca (10%+ owner) sold 15,591 shares @ $194.65 ($3.03M) on 2026-08-06</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr"/>
+      <c r="G655" t="inlineStr"/>
+      <c r="H655" t="inlineStr"/>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000195004726007880/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Rigler Don (Officer) plans to sell 300 shares (~$59.6K) on/after 08/10/2026</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr"/>
+      <c r="G656" t="inlineStr"/>
+      <c r="H656" t="inlineStr"/>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000162828026055837/xslF345X06/wk-form4_1786485228.xml</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Eisen Anthony Mathew (Director) sold 18,000 shares @ $78.73 ($1.42M) on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr"/>
+      <c r="G657" t="inlineStr"/>
+      <c r="H657" t="inlineStr"/>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726007931/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$472.9K) on/after 08/11/2026</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr"/>
+      <c r="G658" t="inlineStr"/>
+      <c r="H658" t="inlineStr"/>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726007863/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$470.8K) on/after 08/10/2026</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr"/>
+      <c r="G659" t="inlineStr"/>
+      <c r="H659" t="inlineStr"/>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>WSM</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Williams-Sonoma Inc.</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/719955/000071995526000196/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Yearout Karalyn (EVP CHIEF TALENT OFFICER) sold 522 shares @ $246.39 ($128.6K) on 2026-08-07</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr"/>
+      <c r="G660" t="inlineStr"/>
+      <c r="H660" t="inlineStr"/>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1858985/000185898526000018/onholdingag-20260630.htm</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 6-K</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr"/>
+      <c r="G661" t="inlineStr"/>
+      <c r="H661" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -888,11 +888,7 @@
           <t>https://investors.global-e.com/corporate-governance/management-team</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>https://www.global-e.com/careers/</t>
-        </is>
-      </c>
+      <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>https://www.global-e.com/platform/</t>
@@ -1138,7 +1134,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>https://www.wayfair.com/media-room/</t>
+          <t>https://investor.wayfair.com/news</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1151,16 +1147,8 @@
           <t>https://www.aboutwayfair.com/careers</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>https://partners.wayfair.com/</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>https://www.wayfair.com/terms-conditions/</t>
-        </is>
-      </c>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
       <c r="J7" s="7" t="inlineStr">
         <is>
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=W</t>
@@ -1409,11 +1397,7 @@
           <t>https://careers.doordash.com</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>https://merchants.doordash.com/en-us/products/merchant-pricing</t>
-        </is>
-      </c>
+      <c r="H10" s="4" t="n"/>
       <c r="I10" s="4" t="inlineStr">
         <is>
           <t>https://help.doordash.com/consumers/s/terms-of-service</t>
@@ -1659,7 +1643,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>https://ir.mtch.com/investor-relations/news-events/news-events/default.aspx</t>
+          <t>https://mtch.com/news</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1669,7 +1653,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>https://jobs.mtch.com</t>
+          <t>https://mtch.com/careers</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -2605,12 +2589,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>https://www.sezzle.com/blog</t>
+          <t>https://sezzle.com/news</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>https://investors.sezzle.com/leadership/default.aspx</t>
+          <t>https://sezzle.com/governance/leadership</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -2686,7 +2670,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>https://ir.dave.com</t>
+          <t>https://investors.dave.com</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -3139,11 +3123,7 @@
           <t>https://www.upstart.com/</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>https://www.upstart.com/terms</t>
-        </is>
-      </c>
+      <c r="I30" s="4" t="n"/>
       <c r="J30" s="4" t="inlineStr">
         <is>
           <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=UPST</t>
@@ -3288,7 +3268,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>https://ir.williams-sonoma.com</t>
+          <t>https://ir.williams-sonomainc.com</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -3303,7 +3283,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>https://careers.williams-sonoma.com</t>
+          <t>https://www.williams-sonoma.com/careers</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -3379,7 +3359,7 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>https://somnigroup.com/newsroom/default.aspx</t>
+          <t>https://www.somnigroup.com/news</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -3392,14 +3372,10 @@
           <t>https://somnigroup.com/careers/default.aspx</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>https://www.tempurpedic.com/shop-mattresses/</t>
-        </is>
-      </c>
+      <c r="H33" s="7" t="n"/>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>https://somnigroup.com/legal/default.aspx</t>
+          <t>https://www.somnigroup.com/terms</t>
         </is>
       </c>
       <c r="J33" s="7" t="inlineStr">
@@ -3465,7 +3441,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>https://ir.enova.com/news-events/news-releases/default.aspx</t>
+          <t>https://www.enova.com/newsroom</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -3473,11 +3449,7 @@
           <t>https://ir.enova.com/corporate-governance/leadership-team/default.aspx</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>https://www.enova.com/careers/</t>
-        </is>
-      </c>
+      <c r="G34" s="4" t="n"/>
       <c r="H34" s="4" t="inlineStr">
         <is>
           <t>https://www.enova.com/brands/</t>
@@ -6248,600 +6220,593 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId613"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6853,7 +6818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H661"/>
+  <dimension ref="A1:H639"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24063,666 +24028,6 @@
           <t>[ROUTINE] Insider trade — Rogers Chris (President and CEO) sold 4,933 shares @ $50.00 ($246.7K) on 2026-08-07</t>
         </is>
       </c>
-    </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B640" t="inlineStr">
-        <is>
-          <t>WIX</t>
-        </is>
-      </c>
-      <c r="C640" t="inlineStr">
-        <is>
-          <t>Wix.com Ltd.</t>
-        </is>
-      </c>
-      <c r="D640" t="inlineStr">
-        <is>
-          <t>https://www.wix.com/press-room/home/post/wix-launches-symphony-by-wix-a-new-standalone-multi-agent-system-built-for-smbs</t>
-        </is>
-      </c>
-      <c r="E640" t="inlineStr">
-        <is>
-          <t>newsroom: Wix Launches Symphony by Wix, a New Standalone Multi-Agent System Built for SMBs</t>
-        </is>
-      </c>
-      <c r="F640" t="inlineStr"/>
-      <c r="G640" t="inlineStr"/>
-      <c r="H640" t="inlineStr"/>
-    </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B641" t="inlineStr">
-        <is>
-          <t>WIX</t>
-        </is>
-      </c>
-      <c r="C641" t="inlineStr">
-        <is>
-          <t>Wix.com Ltd.</t>
-        </is>
-      </c>
-      <c r="D641" t="inlineStr">
-        <is>
-          <t>https://support.wix.com/en/article/terms-of-use</t>
-        </is>
-      </c>
-      <c r="E641" t="inlineStr">
-        <is>
-          <t>terms: change detected</t>
-        </is>
-      </c>
-      <c r="F641" t="inlineStr"/>
-      <c r="G641" t="inlineStr"/>
-      <c r="H641" t="inlineStr"/>
-    </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B642" t="inlineStr">
-        <is>
-          <t>WIX</t>
-        </is>
-      </c>
-      <c r="C642" t="inlineStr">
-        <is>
-          <t>Wix.com Ltd.</t>
-        </is>
-      </c>
-      <c r="D642" t="inlineStr">
-        <is>
-          <t>https://www.wix.com/upgrade/website</t>
-        </is>
-      </c>
-      <c r="E642" t="inlineStr">
-        <is>
-          <t>pricing: change detected</t>
-        </is>
-      </c>
-      <c r="F642" t="inlineStr"/>
-      <c r="G642" t="inlineStr"/>
-      <c r="H642" t="inlineStr"/>
-    </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B643" t="inlineStr">
-        <is>
-          <t>GLBE</t>
-        </is>
-      </c>
-      <c r="C643" t="inlineStr">
-        <is>
-          <t>Global-E Online Ltd.</t>
-        </is>
-      </c>
-      <c r="D643" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1835963/000117891326004050/zk2635930.htm</t>
-        </is>
-      </c>
-      <c r="E643" t="inlineStr">
-        <is>
-          <t>[UNKNOWN] Form 6-K</t>
-        </is>
-      </c>
-      <c r="F643" t="inlineStr"/>
-      <c r="G643" t="inlineStr"/>
-      <c r="H643" t="inlineStr"/>
-    </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B644" t="inlineStr">
-        <is>
-          <t>GLBE</t>
-        </is>
-      </c>
-      <c r="C644" t="inlineStr">
-        <is>
-          <t>Global-E Online Ltd.</t>
-        </is>
-      </c>
-      <c r="D644" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1835963/000119312526343811/xslF345X06/ownership.xml</t>
-        </is>
-      </c>
-      <c r="E644" t="inlineStr">
-        <is>
-          <t>[ROUTINE] Insider trade — Schlachet Amir (CEO) sold 322 shares @ $42.07 ($13.5K) on 2026-08-10</t>
-        </is>
-      </c>
-      <c r="F644" t="inlineStr"/>
-      <c r="G644" t="inlineStr"/>
-      <c r="H644" t="inlineStr"/>
-    </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B645" t="inlineStr">
-        <is>
-          <t>GLBE</t>
-        </is>
-      </c>
-      <c r="C645" t="inlineStr">
-        <is>
-          <t>Global-E Online Ltd.</t>
-        </is>
-      </c>
-      <c r="D645" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1835963/000119312526342619/xslF345X06/ownership.xml</t>
-        </is>
-      </c>
-      <c r="E645" t="inlineStr">
-        <is>
-          <t>[ROUTINE] Insider trade — Schlachet Amir (CEO) sold 100,000 shares @ $42.20 ($4.22M) on 2026-08-07</t>
-        </is>
-      </c>
-      <c r="F645" t="inlineStr"/>
-      <c r="G645" t="inlineStr"/>
-      <c r="H645" t="inlineStr"/>
-    </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B646" t="inlineStr">
-        <is>
-          <t>EBAY</t>
-        </is>
-      </c>
-      <c r="C646" t="inlineStr">
-        <is>
-          <t>eBay Inc.</t>
-        </is>
-      </c>
-      <c r="D646" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1065088/000106508826000181/xslF345X06/form4.xml</t>
-        </is>
-      </c>
-      <c r="E646" t="inlineStr">
-        <is>
-          <t>[ROUTINE] Insider trade — Rebecca Spencer (VP, Chief Accounting Officer) sold 5,190 shares @ $107.79 ($559.4K) on 2026-08-10</t>
-        </is>
-      </c>
-      <c r="F646" t="inlineStr"/>
-      <c r="G646" t="inlineStr"/>
-      <c r="H646" t="inlineStr"/>
-    </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B647" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="C647" t="inlineStr">
-        <is>
-          <t>Wayfair Inc.</t>
-        </is>
-      </c>
-      <c r="D647" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1616707/000195917326005813/xsl144X01/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="E647" t="inlineStr">
-        <is>
-          <t>[ROUTINE] Notice of proposed insider sale — Shah Niraj (Officer) plans to sell 6,000 shares (~$636.0K) on/after 08/10/2026</t>
-        </is>
-      </c>
-      <c r="F647" t="inlineStr"/>
-      <c r="G647" t="inlineStr"/>
-      <c r="H647" t="inlineStr"/>
-    </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B648" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="C648" t="inlineStr">
-        <is>
-          <t>Wayfair Inc.</t>
-        </is>
-      </c>
-      <c r="D648" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1616707/000195917326005812/xsl144X01/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="E648" t="inlineStr">
-        <is>
-          <t>[ROUTINE] Notice of proposed insider sale — Conine Steven (Officer) plans to sell 6,000 shares (~$636.0K) on/after 08/10/2026</t>
-        </is>
-      </c>
-      <c r="F648" t="inlineStr"/>
-      <c r="G648" t="inlineStr"/>
-      <c r="H648" t="inlineStr"/>
-    </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B649" t="inlineStr">
-        <is>
-          <t>CART</t>
-        </is>
-      </c>
-      <c r="C649" t="inlineStr">
-        <is>
-          <t>Maplebear Inc. (Instacart)</t>
-        </is>
-      </c>
-      <c r="D649" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/instacart</t>
-        </is>
-      </c>
-      <c r="E649" t="inlineStr">
-        <is>
-          <t>1 new non-senior roles posted</t>
-        </is>
-      </c>
-      <c r="F649" t="inlineStr"/>
-      <c r="G649" t="inlineStr"/>
-      <c r="H649" t="inlineStr"/>
-    </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B650" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-      <c r="C650" t="inlineStr">
-        <is>
-          <t>Zillow Group Inc.</t>
-        </is>
-      </c>
-      <c r="D650" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1617640/000192109426000831/xsl144X01/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="E650" t="inlineStr">
-        <is>
-          <t>[ROUTINE] Notice of proposed insider sale — Cormier Thielke Claire (Director) plans to sell 1,187 shares (~$39.3K) on/after 08/11/2026</t>
-        </is>
-      </c>
-      <c r="F650" t="inlineStr"/>
-      <c r="G650" t="inlineStr"/>
-      <c r="H650" t="inlineStr"/>
-    </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B651" t="inlineStr">
-        <is>
-          <t>CSGP</t>
-        </is>
-      </c>
-      <c r="C651" t="inlineStr">
-        <is>
-          <t>CoStar Group Inc.</t>
-        </is>
-      </c>
-      <c r="D651" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1057352/000147276226000012/xslF345X06/wk-form4_1786392398.xml</t>
-        </is>
-      </c>
-      <c r="E651" t="inlineStr">
-        <is>
-          <t>[ROUTINE] Insider trade — Cann Cynthia Cammett (Chief Accounting Officer) sold 4,788 shares @ $30.78 ($147.4K) on 2026-08-07</t>
-        </is>
-      </c>
-      <c r="F651" t="inlineStr"/>
-      <c r="G651" t="inlineStr"/>
-      <c r="H651" t="inlineStr"/>
-    </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B652" t="inlineStr">
-        <is>
-          <t>CSGP</t>
-        </is>
-      </c>
-      <c r="C652" t="inlineStr">
-        <is>
-          <t>CoStar Group Inc.</t>
-        </is>
-      </c>
-      <c r="D652" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1057352/000135168926000005/xslF345X06/wk-form4_1786392390.xml</t>
-        </is>
-      </c>
-      <c r="E652" t="inlineStr">
-        <is>
-          <t>[ROUTINE] Insider trade — Hill John W (Director) sold 3,500 shares @ $30.21 ($105.7K) on 2026-08-05</t>
-        </is>
-      </c>
-      <c r="F652" t="inlineStr"/>
-      <c r="G652" t="inlineStr"/>
-      <c r="H652" t="inlineStr"/>
-    </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B653" t="inlineStr">
-        <is>
-          <t>APPF</t>
-        </is>
-      </c>
-      <c r="C653" t="inlineStr">
-        <is>
-          <t>AppFolio Inc.</t>
-        </is>
-      </c>
-      <c r="D653" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1433195/000195004726007950/xsl144X01/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="E653" t="inlineStr">
-        <is>
-          <t>[ROUTINE] Notice of proposed insider sale — Pickering Evan (Officer) plans to sell 141 shares (~$28.1K) on/after 08/11/2026</t>
-        </is>
-      </c>
-      <c r="F653" t="inlineStr"/>
-      <c r="G653" t="inlineStr"/>
-      <c r="H653" t="inlineStr"/>
-    </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B654" t="inlineStr">
-        <is>
-          <t>APPF</t>
-        </is>
-      </c>
-      <c r="C654" t="inlineStr">
-        <is>
-          <t>AppFolio Inc.</t>
-        </is>
-      </c>
-      <c r="D654" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1433195/000093833326000012/xslF345X06/form4-08102026_090836.xml</t>
-        </is>
-      </c>
-      <c r="E654" t="inlineStr">
-        <is>
-          <t>[ROUTINE] Insider trade — Maurice J Duca (10%+ owner) sold 5,809 shares @ $198.44 ($1.15M) on 2026-08-07</t>
-        </is>
-      </c>
-      <c r="F654" t="inlineStr"/>
-      <c r="G654" t="inlineStr"/>
-      <c r="H654" t="inlineStr"/>
-    </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B655" t="inlineStr">
-        <is>
-          <t>APPF</t>
-        </is>
-      </c>
-      <c r="C655" t="inlineStr">
-        <is>
-          <t>AppFolio Inc.</t>
-        </is>
-      </c>
-      <c r="D655" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1433195/000093833326000011/xslF345X06/form4-08102026_090853.xml</t>
-        </is>
-      </c>
-      <c r="E655" t="inlineStr">
-        <is>
-          <t>[ROUTINE] Insider trade — Maurice J Duca (10%+ owner) sold 15,591 shares @ $194.65 ($3.03M) on 2026-08-06</t>
-        </is>
-      </c>
-      <c r="F655" t="inlineStr"/>
-      <c r="G655" t="inlineStr"/>
-      <c r="H655" t="inlineStr"/>
-    </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B656" t="inlineStr">
-        <is>
-          <t>APPF</t>
-        </is>
-      </c>
-      <c r="C656" t="inlineStr">
-        <is>
-          <t>AppFolio Inc.</t>
-        </is>
-      </c>
-      <c r="D656" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1433195/000195004726007880/xsl144X01/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="E656" t="inlineStr">
-        <is>
-          <t>[ROUTINE] Notice of proposed insider sale — Rigler Don (Officer) plans to sell 300 shares (~$59.6K) on/after 08/10/2026</t>
-        </is>
-      </c>
-      <c r="F656" t="inlineStr"/>
-      <c r="G656" t="inlineStr"/>
-      <c r="H656" t="inlineStr"/>
-    </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B657" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C657" t="inlineStr">
-        <is>
-          <t>Block Inc. (fmr. Square)</t>
-        </is>
-      </c>
-      <c r="D657" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1512673/000162828026055837/xslF345X06/wk-form4_1786485228.xml</t>
-        </is>
-      </c>
-      <c r="E657" t="inlineStr">
-        <is>
-          <t>[ROUTINE] Insider trade — Eisen Anthony Mathew (Director) sold 18,000 shares @ $78.73 ($1.42M) on 2026-08-07</t>
-        </is>
-      </c>
-      <c r="F657" t="inlineStr"/>
-      <c r="G657" t="inlineStr"/>
-      <c r="H657" t="inlineStr"/>
-    </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B658" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C658" t="inlineStr">
-        <is>
-          <t>Block Inc. (fmr. Square)</t>
-        </is>
-      </c>
-      <c r="D658" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726007931/xsl144X01/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="E658" t="inlineStr">
-        <is>
-          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$472.9K) on/after 08/11/2026</t>
-        </is>
-      </c>
-      <c r="F658" t="inlineStr"/>
-      <c r="G658" t="inlineStr"/>
-      <c r="H658" t="inlineStr"/>
-    </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B659" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C659" t="inlineStr">
-        <is>
-          <t>Block Inc. (fmr. Square)</t>
-        </is>
-      </c>
-      <c r="D659" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726007863/xsl144X01/primary_doc.xml</t>
-        </is>
-      </c>
-      <c r="E659" t="inlineStr">
-        <is>
-          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$470.8K) on/after 08/10/2026</t>
-        </is>
-      </c>
-      <c r="F659" t="inlineStr"/>
-      <c r="G659" t="inlineStr"/>
-      <c r="H659" t="inlineStr"/>
-    </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B660" t="inlineStr">
-        <is>
-          <t>WSM</t>
-        </is>
-      </c>
-      <c r="C660" t="inlineStr">
-        <is>
-          <t>Williams-Sonoma Inc.</t>
-        </is>
-      </c>
-      <c r="D660" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/719955/000071995526000196/xslF345X06/form4.xml</t>
-        </is>
-      </c>
-      <c r="E660" t="inlineStr">
-        <is>
-          <t>[ROUTINE] Insider trade — Yearout Karalyn (EVP CHIEF TALENT OFFICER) sold 522 shares @ $246.39 ($128.6K) on 2026-08-07</t>
-        </is>
-      </c>
-      <c r="F660" t="inlineStr"/>
-      <c r="G660" t="inlineStr"/>
-      <c r="H660" t="inlineStr"/>
-    </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B661" t="inlineStr">
-        <is>
-          <t>ONON</t>
-        </is>
-      </c>
-      <c r="C661" t="inlineStr">
-        <is>
-          <t>On Holding AG</t>
-        </is>
-      </c>
-      <c r="D661" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1858985/000185898526000018/onholdingag-20260630.htm</t>
-        </is>
-      </c>
-      <c r="E661" t="inlineStr">
-        <is>
-          <t>[UNKNOWN] Form 6-K</t>
-        </is>
-      </c>
-      <c r="F661" t="inlineStr"/>
-      <c r="G661" t="inlineStr"/>
-      <c r="H661" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T81"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -665,6 +665,11 @@
           <t>Pricing Selector</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -760,6 +765,11 @@
           <t>main</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -856,6 +866,11 @@
           <t>main</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -938,6 +953,11 @@
       <c r="R4" t="b">
         <v>1</v>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -1024,6 +1044,11 @@
       <c r="R5" t="b">
         <v>1</v>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1109,6 +1134,11 @@
       </c>
       <c r="R6" t="b">
         <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="52" customHeight="1">
@@ -1188,6 +1218,11 @@
       <c r="R7" t="b">
         <v>1</v>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1274,6 +1309,11 @@
       <c r="R8" t="b">
         <v>1</v>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="52" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -1360,6 +1400,11 @@
       <c r="R9" t="b">
         <v>1</v>
       </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1442,6 +1487,11 @@
       <c r="R10" t="b">
         <v>1</v>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -1533,6 +1583,11 @@
           <t>main</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1619,6 +1674,11 @@
       <c r="R12" t="b">
         <v>1</v>
       </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -1705,6 +1765,11 @@
       <c r="R13" t="b">
         <v>1</v>
       </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1791,6 +1856,11 @@
       <c r="R14" t="b">
         <v>1</v>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1877,6 +1947,11 @@
       <c r="R15" t="b">
         <v>1</v>
       </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1963,6 +2038,11 @@
       <c r="R16" t="b">
         <v>1</v>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -2049,6 +2129,11 @@
       <c r="R17" t="b">
         <v>1</v>
       </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -2135,6 +2220,11 @@
       <c r="R18" t="b">
         <v>1</v>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
@@ -2221,6 +2311,11 @@
       <c r="R19" t="b">
         <v>1</v>
       </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -2307,6 +2402,11 @@
       <c r="R20" t="b">
         <v>1</v>
       </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -2393,6 +2493,11 @@
       <c r="R21" t="b">
         <v>1</v>
       </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -2479,6 +2584,11 @@
       <c r="R22" t="b">
         <v>1</v>
       </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -2565,6 +2675,11 @@
       <c r="R23" t="b">
         <v>1</v>
       </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -2651,6 +2766,11 @@
       <c r="R24" t="b">
         <v>1</v>
       </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -2737,6 +2857,11 @@
       <c r="R25" t="b">
         <v>1</v>
       </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -2823,6 +2948,11 @@
       <c r="R26" t="b">
         <v>1</v>
       </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
@@ -2909,6 +3039,11 @@
       <c r="R27" t="b">
         <v>1</v>
       </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="52" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
@@ -2995,6 +3130,11 @@
       <c r="R28" t="b">
         <v>1</v>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="52" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
@@ -3081,6 +3221,11 @@
       <c r="R29" t="b">
         <v>1</v>
       </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="52" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -3163,6 +3308,11 @@
       <c r="R30" t="b">
         <v>1</v>
       </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="52" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
@@ -3249,6 +3399,11 @@
       <c r="R31" t="b">
         <v>1</v>
       </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="52" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -3335,6 +3490,11 @@
       <c r="R32" t="b">
         <v>1</v>
       </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="52" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -3417,6 +3577,11 @@
       <c r="R33" t="b">
         <v>1</v>
       </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="52" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -3499,6 +3664,11 @@
       <c r="R34" t="b">
         <v>1</v>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="52" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
@@ -3585,6 +3755,11 @@
       <c r="R35" t="b">
         <v>1</v>
       </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="52" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -3671,6 +3846,11 @@
       <c r="R36" t="b">
         <v>1</v>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3731,6 +3911,11 @@
       <c r="R37" t="b">
         <v>1</v>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3796,6 +3981,11 @@
       <c r="R38" t="b">
         <v>1</v>
       </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3836,6 +4026,11 @@
       <c r="R39" t="b">
         <v>1</v>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3906,6 +4101,11 @@
       <c r="R40" t="b">
         <v>1</v>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3956,6 +4156,11 @@
       <c r="R41" t="b">
         <v>1</v>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4021,6 +4226,11 @@
       <c r="R42" t="b">
         <v>1</v>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4081,6 +4291,11 @@
       <c r="R43" t="b">
         <v>1</v>
       </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4146,6 +4361,11 @@
       <c r="R44" t="b">
         <v>1</v>
       </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4211,6 +4431,11 @@
       <c r="R45" t="b">
         <v>1</v>
       </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4269,7 +4494,7 @@
         </is>
       </c>
       <c r="R46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -4334,7 +4559,7 @@
         </is>
       </c>
       <c r="R47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4394,7 +4619,7 @@
         </is>
       </c>
       <c r="R48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4454,7 +4679,7 @@
         </is>
       </c>
       <c r="R49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -4511,6 +4736,11 @@
       <c r="R50" t="b">
         <v>1</v>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4566,6 +4796,11 @@
       <c r="R51" t="b">
         <v>1</v>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4626,6 +4861,11 @@
       <c r="R52" t="b">
         <v>1</v>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4686,6 +4926,11 @@
       <c r="R53" t="b">
         <v>1</v>
       </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4746,6 +4991,11 @@
       <c r="R54" t="b">
         <v>1</v>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4801,6 +5051,11 @@
       <c r="R55" t="b">
         <v>1</v>
       </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4861,6 +5116,11 @@
       <c r="R56" t="b">
         <v>1</v>
       </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4916,6 +5176,11 @@
       <c r="R57" t="b">
         <v>1</v>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4971,6 +5236,11 @@
       <c r="R58" t="b">
         <v>1</v>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5031,6 +5301,11 @@
       <c r="R59" t="b">
         <v>1</v>
       </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5091,6 +5366,11 @@
       <c r="R60" t="b">
         <v>1</v>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5146,6 +5426,11 @@
       <c r="R61" t="b">
         <v>1</v>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5181,6 +5466,11 @@
       <c r="R62" t="b">
         <v>1</v>
       </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5236,6 +5526,11 @@
       <c r="R63" t="b">
         <v>1</v>
       </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5296,6 +5591,11 @@
       <c r="R64" t="b">
         <v>1</v>
       </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5351,6 +5651,11 @@
       <c r="R65" t="b">
         <v>1</v>
       </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5401,6 +5706,11 @@
       <c r="R66" t="b">
         <v>1</v>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5456,6 +5766,11 @@
       <c r="R67" t="b">
         <v>1</v>
       </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5511,6 +5826,11 @@
       <c r="R68" t="b">
         <v>1</v>
       </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5566,6 +5886,11 @@
       <c r="R69" t="b">
         <v>1</v>
       </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5601,6 +5926,11 @@
       <c r="R70" t="b">
         <v>1</v>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5656,6 +5986,11 @@
       <c r="R71" t="b">
         <v>1</v>
       </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5711,6 +6046,11 @@
       <c r="R72" t="b">
         <v>1</v>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5761,6 +6101,11 @@
       <c r="R73" t="b">
         <v>1</v>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5816,6 +6161,11 @@
       <c r="R74" t="b">
         <v>1</v>
       </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5871,6 +6221,11 @@
       <c r="R75" t="b">
         <v>1</v>
       </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5931,6 +6286,11 @@
       <c r="R76" t="b">
         <v>1</v>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5986,6 +6346,11 @@
       <c r="R77" t="b">
         <v>1</v>
       </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6041,6 +6406,11 @@
       <c r="R78" t="b">
         <v>1</v>
       </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6081,6 +6451,11 @@
       <c r="R79" t="b">
         <v>1</v>
       </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6136,6 +6511,11 @@
       <c r="R80" t="b">
         <v>1</v>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6190,6 +6570,11 @@
       </c>
       <c r="R81" t="b">
         <v>1</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H639"/>
+  <dimension ref="A1:H650"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24413,6 +24413,336 @@
           <t>[ROUTINE] Insider trade — Rogers Chris (President and CEO) sold 4,933 shares @ $50.00 ($246.7K) on 2026-08-07</t>
         </is>
       </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr"/>
+      <c r="G640" t="inlineStr"/>
+      <c r="H640" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr"/>
+      <c r="G641" t="inlineStr"/>
+      <c r="H641" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>GoDaddy Inc.</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>https://careers.godaddy.com</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr"/>
+      <c r="G642" t="inlineStr"/>
+      <c r="H642" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr"/>
+      <c r="G643" t="inlineStr"/>
+      <c r="H643" t="inlineStr"/>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/sell</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr"/>
+      <c r="G644" t="inlineStr"/>
+      <c r="H644" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>https://careers.duolingo.com/jobs/8700588002?gh_jid=8700588002</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>New senior role: Director of Ad Platform Operations</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr"/>
+      <c r="G645" t="inlineStr"/>
+      <c r="H645" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>https://careers.duolingo.com/jobs/8700582002?gh_jid=8700582002</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>New senior role: Director of Ad Platform Operations</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr"/>
+      <c r="G646" t="inlineStr"/>
+      <c r="H646" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000116755726000135/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form SCHEDULE 13G</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr"/>
+      <c r="G647" t="inlineStr"/>
+      <c r="H647" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr"/>
+      <c r="G648" t="inlineStr"/>
+      <c r="H648" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>8 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr"/>
+      <c r="G649" t="inlineStr"/>
+      <c r="H649" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr"/>
+      <c r="G650" t="inlineStr"/>
+      <c r="H650" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H650"/>
+  <dimension ref="A1:H672"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24440,9 +24440,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F640" t="inlineStr"/>
-      <c r="G640" t="inlineStr"/>
-      <c r="H640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -24470,9 +24467,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F641" t="inlineStr"/>
-      <c r="G641" t="inlineStr"/>
-      <c r="H641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -24500,9 +24494,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F642" t="inlineStr"/>
-      <c r="G642" t="inlineStr"/>
-      <c r="H642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -24530,9 +24521,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F643" t="inlineStr"/>
-      <c r="G643" t="inlineStr"/>
-      <c r="H643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -24560,9 +24548,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F644" t="inlineStr"/>
-      <c r="G644" t="inlineStr"/>
-      <c r="H644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -24590,9 +24575,6 @@
           <t>New senior role: Director of Ad Platform Operations</t>
         </is>
       </c>
-      <c r="F645" t="inlineStr"/>
-      <c r="G645" t="inlineStr"/>
-      <c r="H645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -24620,9 +24602,6 @@
           <t>New senior role: Director of Ad Platform Operations</t>
         </is>
       </c>
-      <c r="F646" t="inlineStr"/>
-      <c r="G646" t="inlineStr"/>
-      <c r="H646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -24650,9 +24629,6 @@
           <t>[UNKNOWN] Form SCHEDULE 13G</t>
         </is>
       </c>
-      <c r="F647" t="inlineStr"/>
-      <c r="G647" t="inlineStr"/>
-      <c r="H647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -24680,9 +24656,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F648" t="inlineStr"/>
-      <c r="G648" t="inlineStr"/>
-      <c r="H648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -24710,9 +24683,6 @@
           <t>8 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F649" t="inlineStr"/>
-      <c r="G649" t="inlineStr"/>
-      <c r="H649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -24740,9 +24710,624 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F650" t="inlineStr"/>
-      <c r="G650" t="inlineStr"/>
-      <c r="H650" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>AppLovin Corporation</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>https://www.applovin.com/blog/</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Warner Music Group Corp.</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1319161/000031302826000042/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form SCHEDULE 13G</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>https://mediacenter.adp.com</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr"/>
+      <c r="G665" t="inlineStr"/>
+      <c r="H665" t="inlineStr"/>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>GoDaddy Inc.</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>https://careers.godaddy.com</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr"/>
+      <c r="G666" t="inlineStr"/>
+      <c r="H666" t="inlineStr"/>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr"/>
+      <c r="G667" t="inlineStr"/>
+      <c r="H667" t="inlineStr"/>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>https://www.etsy.com/sell</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr"/>
+      <c r="G668" t="inlineStr"/>
+      <c r="H668" t="inlineStr"/>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/duolingo</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr"/>
+      <c r="G669" t="inlineStr"/>
+      <c r="H669" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr"/>
+      <c r="G670" t="inlineStr"/>
+      <c r="H670" t="inlineStr"/>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>https://dave.com/extra-cash-account</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr"/>
+      <c r="G671" t="inlineStr"/>
+      <c r="H671" t="inlineStr"/>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>https://dave.com/careers</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr"/>
+      <c r="G672" t="inlineStr"/>
+      <c r="H672" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H672"/>
+  <dimension ref="A1:H745"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -25115,9 +25115,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F665" t="inlineStr"/>
-      <c r="G665" t="inlineStr"/>
-      <c r="H665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -25145,9 +25142,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F666" t="inlineStr"/>
-      <c r="G666" t="inlineStr"/>
-      <c r="H666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -25175,9 +25169,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F667" t="inlineStr"/>
-      <c r="G667" t="inlineStr"/>
-      <c r="H667" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -25205,9 +25196,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F668" t="inlineStr"/>
-      <c r="G668" t="inlineStr"/>
-      <c r="H668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -25235,9 +25223,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F669" t="inlineStr"/>
-      <c r="G669" t="inlineStr"/>
-      <c r="H669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -25265,9 +25250,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F670" t="inlineStr"/>
-      <c r="G670" t="inlineStr"/>
-      <c r="H670" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -25295,9 +25277,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F671" t="inlineStr"/>
-      <c r="G671" t="inlineStr"/>
-      <c r="H671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -25325,9 +25304,2112 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F672" t="inlineStr"/>
-      <c r="G672" t="inlineStr"/>
-      <c r="H672" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1075531/000195004726008019/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Steenbergen Ewout (Officer) plans to sell 20,000 shares (~$4.26M) on/after 08/12/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>SPHR</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Sphere Entertainment Co.</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1795250/000089542126000239/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Choice Hotels International, Inc.</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1046311/000089542126000224/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326012279/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Olivan Javier (Chief Operating Officer) sold 1,692 shares @ $600.69 ($1.02M) on 2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000210687326000012/xslF345X06/wk-form4_1786570883.xml</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Brown Claude Leonard (Chief Business Officer) sold 12,240 shares @ $23.88 ($292.3K) on 2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000177391426000019/xslF345X06/wk-form4_1786570823.xml</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Silbermann Benjamin (Director) sold 93,750 shares @ $23.55 ($2.21M) on 2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000192109426000837/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Silbermann Benjamin (Director) plans to sell 46,875 shares (~$1.09M) on/after 08/12/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/press</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1713445/000171344526000107/rddt-20260812.htm</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com/premium</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>NYT</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>The New York Times Company</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/71691/000121465926010012/xslF345X06/marketforms-73757.xml</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Perpich David S. (Director) 131 shares withheld for taxes (vest event) on 2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>LIF</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>LIF (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1581760/000158176026000144/xslF345X06/wk-form4_1786565261.xml</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Morin Brit (Director) sold 15,582 shares @ $65.00 ($1.01M) on 2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000162828026056359/xslF345X06/wk-form4_1786569380.xml</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Ciongoli Adam G. (Chief Legal and Policy Officer) granted 57,485 Restricted Stock Units on 2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000162828026056358/xslF345X06/wk-form4_1786569337.xml</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Tomsic Steven (Chief Financial Officer) granted 76,646 Restricted Stock Units on 2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000162828026056356/xslF345X06/wk-form4_1786569313.xml</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lachlan K Murdoch (Executive Chair, CEO) granted 383,235 Restricted Stock Units on 2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000162828026056354/xslF345X06/wk-form4_1786569279.xml</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — John Nallen (President, COO) granted 124,551 Restricted Stock Units on 2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1337634/000162828026056402/stub-20260630.htm</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Quarterly report</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1337634/000162828026056250/stub-20260812.htm</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr"/>
+      <c r="G701" t="inlineStr"/>
+      <c r="H701" t="inlineStr"/>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000110465926095098/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr"/>
+      <c r="G702" t="inlineStr"/>
+      <c r="H702" t="inlineStr"/>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr"/>
+      <c r="G703" t="inlineStr"/>
+      <c r="H703" t="inlineStr"/>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065088/000094726326000070/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form SCHEDULE 13G</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr"/>
+      <c r="G704" t="inlineStr"/>
+      <c r="H704" t="inlineStr"/>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Wayfair Inc.</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1616707/000142284926000136/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr"/>
+      <c r="G705" t="inlineStr"/>
+      <c r="H705" t="inlineStr"/>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Wayfair Inc.</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1616707/000195917326005958/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Conine Steven (Officer) plans to sell 69,000 shares (~$7.13M) on/after 08/12/2026</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr"/>
+      <c r="G706" t="inlineStr"/>
+      <c r="H706" t="inlineStr"/>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Wayfair Inc.</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1616707/000195917326005957/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Shah Niraj (Officer) plans to sell 69,000 shares (~$7.13M) on/after 08/12/2026</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr"/>
+      <c r="G707" t="inlineStr"/>
+      <c r="H707" t="inlineStr"/>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1370637/000206822926000013/xslF345X06/form4-08122026_090836.xml</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Colburn Richard Edward III (Chief Product &amp; Tech Officer) sold 8,252 shares @ $82.09 ($677.4K) on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr"/>
+      <c r="G708" t="inlineStr"/>
+      <c r="H708" t="inlineStr"/>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000160784126000019/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Us (Ttgp), Ltd. Sc (10%+ owner) other: 5,203,747 shares on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr"/>
+      <c r="G709" t="inlineStr"/>
+      <c r="H709" t="inlineStr"/>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000160784126000018/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Us (Ttgp), Ltd. Sc (10%+ owner) other: 5,203,747 shares on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr"/>
+      <c r="G710" t="inlineStr"/>
+      <c r="H710" t="inlineStr"/>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000119312526346963/xslSCHEDULE_13D_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ active owner disclosure</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr"/>
+      <c r="G711" t="inlineStr"/>
+      <c r="H711" t="inlineStr"/>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/duolingo</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr"/>
+      <c r="G712" t="inlineStr"/>
+      <c r="H712" t="inlineStr"/>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>https://blog.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr"/>
+      <c r="G713" t="inlineStr"/>
+      <c r="H713" t="inlineStr"/>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000162828026056405/xslSCHEDULE_13G_X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr"/>
+      <c r="G714" t="inlineStr"/>
+      <c r="H714" t="inlineStr"/>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000162828026056396/xslF345X06/wk-form4_1786572135.xml</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sallie Krawcheck (Director) granted 4,592 shares on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr"/>
+      <c r="G715" t="inlineStr"/>
+      <c r="H715" t="inlineStr"/>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000162828026056394/xslF345X06/wk-form3_1786572111.xml</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>[ROUTINE] New insider — initial ownership statement</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr"/>
+      <c r="G716" t="inlineStr"/>
+      <c r="H716" t="inlineStr"/>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>https://zillow.mediaroom.com</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr"/>
+      <c r="G717" t="inlineStr"/>
+      <c r="H717" t="inlineStr"/>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000162828026056364/xslF345X06/wk-form4_1786569955.xml</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Cormier Thielke Claire (Director) sold 1,187 shares @ $33.09 ($39.3K) on 2026-08-11</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr"/>
+      <c r="G718" t="inlineStr"/>
+      <c r="H718" t="inlineStr"/>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>RKT</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Rocket Companies Inc.</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1805284/000142284926000132/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form SCHEDULE 13G</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr"/>
+      <c r="G719" t="inlineStr"/>
+      <c r="H719" t="inlineStr"/>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr"/>
+      <c r="G720" t="inlineStr"/>
+      <c r="H720" t="inlineStr"/>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000205490526000008/xslF345X06/wk-form4_1786571440.xml</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Barat Elizabeth Erin (Chief People Officer) 1,244 shares withheld for taxes (vest event) on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr"/>
+      <c r="G721" t="inlineStr"/>
+      <c r="H721" t="inlineStr"/>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000208297526000008/xslF345X06/wk-form4_1786571290.xml</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Rigler Don (Principal Accounting Officer) sold 150 shares @ $195.87 ($29.4K) on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr"/>
+      <c r="G722" t="inlineStr"/>
+      <c r="H722" t="inlineStr"/>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000183740026000012/xslF345X06/wk-form4_1786571025.xml</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Trigg William Shane (Chief Executive Officer) 3,718 shares withheld for taxes (vest event) on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr"/>
+      <c r="G723" t="inlineStr"/>
+      <c r="H723" t="inlineStr"/>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000204337926000010/xslF345X06/wk-form4_1786570910.xml</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Eaton Timothy Mathias (Chief Financial Officer) 949 shares withheld for taxes (vest event) on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr"/>
+      <c r="G724" t="inlineStr"/>
+      <c r="H724" t="inlineStr"/>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000209574426000012/xslF345X06/wk-form4_1786570742.xml</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Pickering Evan (General Counsel) sold 463 shares @ $200.66 ($92.9K) on 2026-08-11</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr"/>
+      <c r="G725" t="inlineStr"/>
+      <c r="H725" t="inlineStr"/>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000093833326000014/xslF345X06/form4-08122026_090824.xml</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Maurice J Duca (10%+ owner) sold 5,442 shares @ $201.13 ($1.09M) on 2026-08-11</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr"/>
+      <c r="G726" t="inlineStr"/>
+      <c r="H726" t="inlineStr"/>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000093833326000013/xslF345X06/form4-08122026_090836.xml</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Maurice J Duca (10%+ owner) sold 15,958 shares @ $199.22 ($3.18M) on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr"/>
+      <c r="G727" t="inlineStr"/>
+      <c r="H727" t="inlineStr"/>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000195004726008024/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Pickering Evan (Officer) plans to sell 322 shares (~$65.4K) on/after 08/12/2026</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr"/>
+      <c r="G728" t="inlineStr"/>
+      <c r="H728" t="inlineStr"/>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726008009/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$471.7K) on/after 08/12/2026</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr"/>
+      <c r="G729" t="inlineStr"/>
+      <c r="H729" t="inlineStr"/>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Sezzle Inc.</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>https://investors.sezzle.com</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr"/>
+      <c r="G730" t="inlineStr"/>
+      <c r="H730" t="inlineStr"/>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Sezzle Inc.</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1662991/000166299126000142/xslF345X06/wk-form4_1786569970.xml</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Youakim Charles (Executive Chairman and CEO) 6,978 shares withheld for taxes (vest event) on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr"/>
+      <c r="G731" t="inlineStr"/>
+      <c r="H731" t="inlineStr"/>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Sezzle Inc.</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1662991/000166299126000140/xslF345X06/wk-form4_1786569862.xml</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Paradis Paul (Director &amp; President) 7,110 shares withheld for taxes (vest event) on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr"/>
+      <c r="G732" t="inlineStr"/>
+      <c r="H732" t="inlineStr"/>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Sezzle Inc.</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1662991/000166299126000137/xslF345X06/wk-form4_1786569637.xml</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Krause Justin (SVP FINANCE AND CONTROLLER) 1,571 shares withheld for taxes (vest event) on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr"/>
+      <c r="G733" t="inlineStr"/>
+      <c r="H733" t="inlineStr"/>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Sezzle Inc.</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1662991/000166299126000135/xslF345X06/wk-form4_1786569541.xml</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sabzivand Amin (Chief Operating Officer) 6,973 shares withheld for taxes (vest event) on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr"/>
+      <c r="G734" t="inlineStr"/>
+      <c r="H734" t="inlineStr"/>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Sezzle Inc.</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1662991/000166299126000133/xslF345X06/wk-form4_1786569469.xml</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Brading Lee Dickson (Chief Financial Officer) 1,405 shares withheld for taxes (vest event) on 2026-08-10</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr"/>
+      <c r="G735" t="inlineStr"/>
+      <c r="H735" t="inlineStr"/>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Sezzle Inc.</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1662991/000166299126000132/sezl-20260812.htm</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr"/>
+      <c r="G736" t="inlineStr"/>
+      <c r="H736" t="inlineStr"/>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr"/>
+      <c r="G737" t="inlineStr"/>
+      <c r="H737" t="inlineStr"/>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1820953/000142284926000118/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr"/>
+      <c r="G738" t="inlineStr"/>
+      <c r="H738" t="inlineStr"/>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1820953/000195004726008041/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Watson Noel (Officer) plans to sell 2,000 shares (~$153.4K) on/after 08/12/2026</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr"/>
+      <c r="G739" t="inlineStr"/>
+      <c r="H739" t="inlineStr"/>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>https://newsroom.aboutrobinhood.com</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr"/>
+      <c r="G740" t="inlineStr"/>
+      <c r="H740" t="inlineStr"/>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000095010326012262/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>[ROUTINE] New insider — initial ownership statement</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr"/>
+      <c r="G741" t="inlineStr"/>
+      <c r="H741" t="inlineStr"/>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>WSM</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Williams-Sonoma Inc.</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>https://www.williams-sonoma.com/</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr"/>
+      <c r="G742" t="inlineStr"/>
+      <c r="H742" t="inlineStr"/>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr"/>
+      <c r="G743" t="inlineStr"/>
+      <c r="H743" t="inlineStr"/>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1858985/000095010326012255/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr"/>
+      <c r="G744" t="inlineStr"/>
+      <c r="H744" t="inlineStr"/>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1858985/000095010326012253/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form SCHEDULE 13G</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr"/>
+      <c r="G745" t="inlineStr"/>
+      <c r="H745" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H745"/>
+  <dimension ref="A1:H824"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -26087,9 +26087,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F701" t="inlineStr"/>
-      <c r="G701" t="inlineStr"/>
-      <c r="H701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -26117,9 +26114,6 @@
           <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
         </is>
       </c>
-      <c r="F702" t="inlineStr"/>
-      <c r="G702" t="inlineStr"/>
-      <c r="H702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -26147,9 +26141,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F703" t="inlineStr"/>
-      <c r="G703" t="inlineStr"/>
-      <c r="H703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -26177,9 +26168,6 @@
           <t>[UNKNOWN] Form SCHEDULE 13G</t>
         </is>
       </c>
-      <c r="F704" t="inlineStr"/>
-      <c r="G704" t="inlineStr"/>
-      <c r="H704" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -26207,9 +26195,6 @@
           <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
         </is>
       </c>
-      <c r="F705" t="inlineStr"/>
-      <c r="G705" t="inlineStr"/>
-      <c r="H705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -26237,9 +26222,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Conine Steven (Officer) plans to sell 69,000 shares (~$7.13M) on/after 08/12/2026</t>
         </is>
       </c>
-      <c r="F706" t="inlineStr"/>
-      <c r="G706" t="inlineStr"/>
-      <c r="H706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -26267,9 +26249,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Shah Niraj (Officer) plans to sell 69,000 shares (~$7.13M) on/after 08/12/2026</t>
         </is>
       </c>
-      <c r="F707" t="inlineStr"/>
-      <c r="G707" t="inlineStr"/>
-      <c r="H707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -26297,9 +26276,6 @@
           <t>[ROUTINE] Insider trade — Colburn Richard Edward III (Chief Product &amp; Tech Officer) sold 8,252 shares @ $82.09 ($677.4K) on 2026-08-10</t>
         </is>
       </c>
-      <c r="F708" t="inlineStr"/>
-      <c r="G708" t="inlineStr"/>
-      <c r="H708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -26327,9 +26303,6 @@
           <t>[ROUTINE] Insider trade — Us (Ttgp), Ltd. Sc (10%+ owner) other: 5,203,747 shares on 2026-08-10</t>
         </is>
       </c>
-      <c r="F709" t="inlineStr"/>
-      <c r="G709" t="inlineStr"/>
-      <c r="H709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -26357,9 +26330,6 @@
           <t>[ROUTINE] Insider trade — Us (Ttgp), Ltd. Sc (10%+ owner) other: 5,203,747 shares on 2026-08-10</t>
         </is>
       </c>
-      <c r="F710" t="inlineStr"/>
-      <c r="G710" t="inlineStr"/>
-      <c r="H710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -26387,9 +26357,6 @@
           <t>[MATERIAL] Update to 5%+ active owner disclosure</t>
         </is>
       </c>
-      <c r="F711" t="inlineStr"/>
-      <c r="G711" t="inlineStr"/>
-      <c r="H711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -26417,9 +26384,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F712" t="inlineStr"/>
-      <c r="G712" t="inlineStr"/>
-      <c r="H712" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -26447,9 +26411,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F713" t="inlineStr"/>
-      <c r="G713" t="inlineStr"/>
-      <c r="H713" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -26477,9 +26438,6 @@
           <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
         </is>
       </c>
-      <c r="F714" t="inlineStr"/>
-      <c r="G714" t="inlineStr"/>
-      <c r="H714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -26507,9 +26465,6 @@
           <t>[ROUTINE] Insider trade — Sallie Krawcheck (Director) granted 4,592 shares on 2026-08-10</t>
         </is>
       </c>
-      <c r="F715" t="inlineStr"/>
-      <c r="G715" t="inlineStr"/>
-      <c r="H715" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -26537,9 +26492,6 @@
           <t>[ROUTINE] New insider — initial ownership statement</t>
         </is>
       </c>
-      <c r="F716" t="inlineStr"/>
-      <c r="G716" t="inlineStr"/>
-      <c r="H716" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -26567,9 +26519,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F717" t="inlineStr"/>
-      <c r="G717" t="inlineStr"/>
-      <c r="H717" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -26597,9 +26546,6 @@
           <t>[ROUTINE] Insider trade — Cormier Thielke Claire (Director) sold 1,187 shares @ $33.09 ($39.3K) on 2026-08-11</t>
         </is>
       </c>
-      <c r="F718" t="inlineStr"/>
-      <c r="G718" t="inlineStr"/>
-      <c r="H718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -26627,9 +26573,6 @@
           <t>[UNKNOWN] Form SCHEDULE 13G</t>
         </is>
       </c>
-      <c r="F719" t="inlineStr"/>
-      <c r="G719" t="inlineStr"/>
-      <c r="H719" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -26657,9 +26600,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F720" t="inlineStr"/>
-      <c r="G720" t="inlineStr"/>
-      <c r="H720" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -26687,9 +26627,6 @@
           <t>[ROUTINE] Insider trade — Barat Elizabeth Erin (Chief People Officer) 1,244 shares withheld for taxes (vest event) on 2026-08-10</t>
         </is>
       </c>
-      <c r="F721" t="inlineStr"/>
-      <c r="G721" t="inlineStr"/>
-      <c r="H721" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -26717,9 +26654,6 @@
           <t>[ROUTINE] Insider trade — Rigler Don (Principal Accounting Officer) sold 150 shares @ $195.87 ($29.4K) on 2026-08-10</t>
         </is>
       </c>
-      <c r="F722" t="inlineStr"/>
-      <c r="G722" t="inlineStr"/>
-      <c r="H722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -26747,9 +26681,6 @@
           <t>[ROUTINE] Insider trade — Trigg William Shane (Chief Executive Officer) 3,718 shares withheld for taxes (vest event) on 2026-08-10</t>
         </is>
       </c>
-      <c r="F723" t="inlineStr"/>
-      <c r="G723" t="inlineStr"/>
-      <c r="H723" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -26777,9 +26708,6 @@
           <t>[ROUTINE] Insider trade — Eaton Timothy Mathias (Chief Financial Officer) 949 shares withheld for taxes (vest event) on 2026-08-10</t>
         </is>
       </c>
-      <c r="F724" t="inlineStr"/>
-      <c r="G724" t="inlineStr"/>
-      <c r="H724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -26807,9 +26735,6 @@
           <t>[ROUTINE] Insider trade — Pickering Evan (General Counsel) sold 463 shares @ $200.66 ($92.9K) on 2026-08-11</t>
         </is>
       </c>
-      <c r="F725" t="inlineStr"/>
-      <c r="G725" t="inlineStr"/>
-      <c r="H725" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -26837,9 +26762,6 @@
           <t>[ROUTINE] Insider trade — Maurice J Duca (10%+ owner) sold 5,442 shares @ $201.13 ($1.09M) on 2026-08-11</t>
         </is>
       </c>
-      <c r="F726" t="inlineStr"/>
-      <c r="G726" t="inlineStr"/>
-      <c r="H726" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -26867,9 +26789,6 @@
           <t>[ROUTINE] Insider trade — Maurice J Duca (10%+ owner) sold 15,958 shares @ $199.22 ($3.18M) on 2026-08-10</t>
         </is>
       </c>
-      <c r="F727" t="inlineStr"/>
-      <c r="G727" t="inlineStr"/>
-      <c r="H727" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -26897,9 +26816,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Pickering Evan (Officer) plans to sell 322 shares (~$65.4K) on/after 08/12/2026</t>
         </is>
       </c>
-      <c r="F728" t="inlineStr"/>
-      <c r="G728" t="inlineStr"/>
-      <c r="H728" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
@@ -26927,9 +26843,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$471.7K) on/after 08/12/2026</t>
         </is>
       </c>
-      <c r="F729" t="inlineStr"/>
-      <c r="G729" t="inlineStr"/>
-      <c r="H729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -26957,9 +26870,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F730" t="inlineStr"/>
-      <c r="G730" t="inlineStr"/>
-      <c r="H730" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
@@ -26987,9 +26897,6 @@
           <t>[ROUTINE] Insider trade — Youakim Charles (Executive Chairman and CEO) 6,978 shares withheld for taxes (vest event) on 2026-08-10</t>
         </is>
       </c>
-      <c r="F731" t="inlineStr"/>
-      <c r="G731" t="inlineStr"/>
-      <c r="H731" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -27017,9 +26924,6 @@
           <t>[ROUTINE] Insider trade — Paradis Paul (Director &amp; President) 7,110 shares withheld for taxes (vest event) on 2026-08-10</t>
         </is>
       </c>
-      <c r="F732" t="inlineStr"/>
-      <c r="G732" t="inlineStr"/>
-      <c r="H732" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -27047,9 +26951,6 @@
           <t>[ROUTINE] Insider trade — Krause Justin (SVP FINANCE AND CONTROLLER) 1,571 shares withheld for taxes (vest event) on 2026-08-10</t>
         </is>
       </c>
-      <c r="F733" t="inlineStr"/>
-      <c r="G733" t="inlineStr"/>
-      <c r="H733" t="inlineStr"/>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
@@ -27077,9 +26978,6 @@
           <t>[ROUTINE] Insider trade — Sabzivand Amin (Chief Operating Officer) 6,973 shares withheld for taxes (vest event) on 2026-08-10</t>
         </is>
       </c>
-      <c r="F734" t="inlineStr"/>
-      <c r="G734" t="inlineStr"/>
-      <c r="H734" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -27107,9 +27005,6 @@
           <t>[ROUTINE] Insider trade — Brading Lee Dickson (Chief Financial Officer) 1,405 shares withheld for taxes (vest event) on 2026-08-10</t>
         </is>
       </c>
-      <c r="F735" t="inlineStr"/>
-      <c r="G735" t="inlineStr"/>
-      <c r="H735" t="inlineStr"/>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
@@ -27137,9 +27032,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F736" t="inlineStr"/>
-      <c r="G736" t="inlineStr"/>
-      <c r="H736" t="inlineStr"/>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
@@ -27167,9 +27059,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F737" t="inlineStr"/>
-      <c r="G737" t="inlineStr"/>
-      <c r="H737" t="inlineStr"/>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -27197,9 +27086,6 @@
           <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
         </is>
       </c>
-      <c r="F738" t="inlineStr"/>
-      <c r="G738" t="inlineStr"/>
-      <c r="H738" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
@@ -27227,9 +27113,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Watson Noel (Officer) plans to sell 2,000 shares (~$153.4K) on/after 08/12/2026</t>
         </is>
       </c>
-      <c r="F739" t="inlineStr"/>
-      <c r="G739" t="inlineStr"/>
-      <c r="H739" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
@@ -27257,9 +27140,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F740" t="inlineStr"/>
-      <c r="G740" t="inlineStr"/>
-      <c r="H740" t="inlineStr"/>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -27287,9 +27167,6 @@
           <t>[ROUTINE] New insider — initial ownership statement</t>
         </is>
       </c>
-      <c r="F741" t="inlineStr"/>
-      <c r="G741" t="inlineStr"/>
-      <c r="H741" t="inlineStr"/>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
@@ -27317,9 +27194,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F742" t="inlineStr"/>
-      <c r="G742" t="inlineStr"/>
-      <c r="H742" t="inlineStr"/>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -27347,9 +27221,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F743" t="inlineStr"/>
-      <c r="G743" t="inlineStr"/>
-      <c r="H743" t="inlineStr"/>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
@@ -27377,9 +27248,6 @@
           <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
         </is>
       </c>
-      <c r="F744" t="inlineStr"/>
-      <c r="G744" t="inlineStr"/>
-      <c r="H744" t="inlineStr"/>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
@@ -27407,9 +27275,2265 @@
           <t>[UNKNOWN] Form SCHEDULE 13G</t>
         </is>
       </c>
-      <c r="F745" t="inlineStr"/>
-      <c r="G745" t="inlineStr"/>
-      <c r="H745" t="inlineStr"/>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000155278126000443/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form SCHEDULE 13G</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1324424/000122520826007100/xslF345X06/doc4.xml</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Dzielak Robert J (Chief Legal Officer &amp; Sec'y) sold 3,003 shares @ $315.00 ($945.9K) on 2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1324424/000194984626000510/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Jacobson Craig A (Director) plans to sell 3,133 shares (~$1.03M) on/after 08/13/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1075531/000157491826000006/xslF345X06/form4-08132026_080828.xml</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Steenbergen Ewout L (CHIEF FINANCIAL OFFICER) sold 20,000 shares @ $211.03 ($4.22M) on 2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000179033026000007/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lin Alfred (Director) C: 4,105,236 shares on 2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000119312526349303/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Blecharczyk Nathan (Chief Strategy Officer) C: 400 shares on 2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Choice Hotels International, Inc.</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1046311/000139834426014369/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>https://blog.google</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/press</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>AppLovin Corporation</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>https://www.applovin.com/legal/</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>NYT</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>The New York Times Company</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/71691/000198079026000012/xslF345X06/wk-form4_1786632796.xml</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Bardeen William (EVP, Chief Financial Officer) 485 shares withheld for taxes (vest event) on 2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>LIF</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>LIF (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1581760/000195917326005969/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Prober Charles J. (Director) plans to sell 7,930 shares (~$385.3K) on/after 08/13/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/news/</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/712515/000114036126032929/ef20079519_1512g.htm</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 15-12G</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/896878/000162828026056894/xslF345X06/wk-form4_1786662000.xml</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hilliard Caryl Lyn (EVP, People and Places) 90 shares withheld for taxes (vest event) on 2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/896878/000162828026056892/xslF345X06/wk-form4_1786661929.xml</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hanebrink Anton (EVP, Corp Strategy and Dev) 197 shares withheld for taxes (vest event) on 2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/896878/000162828026056890/xslF345X06/wk-form4_1786661831.xml</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Cozzens Tyler Ralph (EVP, Gen. Counsel &amp; Corp. Sec.) 56 shares withheld for taxes (vest event) on 2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/896878/000162828026056888/xslF345X06/wk-form4_1786661750.xml</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Aujla Sandeep (EVP and CFO) 120 shares withheld for taxes (vest event) on 2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>https://mediacenter.adp.com</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000195917326005972/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Scutt Joshua (Policy-Making Officer) plans to sell 118 shares (~$17.2K) on/after 08/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>https://news.shopify.com</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr"/>
+      <c r="G783" t="inlineStr"/>
+      <c r="H783" t="inlineStr"/>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr"/>
+      <c r="G784" t="inlineStr"/>
+      <c r="H784" t="inlineStr"/>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>https://investors.wix.com/board-of-directors</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr"/>
+      <c r="G785" t="inlineStr"/>
+      <c r="H785" t="inlineStr"/>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000090221926000249/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr"/>
+      <c r="G786" t="inlineStr"/>
+      <c r="H786" t="inlineStr"/>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>GLBE</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Global-E Online Ltd.</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835963/000119312526348852/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Schlachet Amir (CEO) sold 16,814 shares @ $42.41 ($713.1K) on 2026-08-12</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr"/>
+      <c r="G787" t="inlineStr"/>
+      <c r="H787" t="inlineStr"/>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>GoDaddy Inc.</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1609711/000160971126000096/xslF345X06/wk-form4_1786658108.xml</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Palitwanon Phontip (Chief Accounting Officer) sold 2,261 shares @ $91.81 ($207.6K) on 2026-08-11</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr"/>
+      <c r="G788" t="inlineStr"/>
+      <c r="H788" t="inlineStr"/>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr"/>
+      <c r="G789" t="inlineStr"/>
+      <c r="H789" t="inlineStr"/>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>https://www.ebayinc.com/stories/news/</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr"/>
+      <c r="G790" t="inlineStr"/>
+      <c r="H790" t="inlineStr"/>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>CHWY</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Chewy Inc.</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1766502/000116755726000182/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr"/>
+      <c r="G791" t="inlineStr"/>
+      <c r="H791" t="inlineStr"/>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr"/>
+      <c r="G792" t="inlineStr"/>
+      <c r="H792" t="inlineStr"/>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr"/>
+      <c r="G793" t="inlineStr"/>
+      <c r="H793" t="inlineStr"/>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr"/>
+      <c r="G794" t="inlineStr"/>
+      <c r="H794" t="inlineStr"/>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000192109426000862/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Reuter Emily (Officer) plans to sell 25,000 shares (~$1.25M) on/after 08/13/2026</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr"/>
+      <c r="G795" t="inlineStr"/>
+      <c r="H795" t="inlineStr"/>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/duolingo</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>4 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr"/>
+      <c r="G796" t="inlineStr"/>
+      <c r="H796" t="inlineStr"/>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>https://blog.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr"/>
+      <c r="G797" t="inlineStr"/>
+      <c r="H797" t="inlineStr"/>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>https://ir.mtch.com/leadership/default.aspx</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr"/>
+      <c r="G798" t="inlineStr"/>
+      <c r="H798" t="inlineStr"/>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>https://mtch.com/news</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr"/>
+      <c r="G799" t="inlineStr"/>
+      <c r="H799" t="inlineStr"/>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>https://mtch.com/careers</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr"/>
+      <c r="G800" t="inlineStr"/>
+      <c r="H800" t="inlineStr"/>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/891103/000089110326000131/xslF345X06/wk-form4_1786655267.xml</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Schiffman Glenn (Director) BOUGHT 3,000 shares @ $36.63 ($109.9K) on 2026-08-11</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr"/>
+      <c r="G801" t="inlineStr"/>
+      <c r="H801" t="inlineStr"/>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>https://www.zillowgroup.com/about-us/our-leaders/</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr"/>
+      <c r="G802" t="inlineStr"/>
+      <c r="H802" t="inlineStr"/>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000192109426000855/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Wacksman Jeremy (Officer) plans to sell 5,786 shares (~$198.1K) on/after 08/13/2026</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr"/>
+      <c r="G803" t="inlineStr"/>
+      <c r="H803" t="inlineStr"/>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000192109426000854/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Spaulding Dan (Officer) plans to sell 1,966 shares (~$67.3K) on/after 08/13/2026</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr"/>
+      <c r="G804" t="inlineStr"/>
+      <c r="H804" t="inlineStr"/>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000192109426000853/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Samuelson Errol G (Officer) plans to sell 3,154 shares (~$108.0K) on/after 08/13/2026</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr"/>
+      <c r="G805" t="inlineStr"/>
+      <c r="H805" t="inlineStr"/>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000192109426000852/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Rock Jennifer (Officer) plans to sell 990 shares (~$33.9K) on/after 08/13/2026</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr"/>
+      <c r="G806" t="inlineStr"/>
+      <c r="H806" t="inlineStr"/>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000192109426000851/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Owens Bradley D. (Former Affiliate) plans to sell 2,148 shares (~$73.6K) on/after 08/13/2026</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr"/>
+      <c r="G807" t="inlineStr"/>
+      <c r="H807" t="inlineStr"/>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000192109426000850/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Hofmann Jeremy (Officer) plans to sell 3,510 shares (~$120.2K) on/after 08/13/2026</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr"/>
+      <c r="G808" t="inlineStr"/>
+      <c r="H808" t="inlineStr"/>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000192109426000849/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Choo Jun (Former Affiliate) plans to sell 1,617 shares (~$55.4K) on/after 08/13/2026</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr"/>
+      <c r="G809" t="inlineStr"/>
+      <c r="H809" t="inlineStr"/>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000192109426000848/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Beitel David A. (Officer) plans to sell 1,798 shares (~$61.6K) on/after 08/13/2026</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr"/>
+      <c r="G810" t="inlineStr"/>
+      <c r="H810" t="inlineStr"/>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000117266126003361/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr"/>
+      <c r="G811" t="inlineStr"/>
+      <c r="H811" t="inlineStr"/>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000117266126003360/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr"/>
+      <c r="G812" t="inlineStr"/>
+      <c r="H812" t="inlineStr"/>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr"/>
+      <c r="G813" t="inlineStr"/>
+      <c r="H813" t="inlineStr"/>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000093833326000016/xslSCHEDULE_13D_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ active owner disclosure</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr"/>
+      <c r="G814" t="inlineStr"/>
+      <c r="H814" t="inlineStr"/>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726008078/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$475.0K) on/after 08/13/2026</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr"/>
+      <c r="G815" t="inlineStr"/>
+      <c r="H815" t="inlineStr"/>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>6 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr"/>
+      <c r="G816" t="inlineStr"/>
+      <c r="H816" t="inlineStr"/>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>https://pos.toasttab.com/leadership</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr"/>
+      <c r="G817" t="inlineStr"/>
+      <c r="H817" t="inlineStr"/>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>https://pos.toasttab.com/pricing</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr"/>
+      <c r="G818" t="inlineStr"/>
+      <c r="H818" t="inlineStr"/>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1650164/000165016426000180/xslF345X06/wk-form4_1786654873.xml</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Vassil Jonathan (Chief Revenue Officer) sold 13,797 shares @ $36.01 ($496.9K) on 2026-08-11</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr"/>
+      <c r="G819" t="inlineStr"/>
+      <c r="H819" t="inlineStr"/>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr"/>
+      <c r="G820" t="inlineStr"/>
+      <c r="H820" t="inlineStr"/>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>4 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr"/>
+      <c r="G821" t="inlineStr"/>
+      <c r="H821" t="inlineStr"/>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000178387926000126/xslF345X06/wk-form4_1786653495.xml</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Robinhood Markets, Inc. (10%+ owner) sold 12,695 shares @ $28.05 ($356.1K) on 2026-08-11</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr"/>
+      <c r="G822" t="inlineStr"/>
+      <c r="H822" t="inlineStr"/>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr"/>
+      <c r="G823" t="inlineStr"/>
+      <c r="H823" t="inlineStr"/>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr"/>
+      <c r="G824" t="inlineStr"/>
+      <c r="H824" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H824"/>
+  <dimension ref="A1:H856"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -28301,9 +28301,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F783" t="inlineStr"/>
-      <c r="G783" t="inlineStr"/>
-      <c r="H783" t="inlineStr"/>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
@@ -28331,9 +28328,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F784" t="inlineStr"/>
-      <c r="G784" t="inlineStr"/>
-      <c r="H784" t="inlineStr"/>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
@@ -28361,9 +28355,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F785" t="inlineStr"/>
-      <c r="G785" t="inlineStr"/>
-      <c r="H785" t="inlineStr"/>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -28391,9 +28382,6 @@
           <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
         </is>
       </c>
-      <c r="F786" t="inlineStr"/>
-      <c r="G786" t="inlineStr"/>
-      <c r="H786" t="inlineStr"/>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -28421,9 +28409,6 @@
           <t>[ROUTINE] Insider trade — Schlachet Amir (CEO) sold 16,814 shares @ $42.41 ($713.1K) on 2026-08-12</t>
         </is>
       </c>
-      <c r="F787" t="inlineStr"/>
-      <c r="G787" t="inlineStr"/>
-      <c r="H787" t="inlineStr"/>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -28451,9 +28436,6 @@
           <t>[ROUTINE] Insider trade — Palitwanon Phontip (Chief Accounting Officer) sold 2,261 shares @ $91.81 ($207.6K) on 2026-08-11</t>
         </is>
       </c>
-      <c r="F788" t="inlineStr"/>
-      <c r="G788" t="inlineStr"/>
-      <c r="H788" t="inlineStr"/>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -28481,9 +28463,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F789" t="inlineStr"/>
-      <c r="G789" t="inlineStr"/>
-      <c r="H789" t="inlineStr"/>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
@@ -28511,9 +28490,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F790" t="inlineStr"/>
-      <c r="G790" t="inlineStr"/>
-      <c r="H790" t="inlineStr"/>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -28541,9 +28517,6 @@
           <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
         </is>
       </c>
-      <c r="F791" t="inlineStr"/>
-      <c r="G791" t="inlineStr"/>
-      <c r="H791" t="inlineStr"/>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -28571,9 +28544,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F792" t="inlineStr"/>
-      <c r="G792" t="inlineStr"/>
-      <c r="H792" t="inlineStr"/>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
@@ -28601,9 +28571,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F793" t="inlineStr"/>
-      <c r="G793" t="inlineStr"/>
-      <c r="H793" t="inlineStr"/>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
@@ -28631,9 +28598,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F794" t="inlineStr"/>
-      <c r="G794" t="inlineStr"/>
-      <c r="H794" t="inlineStr"/>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
@@ -28661,9 +28625,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Reuter Emily (Officer) plans to sell 25,000 shares (~$1.25M) on/after 08/13/2026</t>
         </is>
       </c>
-      <c r="F795" t="inlineStr"/>
-      <c r="G795" t="inlineStr"/>
-      <c r="H795" t="inlineStr"/>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -28691,9 +28652,6 @@
           <t>4 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F796" t="inlineStr"/>
-      <c r="G796" t="inlineStr"/>
-      <c r="H796" t="inlineStr"/>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
@@ -28721,9 +28679,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F797" t="inlineStr"/>
-      <c r="G797" t="inlineStr"/>
-      <c r="H797" t="inlineStr"/>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
@@ -28751,9 +28706,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F798" t="inlineStr"/>
-      <c r="G798" t="inlineStr"/>
-      <c r="H798" t="inlineStr"/>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -28781,9 +28733,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F799" t="inlineStr"/>
-      <c r="G799" t="inlineStr"/>
-      <c r="H799" t="inlineStr"/>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
@@ -28811,9 +28760,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F800" t="inlineStr"/>
-      <c r="G800" t="inlineStr"/>
-      <c r="H800" t="inlineStr"/>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -28841,9 +28787,6 @@
           <t>[ROUTINE] Insider trade — Schiffman Glenn (Director) BOUGHT 3,000 shares @ $36.63 ($109.9K) on 2026-08-11</t>
         </is>
       </c>
-      <c r="F801" t="inlineStr"/>
-      <c r="G801" t="inlineStr"/>
-      <c r="H801" t="inlineStr"/>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -28871,9 +28814,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F802" t="inlineStr"/>
-      <c r="G802" t="inlineStr"/>
-      <c r="H802" t="inlineStr"/>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
@@ -28901,9 +28841,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Wacksman Jeremy (Officer) plans to sell 5,786 shares (~$198.1K) on/after 08/13/2026</t>
         </is>
       </c>
-      <c r="F803" t="inlineStr"/>
-      <c r="G803" t="inlineStr"/>
-      <c r="H803" t="inlineStr"/>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
@@ -28931,9 +28868,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Spaulding Dan (Officer) plans to sell 1,966 shares (~$67.3K) on/after 08/13/2026</t>
         </is>
       </c>
-      <c r="F804" t="inlineStr"/>
-      <c r="G804" t="inlineStr"/>
-      <c r="H804" t="inlineStr"/>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
@@ -28961,9 +28895,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Samuelson Errol G (Officer) plans to sell 3,154 shares (~$108.0K) on/after 08/13/2026</t>
         </is>
       </c>
-      <c r="F805" t="inlineStr"/>
-      <c r="G805" t="inlineStr"/>
-      <c r="H805" t="inlineStr"/>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
@@ -28991,9 +28922,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Rock Jennifer (Officer) plans to sell 990 shares (~$33.9K) on/after 08/13/2026</t>
         </is>
       </c>
-      <c r="F806" t="inlineStr"/>
-      <c r="G806" t="inlineStr"/>
-      <c r="H806" t="inlineStr"/>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
@@ -29021,9 +28949,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Owens Bradley D. (Former Affiliate) plans to sell 2,148 shares (~$73.6K) on/after 08/13/2026</t>
         </is>
       </c>
-      <c r="F807" t="inlineStr"/>
-      <c r="G807" t="inlineStr"/>
-      <c r="H807" t="inlineStr"/>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
@@ -29051,9 +28976,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Hofmann Jeremy (Officer) plans to sell 3,510 shares (~$120.2K) on/after 08/13/2026</t>
         </is>
       </c>
-      <c r="F808" t="inlineStr"/>
-      <c r="G808" t="inlineStr"/>
-      <c r="H808" t="inlineStr"/>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
@@ -29081,9 +29003,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Choo Jun (Former Affiliate) plans to sell 1,617 shares (~$55.4K) on/after 08/13/2026</t>
         </is>
       </c>
-      <c r="F809" t="inlineStr"/>
-      <c r="G809" t="inlineStr"/>
-      <c r="H809" t="inlineStr"/>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
@@ -29111,9 +29030,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Beitel David A. (Officer) plans to sell 1,798 shares (~$61.6K) on/after 08/13/2026</t>
         </is>
       </c>
-      <c r="F810" t="inlineStr"/>
-      <c r="G810" t="inlineStr"/>
-      <c r="H810" t="inlineStr"/>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
@@ -29141,9 +29057,6 @@
           <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
         </is>
       </c>
-      <c r="F811" t="inlineStr"/>
-      <c r="G811" t="inlineStr"/>
-      <c r="H811" t="inlineStr"/>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
@@ -29171,9 +29084,6 @@
           <t>[MATERIAL] Update to 5%+ passive owner disclosure</t>
         </is>
       </c>
-      <c r="F812" t="inlineStr"/>
-      <c r="G812" t="inlineStr"/>
-      <c r="H812" t="inlineStr"/>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -29201,9 +29111,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F813" t="inlineStr"/>
-      <c r="G813" t="inlineStr"/>
-      <c r="H813" t="inlineStr"/>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -29231,9 +29138,6 @@
           <t>[MATERIAL] Update to 5%+ active owner disclosure</t>
         </is>
       </c>
-      <c r="F814" t="inlineStr"/>
-      <c r="G814" t="inlineStr"/>
-      <c r="H814" t="inlineStr"/>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
@@ -29261,9 +29165,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$475.0K) on/after 08/13/2026</t>
         </is>
       </c>
-      <c r="F815" t="inlineStr"/>
-      <c r="G815" t="inlineStr"/>
-      <c r="H815" t="inlineStr"/>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -29291,9 +29192,6 @@
           <t>6 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F816" t="inlineStr"/>
-      <c r="G816" t="inlineStr"/>
-      <c r="H816" t="inlineStr"/>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
@@ -29321,9 +29219,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F817" t="inlineStr"/>
-      <c r="G817" t="inlineStr"/>
-      <c r="H817" t="inlineStr"/>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
@@ -29351,9 +29246,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F818" t="inlineStr"/>
-      <c r="G818" t="inlineStr"/>
-      <c r="H818" t="inlineStr"/>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
@@ -29381,9 +29273,6 @@
           <t>[ROUTINE] Insider trade — Vassil Jonathan (Chief Revenue Officer) sold 13,797 shares @ $36.01 ($496.9K) on 2026-08-11</t>
         </is>
       </c>
-      <c r="F819" t="inlineStr"/>
-      <c r="G819" t="inlineStr"/>
-      <c r="H819" t="inlineStr"/>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
@@ -29411,9 +29300,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F820" t="inlineStr"/>
-      <c r="G820" t="inlineStr"/>
-      <c r="H820" t="inlineStr"/>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
@@ -29441,9 +29327,6 @@
           <t>4 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F821" t="inlineStr"/>
-      <c r="G821" t="inlineStr"/>
-      <c r="H821" t="inlineStr"/>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
@@ -29471,9 +29354,6 @@
           <t>[ROUTINE] Insider trade — Robinhood Markets, Inc. (10%+ owner) sold 12,695 shares @ $28.05 ($356.1K) on 2026-08-11</t>
         </is>
       </c>
-      <c r="F822" t="inlineStr"/>
-      <c r="G822" t="inlineStr"/>
-      <c r="H822" t="inlineStr"/>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
@@ -29501,9 +29381,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F823" t="inlineStr"/>
-      <c r="G823" t="inlineStr"/>
-      <c r="H823" t="inlineStr"/>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
@@ -29531,9 +29408,915 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F824" t="inlineStr"/>
-      <c r="G824" t="inlineStr"/>
-      <c r="H824" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>AppLovin Corporation</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>https://www.applovin.com/blog/</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>BBY</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Best Buy Co., Inc.</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>https://www.bestbuy.com/site/help-topics/terms-and-conditions/pcmcat204400050067.c</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/news/</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr"/>
+      <c r="G842" t="inlineStr"/>
+      <c r="H842" t="inlineStr"/>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr"/>
+      <c r="G843" t="inlineStr"/>
+      <c r="H843" t="inlineStr"/>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>4 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr"/>
+      <c r="G844" t="inlineStr"/>
+      <c r="H844" t="inlineStr"/>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr"/>
+      <c r="G845" t="inlineStr"/>
+      <c r="H845" t="inlineStr"/>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>https://mtch.com/news</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr"/>
+      <c r="G846" t="inlineStr"/>
+      <c r="H846" t="inlineStr"/>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr"/>
+      <c r="G847" t="inlineStr"/>
+      <c r="H847" t="inlineStr"/>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>https://investors.block.xyz</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr"/>
+      <c r="G848" t="inlineStr"/>
+      <c r="H848" t="inlineStr"/>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>19 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr"/>
+      <c r="G849" t="inlineStr"/>
+      <c r="H849" t="inlineStr"/>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>https://dave.com/careers</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr"/>
+      <c r="G850" t="inlineStr"/>
+      <c r="H850" t="inlineStr"/>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>5 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr"/>
+      <c r="G851" t="inlineStr"/>
+      <c r="H851" t="inlineStr"/>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr"/>
+      <c r="G852" t="inlineStr"/>
+      <c r="H852" t="inlineStr"/>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>https://www.upstart.com/blog</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr"/>
+      <c r="G853" t="inlineStr"/>
+      <c r="H853" t="inlineStr"/>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr"/>
+      <c r="G854" t="inlineStr"/>
+      <c r="H854" t="inlineStr"/>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1858985/000185991226000006/xslF345X06/form4-08172026_120818.xml</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Coppetti Caspar Felix (Executive Officer &amp; Co-CEO) BOUGHT 65,000 shares @ $30.67 ($1.99M) on 2026-08-14</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr"/>
+      <c r="G855" t="inlineStr"/>
+      <c r="H855" t="inlineStr"/>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1858985/000185988926000006/xslF345X06/form4-08172026_120801.xml</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Bernhard Olivier (Executive Officer) BOUGHT 65,000 shares @ $30.67 ($1.99M) on 2026-08-14</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr"/>
+      <c r="G856" t="inlineStr"/>
+      <c r="H856" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H856"/>
+  <dimension ref="A1:H946"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -29894,9 +29894,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F842" t="inlineStr"/>
-      <c r="G842" t="inlineStr"/>
-      <c r="H842" t="inlineStr"/>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
@@ -29924,9 +29921,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F843" t="inlineStr"/>
-      <c r="G843" t="inlineStr"/>
-      <c r="H843" t="inlineStr"/>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
@@ -29954,9 +29948,6 @@
           <t>4 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F844" t="inlineStr"/>
-      <c r="G844" t="inlineStr"/>
-      <c r="H844" t="inlineStr"/>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
@@ -29984,9 +29975,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F845" t="inlineStr"/>
-      <c r="G845" t="inlineStr"/>
-      <c r="H845" t="inlineStr"/>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
@@ -30014,9 +30002,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F846" t="inlineStr"/>
-      <c r="G846" t="inlineStr"/>
-      <c r="H846" t="inlineStr"/>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
@@ -30044,9 +30029,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F847" t="inlineStr"/>
-      <c r="G847" t="inlineStr"/>
-      <c r="H847" t="inlineStr"/>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
@@ -30074,9 +30056,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F848" t="inlineStr"/>
-      <c r="G848" t="inlineStr"/>
-      <c r="H848" t="inlineStr"/>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
@@ -30104,9 +30083,6 @@
           <t>19 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F849" t="inlineStr"/>
-      <c r="G849" t="inlineStr"/>
-      <c r="H849" t="inlineStr"/>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
@@ -30134,9 +30110,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F850" t="inlineStr"/>
-      <c r="G850" t="inlineStr"/>
-      <c r="H850" t="inlineStr"/>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
@@ -30164,9 +30137,6 @@
           <t>5 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F851" t="inlineStr"/>
-      <c r="G851" t="inlineStr"/>
-      <c r="H851" t="inlineStr"/>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
@@ -30194,9 +30164,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F852" t="inlineStr"/>
-      <c r="G852" t="inlineStr"/>
-      <c r="H852" t="inlineStr"/>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
@@ -30224,9 +30191,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F853" t="inlineStr"/>
-      <c r="G853" t="inlineStr"/>
-      <c r="H853" t="inlineStr"/>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
@@ -30254,9 +30218,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F854" t="inlineStr"/>
-      <c r="G854" t="inlineStr"/>
-      <c r="H854" t="inlineStr"/>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -30284,9 +30245,6 @@
           <t>[ROUTINE] Insider trade — Coppetti Caspar Felix (Executive Officer &amp; Co-CEO) BOUGHT 65,000 shares @ $30.67 ($1.99M) on 2026-08-14</t>
         </is>
       </c>
-      <c r="F855" t="inlineStr"/>
-      <c r="G855" t="inlineStr"/>
-      <c r="H855" t="inlineStr"/>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
@@ -30314,9 +30272,2589 @@
           <t>[ROUTINE] Insider trade — Bernhard Olivier (Executive Officer) BOUGHT 65,000 shares @ $30.67 ($1.99M) on 2026-08-14</t>
         </is>
       </c>
-      <c r="F856" t="inlineStr"/>
-      <c r="G856" t="inlineStr"/>
-      <c r="H856" t="inlineStr"/>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1032975/000147522326000003/xslF345X06/form4-08172026_080820.xml</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Harnett Samantha (CHIEF LEGAL OFFICER) granted 15,247 Registered Shares on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Garmin Ltd.</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>https://newsroom.garmin.com</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1324424/000122520826007141/xslF345X06/doc4.xml</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Jacobson Craig A (Director) sold 3,133 shares @ $328.52 ($1.03M) on 2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>https://www.bookingholdings.com/careers</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1075531/000196430626000389/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Vanessa Ames Wittman (Officer) plans to sell 375 shares (~$79.1K) on/after 08/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000195917326006052/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Blecharczyk Nathan (Officer) plans to sell 13,615 shares (~$2.51M) on/after 08/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000192109426000889/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Morrow Rebecca (Officer) plans to sell 17,336 shares (~$90.1K) on/after 08/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000192109426000888/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Mohan Ajit (Officer) plans to sell 54,608 shares (~$283.8K) on/after 08/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000192109426000887/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Hott Douglas (Officer) plans to sell 131,884 shares (~$685.5K) on/after 08/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000192109426000886/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Briers Zachary M (Officer) plans to sell 136,504 shares (~$709.5K) on/after 08/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>LIF</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>LIF (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1581760/000158176026000146/xslF345X06/wk-form4_1786998322.xml</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Prober Charles J. (Director) sold 7,930 shares @ $48.59 ($385.3K) on 2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/news/</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1744489/000162828026057481/xslF345X06/wk-form4_1787004533.xml</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Brent Woodford (EVP, Control, Fin Plan &amp; Tax) sold 7,238 shares @ $105.31 ($762.2K) on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>https://www.livenationentertainment.com/careers</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1337634/000196858226000844/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Mark Streams (Officer, Director) plans to sell 334,746 shares (~$2.65M) on/after 08/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/946581/000214700726000007/xslSCHEDULE_13G_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form SCHEDULE 13G</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/946581/000195917326006066/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Sheresky Michael (Director) plans to sell 127 shares (~$31.1K) on/after 08/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/946581/000195917326006064/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Srinivasan LaVerne Evans (Director) plans to sell 362 shares (~$88.7K) on/after 08/17/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/896878/000162828026057506/xslF345X06/wk-form4_1787009130.xml</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hotz Lauren D (SVP, Chief Accounting Officer) granted 402 Restricted Stock Units (MSPP Purchased Award) on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/896878/000162828026057504/xslF345X06/wk-form4_1787009038.xml</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Cozzens Tyler Ralph (EVP, Gen. Counsel &amp; Corp. Sec.) granted 414 Restricted Stock Units (MSPP Purchased Award) on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/896878/000162828026057501/xslF345X06/wk-form4_1787008933.xml</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hilliard Caryl Lyn (EVP, People and Places) granted 528 Restricted Stock Units (MSPP Purchased Award) on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Paychex, Inc.</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/723531/000119312526353992/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Simmons Christopher C (VP, Controller &amp; Treasurer) 130 shares withheld for taxes (vest event) on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159787026000005/xslF345X06/wk-form4_1786996986.xml</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sarowitz Steven I (Director) sold 15,107 shares @ $151.65 ($2.29M) on 2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000195516026000003/xslF345X06/wk-form4_1786996920.xml</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Scutt Joshua (SVP Chief Revenue Officer) sold 118 shares @ $144.64 ($17.1K) on 2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr"/>
+      <c r="G896" t="inlineStr"/>
+      <c r="H896" t="inlineStr"/>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>GLBE</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Global-E Online Ltd.</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835963/000119312526353610/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Schlachet Amir (CEO) sold 81,556 shares @ $42.30 ($3.45M) on 2026-08-14</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr"/>
+      <c r="G897" t="inlineStr"/>
+      <c r="H897" t="inlineStr"/>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>GLBE</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Global-E Online Ltd.</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835963/000119312526353602/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Schlachet Amir (CEO) sold 100,000 shares @ $42.10 ($4.21M) on 2026-08-13</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr"/>
+      <c r="G898" t="inlineStr"/>
+      <c r="H898" t="inlineStr"/>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr"/>
+      <c r="G899" t="inlineStr"/>
+      <c r="H899" t="inlineStr"/>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>https://www.ebayinc.com/stories/news/</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr"/>
+      <c r="G900" t="inlineStr"/>
+      <c r="H900" t="inlineStr"/>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1370637/000196922326000914/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Blow Marla J (Director) plans to sell 300 shares (~$24.3K) on/after 08/17/2026</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr"/>
+      <c r="G901" t="inlineStr"/>
+      <c r="H901" t="inlineStr"/>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1370637/000196922326000910/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Buckley Merilee (Officer) plans to sell 405 shares (~$32.9K) on/after 08/17/2026</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr"/>
+      <c r="G902" t="inlineStr"/>
+      <c r="H902" t="inlineStr"/>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr"/>
+      <c r="G903" t="inlineStr"/>
+      <c r="H903" t="inlineStr"/>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000184970926000016/xslF345X06/form4-08172026_040801.xml</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Inukonda Ravi (CHIEF FINANCIAL OFFICER) sold 1,017 shares @ $213.67 ($217.3K) on 2026-08-13</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr"/>
+      <c r="G904" t="inlineStr"/>
+      <c r="H904" t="inlineStr"/>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr"/>
+      <c r="G905" t="inlineStr"/>
+      <c r="H905" t="inlineStr"/>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr"/>
+      <c r="G906" t="inlineStr"/>
+      <c r="H906" t="inlineStr"/>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000119312526354331/xslSCHEDULE_13D_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ active owner disclosure</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr"/>
+      <c r="G907" t="inlineStr"/>
+      <c r="H907" t="inlineStr"/>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000165168726000017/xslF345X06/wk-form4_1786997595.xml</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lisa Blackwood-Kapral (Chief Accounting Officer) 6,103 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr"/>
+      <c r="G908" t="inlineStr"/>
+      <c r="H908" t="inlineStr"/>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000199010626000019/xslF345X06/wk-form4_1786997522.xml</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Fong Morgan (Chief Legal Officer) 14,167 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr"/>
+      <c r="G909" t="inlineStr"/>
+      <c r="H909" t="inlineStr"/>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000202205026000009/xslF345X06/wk-form4_1786997211.xml</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Reuter Emily (CHIEF FINANCIAL OFFICER) sold 25,000 shares @ $50.01 ($1.25M) on 2026-08-13</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr"/>
+      <c r="G910" t="inlineStr"/>
+      <c r="H910" t="inlineStr"/>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000208293026000014/xslF345X06/wk-form4_1786997068.xml</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Rogers Chris (President and CEO) 43,807 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr"/>
+      <c r="G911" t="inlineStr"/>
+      <c r="H911" t="inlineStr"/>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/duolingo</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr"/>
+      <c r="G912" t="inlineStr"/>
+      <c r="H912" t="inlineStr"/>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000195004726008292/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Chen Stephen (Officer) plans to sell 1,024 shares (~$132.2K) on/after 08/17/2026</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr"/>
+      <c r="G913" t="inlineStr"/>
+      <c r="H913" t="inlineStr"/>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000195004726008291/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Glance Natalie (Officer) plans to sell 2,751 shares (~$355.2K) on/after 08/17/2026</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr"/>
+      <c r="G914" t="inlineStr"/>
+      <c r="H914" t="inlineStr"/>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000195004726008290/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Meese Robert (Officer) plans to sell 1,354 shares (~$174.8K) on/after 08/17/2026</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr"/>
+      <c r="G915" t="inlineStr"/>
+      <c r="H915" t="inlineStr"/>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>https://zillow.mediaroom.com</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr"/>
+      <c r="G916" t="inlineStr"/>
+      <c r="H916" t="inlineStr"/>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000162828026057477/xslF345X06/wk-form3_1787004248.xml</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>[ROUTINE] New insider — initial ownership statement</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr"/>
+      <c r="G917" t="inlineStr"/>
+      <c r="H917" t="inlineStr"/>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000162828026057471/xslF345X06/wk-form4_1787004012.xml</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Beitel David A. (Chief Technology Officer) sold 1,798 shares @ $34.24 ($61.6K) on 2026-08-13</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr"/>
+      <c r="G918" t="inlineStr"/>
+      <c r="H918" t="inlineStr"/>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000162828026057470/xslF345X06/wk-form4_1787003968.xml</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Rock Jennifer (Chief Accounting Officer) sold 990 shares @ $34.24 ($33.9K) on 2026-08-13</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr"/>
+      <c r="G919" t="inlineStr"/>
+      <c r="H919" t="inlineStr"/>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000162828026057468/xslF345X06/wk-form4_1787003923.xml</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Samuelson Errol G (Chief Industry Dev. Officer) sold 3,154 shares @ $34.24 ($108.0K) on 2026-08-13</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr"/>
+      <c r="G920" t="inlineStr"/>
+      <c r="H920" t="inlineStr"/>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000162828026057467/xslF345X06/wk-form4_1787003880.xml</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Spaulding Dan (Chief People Officer) sold 5,135 shares @ $34.94 ($179.4K) on 2026-08-13</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr"/>
+      <c r="G921" t="inlineStr"/>
+      <c r="H921" t="inlineStr"/>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000162828026057466/xslF345X06/wk-form4_1787003834.xml</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hofmann Jeremy (COO &amp; CFO) sold 9,171 shares @ $34.20 ($313.7K) on 2026-08-13</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr"/>
+      <c r="G922" t="inlineStr"/>
+      <c r="H922" t="inlineStr"/>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000162828026057465/xslF345X06/wk-form4_1787003789.xml</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Wacksman Jeremy (Chief Executive Officer) sold 15,125 shares @ $34.20 ($517.3K) on 2026-08-13</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr"/>
+      <c r="G923" t="inlineStr"/>
+      <c r="H923" t="inlineStr"/>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000192109426000878/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Wacksman Jeremy (Officer) plans to sell 9,339 shares (~$319.2K) on/after 08/17/2026</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr"/>
+      <c r="G924" t="inlineStr"/>
+      <c r="H924" t="inlineStr"/>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000192109426000877/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Hofmann Jeremy (Officer) plans to sell 5,661 shares (~$193.5K) on/after 08/17/2026</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr"/>
+      <c r="G925" t="inlineStr"/>
+      <c r="H925" t="inlineStr"/>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>RKT</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Rocket Companies Inc.</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1805284/000180528426000087/xslF345X06/wk-form4_1786997480.xml</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Watterson Sarah (Director) granted 14,566 shares on 2026-08-17</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr"/>
+      <c r="G926" t="inlineStr"/>
+      <c r="H926" t="inlineStr"/>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>RKT</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>Rocket Companies Inc.</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1805284/000180528426000086/xslF345X06/wk-form3_1786997383.xml</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>[ROUTINE] New insider — initial ownership statement</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr"/>
+      <c r="G927" t="inlineStr"/>
+      <c r="H927" t="inlineStr"/>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>RKT</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Rocket Companies Inc.</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1805284/000162828026057366/rkt-20260817.htm</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr"/>
+      <c r="G928" t="inlineStr"/>
+      <c r="H928" t="inlineStr"/>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr"/>
+      <c r="G929" t="inlineStr"/>
+      <c r="H929" t="inlineStr"/>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000183740026000014/xslF345X06/wk-form4_1787004565.xml</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Trigg William Shane (Chief Executive Officer) sold 2,057 shares @ $205.00 ($421.7K) on 2026-08-14</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr"/>
+      <c r="G930" t="inlineStr"/>
+      <c r="H930" t="inlineStr"/>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>https://investors.block.xyz</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr"/>
+      <c r="G931" t="inlineStr"/>
+      <c r="H931" t="inlineStr"/>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726008270/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$489.8K) on/after 08/17/2026</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr"/>
+      <c r="G932" t="inlineStr"/>
+      <c r="H932" t="inlineStr"/>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>PayPal Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1633917/000189608626000010/xslF345X06/edgardoc.xml</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Kereere Suzan (President, Global Markets) 4,341 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr"/>
+      <c r="G933" t="inlineStr"/>
+      <c r="H933" t="inlineStr"/>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr"/>
+      <c r="G934" t="inlineStr"/>
+      <c r="H934" t="inlineStr"/>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>https://dave.com/careers</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr"/>
+      <c r="G935" t="inlineStr"/>
+      <c r="H935" t="inlineStr"/>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr"/>
+      <c r="G936" t="inlineStr"/>
+      <c r="H936" t="inlineStr"/>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>KLAR</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Klarna Group plc</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>https://investors.klarna.com</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr"/>
+      <c r="G937" t="inlineStr"/>
+      <c r="H937" t="inlineStr"/>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr"/>
+      <c r="G938" t="inlineStr"/>
+      <c r="H938" t="inlineStr"/>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000178387926000128/xslF345X06/wk-form4_1787000835.xml</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Robinhood Markets, Inc. (10%+ owner) sold 15,310 shares @ $28.65 ($438.6K) on 2026-08-13</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr"/>
+      <c r="G939" t="inlineStr"/>
+      <c r="H939" t="inlineStr"/>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>https://www.upstart.com/blog</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr"/>
+      <c r="G940" t="inlineStr"/>
+      <c r="H940" t="inlineStr"/>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1647639/000192109426000892/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Datta Sanjay (Officer) plans to sell 2,033 shares (~$59.7K) on/after 08/17/2026</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr"/>
+      <c r="G941" t="inlineStr"/>
+      <c r="H941" t="inlineStr"/>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1647639/000192109426000891/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Darling Scott (Officer) plans to sell 814 shares (~$23.9K) on/after 08/17/2026</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr"/>
+      <c r="G942" t="inlineStr"/>
+      <c r="H942" t="inlineStr"/>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1647639/000192109426000890/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Blankmeyer Andrea (Officer) plans to sell 7,175 shares (~$210.6K) on/after 08/17/2026</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr"/>
+      <c r="G943" t="inlineStr"/>
+      <c r="H943" t="inlineStr"/>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>WSM</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>Williams-Sonoma Inc.</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>https://www.williams-sonoma.com/</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr"/>
+      <c r="G944" t="inlineStr"/>
+      <c r="H944" t="inlineStr"/>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr"/>
+      <c r="G945" t="inlineStr"/>
+      <c r="H945" t="inlineStr"/>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1858985/000185988926000006/xslF345X06/form4-08172026_120801.xml</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Bernhard Olivier (Executive Officer) BOUGHT 65,000 shares @ $30.67 ($1.99M) on 2026-08-14</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr"/>
+      <c r="G946" t="inlineStr"/>
+      <c r="H946" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H946"/>
+  <dimension ref="A1:H1063"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -31352,9 +31352,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F896" t="inlineStr"/>
-      <c r="G896" t="inlineStr"/>
-      <c r="H896" t="inlineStr"/>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
@@ -31382,9 +31379,6 @@
           <t>[ROUTINE] Insider trade — Schlachet Amir (CEO) sold 81,556 shares @ $42.30 ($3.45M) on 2026-08-14</t>
         </is>
       </c>
-      <c r="F897" t="inlineStr"/>
-      <c r="G897" t="inlineStr"/>
-      <c r="H897" t="inlineStr"/>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
@@ -31412,9 +31406,6 @@
           <t>[ROUTINE] Insider trade — Schlachet Amir (CEO) sold 100,000 shares @ $42.10 ($4.21M) on 2026-08-13</t>
         </is>
       </c>
-      <c r="F898" t="inlineStr"/>
-      <c r="G898" t="inlineStr"/>
-      <c r="H898" t="inlineStr"/>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
@@ -31442,9 +31433,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F899" t="inlineStr"/>
-      <c r="G899" t="inlineStr"/>
-      <c r="H899" t="inlineStr"/>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
@@ -31472,9 +31460,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F900" t="inlineStr"/>
-      <c r="G900" t="inlineStr"/>
-      <c r="H900" t="inlineStr"/>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
@@ -31502,9 +31487,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Blow Marla J (Director) plans to sell 300 shares (~$24.3K) on/after 08/17/2026</t>
         </is>
       </c>
-      <c r="F901" t="inlineStr"/>
-      <c r="G901" t="inlineStr"/>
-      <c r="H901" t="inlineStr"/>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
@@ -31532,9 +31514,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Buckley Merilee (Officer) plans to sell 405 shares (~$32.9K) on/after 08/17/2026</t>
         </is>
       </c>
-      <c r="F902" t="inlineStr"/>
-      <c r="G902" t="inlineStr"/>
-      <c r="H902" t="inlineStr"/>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
@@ -31562,9 +31541,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F903" t="inlineStr"/>
-      <c r="G903" t="inlineStr"/>
-      <c r="H903" t="inlineStr"/>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
@@ -31592,9 +31568,6 @@
           <t>[ROUTINE] Insider trade — Inukonda Ravi (CHIEF FINANCIAL OFFICER) sold 1,017 shares @ $213.67 ($217.3K) on 2026-08-13</t>
         </is>
       </c>
-      <c r="F904" t="inlineStr"/>
-      <c r="G904" t="inlineStr"/>
-      <c r="H904" t="inlineStr"/>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
@@ -31622,9 +31595,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F905" t="inlineStr"/>
-      <c r="G905" t="inlineStr"/>
-      <c r="H905" t="inlineStr"/>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
@@ -31652,9 +31622,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F906" t="inlineStr"/>
-      <c r="G906" t="inlineStr"/>
-      <c r="H906" t="inlineStr"/>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
@@ -31682,9 +31649,6 @@
           <t>[MATERIAL] Update to 5%+ active owner disclosure</t>
         </is>
       </c>
-      <c r="F907" t="inlineStr"/>
-      <c r="G907" t="inlineStr"/>
-      <c r="H907" t="inlineStr"/>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
@@ -31712,9 +31676,6 @@
           <t>[ROUTINE] Insider trade — Lisa Blackwood-Kapral (Chief Accounting Officer) 6,103 shares withheld for taxes (vest event) on 2026-08-15</t>
         </is>
       </c>
-      <c r="F908" t="inlineStr"/>
-      <c r="G908" t="inlineStr"/>
-      <c r="H908" t="inlineStr"/>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
@@ -31742,9 +31703,6 @@
           <t>[ROUTINE] Insider trade — Fong Morgan (Chief Legal Officer) 14,167 shares withheld for taxes (vest event) on 2026-08-15</t>
         </is>
       </c>
-      <c r="F909" t="inlineStr"/>
-      <c r="G909" t="inlineStr"/>
-      <c r="H909" t="inlineStr"/>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
@@ -31772,9 +31730,6 @@
           <t>[ROUTINE] Insider trade — Reuter Emily (CHIEF FINANCIAL OFFICER) sold 25,000 shares @ $50.01 ($1.25M) on 2026-08-13</t>
         </is>
       </c>
-      <c r="F910" t="inlineStr"/>
-      <c r="G910" t="inlineStr"/>
-      <c r="H910" t="inlineStr"/>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
@@ -31802,9 +31757,6 @@
           <t>[ROUTINE] Insider trade — Rogers Chris (President and CEO) 43,807 shares withheld for taxes (vest event) on 2026-08-15</t>
         </is>
       </c>
-      <c r="F911" t="inlineStr"/>
-      <c r="G911" t="inlineStr"/>
-      <c r="H911" t="inlineStr"/>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
@@ -31832,9 +31784,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F912" t="inlineStr"/>
-      <c r="G912" t="inlineStr"/>
-      <c r="H912" t="inlineStr"/>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
@@ -31862,9 +31811,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Chen Stephen (Officer) plans to sell 1,024 shares (~$132.2K) on/after 08/17/2026</t>
         </is>
       </c>
-      <c r="F913" t="inlineStr"/>
-      <c r="G913" t="inlineStr"/>
-      <c r="H913" t="inlineStr"/>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
@@ -31892,9 +31838,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Glance Natalie (Officer) plans to sell 2,751 shares (~$355.2K) on/after 08/17/2026</t>
         </is>
       </c>
-      <c r="F914" t="inlineStr"/>
-      <c r="G914" t="inlineStr"/>
-      <c r="H914" t="inlineStr"/>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
@@ -31922,9 +31865,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Meese Robert (Officer) plans to sell 1,354 shares (~$174.8K) on/after 08/17/2026</t>
         </is>
       </c>
-      <c r="F915" t="inlineStr"/>
-      <c r="G915" t="inlineStr"/>
-      <c r="H915" t="inlineStr"/>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
@@ -31952,9 +31892,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F916" t="inlineStr"/>
-      <c r="G916" t="inlineStr"/>
-      <c r="H916" t="inlineStr"/>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
@@ -31982,9 +31919,6 @@
           <t>[ROUTINE] New insider — initial ownership statement</t>
         </is>
       </c>
-      <c r="F917" t="inlineStr"/>
-      <c r="G917" t="inlineStr"/>
-      <c r="H917" t="inlineStr"/>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
@@ -32012,9 +31946,6 @@
           <t>[ROUTINE] Insider trade — Beitel David A. (Chief Technology Officer) sold 1,798 shares @ $34.24 ($61.6K) on 2026-08-13</t>
         </is>
       </c>
-      <c r="F918" t="inlineStr"/>
-      <c r="G918" t="inlineStr"/>
-      <c r="H918" t="inlineStr"/>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
@@ -32042,9 +31973,6 @@
           <t>[ROUTINE] Insider trade — Rock Jennifer (Chief Accounting Officer) sold 990 shares @ $34.24 ($33.9K) on 2026-08-13</t>
         </is>
       </c>
-      <c r="F919" t="inlineStr"/>
-      <c r="G919" t="inlineStr"/>
-      <c r="H919" t="inlineStr"/>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
@@ -32072,9 +32000,6 @@
           <t>[ROUTINE] Insider trade — Samuelson Errol G (Chief Industry Dev. Officer) sold 3,154 shares @ $34.24 ($108.0K) on 2026-08-13</t>
         </is>
       </c>
-      <c r="F920" t="inlineStr"/>
-      <c r="G920" t="inlineStr"/>
-      <c r="H920" t="inlineStr"/>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
@@ -32102,9 +32027,6 @@
           <t>[ROUTINE] Insider trade — Spaulding Dan (Chief People Officer) sold 5,135 shares @ $34.94 ($179.4K) on 2026-08-13</t>
         </is>
       </c>
-      <c r="F921" t="inlineStr"/>
-      <c r="G921" t="inlineStr"/>
-      <c r="H921" t="inlineStr"/>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
@@ -32132,9 +32054,6 @@
           <t>[ROUTINE] Insider trade — Hofmann Jeremy (COO &amp; CFO) sold 9,171 shares @ $34.20 ($313.7K) on 2026-08-13</t>
         </is>
       </c>
-      <c r="F922" t="inlineStr"/>
-      <c r="G922" t="inlineStr"/>
-      <c r="H922" t="inlineStr"/>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
@@ -32162,9 +32081,6 @@
           <t>[ROUTINE] Insider trade — Wacksman Jeremy (Chief Executive Officer) sold 15,125 shares @ $34.20 ($517.3K) on 2026-08-13</t>
         </is>
       </c>
-      <c r="F923" t="inlineStr"/>
-      <c r="G923" t="inlineStr"/>
-      <c r="H923" t="inlineStr"/>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
@@ -32192,9 +32108,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Wacksman Jeremy (Officer) plans to sell 9,339 shares (~$319.2K) on/after 08/17/2026</t>
         </is>
       </c>
-      <c r="F924" t="inlineStr"/>
-      <c r="G924" t="inlineStr"/>
-      <c r="H924" t="inlineStr"/>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
@@ -32222,9 +32135,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Hofmann Jeremy (Officer) plans to sell 5,661 shares (~$193.5K) on/after 08/17/2026</t>
         </is>
       </c>
-      <c r="F925" t="inlineStr"/>
-      <c r="G925" t="inlineStr"/>
-      <c r="H925" t="inlineStr"/>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
@@ -32252,9 +32162,6 @@
           <t>[ROUTINE] Insider trade — Watterson Sarah (Director) granted 14,566 shares on 2026-08-17</t>
         </is>
       </c>
-      <c r="F926" t="inlineStr"/>
-      <c r="G926" t="inlineStr"/>
-      <c r="H926" t="inlineStr"/>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
@@ -32282,9 +32189,6 @@
           <t>[ROUTINE] New insider — initial ownership statement</t>
         </is>
       </c>
-      <c r="F927" t="inlineStr"/>
-      <c r="G927" t="inlineStr"/>
-      <c r="H927" t="inlineStr"/>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
@@ -32312,9 +32216,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F928" t="inlineStr"/>
-      <c r="G928" t="inlineStr"/>
-      <c r="H928" t="inlineStr"/>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
@@ -32342,9 +32243,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F929" t="inlineStr"/>
-      <c r="G929" t="inlineStr"/>
-      <c r="H929" t="inlineStr"/>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
@@ -32372,9 +32270,6 @@
           <t>[ROUTINE] Insider trade — Trigg William Shane (Chief Executive Officer) sold 2,057 shares @ $205.00 ($421.7K) on 2026-08-14</t>
         </is>
       </c>
-      <c r="F930" t="inlineStr"/>
-      <c r="G930" t="inlineStr"/>
-      <c r="H930" t="inlineStr"/>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
@@ -32402,9 +32297,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F931" t="inlineStr"/>
-      <c r="G931" t="inlineStr"/>
-      <c r="H931" t="inlineStr"/>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
@@ -32432,9 +32324,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$489.8K) on/after 08/17/2026</t>
         </is>
       </c>
-      <c r="F932" t="inlineStr"/>
-      <c r="G932" t="inlineStr"/>
-      <c r="H932" t="inlineStr"/>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
@@ -32462,9 +32351,6 @@
           <t>[ROUTINE] Insider trade — Kereere Suzan (President, Global Markets) 4,341 shares withheld for taxes (vest event) on 2026-08-15</t>
         </is>
       </c>
-      <c r="F933" t="inlineStr"/>
-      <c r="G933" t="inlineStr"/>
-      <c r="H933" t="inlineStr"/>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
@@ -32492,9 +32378,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F934" t="inlineStr"/>
-      <c r="G934" t="inlineStr"/>
-      <c r="H934" t="inlineStr"/>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
@@ -32522,9 +32405,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F935" t="inlineStr"/>
-      <c r="G935" t="inlineStr"/>
-      <c r="H935" t="inlineStr"/>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
@@ -32552,9 +32432,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F936" t="inlineStr"/>
-      <c r="G936" t="inlineStr"/>
-      <c r="H936" t="inlineStr"/>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
@@ -32582,9 +32459,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F937" t="inlineStr"/>
-      <c r="G937" t="inlineStr"/>
-      <c r="H937" t="inlineStr"/>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
@@ -32612,9 +32486,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F938" t="inlineStr"/>
-      <c r="G938" t="inlineStr"/>
-      <c r="H938" t="inlineStr"/>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
@@ -32642,9 +32513,6 @@
           <t>[ROUTINE] Insider trade — Robinhood Markets, Inc. (10%+ owner) sold 15,310 shares @ $28.65 ($438.6K) on 2026-08-13</t>
         </is>
       </c>
-      <c r="F939" t="inlineStr"/>
-      <c r="G939" t="inlineStr"/>
-      <c r="H939" t="inlineStr"/>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
@@ -32672,9 +32540,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F940" t="inlineStr"/>
-      <c r="G940" t="inlineStr"/>
-      <c r="H940" t="inlineStr"/>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
@@ -32702,9 +32567,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Datta Sanjay (Officer) plans to sell 2,033 shares (~$59.7K) on/after 08/17/2026</t>
         </is>
       </c>
-      <c r="F941" t="inlineStr"/>
-      <c r="G941" t="inlineStr"/>
-      <c r="H941" t="inlineStr"/>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
@@ -32732,9 +32594,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Darling Scott (Officer) plans to sell 814 shares (~$23.9K) on/after 08/17/2026</t>
         </is>
       </c>
-      <c r="F942" t="inlineStr"/>
-      <c r="G942" t="inlineStr"/>
-      <c r="H942" t="inlineStr"/>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
@@ -32762,9 +32621,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Blankmeyer Andrea (Officer) plans to sell 7,175 shares (~$210.6K) on/after 08/17/2026</t>
         </is>
       </c>
-      <c r="F943" t="inlineStr"/>
-      <c r="G943" t="inlineStr"/>
-      <c r="H943" t="inlineStr"/>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
@@ -32792,9 +32648,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F944" t="inlineStr"/>
-      <c r="G944" t="inlineStr"/>
-      <c r="H944" t="inlineStr"/>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
@@ -32822,9 +32675,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F945" t="inlineStr"/>
-      <c r="G945" t="inlineStr"/>
-      <c r="H945" t="inlineStr"/>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
@@ -32852,9 +32702,3270 @@
           <t>[ROUTINE] Insider trade — Bernhard Olivier (Executive Officer) BOUGHT 65,000 shares @ $30.67 ($1.99M) on 2026-08-14</t>
         </is>
       </c>
-      <c r="F946" t="inlineStr"/>
-      <c r="G946" t="inlineStr"/>
-      <c r="H946" t="inlineStr"/>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Garmin Ltd.</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1121788/000196922326000923/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Cheng-Wei Wang (Officer) plans to sell 9,941 shares (~$2.98M) on/after 08/18/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000211186726000012/xslF345X06/primarydocument.xml</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Krishnamurthy Balaji (A) (Chief Financial Officer) 2,247 shares withheld for taxes (vest event) on 2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000207176126000010/xslF345X06/primarydocument.xml</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Macdonald Andrew (See Remarks) 5,684 shares withheld for taxes (vest event) on 2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000162620126000019/xslF345X06/primarydocument.xml</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — West Tony (See Remarks) 3,570 shares withheld for taxes (vest event) on 2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000177529726000011/xslF345X06/primarydocument.xml</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hazelbaker Jill (See Remarks) 4,626 shares withheld for taxes (vest event) on 2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000152532126000009/xslF345X06/primarydocument.xml</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Ceremony Glen (See Remarks) 3,278 shares withheld for taxes (vest event) on 2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1324424/000195004726008363/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Soliday Lance (Officer) plans to sell 2,810 shares (~$909.5K) on/after 08/18/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1324424/000122520826007169/xslF345X06/doc4.xml</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Gorin Ariane (Chief Executive Officer) 6,660 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1324424/000122520826007168/xslF345X06/doc4.xml</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Soliday Lance A (SVP &amp; Chief Accounting Officer) 481 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1324424/000122520826007167/xslF345X06/doc4.xml</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Diller Barry (Chairman &amp; Sr. Executive) 4,528 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1324424/000122520826007166/xslF345X06/doc4.xml</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Andersen Derek (Chief Financial Officer) 3,624 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1324424/000122520826007165/xslF345X06/doc4.xml</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Dara Khosrowshahi (Director) gift: 15,000 shares on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1324424/000122520826007164/xslF345X06/doc4.xml</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Dzielak Robert J (Chief Legal Officer &amp; Sec'y) sold 2,000 shares @ $330.50 ($661.0K) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1075531/000121461226000007/xslF345X06/form4-08182026_080826.xml</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Peter J Millones (EXECUTIVE VP, GENERAL COUNSEL) sold 50,050 shares @ $207.59 ($10.39M) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1075531/000122926526000022/xslF345X06/form4-08182026_080845.xml</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Vanessa Ames Wittman (Director) sold 375 shares @ $211.00 ($79.1K) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>Choice Hotels International, Inc.</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1046311/000119312526355202/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Abdalla Noha (Chief Marketing Officer) 503 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326012611/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Powell Dina H. (President and Vice Chairman) 3,518 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326012610/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — White Dana (Director) option exercise: 110 shares on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326012609/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Arnold John Douglas (Director) option exercise: 167 shares on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326012608/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Elkann John (Director) 8 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326012607/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Susan J Li (Chief Financial Officer) sold 2,127 shares @ $689.85 ($1.47M) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326012606/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Anderson Aaron (Chief Accounting Officer) 1,216 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326012605/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Cox Christopher K (Chief Product Officer) 8,127 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326012604/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Collison Patrick (Director) option exercise: 103 shares on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326012603/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Bosworth Andrew (Chief Technology Officer) 8,127 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326012602/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Mahoney Curtis J. (Chief Legal Officer) 2,359 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326012600/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Songhurst Charles (Director) 14 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326012599/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Olivan Javier (Chief Operating Officer) 7,744 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000192109426000900/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Bosworth Andrew (Officer) plans to sell 7,848 shares (~$4.38M) on/after 08/18/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000192109426000899/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Susan J Li (Officer) plans to sell 9,196 shares (~$5.06M) on/after 08/18/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000192109426000898/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Mahoney Curtis J. (Officer) plans to sell 1,559 shares (~$869.9K) on/after 08/18/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>https://blog.google</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000192109426000896/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Silbermann Benjamin (Director) plans to sell 46,875 shares (~$1.10M) on/after 08/18/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>https://investor.redditinc.com</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1713445/000182701126000033/xslF345X06/wk-form4_1787087348.xml</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Huffman Steve Ladd (CEO &amp; President) sold 18,000 shares @ $178.16 ($3.21M) on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1713445/000166365126000016/xslF345X06/wk-form4_1787087222.xml</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Wong Jennifer L. (Chief Operating Officer) sold 75,000 shares @ $178.55 ($13.39M) on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1639920/000114036126033570/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Jenkins Dustee (Chief Public Affairs Officer) sold 3,810 shares @ $512.92 ($1.95M) on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>LIF</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>LIF (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1581760/000195917326006180/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Hulls Chris (Director) plans to sell 250,000 shares (~$11.71M) on/after 08/18/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/news/</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000162828026057765/xslF345X06/wk-form4_1787088175.xml</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Tomsic Steven (Chief Financial Officer) 40,020 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000162828026057764/xslF345X06/wk-form4_1787088162.xml</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Ciongoli Adam G. (Chief Legal and Policy Officer) 25,052 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000162828026057763/xslF345X06/wk-form4_1787088150.xml</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — John Nallen (President, COO) 65,864 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000162828026057762/xslF345X06/wk-form4_1787088137.xml</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lachlan K Murdoch (Executive Chair, CEO) 142,947 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000162828026057761/xslF345X06/wk-form4_1787088118.xml</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Keith Rupert Murdoch (Insider) 19,447 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>https://www.livenationentertainment.com/careers</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1337634/000196858226000857/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Constance P. James (Officer) plans to sell 116,644 shares (~$830.5K) on/after 08/18/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1337634/000196858226000854/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Scott Michael Fitzgerald (Officer) plans to sell 84,970 shares (~$597.3K) on/after 08/18/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/946581/000094658126000075/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Siminoff Ellen F (Director) sold 334 shares @ $242.34 ($80.9K) on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/946581/000094658126000073/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Srinivasan LaVerne Evans (Director) sold 362 shares @ $245.01 ($88.7K) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/946581/000094658126000071/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sheresky Michael (Director) sold 127 shares @ $245.01 ($31.1K) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>https://mediacenter.adp.com</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000195004726008335/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Rost Nicholas (Officer) plans to sell 520 shares (~$75.6K) on/after 08/18/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000134092226000002/xslF345X06/wk-form4_1787083491.xml</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Conway Craig (Director) granted 2,207 Common Stock, par value $0.001 on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000098/xslF345X06/wk-form4_1787083449.xml</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Robinson Kenneth B. (Director) granted 2,207 Common Stock, par value $0.001 on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000097/xslF345X06/wk-form4_1787083442.xml</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Glenn Ryan (Chief Financial Officer) granted 71,034 Common Stock, par value $0.001 on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000096/xslF345X06/wk-form4_1787083436.xml</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — King Melissa Ann (SVP Product and Technology) granted 37,977 Common Stock, par value $0.001 on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000095/xslF345X06/wk-form4_1787083428.xml</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Breard Linda M. (Director) granted 2,207 Common Stock, par value $0.001 on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000094/xslF345X06/wk-form4_1787083423.xml</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Williams Toby J. (President and CEO) sold 12,000 shares @ $148.52 ($1.78M) on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000093/xslF345X06/wk-form4_1787083415.xml</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Breen Virginia G (Director) granted 2,207 Common Stock, par value $0.001 on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000092/xslF345X06/wk-form4_1787083409.xml</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Scutt Joshua (SVP Chief Revenue Officer) granted 45,064 Common Stock, par value $0.001 on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000091/xslF345X06/wk-form4_1787083404.xml</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Rost Nicholas (VP CAO &amp; Treasurer) granted 7,981 Common Stock, par value $0.001 on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000090/xslF345X06/wk-form4_1787083399.xml</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Ronald V Waters (Director) granted 2,207 Common Stock, par value $0.001 on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000089/xslF345X06/wk-form4_1787083393.xml</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Cappotelli Andrew (Sr Vice President Operations) granted 34,585 Common Stock, par value $0.001 on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000088/xslF345X06/wk-form4_1787083387.xml</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Pederson Robin Le (Director) granted 2,207 Common Stock, par value $0.001 on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000087/xslF345X06/wk-form4_1787083381.xml</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Beauchamp Steven R (Executive Chairman) sold 15,000 shares @ $148.52 ($2.23M) on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000086/xslF345X06/wk-form4_1787083374.xml</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sarowitz Steven I (Director) sold 586 shares @ $151.12 ($88.6K) on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr"/>
+      <c r="G1029" t="inlineStr"/>
+      <c r="H1029" t="inlineStr"/>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>GLBE</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Global-E Online Ltd.</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835963/000119312526355383/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Debbi Nir (President) sold 14,582 shares @ $41.18 ($600.5K) on 2026-08-17</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr"/>
+      <c r="G1030" t="inlineStr"/>
+      <c r="H1030" t="inlineStr"/>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr"/>
+      <c r="G1031" t="inlineStr"/>
+      <c r="H1031" t="inlineStr"/>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>https://www.ebayinc.com/stories/news/</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr"/>
+      <c r="G1032" t="inlineStr"/>
+      <c r="H1032" t="inlineStr"/>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065088/000106508826000186/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Samantha Wellington (SVP, Chief Legal Officer) 970 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr"/>
+      <c r="G1033" t="inlineStr"/>
+      <c r="H1033" t="inlineStr"/>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065088/000106508826000184/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sweetnam Jordan Douglas Bradley (SVP, Chief Commercial Officer) 2,294 shares withheld for taxes (vest event) on 2026-08-15</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr"/>
+      <c r="G1034" t="inlineStr"/>
+      <c r="H1034" t="inlineStr"/>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065088/000195004726008333/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Sweetnam Jordan (Officer) plans to sell 1,014 shares (~$102.4K) on/after 08/18/2026</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr"/>
+      <c r="G1035" t="inlineStr"/>
+      <c r="H1035" t="inlineStr"/>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr"/>
+      <c r="G1036" t="inlineStr"/>
+      <c r="H1036" t="inlineStr"/>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr"/>
+      <c r="G1037" t="inlineStr"/>
+      <c r="H1037" t="inlineStr"/>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr"/>
+      <c r="G1038" t="inlineStr"/>
+      <c r="H1038" t="inlineStr"/>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/duolingo</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr"/>
+      <c r="G1039" t="inlineStr"/>
+      <c r="H1039" t="inlineStr"/>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>https://blog.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr"/>
+      <c r="G1040" t="inlineStr"/>
+      <c r="H1040" t="inlineStr"/>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000162828026057818/duol-20260818.htm</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr"/>
+      <c r="G1041" t="inlineStr"/>
+      <c r="H1041" t="inlineStr"/>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000195004726008328/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Glance Natalie (Officer) plans to sell 1,539 shares (~$200.3K) on/after 08/18/2026</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr"/>
+      <c r="G1042" t="inlineStr"/>
+      <c r="H1042" t="inlineStr"/>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/891103/000195004726008312/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Hosseini Hesam (Officer) plans to sell 2,753 shares (~$107.3K) on/after 08/18/2026</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr"/>
+      <c r="G1043" t="inlineStr"/>
+      <c r="H1043" t="inlineStr"/>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr"/>
+      <c r="G1044" t="inlineStr"/>
+      <c r="H1044" t="inlineStr"/>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000093833326000020/xslF345X06/form4-08182026_110844.xml</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Maurice J Duca (10%+ owner) sold 5,600 shares @ $195.89 ($1.10M) on 2026-08-17</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr"/>
+      <c r="G1045" t="inlineStr"/>
+      <c r="H1045" t="inlineStr"/>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000093833326000019/xslF345X06/form4-08182026_110848.xml</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Maurice J Duca (10%+ owner) sold 15,800 shares @ $200.11 ($3.16M) on 2026-08-14</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr"/>
+      <c r="G1046" t="inlineStr"/>
+      <c r="H1046" t="inlineStr"/>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000190875126000006/xslF345X06/wk-form4a_1787093446.xml</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 4/A</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr"/>
+      <c r="G1047" t="inlineStr"/>
+      <c r="H1047" t="inlineStr"/>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000215038726000004/xslF345X06/wk-form4a_1787093062.xml</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 4/A</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr"/>
+      <c r="G1048" t="inlineStr"/>
+      <c r="H1048" t="inlineStr"/>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000190875126000004/xslF345X06/wk-form3a_1787092697.xml</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 3/A</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr"/>
+      <c r="G1049" t="inlineStr"/>
+      <c r="H1049" t="inlineStr"/>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000215038726000002/xslF345X06/wk-form3a_1787092184.xml</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 3/A</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr"/>
+      <c r="G1050" t="inlineStr"/>
+      <c r="H1050" t="inlineStr"/>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726008345/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$475.0K) on/after 08/18/2026</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr"/>
+      <c r="G1051" t="inlineStr"/>
+      <c r="H1051" t="inlineStr"/>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>PayPal Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1633917/000195004726008332/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Kereere Suzan (Officer) plans to sell 4,162 shares (~$251.7K) on/after 08/18/2026</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr"/>
+      <c r="G1052" t="inlineStr"/>
+      <c r="H1052" t="inlineStr"/>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>https://careers.toasttab.com/jobs?gh_jid=7960104</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>New senior role: Regional Vice President, Sales</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr"/>
+      <c r="G1053" t="inlineStr"/>
+      <c r="H1053" t="inlineStr"/>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>13 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr"/>
+      <c r="G1054" t="inlineStr"/>
+      <c r="H1054" t="inlineStr"/>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>Sezzle Inc.</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1662991/000166299126000144/sezl-20260812.htm</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr"/>
+      <c r="G1055" t="inlineStr"/>
+      <c r="H1055" t="inlineStr"/>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/7894014003</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>New senior role: Vice President, People Business Partner &amp; Employee Relations</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr"/>
+      <c r="G1056" t="inlineStr"/>
+      <c r="H1056" t="inlineStr"/>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>6 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr"/>
+      <c r="G1057" t="inlineStr"/>
+      <c r="H1057" t="inlineStr"/>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>https://www.affirm.com/terms</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr"/>
+      <c r="G1058" t="inlineStr"/>
+      <c r="H1058" t="inlineStr"/>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>https://www.affirm.com/business</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr"/>
+      <c r="G1059" t="inlineStr"/>
+      <c r="H1059" t="inlineStr"/>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>KLAR</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Klarna Group plc</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2003292/000162828026057573/form6-kxklarnagroupplcxh126.htm</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 6-K</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr"/>
+      <c r="G1060" t="inlineStr"/>
+      <c r="H1060" t="inlineStr"/>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>4 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr"/>
+      <c r="G1061" t="inlineStr"/>
+      <c r="H1061" t="inlineStr"/>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000187091426000023/xslF345X06/wk-form4_1787085591.xml</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Bhatt Baiju (Director) sold 50,317 shares @ $96.80 ($4.87M) on 2026-08-14</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr"/>
+      <c r="G1062" t="inlineStr"/>
+      <c r="H1062" t="inlineStr"/>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr"/>
+      <c r="G1063" t="inlineStr"/>
+      <c r="H1063" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1063"/>
+  <dimension ref="A1:H1170"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -34943,9 +34943,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1029" t="inlineStr"/>
-      <c r="G1029" t="inlineStr"/>
-      <c r="H1029" t="inlineStr"/>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
@@ -34973,9 +34970,6 @@
           <t>[ROUTINE] Insider trade — Debbi Nir (President) sold 14,582 shares @ $41.18 ($600.5K) on 2026-08-17</t>
         </is>
       </c>
-      <c r="F1030" t="inlineStr"/>
-      <c r="G1030" t="inlineStr"/>
-      <c r="H1030" t="inlineStr"/>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
@@ -35003,9 +34997,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F1031" t="inlineStr"/>
-      <c r="G1031" t="inlineStr"/>
-      <c r="H1031" t="inlineStr"/>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
@@ -35033,9 +35024,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1032" t="inlineStr"/>
-      <c r="G1032" t="inlineStr"/>
-      <c r="H1032" t="inlineStr"/>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
@@ -35063,9 +35051,6 @@
           <t>[ROUTINE] Insider trade — Samantha Wellington (SVP, Chief Legal Officer) 970 shares withheld for taxes (vest event) on 2026-08-15</t>
         </is>
       </c>
-      <c r="F1033" t="inlineStr"/>
-      <c r="G1033" t="inlineStr"/>
-      <c r="H1033" t="inlineStr"/>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
@@ -35093,9 +35078,6 @@
           <t>[ROUTINE] Insider trade — Sweetnam Jordan Douglas Bradley (SVP, Chief Commercial Officer) 2,294 shares withheld for taxes (vest event) on 2026-08-15</t>
         </is>
       </c>
-      <c r="F1034" t="inlineStr"/>
-      <c r="G1034" t="inlineStr"/>
-      <c r="H1034" t="inlineStr"/>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
@@ -35123,9 +35105,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Sweetnam Jordan (Officer) plans to sell 1,014 shares (~$102.4K) on/after 08/18/2026</t>
         </is>
       </c>
-      <c r="F1035" t="inlineStr"/>
-      <c r="G1035" t="inlineStr"/>
-      <c r="H1035" t="inlineStr"/>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
@@ -35153,9 +35132,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1036" t="inlineStr"/>
-      <c r="G1036" t="inlineStr"/>
-      <c r="H1036" t="inlineStr"/>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
@@ -35183,9 +35159,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1037" t="inlineStr"/>
-      <c r="G1037" t="inlineStr"/>
-      <c r="H1037" t="inlineStr"/>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
@@ -35213,9 +35186,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F1038" t="inlineStr"/>
-      <c r="G1038" t="inlineStr"/>
-      <c r="H1038" t="inlineStr"/>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
@@ -35243,9 +35213,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1039" t="inlineStr"/>
-      <c r="G1039" t="inlineStr"/>
-      <c r="H1039" t="inlineStr"/>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
@@ -35273,9 +35240,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1040" t="inlineStr"/>
-      <c r="G1040" t="inlineStr"/>
-      <c r="H1040" t="inlineStr"/>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
@@ -35303,9 +35267,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F1041" t="inlineStr"/>
-      <c r="G1041" t="inlineStr"/>
-      <c r="H1041" t="inlineStr"/>
     </row>
     <row r="1042">
       <c r="A1042" t="inlineStr">
@@ -35333,9 +35294,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Glance Natalie (Officer) plans to sell 1,539 shares (~$200.3K) on/after 08/18/2026</t>
         </is>
       </c>
-      <c r="F1042" t="inlineStr"/>
-      <c r="G1042" t="inlineStr"/>
-      <c r="H1042" t="inlineStr"/>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
@@ -35363,9 +35321,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Hosseini Hesam (Officer) plans to sell 2,753 shares (~$107.3K) on/after 08/18/2026</t>
         </is>
       </c>
-      <c r="F1043" t="inlineStr"/>
-      <c r="G1043" t="inlineStr"/>
-      <c r="H1043" t="inlineStr"/>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
@@ -35393,9 +35348,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1044" t="inlineStr"/>
-      <c r="G1044" t="inlineStr"/>
-      <c r="H1044" t="inlineStr"/>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
@@ -35423,9 +35375,6 @@
           <t>[ROUTINE] Insider trade — Maurice J Duca (10%+ owner) sold 5,600 shares @ $195.89 ($1.10M) on 2026-08-17</t>
         </is>
       </c>
-      <c r="F1045" t="inlineStr"/>
-      <c r="G1045" t="inlineStr"/>
-      <c r="H1045" t="inlineStr"/>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
@@ -35453,9 +35402,6 @@
           <t>[ROUTINE] Insider trade — Maurice J Duca (10%+ owner) sold 15,800 shares @ $200.11 ($3.16M) on 2026-08-14</t>
         </is>
       </c>
-      <c r="F1046" t="inlineStr"/>
-      <c r="G1046" t="inlineStr"/>
-      <c r="H1046" t="inlineStr"/>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
@@ -35483,9 +35429,6 @@
           <t>[UNKNOWN] Form 4/A</t>
         </is>
       </c>
-      <c r="F1047" t="inlineStr"/>
-      <c r="G1047" t="inlineStr"/>
-      <c r="H1047" t="inlineStr"/>
     </row>
     <row r="1048">
       <c r="A1048" t="inlineStr">
@@ -35513,9 +35456,6 @@
           <t>[UNKNOWN] Form 4/A</t>
         </is>
       </c>
-      <c r="F1048" t="inlineStr"/>
-      <c r="G1048" t="inlineStr"/>
-      <c r="H1048" t="inlineStr"/>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
@@ -35543,9 +35483,6 @@
           <t>[UNKNOWN] Form 3/A</t>
         </is>
       </c>
-      <c r="F1049" t="inlineStr"/>
-      <c r="G1049" t="inlineStr"/>
-      <c r="H1049" t="inlineStr"/>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
@@ -35573,9 +35510,6 @@
           <t>[UNKNOWN] Form 3/A</t>
         </is>
       </c>
-      <c r="F1050" t="inlineStr"/>
-      <c r="G1050" t="inlineStr"/>
-      <c r="H1050" t="inlineStr"/>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
@@ -35603,9 +35537,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$475.0K) on/after 08/18/2026</t>
         </is>
       </c>
-      <c r="F1051" t="inlineStr"/>
-      <c r="G1051" t="inlineStr"/>
-      <c r="H1051" t="inlineStr"/>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
@@ -35633,9 +35564,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Kereere Suzan (Officer) plans to sell 4,162 shares (~$251.7K) on/after 08/18/2026</t>
         </is>
       </c>
-      <c r="F1052" t="inlineStr"/>
-      <c r="G1052" t="inlineStr"/>
-      <c r="H1052" t="inlineStr"/>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
@@ -35663,9 +35591,6 @@
           <t>New senior role: Regional Vice President, Sales</t>
         </is>
       </c>
-      <c r="F1053" t="inlineStr"/>
-      <c r="G1053" t="inlineStr"/>
-      <c r="H1053" t="inlineStr"/>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
@@ -35693,9 +35618,6 @@
           <t>13 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1054" t="inlineStr"/>
-      <c r="G1054" t="inlineStr"/>
-      <c r="H1054" t="inlineStr"/>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
@@ -35723,9 +35645,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F1055" t="inlineStr"/>
-      <c r="G1055" t="inlineStr"/>
-      <c r="H1055" t="inlineStr"/>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
@@ -35753,9 +35672,6 @@
           <t>New senior role: Vice President, People Business Partner &amp; Employee Relations</t>
         </is>
       </c>
-      <c r="F1056" t="inlineStr"/>
-      <c r="G1056" t="inlineStr"/>
-      <c r="H1056" t="inlineStr"/>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
@@ -35783,9 +35699,6 @@
           <t>6 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1057" t="inlineStr"/>
-      <c r="G1057" t="inlineStr"/>
-      <c r="H1057" t="inlineStr"/>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
@@ -35813,9 +35726,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F1058" t="inlineStr"/>
-      <c r="G1058" t="inlineStr"/>
-      <c r="H1058" t="inlineStr"/>
     </row>
     <row r="1059">
       <c r="A1059" t="inlineStr">
@@ -35843,9 +35753,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F1059" t="inlineStr"/>
-      <c r="G1059" t="inlineStr"/>
-      <c r="H1059" t="inlineStr"/>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
@@ -35873,9 +35780,6 @@
           <t>[UNKNOWN] Form 6-K</t>
         </is>
       </c>
-      <c r="F1060" t="inlineStr"/>
-      <c r="G1060" t="inlineStr"/>
-      <c r="H1060" t="inlineStr"/>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
@@ -35903,9 +35807,6 @@
           <t>4 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1061" t="inlineStr"/>
-      <c r="G1061" t="inlineStr"/>
-      <c r="H1061" t="inlineStr"/>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
@@ -35933,9 +35834,6 @@
           <t>[ROUTINE] Insider trade — Bhatt Baiju (Director) sold 50,317 shares @ $96.80 ($4.87M) on 2026-08-14</t>
         </is>
       </c>
-      <c r="F1062" t="inlineStr"/>
-      <c r="G1062" t="inlineStr"/>
-      <c r="H1062" t="inlineStr"/>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
@@ -35963,9 +35861,3048 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1063" t="inlineStr"/>
-      <c r="G1063" t="inlineStr"/>
-      <c r="H1063" t="inlineStr"/>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Garmin Ltd.</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1121788/000101410826000046/xslF345X06/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Jonathan Burrell (Director) gift: 41,000 Registered Shares on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000155278126000454/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Uber Technologies, Inc (10%+ owner) sold 72,000,000 shares @ $6.55 ($471.60M) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1543151/000155278126000453/xslSCHEDULE_13D_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ active owner disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000119312526357265/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Blecharczyk Nathan (Chief Strategy Officer) sold 13,615 shares @ $182.86 ($2.49M) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Choice Hotels International, Inc.</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1046311/000119312526356565/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — William L Jews (Director) sold 5,057 shares @ $106.98 ($541.0K) on 2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Choice Hotels International, Inc.</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1046311/000162828026057848/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — William Jews (Board Member) plans to sell 5,057 shares (~$540.0K) on/after 08/18/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>https://blog.google</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000206218226000008/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Mohan Ajit (Chief Business Officer) sold 54,608 shares @ $5.20 ($283.8K) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000172739626000009/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Morrow Rebecca (Chief Accounting Officer) sold 17,336 shares @ $5.20 ($90.1K) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000209619626000006/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Briers Zachary M (General Counsel) sold 204,044 shares @ $5.16 ($1.05M) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000213325526000016/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hott Douglas (Chief Financial Officer) sold 131,884 shares @ $5.20 ($685.5K) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1564408/000192109426000913/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Briers Zachary M (Officer) plans to sell 67,540 shares (~$343.1K) on/after 08/19/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000150629326000110/xslF345X06/wk-form4_1787186655.xml</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Silbermann Benjamin (Director) sold 93,750 shares @ $23.26 ($2.18M) on 2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000158904326000013/xslF345X06/wk-form4_1787185687.xml</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Rajaram Gokul (Director) sold 1,050 shares @ $23.03 ($24.2K) on 2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000192109426000912/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Rajaram Gokul (Director) plans to sell 1,050 shares (~$24.2K) on/after 08/19/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000192109426000911/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Silbermann Benjamin (Director) plans to sell 46,875 shares (~$1.08M) on/after 08/19/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>https://www.redditinc.com/policies/user-agreement</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810806/000168097926000006/xslF345X06/wk-form4_1787174913.xml</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Bromberg Matthew S (President and CEO) granted 880,000 Performance-Based Price Vesting Restricted Stock Units on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810806/000181080626000046/unity-20260817.htm</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810806/000197640826000757/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Dovrat Shlomo (Former Director) plans to sell 58,598 shares (~$2.74M) on/after 08/19/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>LIF</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>LIF (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1581760/000158176026000148/xslF345X06/wk-form4_1787186258.xml</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hulls Chris (Director) sold 250,000 shares @ $46.84 ($11.71M) on 2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1744489/000196430626000402/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Roeder Paul M (Officer) plans to sell 3,596 shares (~$382.3K) on/after 08/19/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>UMG</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>Universal Music Group N.V.</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>https://www.universalmusic.com/news/</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>UMG</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Universal Music Group N.V.</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>https://www.universalmusic.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>Warner Music Group Corp.</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>https://www.wmg.com/news/</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>OUTFRONT Media Inc.</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579877/000195917326006203/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Patrick Martin (Officer) plans to sell 10,000 shares (~$301.0K) on/after 08/19/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>https://en.help.roblox.com/hc/en-us/articles/115004647846</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000195004726008420/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Reinstra Mark (Officer) plans to sell 6,250 shares (~$235.4K) on/after 08/19/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Paychex, Inc.</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>https://www.paychex.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000195004726008394/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Glenn Ryan (Officer) plans to sell 3,346 shares (~$492.9K) on/after 08/19/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000195004726008393/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Scutt Joshua (Officer) plans to sell 4,730 shares (~$696.8K) on/after 08/19/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000195004726008391/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Cappotelli Andrew (Officer) plans to sell 2,550 shares (~$375.7K) on/after 08/19/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000112/xslF345X06/wk-form4_1787169794.xml</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Rost Nicholas (VP CAO &amp; Treasurer) 314 shares withheld for taxes (vest event) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000111/xslF345X06/wk-form4_1787169788.xml</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Cappotelli Andrew (Sr Vice President Operations) 2,063 shares withheld for taxes (vest event) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000110/xslF345X06/wk-form4_1787169783.xml</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — King Melissa Ann (SVP Product and Technology) 1,537 shares withheld for taxes (vest event) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000109/xslF345X06/wk-form4_1787169777.xml</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Scutt Joshua (SVP Chief Revenue Officer) 3,780 shares withheld for taxes (vest event) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000108/xslF345X06/wk-form4_1787169771.xml</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Glenn Ryan (Chief Financial Officer) 6,007 shares withheld for taxes (vest event) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000107/xslF345X06/wk-form4_1787169766.xml</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Beauchamp Steven R (Executive Chairman) 4,088 shares withheld for taxes (vest event) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000106/xslF345X06/wk-form4_1787169760.xml</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Williams Toby J. (President and CEO) 20,462 shares withheld for taxes (vest event) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1402057/000140205726000070/xslF345X06/wk-form4_1787171346.xml</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Kumar Mukesh (See Remarks) 1,147 shares withheld for taxes (vest event) on 2026-08-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr"/>
+      <c r="G1120" t="inlineStr"/>
+      <c r="H1120" t="inlineStr"/>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>GLBE</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>Global-E Online Ltd.</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835963/000119312526356843/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Schlachet Amir (CEO) sold 24,999 shares @ $41.37 ($1.03M) on 2026-08-18</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr"/>
+      <c r="G1121" t="inlineStr"/>
+      <c r="H1121" t="inlineStr"/>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr"/>
+      <c r="G1122" t="inlineStr"/>
+      <c r="H1122" t="inlineStr"/>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>https://www.ebayinc.com/stories/news/</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr"/>
+      <c r="G1123" t="inlineStr"/>
+      <c r="H1123" t="inlineStr"/>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1370637/000181376126000009/xslF345X06/form4-08192026_100811.xml</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Buckley Merilee (CHIEF ACCOUNTING OFFICER) sold 405 shares @ $79.50 ($32.2K) on 2026-08-17</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr"/>
+      <c r="G1124" t="inlineStr"/>
+      <c r="H1124" t="inlineStr"/>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1370637/000173174626000005/xslF345X06/form4-08192026_100840.xml</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Blow Marla J (Director) sold 300 shares @ $79.56 ($23.9K) on 2026-08-17</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr"/>
+      <c r="G1125" t="inlineStr"/>
+      <c r="H1125" t="inlineStr"/>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>6 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr"/>
+      <c r="G1126" t="inlineStr"/>
+      <c r="H1126" t="inlineStr"/>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr"/>
+      <c r="G1127" t="inlineStr"/>
+      <c r="H1127" t="inlineStr"/>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/company/newsroom</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr"/>
+      <c r="G1128" t="inlineStr"/>
+      <c r="H1128" t="inlineStr"/>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000192109426000909/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Rogers Chris (Officer) plans to sell 7,606 shares (~$372.3K) on/after 08/19/2026</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr"/>
+      <c r="G1129" t="inlineStr"/>
+      <c r="H1129" t="inlineStr"/>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000192109426000908/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Gupta Ravi (Director) plans to sell 150,000 shares (~$7.59M) on/after 08/19/2026</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr"/>
+      <c r="G1130" t="inlineStr"/>
+      <c r="H1130" t="inlineStr"/>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/duolingo</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr"/>
+      <c r="G1131" t="inlineStr"/>
+      <c r="H1131" t="inlineStr"/>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>https://blog.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr"/>
+      <c r="G1132" t="inlineStr"/>
+      <c r="H1132" t="inlineStr"/>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000162828026058021/xslF345X06/wk-form4_1787174175.xml</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Glance Natalie (Chief Engineering Officer) sold 4,290 shares @ $132.24 ($567.3K) on 2026-08-17</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr"/>
+      <c r="G1133" t="inlineStr"/>
+      <c r="H1133" t="inlineStr"/>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000162828026058020/xslF345X06/wk-form4_1787174168.xml</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Meese Robert (Chief Business Officer) sold 1,354 shares @ $129.13 ($174.8K) on 2026-08-17</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr"/>
+      <c r="G1134" t="inlineStr"/>
+      <c r="H1134" t="inlineStr"/>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1562088/000162828026058019/xslF345X06/wk-form4_1787174159.xml</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Chen Stephen C. (General Counsel) sold 1,024 shares @ $129.13 ($132.2K) on 2026-08-17</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr"/>
+      <c r="G1135" t="inlineStr"/>
+      <c r="H1135" t="inlineStr"/>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>https://ir.mtch.com/leadership/default.aspx</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr"/>
+      <c r="G1136" t="inlineStr"/>
+      <c r="H1136" t="inlineStr"/>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>https://mtch.com/news</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr"/>
+      <c r="G1137" t="inlineStr"/>
+      <c r="H1137" t="inlineStr"/>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>https://mtch.com/careers</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr"/>
+      <c r="G1138" t="inlineStr"/>
+      <c r="H1138" t="inlineStr"/>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>https://zillow.mediaroom.com</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr"/>
+      <c r="G1139" t="inlineStr"/>
+      <c r="H1139" t="inlineStr"/>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr"/>
+      <c r="G1140" t="inlineStr"/>
+      <c r="H1140" t="inlineStr"/>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000195004726008399/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Eaton Timothy (Officer) plans to sell 373 shares (~$76.1K) on/after 08/19/2026</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr"/>
+      <c r="G1141" t="inlineStr"/>
+      <c r="H1141" t="inlineStr"/>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>https://investors.block.xyz</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr"/>
+      <c r="G1142" t="inlineStr"/>
+      <c r="H1142" t="inlineStr"/>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000162828026058031/xslF345X06/wk-form4_1787175773.xml</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Eisen Anthony Mathew (Director) sold 18,000 shares @ $80.12 ($1.44M) on 2026-08-17</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr"/>
+      <c r="G1143" t="inlineStr"/>
+      <c r="H1143" t="inlineStr"/>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726008390/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$477.3K) on/after 08/19/2026</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr"/>
+      <c r="G1144" t="inlineStr"/>
+      <c r="H1144" t="inlineStr"/>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>https://www.bill.com/press-release</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr"/>
+      <c r="G1145" t="inlineStr"/>
+      <c r="H1145" t="inlineStr"/>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>https://investor.bill.com</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr"/>
+      <c r="G1146" t="inlineStr"/>
+      <c r="H1146" t="inlineStr"/>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000207397026000001/xslF345X06/form4-08192026_090805.xml</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Jain Rohini (Chief Financial Officer) granted 35,262 Performance Stock Units on 2026-08-17</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr"/>
+      <c r="G1147" t="inlineStr"/>
+      <c r="H1147" t="inlineStr"/>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000206742526000002/xslF345X06/form4-08192026_090803.xml</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Cieri Michael (Chief Product Officer) granted 19,590 Performance Stock Units on 2026-08-17</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr"/>
+      <c r="G1148" t="inlineStr"/>
+      <c r="H1148" t="inlineStr"/>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000179549726000003/xslF345X06/form4-08192026_090801.xml</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lacerte Rene A. (CEO) granted 52,893 Performance Stock Units on 2026-08-17</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr"/>
+      <c r="G1149" t="inlineStr"/>
+      <c r="H1149" t="inlineStr"/>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000162828026057932/bill-20260819.htm</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr"/>
+      <c r="G1150" t="inlineStr"/>
+      <c r="H1150" t="inlineStr"/>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>PayPal Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1633917/000189608626000012/xslF345X06/edgardoc.xml</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Kereere Suzan (President, Global Markets) sold 4,162 shares @ $60.96 ($253.7K) on 2026-08-18</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr"/>
+      <c r="G1151" t="inlineStr"/>
+      <c r="H1151" t="inlineStr"/>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>https://careers.toasttab.com/jobs?gh_jid=8094855</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>New senior role: Senior Director of Engineering, Developer and Agent Experience</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr"/>
+      <c r="G1152" t="inlineStr"/>
+      <c r="H1152" t="inlineStr"/>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>https://careers.toasttab.com/jobs?gh_jid=7977158</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>New senior role: Senior Director of Engineering, Developer and Agent Experience</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr"/>
+      <c r="G1153" t="inlineStr"/>
+      <c r="H1153" t="inlineStr"/>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>14 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr"/>
+      <c r="G1154" t="inlineStr"/>
+      <c r="H1154" t="inlineStr"/>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1650164/000195917326006233/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Vassil Jonathan (Officer) plans to sell 13,931 shares (~$501.7K) on/after 08/19/2026</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr"/>
+      <c r="G1155" t="inlineStr"/>
+      <c r="H1155" t="inlineStr"/>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>Sezzle Inc.</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>https://investors.sezzle.com</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr"/>
+      <c r="G1156" t="inlineStr"/>
+      <c r="H1156" t="inlineStr"/>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>https://dave.com/careers</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr"/>
+      <c r="G1157" t="inlineStr"/>
+      <c r="H1157" t="inlineStr"/>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>5 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr"/>
+      <c r="G1158" t="inlineStr"/>
+      <c r="H1158" t="inlineStr"/>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood/jobs/8131201?t=gh_src=&amp;gh_jid=8131201</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>New senior role: Director of Benefits</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr"/>
+      <c r="G1159" t="inlineStr"/>
+      <c r="H1159" t="inlineStr"/>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr"/>
+      <c r="G1160" t="inlineStr"/>
+      <c r="H1160" t="inlineStr"/>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000210858926000020/xslF345X06/wk-form4_1787172165.xml</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Verma Shiv (Chief Financial Officer) sold 3,982 shares @ $95.07 ($378.6K) on 2026-08-17</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr"/>
+      <c r="G1161" t="inlineStr"/>
+      <c r="H1161" t="inlineStr"/>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000178387926000130/xslF345X06/wk-form4_1787172014.xml</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Robinhood Markets, Inc. (10%+ owner) sold 9,584 shares @ $28.33 ($271.5K) on 2026-08-17</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr"/>
+      <c r="G1162" t="inlineStr"/>
+      <c r="H1162" t="inlineStr"/>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>5 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr"/>
+      <c r="G1163" t="inlineStr"/>
+      <c r="H1163" t="inlineStr"/>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1647639/000183280826000015/xslF345X06/wk-form4_1787178025.xml</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Datta Sanjay (President, Capital&amp; Enterprise) sold 2,033 shares @ $29.36 ($59.7K) on 2026-08-17</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr"/>
+      <c r="G1164" t="inlineStr"/>
+      <c r="H1164" t="inlineStr"/>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1647639/000155825926000017/xslF345X06/wk-form4_1787177685.xml</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Darling Scott (Chief Legal Officer) sold 814 shares @ $29.36 ($23.9K) on 2026-08-17</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr"/>
+      <c r="G1165" t="inlineStr"/>
+      <c r="H1165" t="inlineStr"/>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1647639/000212446426000010/xslF345X06/wk-form4_1787177655.xml</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Blankmeyer Andrea (Chief Financial Officer) sold 10,175 shares @ $29.35 ($298.6K) on 2026-08-17</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr"/>
+      <c r="G1166" t="inlineStr"/>
+      <c r="H1166" t="inlineStr"/>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1647639/000192109426000916/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Datta Sanjay (Officer) plans to sell 10,000 shares (~$314.6K) on/after 08/19/2026</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr"/>
+      <c r="G1167" t="inlineStr"/>
+      <c r="H1167" t="inlineStr"/>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1647639/000192109426000915/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Blankmeyer Andrea (Officer) plans to sell 3,000 shares (~$88.0K) on/after 08/19/2026</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr"/>
+      <c r="G1168" t="inlineStr"/>
+      <c r="H1168" t="inlineStr"/>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>ENVA</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Enova International Inc.</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>https://www.enova.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr"/>
+      <c r="G1169" t="inlineStr"/>
+      <c r="H1169" t="inlineStr"/>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr"/>
+      <c r="G1170" t="inlineStr"/>
+      <c r="H1170" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1170"/>
+  <dimension ref="A1:H1242"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -37400,9 +37400,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1120" t="inlineStr"/>
-      <c r="G1120" t="inlineStr"/>
-      <c r="H1120" t="inlineStr"/>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
@@ -37430,9 +37427,6 @@
           <t>[ROUTINE] Insider trade — Schlachet Amir (CEO) sold 24,999 shares @ $41.37 ($1.03M) on 2026-08-18</t>
         </is>
       </c>
-      <c r="F1121" t="inlineStr"/>
-      <c r="G1121" t="inlineStr"/>
-      <c r="H1121" t="inlineStr"/>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
@@ -37460,9 +37454,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F1122" t="inlineStr"/>
-      <c r="G1122" t="inlineStr"/>
-      <c r="H1122" t="inlineStr"/>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
@@ -37490,9 +37481,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1123" t="inlineStr"/>
-      <c r="G1123" t="inlineStr"/>
-      <c r="H1123" t="inlineStr"/>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
@@ -37520,9 +37508,6 @@
           <t>[ROUTINE] Insider trade — Buckley Merilee (CHIEF ACCOUNTING OFFICER) sold 405 shares @ $79.50 ($32.2K) on 2026-08-17</t>
         </is>
       </c>
-      <c r="F1124" t="inlineStr"/>
-      <c r="G1124" t="inlineStr"/>
-      <c r="H1124" t="inlineStr"/>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
@@ -37550,9 +37535,6 @@
           <t>[ROUTINE] Insider trade — Blow Marla J (Director) sold 300 shares @ $79.56 ($23.9K) on 2026-08-17</t>
         </is>
       </c>
-      <c r="F1125" t="inlineStr"/>
-      <c r="G1125" t="inlineStr"/>
-      <c r="H1125" t="inlineStr"/>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
@@ -37580,9 +37562,6 @@
           <t>6 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1126" t="inlineStr"/>
-      <c r="G1126" t="inlineStr"/>
-      <c r="H1126" t="inlineStr"/>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
@@ -37610,9 +37589,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F1127" t="inlineStr"/>
-      <c r="G1127" t="inlineStr"/>
-      <c r="H1127" t="inlineStr"/>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
@@ -37640,9 +37616,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1128" t="inlineStr"/>
-      <c r="G1128" t="inlineStr"/>
-      <c r="H1128" t="inlineStr"/>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
@@ -37670,9 +37643,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Rogers Chris (Officer) plans to sell 7,606 shares (~$372.3K) on/after 08/19/2026</t>
         </is>
       </c>
-      <c r="F1129" t="inlineStr"/>
-      <c r="G1129" t="inlineStr"/>
-      <c r="H1129" t="inlineStr"/>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
@@ -37700,9 +37670,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Gupta Ravi (Director) plans to sell 150,000 shares (~$7.59M) on/after 08/19/2026</t>
         </is>
       </c>
-      <c r="F1130" t="inlineStr"/>
-      <c r="G1130" t="inlineStr"/>
-      <c r="H1130" t="inlineStr"/>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
@@ -37730,9 +37697,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1131" t="inlineStr"/>
-      <c r="G1131" t="inlineStr"/>
-      <c r="H1131" t="inlineStr"/>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
@@ -37760,9 +37724,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1132" t="inlineStr"/>
-      <c r="G1132" t="inlineStr"/>
-      <c r="H1132" t="inlineStr"/>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
@@ -37790,9 +37751,6 @@
           <t>[ROUTINE] Insider trade — Glance Natalie (Chief Engineering Officer) sold 4,290 shares @ $132.24 ($567.3K) on 2026-08-17</t>
         </is>
       </c>
-      <c r="F1133" t="inlineStr"/>
-      <c r="G1133" t="inlineStr"/>
-      <c r="H1133" t="inlineStr"/>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
@@ -37820,9 +37778,6 @@
           <t>[ROUTINE] Insider trade — Meese Robert (Chief Business Officer) sold 1,354 shares @ $129.13 ($174.8K) on 2026-08-17</t>
         </is>
       </c>
-      <c r="F1134" t="inlineStr"/>
-      <c r="G1134" t="inlineStr"/>
-      <c r="H1134" t="inlineStr"/>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
@@ -37850,9 +37805,6 @@
           <t>[ROUTINE] Insider trade — Chen Stephen C. (General Counsel) sold 1,024 shares @ $129.13 ($132.2K) on 2026-08-17</t>
         </is>
       </c>
-      <c r="F1135" t="inlineStr"/>
-      <c r="G1135" t="inlineStr"/>
-      <c r="H1135" t="inlineStr"/>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
@@ -37880,9 +37832,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F1136" t="inlineStr"/>
-      <c r="G1136" t="inlineStr"/>
-      <c r="H1136" t="inlineStr"/>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
@@ -37910,9 +37859,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1137" t="inlineStr"/>
-      <c r="G1137" t="inlineStr"/>
-      <c r="H1137" t="inlineStr"/>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
@@ -37940,9 +37886,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1138" t="inlineStr"/>
-      <c r="G1138" t="inlineStr"/>
-      <c r="H1138" t="inlineStr"/>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
@@ -37970,9 +37913,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1139" t="inlineStr"/>
-      <c r="G1139" t="inlineStr"/>
-      <c r="H1139" t="inlineStr"/>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
@@ -38000,9 +37940,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1140" t="inlineStr"/>
-      <c r="G1140" t="inlineStr"/>
-      <c r="H1140" t="inlineStr"/>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
@@ -38030,9 +37967,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Eaton Timothy (Officer) plans to sell 373 shares (~$76.1K) on/after 08/19/2026</t>
         </is>
       </c>
-      <c r="F1141" t="inlineStr"/>
-      <c r="G1141" t="inlineStr"/>
-      <c r="H1141" t="inlineStr"/>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
@@ -38060,9 +37994,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F1142" t="inlineStr"/>
-      <c r="G1142" t="inlineStr"/>
-      <c r="H1142" t="inlineStr"/>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
@@ -38090,9 +38021,6 @@
           <t>[ROUTINE] Insider trade — Eisen Anthony Mathew (Director) sold 18,000 shares @ $80.12 ($1.44M) on 2026-08-17</t>
         </is>
       </c>
-      <c r="F1143" t="inlineStr"/>
-      <c r="G1143" t="inlineStr"/>
-      <c r="H1143" t="inlineStr"/>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
@@ -38120,9 +38048,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$477.3K) on/after 08/19/2026</t>
         </is>
       </c>
-      <c r="F1144" t="inlineStr"/>
-      <c r="G1144" t="inlineStr"/>
-      <c r="H1144" t="inlineStr"/>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
@@ -38150,9 +38075,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1145" t="inlineStr"/>
-      <c r="G1145" t="inlineStr"/>
-      <c r="H1145" t="inlineStr"/>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
@@ -38180,9 +38102,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F1146" t="inlineStr"/>
-      <c r="G1146" t="inlineStr"/>
-      <c r="H1146" t="inlineStr"/>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
@@ -38210,9 +38129,6 @@
           <t>[ROUTINE] Insider trade — Jain Rohini (Chief Financial Officer) granted 35,262 Performance Stock Units on 2026-08-17</t>
         </is>
       </c>
-      <c r="F1147" t="inlineStr"/>
-      <c r="G1147" t="inlineStr"/>
-      <c r="H1147" t="inlineStr"/>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
@@ -38240,9 +38156,6 @@
           <t>[ROUTINE] Insider trade — Cieri Michael (Chief Product Officer) granted 19,590 Performance Stock Units on 2026-08-17</t>
         </is>
       </c>
-      <c r="F1148" t="inlineStr"/>
-      <c r="G1148" t="inlineStr"/>
-      <c r="H1148" t="inlineStr"/>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
@@ -38270,9 +38183,6 @@
           <t>[ROUTINE] Insider trade — Lacerte Rene A. (CEO) granted 52,893 Performance Stock Units on 2026-08-17</t>
         </is>
       </c>
-      <c r="F1149" t="inlineStr"/>
-      <c r="G1149" t="inlineStr"/>
-      <c r="H1149" t="inlineStr"/>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
@@ -38300,9 +38210,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F1150" t="inlineStr"/>
-      <c r="G1150" t="inlineStr"/>
-      <c r="H1150" t="inlineStr"/>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
@@ -38330,9 +38237,6 @@
           <t>[ROUTINE] Insider trade — Kereere Suzan (President, Global Markets) sold 4,162 shares @ $60.96 ($253.7K) on 2026-08-18</t>
         </is>
       </c>
-      <c r="F1151" t="inlineStr"/>
-      <c r="G1151" t="inlineStr"/>
-      <c r="H1151" t="inlineStr"/>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
@@ -38360,9 +38264,6 @@
           <t>New senior role: Senior Director of Engineering, Developer and Agent Experience</t>
         </is>
       </c>
-      <c r="F1152" t="inlineStr"/>
-      <c r="G1152" t="inlineStr"/>
-      <c r="H1152" t="inlineStr"/>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
@@ -38390,9 +38291,6 @@
           <t>New senior role: Senior Director of Engineering, Developer and Agent Experience</t>
         </is>
       </c>
-      <c r="F1153" t="inlineStr"/>
-      <c r="G1153" t="inlineStr"/>
-      <c r="H1153" t="inlineStr"/>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
@@ -38420,9 +38318,6 @@
           <t>14 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1154" t="inlineStr"/>
-      <c r="G1154" t="inlineStr"/>
-      <c r="H1154" t="inlineStr"/>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
@@ -38450,9 +38345,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Vassil Jonathan (Officer) plans to sell 13,931 shares (~$501.7K) on/after 08/19/2026</t>
         </is>
       </c>
-      <c r="F1155" t="inlineStr"/>
-      <c r="G1155" t="inlineStr"/>
-      <c r="H1155" t="inlineStr"/>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
@@ -38480,9 +38372,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F1156" t="inlineStr"/>
-      <c r="G1156" t="inlineStr"/>
-      <c r="H1156" t="inlineStr"/>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
@@ -38510,9 +38399,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1157" t="inlineStr"/>
-      <c r="G1157" t="inlineStr"/>
-      <c r="H1157" t="inlineStr"/>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
@@ -38540,9 +38426,6 @@
           <t>5 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1158" t="inlineStr"/>
-      <c r="G1158" t="inlineStr"/>
-      <c r="H1158" t="inlineStr"/>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
@@ -38570,9 +38453,6 @@
           <t>New senior role: Director of Benefits</t>
         </is>
       </c>
-      <c r="F1159" t="inlineStr"/>
-      <c r="G1159" t="inlineStr"/>
-      <c r="H1159" t="inlineStr"/>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
@@ -38600,9 +38480,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1160" t="inlineStr"/>
-      <c r="G1160" t="inlineStr"/>
-      <c r="H1160" t="inlineStr"/>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
@@ -38630,9 +38507,6 @@
           <t>[ROUTINE] Insider trade — Verma Shiv (Chief Financial Officer) sold 3,982 shares @ $95.07 ($378.6K) on 2026-08-17</t>
         </is>
       </c>
-      <c r="F1161" t="inlineStr"/>
-      <c r="G1161" t="inlineStr"/>
-      <c r="H1161" t="inlineStr"/>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
@@ -38660,9 +38534,6 @@
           <t>[ROUTINE] Insider trade — Robinhood Markets, Inc. (10%+ owner) sold 9,584 shares @ $28.33 ($271.5K) on 2026-08-17</t>
         </is>
       </c>
-      <c r="F1162" t="inlineStr"/>
-      <c r="G1162" t="inlineStr"/>
-      <c r="H1162" t="inlineStr"/>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
@@ -38690,9 +38561,6 @@
           <t>5 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1163" t="inlineStr"/>
-      <c r="G1163" t="inlineStr"/>
-      <c r="H1163" t="inlineStr"/>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
@@ -38720,9 +38588,6 @@
           <t>[ROUTINE] Insider trade — Datta Sanjay (President, Capital&amp; Enterprise) sold 2,033 shares @ $29.36 ($59.7K) on 2026-08-17</t>
         </is>
       </c>
-      <c r="F1164" t="inlineStr"/>
-      <c r="G1164" t="inlineStr"/>
-      <c r="H1164" t="inlineStr"/>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
@@ -38750,9 +38615,6 @@
           <t>[ROUTINE] Insider trade — Darling Scott (Chief Legal Officer) sold 814 shares @ $29.36 ($23.9K) on 2026-08-17</t>
         </is>
       </c>
-      <c r="F1165" t="inlineStr"/>
-      <c r="G1165" t="inlineStr"/>
-      <c r="H1165" t="inlineStr"/>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
@@ -38780,9 +38642,6 @@
           <t>[ROUTINE] Insider trade — Blankmeyer Andrea (Chief Financial Officer) sold 10,175 shares @ $29.35 ($298.6K) on 2026-08-17</t>
         </is>
       </c>
-      <c r="F1166" t="inlineStr"/>
-      <c r="G1166" t="inlineStr"/>
-      <c r="H1166" t="inlineStr"/>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
@@ -38810,9 +38669,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Datta Sanjay (Officer) plans to sell 10,000 shares (~$314.6K) on/after 08/19/2026</t>
         </is>
       </c>
-      <c r="F1167" t="inlineStr"/>
-      <c r="G1167" t="inlineStr"/>
-      <c r="H1167" t="inlineStr"/>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
@@ -38840,9 +38696,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Blankmeyer Andrea (Officer) plans to sell 3,000 shares (~$88.0K) on/after 08/19/2026</t>
         </is>
       </c>
-      <c r="F1168" t="inlineStr"/>
-      <c r="G1168" t="inlineStr"/>
-      <c r="H1168" t="inlineStr"/>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
@@ -38870,9 +38723,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1169" t="inlineStr"/>
-      <c r="G1169" t="inlineStr"/>
-      <c r="H1169" t="inlineStr"/>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
@@ -38900,9 +38750,2019 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1170" t="inlineStr"/>
-      <c r="G1170" t="inlineStr"/>
-      <c r="H1170" t="inlineStr"/>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>https://ir.logitech.com</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>Garmin Ltd.</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1121788/000119312526359422/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Wang Cheng-Wei (General Manager - Garmin Corp.) sold 9,941 shares @ $299.36 ($2.98M) on 2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1324424/000122520826007235/xslF345X06/doc4.xml</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Soliday Lance A (SVP &amp; Chief Accounting Officer) sold 2,810 shares @ $323.65 ($909.5K) on 2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000195917326006255/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Blecharczyk Nathan (Officer) plans to sell 2,738 shares (~$504.9K) on/after 08/20/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326012729/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Mahoney Curtis J. (Chief Legal Officer) sold 1,559 shares @ $558.00 ($869.9K) on 2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326012727/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Susan J Li (Chief Financial Officer) sold 9,196 shares @ $550.61 ($5.06M) on 2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1326801/000095010326012726/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Bosworth Andrew (Chief Technology Officer) sold 7,848 shares @ $558.00 ($4.38M) on 2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>https://blog.google</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1639920/000114036126033885/ef20080678_6k.htm</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 6-K</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/news/</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1744489/000162828026058293/xslF345X06/wk-form4_1787261642.xml</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Roeder Paul M (Sr EVP and Chief Comm Officer) sold 3,596 shares @ $106.32 ($382.3K) on 2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>UMG</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Universal Music Group N.V.</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>https://www.universalmusic.com/news/</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>UMG</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Universal Music Group N.V.</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>https://www.universalmusic.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1337634/000162828026058309/xslF345X06/wk-form4_1787268402.xml</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Fitzgerald Scott Michael (Principal Accounting Officer) sold 84,970 shares @ $7.08 ($602.0K) on 2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1337634/000162828026058307/xslF345X06/wk-form4_1787268318.xml</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — James Constance P. (Chief Financial Officer) sold 116,644 shares @ $7.06 ($823.0K) on 2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>OUTFRONT Media Inc.</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579877/000183343126000004/xslF345X06/wk-form4_1787258172.xml</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Patrick Martin (SVP, Controller, CAO) sold 10,000 shares @ $30.10 ($301.0K) on 2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000192109426000934/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Reinstra Mark (Officer) plans to sell 17,934 shares (~$680.8K) on/after 08/20/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000192109426000933/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Rawlings Amy Marie (Officer) plans to sell 5,061 shares (~$192.1K) on/after 08/20/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000192109426000932/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Kaufman Matthew D (Officer) plans to sell 14,904 shares (~$565.8K) on/after 08/20/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000192109426000931/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Naveen K. Chopra (Officer) plans to sell 17,509 shares (~$664.7K) on/after 08/20/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000192109426000930/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Sean Jack Buckley (Officer) plans to sell 5,607 shares (~$212.9K) on/after 08/20/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000192109426000929/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Baszucki David (Officer) plans to sell 52,568 shares (~$2.00M) on/after 08/20/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000131509826000161/xslF345X06/wk-form4_1787257008.xml</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Reinstra Mark (Chief Legal Off. &amp; Corp. Sec.) sold 6,250 shares @ $40.00 ($250.0K) on 2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>https://mediacenter.adp.com</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/8670/000195917326006260/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Kwon David (Officer) plans to sell 798 shares (~$223.4K) on/after 08/20/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000125/xslF345X06/wk-form4_1787256438.xml</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sarowitz Steven I (Director) sold 8,539 shares @ $150.20 ($1.28M) on 2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000124/xslF345X06/wk-form4_1787256433.xml</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Scutt Joshua (SVP Chief Revenue Officer) sold 4,730 shares @ $149.82 ($708.6K) on 2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000123/xslF345X06/wk-form4_1787256427.xml</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Reiner Andres (Director) granted 2,207 Common Stock, par value $0.001 on 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000122/xslF345X06/wk-form4_1787256422.xml</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Rost Nicholas (VP CAO &amp; Treasurer) sold 520 shares @ $148.03 ($77.0K) on 2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000121/xslF345X06/wk-form4_1787256417.xml</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Glenn Ryan (Chief Financial Officer) sold 3,345 shares @ $149.75 ($500.9K) on 2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159169826000120/xslF345X06/wk-form4_1787256409.xml</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Cappotelli Andrew (Sr Vice President Operations) sold 2,550 shares @ $149.83 ($382.1K) on 2026-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/pricing</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr"/>
+      <c r="G1220" t="inlineStr"/>
+      <c r="H1220" t="inlineStr"/>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr"/>
+      <c r="G1221" t="inlineStr"/>
+      <c r="H1221" t="inlineStr"/>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr"/>
+      <c r="G1222" t="inlineStr"/>
+      <c r="H1222" t="inlineStr"/>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065088/000106508826000188/xslF345X06/form4.xml</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sweetnam Jordan Douglas Bradley (SVP, Chief Commercial Officer) sold 1,014 shares @ $101.39 ($102.8K) on 2026-08-18</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr"/>
+      <c r="G1223" t="inlineStr"/>
+      <c r="H1223" t="inlineStr"/>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>10 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr"/>
+      <c r="G1224" t="inlineStr"/>
+      <c r="H1224" t="inlineStr"/>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr"/>
+      <c r="G1225" t="inlineStr"/>
+      <c r="H1225" t="inlineStr"/>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/duolingo</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr"/>
+      <c r="G1226" t="inlineStr"/>
+      <c r="H1226" t="inlineStr"/>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr"/>
+      <c r="G1227" t="inlineStr"/>
+      <c r="H1227" t="inlineStr"/>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000093833326000022/xslF345X06/form4-08202026_100813.xml</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Maurice J Duca (10%+ owner) sold 7,001 shares @ $213.52 ($1.49M) on 2026-08-19</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr"/>
+      <c r="G1228" t="inlineStr"/>
+      <c r="H1228" t="inlineStr"/>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000093833326000021/xslF345X06/form4-08202026_100851.xml</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Maurice J Duca (10%+ owner) sold 8,056 shares @ $203.53 ($1.64M) on 2026-08-18</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr"/>
+      <c r="G1229" t="inlineStr"/>
+      <c r="H1229" t="inlineStr"/>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000204337926000012/xslF345X06/wk-form4_1787263190.xml</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Eaton Timothy Mathias (Chief Financial Officer) sold 373 shares @ $202.61 ($75.6K) on 2026-08-19</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr"/>
+      <c r="G1230" t="inlineStr"/>
+      <c r="H1230" t="inlineStr"/>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726008480/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$485.2K) on/after 08/20/2026</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr"/>
+      <c r="G1231" t="inlineStr"/>
+      <c r="H1231" t="inlineStr"/>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000162828026058243/bill-20260630xs8.htm</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Employee stock plan registration</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr"/>
+      <c r="G1232" t="inlineStr"/>
+      <c r="H1232" t="inlineStr"/>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000162828026058238/bill-20260630.htm</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Annual report</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr"/>
+      <c r="G1233" t="inlineStr"/>
+      <c r="H1233" t="inlineStr"/>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>15 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr"/>
+      <c r="G1234" t="inlineStr"/>
+      <c r="H1234" t="inlineStr"/>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>https://pos.toasttab.com/pricing</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr"/>
+      <c r="G1235" t="inlineStr"/>
+      <c r="H1235" t="inlineStr"/>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr"/>
+      <c r="G1236" t="inlineStr"/>
+      <c r="H1236" t="inlineStr"/>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr"/>
+      <c r="G1237" t="inlineStr"/>
+      <c r="H1237" t="inlineStr"/>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr"/>
+      <c r="G1238" t="inlineStr"/>
+      <c r="H1238" t="inlineStr"/>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1647639/000192109426000925/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Mirgorodskaya Natalia (Officer) plans to sell 586 shares (~$16.5K) on/after 08/20/2026</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr"/>
+      <c r="G1239" t="inlineStr"/>
+      <c r="H1239" t="inlineStr"/>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1647639/000192109426000924/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Darling Scott (Officer) plans to sell 7,696 shares (~$216.2K) on/after 08/20/2026</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr"/>
+      <c r="G1240" t="inlineStr"/>
+      <c r="H1240" t="inlineStr"/>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1647639/000192109426000923/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Datta Sanjay (Officer) plans to sell 8,945 shares (~$251.3K) on/after 08/20/2026</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr"/>
+      <c r="G1241" t="inlineStr"/>
+      <c r="H1241" t="inlineStr"/>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr"/>
+      <c r="G1242" t="inlineStr"/>
+      <c r="H1242" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1242"/>
+  <dimension ref="A1:H1276"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -40100,9 +40100,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F1220" t="inlineStr"/>
-      <c r="G1220" t="inlineStr"/>
-      <c r="H1220" t="inlineStr"/>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
@@ -40130,9 +40127,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1221" t="inlineStr"/>
-      <c r="G1221" t="inlineStr"/>
-      <c r="H1221" t="inlineStr"/>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
@@ -40160,9 +40154,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F1222" t="inlineStr"/>
-      <c r="G1222" t="inlineStr"/>
-      <c r="H1222" t="inlineStr"/>
     </row>
     <row r="1223">
       <c r="A1223" t="inlineStr">
@@ -40190,9 +40181,6 @@
           <t>[ROUTINE] Insider trade — Sweetnam Jordan Douglas Bradley (SVP, Chief Commercial Officer) sold 1,014 shares @ $101.39 ($102.8K) on 2026-08-18</t>
         </is>
       </c>
-      <c r="F1223" t="inlineStr"/>
-      <c r="G1223" t="inlineStr"/>
-      <c r="H1223" t="inlineStr"/>
     </row>
     <row r="1224">
       <c r="A1224" t="inlineStr">
@@ -40220,9 +40208,6 @@
           <t>10 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1224" t="inlineStr"/>
-      <c r="G1224" t="inlineStr"/>
-      <c r="H1224" t="inlineStr"/>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
@@ -40250,9 +40235,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F1225" t="inlineStr"/>
-      <c r="G1225" t="inlineStr"/>
-      <c r="H1225" t="inlineStr"/>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
@@ -40280,9 +40262,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1226" t="inlineStr"/>
-      <c r="G1226" t="inlineStr"/>
-      <c r="H1226" t="inlineStr"/>
     </row>
     <row r="1227">
       <c r="A1227" t="inlineStr">
@@ -40310,9 +40289,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1227" t="inlineStr"/>
-      <c r="G1227" t="inlineStr"/>
-      <c r="H1227" t="inlineStr"/>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
@@ -40340,9 +40316,6 @@
           <t>[ROUTINE] Insider trade — Maurice J Duca (10%+ owner) sold 7,001 shares @ $213.52 ($1.49M) on 2026-08-19</t>
         </is>
       </c>
-      <c r="F1228" t="inlineStr"/>
-      <c r="G1228" t="inlineStr"/>
-      <c r="H1228" t="inlineStr"/>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
@@ -40370,9 +40343,6 @@
           <t>[ROUTINE] Insider trade — Maurice J Duca (10%+ owner) sold 8,056 shares @ $203.53 ($1.64M) on 2026-08-18</t>
         </is>
       </c>
-      <c r="F1229" t="inlineStr"/>
-      <c r="G1229" t="inlineStr"/>
-      <c r="H1229" t="inlineStr"/>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
@@ -40400,9 +40370,6 @@
           <t>[ROUTINE] Insider trade — Eaton Timothy Mathias (Chief Financial Officer) sold 373 shares @ $202.61 ($75.6K) on 2026-08-19</t>
         </is>
       </c>
-      <c r="F1230" t="inlineStr"/>
-      <c r="G1230" t="inlineStr"/>
-      <c r="H1230" t="inlineStr"/>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
@@ -40430,9 +40397,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$485.2K) on/after 08/20/2026</t>
         </is>
       </c>
-      <c r="F1231" t="inlineStr"/>
-      <c r="G1231" t="inlineStr"/>
-      <c r="H1231" t="inlineStr"/>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
@@ -40460,9 +40424,6 @@
           <t>[ROUTINE] Employee stock plan registration</t>
         </is>
       </c>
-      <c r="F1232" t="inlineStr"/>
-      <c r="G1232" t="inlineStr"/>
-      <c r="H1232" t="inlineStr"/>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
@@ -40490,9 +40451,6 @@
           <t>[MATERIAL] Annual report</t>
         </is>
       </c>
-      <c r="F1233" t="inlineStr"/>
-      <c r="G1233" t="inlineStr"/>
-      <c r="H1233" t="inlineStr"/>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
@@ -40520,9 +40478,6 @@
           <t>15 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1234" t="inlineStr"/>
-      <c r="G1234" t="inlineStr"/>
-      <c r="H1234" t="inlineStr"/>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
@@ -40550,9 +40505,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F1235" t="inlineStr"/>
-      <c r="G1235" t="inlineStr"/>
-      <c r="H1235" t="inlineStr"/>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
@@ -40580,9 +40532,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1236" t="inlineStr"/>
-      <c r="G1236" t="inlineStr"/>
-      <c r="H1236" t="inlineStr"/>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
@@ -40610,9 +40559,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1237" t="inlineStr"/>
-      <c r="G1237" t="inlineStr"/>
-      <c r="H1237" t="inlineStr"/>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
@@ -40640,9 +40586,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1238" t="inlineStr"/>
-      <c r="G1238" t="inlineStr"/>
-      <c r="H1238" t="inlineStr"/>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
@@ -40670,9 +40613,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Mirgorodskaya Natalia (Officer) plans to sell 586 shares (~$16.5K) on/after 08/20/2026</t>
         </is>
       </c>
-      <c r="F1239" t="inlineStr"/>
-      <c r="G1239" t="inlineStr"/>
-      <c r="H1239" t="inlineStr"/>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
@@ -40700,9 +40640,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Darling Scott (Officer) plans to sell 7,696 shares (~$216.2K) on/after 08/20/2026</t>
         </is>
       </c>
-      <c r="F1240" t="inlineStr"/>
-      <c r="G1240" t="inlineStr"/>
-      <c r="H1240" t="inlineStr"/>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
@@ -40730,9 +40667,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Datta Sanjay (Officer) plans to sell 8,945 shares (~$251.3K) on/after 08/20/2026</t>
         </is>
       </c>
-      <c r="F1241" t="inlineStr"/>
-      <c r="G1241" t="inlineStr"/>
-      <c r="H1241" t="inlineStr"/>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
@@ -40760,9 +40694,975 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1242" t="inlineStr"/>
-      <c r="G1242" t="inlineStr"/>
-      <c r="H1242" t="inlineStr"/>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>https://ir.logitech.com</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>https://www.bookingholdings.com/careers</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr"/>
+      <c r="G1260" t="inlineStr"/>
+      <c r="H1260" t="inlineStr"/>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr"/>
+      <c r="G1261" t="inlineStr"/>
+      <c r="H1261" t="inlineStr"/>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=8112138</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>New senior role: Chief of Staff, Online Grocery</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr"/>
+      <c r="G1262" t="inlineStr"/>
+      <c r="H1262" t="inlineStr"/>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=8112136</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>New senior role: Chief of Staff, Online Grocery</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr"/>
+      <c r="G1263" t="inlineStr"/>
+      <c r="H1263" t="inlineStr"/>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr"/>
+      <c r="G1264" t="inlineStr"/>
+      <c r="H1264" t="inlineStr"/>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr"/>
+      <c r="G1265" t="inlineStr"/>
+      <c r="H1265" t="inlineStr"/>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/duolingo</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr"/>
+      <c r="G1266" t="inlineStr"/>
+      <c r="H1266" t="inlineStr"/>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>https://mtch.com/news</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr"/>
+      <c r="G1267" t="inlineStr"/>
+      <c r="H1267" t="inlineStr"/>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr"/>
+      <c r="G1268" t="inlineStr"/>
+      <c r="H1268" t="inlineStr"/>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>https://investors.block.xyz</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr"/>
+      <c r="G1269" t="inlineStr"/>
+      <c r="H1269" t="inlineStr"/>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>29 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr"/>
+      <c r="G1270" t="inlineStr"/>
+      <c r="H1270" t="inlineStr"/>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>https://dave.com/careers</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr"/>
+      <c r="G1271" t="inlineStr"/>
+      <c r="H1271" t="inlineStr"/>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>8 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr"/>
+      <c r="G1272" t="inlineStr"/>
+      <c r="H1272" t="inlineStr"/>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>10 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr"/>
+      <c r="G1273" t="inlineStr"/>
+      <c r="H1273" t="inlineStr"/>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>https://careers.upstart.com/jobs?gh_jid=8145076</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>New senior role: Head of Borrower Success</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr"/>
+      <c r="G1274" t="inlineStr"/>
+      <c r="H1274" t="inlineStr"/>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr"/>
+      <c r="G1275" t="inlineStr"/>
+      <c r="H1275" t="inlineStr"/>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr"/>
+      <c r="G1276" t="inlineStr"/>
+      <c r="H1276" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1276"/>
+  <dimension ref="A1:H1406"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -41180,9 +41180,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1260" t="inlineStr"/>
-      <c r="G1260" t="inlineStr"/>
-      <c r="H1260" t="inlineStr"/>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
@@ -41210,9 +41207,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F1261" t="inlineStr"/>
-      <c r="G1261" t="inlineStr"/>
-      <c r="H1261" t="inlineStr"/>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
@@ -41240,9 +41234,6 @@
           <t>New senior role: Chief of Staff, Online Grocery</t>
         </is>
       </c>
-      <c r="F1262" t="inlineStr"/>
-      <c r="G1262" t="inlineStr"/>
-      <c r="H1262" t="inlineStr"/>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
@@ -41270,9 +41261,6 @@
           <t>New senior role: Chief of Staff, Online Grocery</t>
         </is>
       </c>
-      <c r="F1263" t="inlineStr"/>
-      <c r="G1263" t="inlineStr"/>
-      <c r="H1263" t="inlineStr"/>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
@@ -41300,9 +41288,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1264" t="inlineStr"/>
-      <c r="G1264" t="inlineStr"/>
-      <c r="H1264" t="inlineStr"/>
     </row>
     <row r="1265">
       <c r="A1265" t="inlineStr">
@@ -41330,9 +41315,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F1265" t="inlineStr"/>
-      <c r="G1265" t="inlineStr"/>
-      <c r="H1265" t="inlineStr"/>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
@@ -41360,9 +41342,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1266" t="inlineStr"/>
-      <c r="G1266" t="inlineStr"/>
-      <c r="H1266" t="inlineStr"/>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
@@ -41390,9 +41369,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1267" t="inlineStr"/>
-      <c r="G1267" t="inlineStr"/>
-      <c r="H1267" t="inlineStr"/>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
@@ -41420,9 +41396,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1268" t="inlineStr"/>
-      <c r="G1268" t="inlineStr"/>
-      <c r="H1268" t="inlineStr"/>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
@@ -41450,9 +41423,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F1269" t="inlineStr"/>
-      <c r="G1269" t="inlineStr"/>
-      <c r="H1269" t="inlineStr"/>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
@@ -41480,9 +41450,6 @@
           <t>29 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1270" t="inlineStr"/>
-      <c r="G1270" t="inlineStr"/>
-      <c r="H1270" t="inlineStr"/>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
@@ -41510,9 +41477,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1271" t="inlineStr"/>
-      <c r="G1271" t="inlineStr"/>
-      <c r="H1271" t="inlineStr"/>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
@@ -41540,9 +41504,6 @@
           <t>8 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1272" t="inlineStr"/>
-      <c r="G1272" t="inlineStr"/>
-      <c r="H1272" t="inlineStr"/>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
@@ -41570,9 +41531,6 @@
           <t>10 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1273" t="inlineStr"/>
-      <c r="G1273" t="inlineStr"/>
-      <c r="H1273" t="inlineStr"/>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
@@ -41600,9 +41558,6 @@
           <t>New senior role: Head of Borrower Success</t>
         </is>
       </c>
-      <c r="F1274" t="inlineStr"/>
-      <c r="G1274" t="inlineStr"/>
-      <c r="H1274" t="inlineStr"/>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
@@ -41630,9 +41585,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1275" t="inlineStr"/>
-      <c r="G1275" t="inlineStr"/>
-      <c r="H1275" t="inlineStr"/>
     </row>
     <row r="1276">
       <c r="A1276" t="inlineStr">
@@ -41660,9 +41612,3696 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1276" t="inlineStr"/>
-      <c r="G1276" t="inlineStr"/>
-      <c r="H1276" t="inlineStr"/>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>https://ir.logitech.com</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>Garmin Ltd.</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>https://newsroom.garmin.com</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1759509/000195004726008684/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Whiteside Janey (Director) plans to sell 5,480 shares (~$96.9K) on/after 08/25/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1759509/000203482626000009/xslF345X06/form4-08242026_100845.xml</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Llewellyn Lindsay Catherine (SEE REMARKS) 23,161 shares withheld for taxes (vest event) on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1759509/000178022726000005/xslF345X06/form4-08242026_100829.xml</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hope Stephen W. (CHIEF ACCOUNTING OFFICER) 29,507 shares withheld for taxes (vest event) on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1759509/000167594826000005/xslF345X06/form4-08242026_100858.xml</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Brewer Erin (CHIEF FINANCIAL OFFICER) 186,735 shares withheld for taxes (vest event) on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1324424/000122520826007317/xslF345X06/doc4.xml</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Dzielak Robert J (Chief Legal Officer &amp; Sec'y) sold 1,004 shares @ $335.00 ($336.3K) on 2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>https://www.bookingholdings.com/about/leadership/</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000195917326006451/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Blecharczyk Nathan (Officer) plans to sell 202,652 shares (~$38.56M) on/after 08/25/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000195917326006405/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Blecharczyk Nathan (Officer) plans to sell 150,640 shares (~$28.76M) on/after 08/24/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>YOU</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>Clear Secure, Inc.</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>https://www.clearme.com/terms</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>https://blog.google</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000192109426000951/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Silbermann Benjamin (Director) plans to sell 46,875 shares (~$1.10M) on/after 08/25/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000205176926000008/xslF345X06/wk-form4_1787603583.xml</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Madrigal Matthew (Chief Product &amp; Tech. Officer) 27,343 shares withheld for taxes (vest event) on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1713445/000195004726008650/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — A Sauerberg Jr 2002 Rev Tr Robert (Director) plans to sell 5,128 shares (~$820.1K) on/after 08/25/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1713445/000182701126000035/xslF345X06/wk-form4_1787606625.xml</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Huffman Steve Ladd (CEO &amp; President) 40,336 shares withheld for taxes (vest event) on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1713445/000192427826000005/xslF345X06/wk-form4_1787606603.xml</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lee Benjamin Seong (Chief Legal Officer) 3,887 shares withheld for taxes (vest event) on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1713445/000192427926000005/xslF345X06/wk-form4_1787606569.xml</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Reynolds Michelle Marie (Chief Accounting Officer) 1,265 shares withheld for taxes (vest event) on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1713445/000166365126000018/xslF345X06/wk-form4_1787606536.xml</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Wong Jennifer L. (Chief Operating Officer) 38,113 shares withheld for taxes (vest event) on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1713445/000169929426000013/xslF345X06/wk-form4_1787606513.xml</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Vollero Andrew (Chief Financial Officer) 10,319 shares withheld for taxes (vest event) on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>AppLovin Corporation</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>https://www.applovin.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810806/000192109426000955/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Bromberg Matthew S (Officer) plans to sell 16,383 shares (~$742.3K) on/after 08/25/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810806/000192109426000954/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Yahes Jarrod (Officer) plans to sell 26,017 shares (~$1.18M) on/after 08/25/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810806/000192109426000953/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Boyden Rebecca Berenice (Officer) plans to sell 1,032 shares (~$46.8K) on/after 08/25/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810806/000192109426000952/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Blum Alexander (Officer) plans to sell 20,595 shares (~$933.1K) on/after 08/25/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com/premium</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>BBY</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>Best Buy Co., Inc.</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>https://www.bestbuy.com/site/help-topics/terms-and-conditions/pcmcat204400050067.c</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>Warner Music Group Corp.</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>https://www.wmg.com/news/</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1335258/000143911526000007/xslF345X06/wk-form4_1787691889.xml</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Capo Brian (Chief Accounting Officer) sold 2,900 shares @ $184.00 ($533.6K) on 2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1335258/000195004726008631/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Capo Brian (Officer) plans to sell 2,900 shares (~$533.6K) on/after 08/24/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1337634/000162828026058959/xslF345X06/wk-form4_1787695297.xml</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Streams Mark (See Remarks) sold 166,676 shares @ $6.78 ($1.13M) on 2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1337634/000196858226000881/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Nayaab Islam (Officer) plans to sell 1,098,682 shares (~$7.33M) on/after 08/25/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>OUTFRONT Media Inc.</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579877/000208290026000006/xslF345X06/wk-form4_1787621565.xml</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Norton James Michael (EVP, CRO, Enterprise) granted 426 shares on 2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>LAMR</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>Lamar Advertising Company</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>https://www.lamar.com/about/careers</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000195004726008680/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Rawlings Amy (Officer) plans to sell 237 shares (~$9.2K) on/after 08/25/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000131509826000177/xslF345X06/wk-form4_1787689755.xml</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sean Jack Buckley (Chief People &amp; Systems Officer) sold 4,321 shares @ $38.68 ($167.1K) on 2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000131509826000175/xslF345X06/wk-form4_1787604042.xml</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Kaufman Matthew D (Chief Safety Officer) sold 14,904 shares @ $37.96 ($565.8K) on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000131509826000174/xslF345X06/wk-form4_1787603989.xml</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sean Jack Buckley (Chief People &amp; Systems Officer) sold 5,607 shares @ $37.97 ($212.9K) on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000131509826000173/xslF345X06/wk-form4_1787603949.xml</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Rawlings Amy Marie (Chief Accounting Officer) sold 5,061 shares @ $37.97 ($192.1K) on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000131509826000172/xslF345X06/wk-form4_1787603884.xml</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Naveen K. Chopra (Chief Financial Officer) sold 17,509 shares @ $37.96 ($664.7K) on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000131509826000171/xslF345X06/wk-form4_1787603853.xml</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Reinstra Mark (Chief Legal Off. &amp; Corp. Sec.) sold 17,934 shares @ $37.96 ($680.8K) on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000131509826000170/xslF345X06/wk-form4_1787603811.xml</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Baszucki David (President &amp; CEO) sold 52,568 shares @ $37.96 ($2.00M) on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000131509826000169/xslF345X06/wk-form4_1787603773.xml</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Baszucki Gregory (Director) other: 1,296 shares on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000131509826000168/xslF345X06/wk-form4_1787603715.xml</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Jason Kilar (Director) other: 1,296 Class  A Common Stock on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000131509826000167/xslF345X06/wk-form4_1787603646.xml</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Mastantuono Gina (Director) other: 1,296 shares on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000192109426000943/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Sean Jack Buckley (Officer) plans to sell 4,321 shares (~$167.1K) on/after 08/24/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>https://investors.intuit.com</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/896878/000089687826000029/intu-20260825.htm</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>https://mediacenter.adp.com</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/8670/000122520826007307/xslF345X06/doc4.xml</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Michaud Brian L. (Executive VP) sold 120 shares @ $279.70 ($33.6K) on 2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/8670/000122520826007306/xslF345X06/doc4.xml</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Kwon David (Corp VP) sold 798 shares @ $280.00 ($223.4K) on 2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>Paychex, Inc.</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>https://www.paychex.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000196858226000875/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Steven I. Sarowitz (Director) plans to sell 75,000 shares (~$11.50M) on/after 08/24/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1347" t="inlineStr"/>
+      <c r="G1347" t="inlineStr"/>
+      <c r="H1347" t="inlineStr"/>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/press-room/home/post/wix-to-participate-in-fireside-chat-at-citi-s-2026-global-technology-conference</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>newsroom: Wix to Participate in Fireside Chat at Citi's 2026 Global Technology Conference</t>
+        </is>
+      </c>
+      <c r="F1348" t="inlineStr"/>
+      <c r="G1348" t="inlineStr"/>
+      <c r="H1348" t="inlineStr"/>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/press-room/home/post/wix-and-gemini-join-forces-to-integrate-website-building-into-everyday-workflows</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>newsroom: Wix and Gemini Join Forces to Integrate Website Building Into Everyday Workflows</t>
+        </is>
+      </c>
+      <c r="F1349" t="inlineStr"/>
+      <c r="G1349" t="inlineStr"/>
+      <c r="H1349" t="inlineStr"/>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000197640826000768/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Nir Zohar (Officer) plans to sell 29,026 shares (~$2.45M) on/after 08/25/2026</t>
+        </is>
+      </c>
+      <c r="F1350" t="inlineStr"/>
+      <c r="G1350" t="inlineStr"/>
+      <c r="H1350" t="inlineStr"/>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000197640826000764/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Nir Zohar (Officer) plans to sell 974 shares (~$79.9K) on/after 08/24/2026</t>
+        </is>
+      </c>
+      <c r="F1351" t="inlineStr"/>
+      <c r="G1351" t="inlineStr"/>
+      <c r="H1351" t="inlineStr"/>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>GLBE</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>Global-E Online Ltd.</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1835963/000119312526362309/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Tamari Shahar (COO) sold 24,999 shares @ $41.63 ($1.04M) on 2026-08-19</t>
+        </is>
+      </c>
+      <c r="F1352" t="inlineStr"/>
+      <c r="G1352" t="inlineStr"/>
+      <c r="H1352" t="inlineStr"/>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F1353" t="inlineStr"/>
+      <c r="G1353" t="inlineStr"/>
+      <c r="H1353" t="inlineStr"/>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>https://www.ebayinc.com/stories/news/</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1354" t="inlineStr"/>
+      <c r="G1354" t="inlineStr"/>
+      <c r="H1354" t="inlineStr"/>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1355" t="inlineStr"/>
+      <c r="G1355" t="inlineStr"/>
+      <c r="H1355" t="inlineStr"/>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726008676/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Xu Tony (Director) plans to sell 3,767 shares (~$862.9K) on/after 08/25/2026</t>
+        </is>
+      </c>
+      <c r="F1356" t="inlineStr"/>
+      <c r="G1356" t="inlineStr"/>
+      <c r="H1356" t="inlineStr"/>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726008674/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Adarkar Prabir (Officer) plans to sell 55,289 shares (~$12.66M) on/after 08/25/2026</t>
+        </is>
+      </c>
+      <c r="F1357" t="inlineStr"/>
+      <c r="G1357" t="inlineStr"/>
+      <c r="H1357" t="inlineStr"/>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726008622/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Xu Tony (Director) plans to sell 29,567 shares (~$6.61M) on/after 08/24/2026</t>
+        </is>
+      </c>
+      <c r="F1358" t="inlineStr"/>
+      <c r="G1358" t="inlineStr"/>
+      <c r="H1358" t="inlineStr"/>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726008621/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Sherringham Tia (Officer) plans to sell 5,223 shares (~$1.17M) on/after 08/24/2026</t>
+        </is>
+      </c>
+      <c r="F1359" t="inlineStr"/>
+      <c r="G1359" t="inlineStr"/>
+      <c r="H1359" t="inlineStr"/>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726008593/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Lee Gordon (Officer) plans to sell 2,204 shares (~$492.6K) on/after 08/24/2026</t>
+        </is>
+      </c>
+      <c r="F1360" t="inlineStr"/>
+      <c r="G1360" t="inlineStr"/>
+      <c r="H1360" t="inlineStr"/>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183261426000028/xslF345X06/form4-08242026_040812.xml</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Tang Stanley (Director) sold 84,526 shares @ $225.03 ($19.02M) on 2026-08-20</t>
+        </is>
+      </c>
+      <c r="F1361" t="inlineStr"/>
+      <c r="G1361" t="inlineStr"/>
+      <c r="H1361" t="inlineStr"/>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000163564826000012/xslF345X06/form4-08242026_040811.xml</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lee Gordon S (CHIEF ACCOUNTING OFFICER) sold 2,911 shares @ $220.62 ($642.2K) on 2026-08-20</t>
+        </is>
+      </c>
+      <c r="F1362" t="inlineStr"/>
+      <c r="G1362" t="inlineStr"/>
+      <c r="H1362" t="inlineStr"/>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183261226000016/xslF345X06/form4-08242026_040809.xml</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Adarkar Prabir (PRESIDENT AND COO) sold 17,126 shares @ $220.62 ($3.78M) on 2026-08-20</t>
+        </is>
+      </c>
+      <c r="F1363" t="inlineStr"/>
+      <c r="G1363" t="inlineStr"/>
+      <c r="H1363" t="inlineStr"/>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000184970926000018/xslF345X06/form4-08242026_040807.xml</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Inukonda Ravi (CHIEF FINANCIAL OFFICER) sold 19,505 shares @ $220.62 ($4.30M) on 2026-08-20</t>
+        </is>
+      </c>
+      <c r="F1364" t="inlineStr"/>
+      <c r="G1364" t="inlineStr"/>
+      <c r="H1364" t="inlineStr"/>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000189968826000014/xslF345X06/form4-08242026_040805.xml</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sherringham Tia (GENERAL COUNSEL AND SECRETARY) sold 7,689 shares @ $220.62 ($1.70M) on 2026-08-20</t>
+        </is>
+      </c>
+      <c r="F1365" t="inlineStr"/>
+      <c r="G1365" t="inlineStr"/>
+      <c r="H1365" t="inlineStr"/>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183355226000014/xslF345X06/form4-08242026_040804.xml</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Yandell Keith (CHIEF BUSINESS OFFICER) sold 7,962 shares @ $220.62 ($1.76M) on 2026-08-20</t>
+        </is>
+      </c>
+      <c r="F1366" t="inlineStr"/>
+      <c r="G1366" t="inlineStr"/>
+      <c r="H1366" t="inlineStr"/>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183239026000021/xslF345X06/form4-08242026_040802.xml</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Fang Andy (Director) sold 1,591 shares @ $220.62 ($351.0K) on 2026-08-20</t>
+        </is>
+      </c>
+      <c r="F1367" t="inlineStr"/>
+      <c r="G1367" t="inlineStr"/>
+      <c r="H1367" t="inlineStr"/>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>9 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1368" t="inlineStr"/>
+      <c r="G1368" t="inlineStr"/>
+      <c r="H1368" t="inlineStr"/>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/company/newsroom</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1369" t="inlineStr"/>
+      <c r="G1369" t="inlineStr"/>
+      <c r="H1369" t="inlineStr"/>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000192109426000941/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Fong Morgan (Officer) plans to sell 18,390 shares (~$918.8K) on/after 08/24/2026</t>
+        </is>
+      </c>
+      <c r="F1370" t="inlineStr"/>
+      <c r="G1370" t="inlineStr"/>
+      <c r="H1370" t="inlineStr"/>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>https://careers.duolingo.com/jobs/8747077002?gh_jid=8747077002</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>New senior role: VP of Product, Growth and Monetization</t>
+        </is>
+      </c>
+      <c r="F1371" t="inlineStr"/>
+      <c r="G1371" t="inlineStr"/>
+      <c r="H1371" t="inlineStr"/>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>https://careers.duolingo.com/jobs/8747060002?gh_jid=8747060002</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>New senior role: VP of Product, Growth and Monetization</t>
+        </is>
+      </c>
+      <c r="F1372" t="inlineStr"/>
+      <c r="G1372" t="inlineStr"/>
+      <c r="H1372" t="inlineStr"/>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/duolingo</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>12 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1373" t="inlineStr"/>
+      <c r="G1373" t="inlineStr"/>
+      <c r="H1373" t="inlineStr"/>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>https://blog.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1374" t="inlineStr"/>
+      <c r="G1374" t="inlineStr"/>
+      <c r="H1374" t="inlineStr"/>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1617640/000161764026000056/z-20260822.htm</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F1375" t="inlineStr"/>
+      <c r="G1375" t="inlineStr"/>
+      <c r="H1375" t="inlineStr"/>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1376" t="inlineStr"/>
+      <c r="G1376" t="inlineStr"/>
+      <c r="H1376" t="inlineStr"/>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>APPF</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>AppFolio Inc.</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1433195/000093833326000023/xslF345X06/form4-08242026_090815.xml</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Maurice J Duca (10%+ owner) sold 9,856 shares @ $218.87 ($2.16M) on 2026-08-20</t>
+        </is>
+      </c>
+      <c r="F1377" t="inlineStr"/>
+      <c r="G1377" t="inlineStr"/>
+      <c r="H1377" t="inlineStr"/>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>https://investors.block.xyz</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F1378" t="inlineStr"/>
+      <c r="G1378" t="inlineStr"/>
+      <c r="H1378" t="inlineStr"/>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726008664/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$490.9K) on/after 08/25/2026</t>
+        </is>
+      </c>
+      <c r="F1379" t="inlineStr"/>
+      <c r="G1379" t="inlineStr"/>
+      <c r="H1379" t="inlineStr"/>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000162828026058747/xslF345X06/wk-form4_1787615759.xml</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Eisen Anthony Mathew (Director) sold 18,000 shares @ $80.80 ($1.45M) on 2026-08-20</t>
+        </is>
+      </c>
+      <c r="F1380" t="inlineStr"/>
+      <c r="G1380" t="inlineStr"/>
+      <c r="H1380" t="inlineStr"/>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000162828026058746/xslF345X06/wk-form4_1787615716.xml</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Jennings Owen Britton (Business Lead) sold 1,901 shares @ $81.04 ($154.1K) on 2026-08-21</t>
+        </is>
+      </c>
+      <c r="F1381" t="inlineStr"/>
+      <c r="G1381" t="inlineStr"/>
+      <c r="H1381" t="inlineStr"/>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000162828026058745/xslF345X06/wk-form4_1787615675.xml</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Grassadonia Brian (Ecosystem Lead) sold 8,173 shares @ $82.42 ($673.6K) on 2026-08-24</t>
+        </is>
+      </c>
+      <c r="F1382" t="inlineStr"/>
+      <c r="G1382" t="inlineStr"/>
+      <c r="H1382" t="inlineStr"/>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000162828026058744/xslF345X06/wk-form4_1787615641.xml</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Ahuja Amrita (CFO &amp; COO) sold 12,612 shares @ $81.84 ($1.03M) on 2026-08-21</t>
+        </is>
+      </c>
+      <c r="F1383" t="inlineStr"/>
+      <c r="G1383" t="inlineStr"/>
+      <c r="H1383" t="inlineStr"/>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000162828026058743/xslF345X06/wk-form4_1787615575.xml</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Esperanza Chrysty (Chief Legal Officer) 8,376 shares withheld for taxes (vest event) on 2026-08-20</t>
+        </is>
+      </c>
+      <c r="F1384" t="inlineStr"/>
+      <c r="G1384" t="inlineStr"/>
+      <c r="H1384" t="inlineStr"/>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000162828026058741/xslF345X06/wk-form4_1787615330.xml</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Acosta Andrea (Chief Accounting Officer) 5,709 shares withheld for taxes (vest event) on 2026-08-20</t>
+        </is>
+      </c>
+      <c r="F1385" t="inlineStr"/>
+      <c r="G1385" t="inlineStr"/>
+      <c r="H1385" t="inlineStr"/>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726008589/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$488.9K) on/after 08/24/2026</t>
+        </is>
+      </c>
+      <c r="F1386" t="inlineStr"/>
+      <c r="G1386" t="inlineStr"/>
+      <c r="H1386" t="inlineStr"/>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726008581/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Ahuja Amrita (Officer) plans to sell 9,511 shares (~$784.0K) on/after 08/24/2026</t>
+        </is>
+      </c>
+      <c r="F1387" t="inlineStr"/>
+      <c r="G1387" t="inlineStr"/>
+      <c r="H1387" t="inlineStr"/>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726008580/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Grassadonia Brian (Officer) plans to sell 8,173 shares (~$673.6K) on/after 08/24/2026</t>
+        </is>
+      </c>
+      <c r="F1388" t="inlineStr"/>
+      <c r="G1388" t="inlineStr"/>
+      <c r="H1388" t="inlineStr"/>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726008578/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — B Jennings Owen (Officer) plans to sell 1,317 shares (~$107.3K) on/after 08/24/2026</t>
+        </is>
+      </c>
+      <c r="F1389" t="inlineStr"/>
+      <c r="G1389" t="inlineStr"/>
+      <c r="H1389" t="inlineStr"/>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000092189526002296/xslSCHEDULE_13D_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ active owner disclosure</t>
+        </is>
+      </c>
+      <c r="F1390" t="inlineStr"/>
+      <c r="G1390" t="inlineStr"/>
+      <c r="H1390" t="inlineStr"/>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>https://careers.toasttab.com/jobs?gh_jid=7996612</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>New senior role: Director of Product Management, Enterprise</t>
+        </is>
+      </c>
+      <c r="F1391" t="inlineStr"/>
+      <c r="G1391" t="inlineStr"/>
+      <c r="H1391" t="inlineStr"/>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>29 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1392" t="inlineStr"/>
+      <c r="G1392" t="inlineStr"/>
+      <c r="H1392" t="inlineStr"/>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1650164/000165016426000185/xslF345X06/wk-form4_1787690180.xml</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Vassil Jonathan (Chief Revenue Officer) sold 85,280 shares @ $36.34 ($3.10M) on 2026-08-21</t>
+        </is>
+      </c>
+      <c r="F1393" t="inlineStr"/>
+      <c r="G1393" t="inlineStr"/>
+      <c r="H1393" t="inlineStr"/>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>Sezzle Inc.</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1662991/000195917326006428/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Brehm Kyle M. (Director) plans to sell 1,000 shares (~$118.2K) on/after 08/25/2026</t>
+        </is>
+      </c>
+      <c r="F1394" t="inlineStr"/>
+      <c r="G1394" t="inlineStr"/>
+      <c r="H1394" t="inlineStr"/>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>Sezzle Inc.</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1662991/000166299126000146/xslF345X06/wk-form4_1787607068.xml</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Khurana Rajeev (General Counsel) BOUGHT 129 shares @ $115.88 ($15.0K) on 2026-08-20</t>
+        </is>
+      </c>
+      <c r="F1395" t="inlineStr"/>
+      <c r="G1395" t="inlineStr"/>
+      <c r="H1395" t="inlineStr"/>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>https://dave.com/careers</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1396" t="inlineStr"/>
+      <c r="G1396" t="inlineStr"/>
+      <c r="H1396" t="inlineStr"/>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1397" t="inlineStr"/>
+      <c r="G1397" t="inlineStr"/>
+      <c r="H1397" t="inlineStr"/>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>KLAR</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>Klarna Group plc</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>https://investors.klarna.com/governance/leadership/default.aspx</t>
+        </is>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F1398" t="inlineStr"/>
+      <c r="G1398" t="inlineStr"/>
+      <c r="H1398" t="inlineStr"/>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1399" t="inlineStr"/>
+      <c r="G1399" t="inlineStr"/>
+      <c r="H1399" t="inlineStr"/>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000178387926000134/xslF345X06/wk-form4_1787689935.xml</t>
+        </is>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Robinhood Markets, Inc. (10%+ owner) sold 10,167 shares @ $26.82 ($272.7K) on 2026-08-21</t>
+        </is>
+      </c>
+      <c r="F1400" t="inlineStr"/>
+      <c r="G1400" t="inlineStr"/>
+      <c r="H1400" t="inlineStr"/>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1401" t="inlineStr"/>
+      <c r="G1401" t="inlineStr"/>
+      <c r="H1401" t="inlineStr"/>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1647639/000192109426000956/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Mirgorodskaya Natalia (Officer) plans to sell 913 shares (~$27.4K) on/after 08/25/2026</t>
+        </is>
+      </c>
+      <c r="F1402" t="inlineStr"/>
+      <c r="G1402" t="inlineStr"/>
+      <c r="H1402" t="inlineStr"/>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>WSM</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>Williams-Sonoma Inc.</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/719955/000071995526000203/wsm-20260826.htm</t>
+        </is>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F1403" t="inlineStr"/>
+      <c r="G1403" t="inlineStr"/>
+      <c r="H1403" t="inlineStr"/>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>SGI</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>Somnigroup International Inc. (fmr. Tempur Sealy)</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1206264/000120626426000117/sgi-20260825.htm</t>
+        </is>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F1404" t="inlineStr"/>
+      <c r="G1404" t="inlineStr"/>
+      <c r="H1404" t="inlineStr"/>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>ENVA</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>Enova International Inc.</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1529864/000162828026058974/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — David Fisher (Officer) plans to sell 28,500 shares (~$7.12M) on/after 08/25/2026</t>
+        </is>
+      </c>
+      <c r="F1405" t="inlineStr"/>
+      <c r="G1405" t="inlineStr"/>
+      <c r="H1405" t="inlineStr"/>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1406" t="inlineStr"/>
+      <c r="G1406" t="inlineStr"/>
+      <c r="H1406" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1406"/>
+  <dimension ref="A1:H1500"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -43529,9 +43529,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1347" t="inlineStr"/>
-      <c r="G1347" t="inlineStr"/>
-      <c r="H1347" t="inlineStr"/>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
@@ -43559,9 +43556,6 @@
           <t>newsroom: Wix to Participate in Fireside Chat at Citi's 2026 Global Technology Conference</t>
         </is>
       </c>
-      <c r="F1348" t="inlineStr"/>
-      <c r="G1348" t="inlineStr"/>
-      <c r="H1348" t="inlineStr"/>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
@@ -43589,9 +43583,6 @@
           <t>newsroom: Wix and Gemini Join Forces to Integrate Website Building Into Everyday Workflows</t>
         </is>
       </c>
-      <c r="F1349" t="inlineStr"/>
-      <c r="G1349" t="inlineStr"/>
-      <c r="H1349" t="inlineStr"/>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
@@ -43619,9 +43610,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Nir Zohar (Officer) plans to sell 29,026 shares (~$2.45M) on/after 08/25/2026</t>
         </is>
       </c>
-      <c r="F1350" t="inlineStr"/>
-      <c r="G1350" t="inlineStr"/>
-      <c r="H1350" t="inlineStr"/>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
@@ -43649,9 +43637,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Nir Zohar (Officer) plans to sell 974 shares (~$79.9K) on/after 08/24/2026</t>
         </is>
       </c>
-      <c r="F1351" t="inlineStr"/>
-      <c r="G1351" t="inlineStr"/>
-      <c r="H1351" t="inlineStr"/>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
@@ -43679,9 +43664,6 @@
           <t>[ROUTINE] Insider trade — Tamari Shahar (COO) sold 24,999 shares @ $41.63 ($1.04M) on 2026-08-19</t>
         </is>
       </c>
-      <c r="F1352" t="inlineStr"/>
-      <c r="G1352" t="inlineStr"/>
-      <c r="H1352" t="inlineStr"/>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
@@ -43709,9 +43691,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F1353" t="inlineStr"/>
-      <c r="G1353" t="inlineStr"/>
-      <c r="H1353" t="inlineStr"/>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
@@ -43739,9 +43718,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1354" t="inlineStr"/>
-      <c r="G1354" t="inlineStr"/>
-      <c r="H1354" t="inlineStr"/>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
@@ -43769,9 +43745,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1355" t="inlineStr"/>
-      <c r="G1355" t="inlineStr"/>
-      <c r="H1355" t="inlineStr"/>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
@@ -43799,9 +43772,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Xu Tony (Director) plans to sell 3,767 shares (~$862.9K) on/after 08/25/2026</t>
         </is>
       </c>
-      <c r="F1356" t="inlineStr"/>
-      <c r="G1356" t="inlineStr"/>
-      <c r="H1356" t="inlineStr"/>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
@@ -43829,9 +43799,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Adarkar Prabir (Officer) plans to sell 55,289 shares (~$12.66M) on/after 08/25/2026</t>
         </is>
       </c>
-      <c r="F1357" t="inlineStr"/>
-      <c r="G1357" t="inlineStr"/>
-      <c r="H1357" t="inlineStr"/>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
@@ -43859,9 +43826,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Xu Tony (Director) plans to sell 29,567 shares (~$6.61M) on/after 08/24/2026</t>
         </is>
       </c>
-      <c r="F1358" t="inlineStr"/>
-      <c r="G1358" t="inlineStr"/>
-      <c r="H1358" t="inlineStr"/>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
@@ -43889,9 +43853,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Sherringham Tia (Officer) plans to sell 5,223 shares (~$1.17M) on/after 08/24/2026</t>
         </is>
       </c>
-      <c r="F1359" t="inlineStr"/>
-      <c r="G1359" t="inlineStr"/>
-      <c r="H1359" t="inlineStr"/>
     </row>
     <row r="1360">
       <c r="A1360" t="inlineStr">
@@ -43919,9 +43880,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Lee Gordon (Officer) plans to sell 2,204 shares (~$492.6K) on/after 08/24/2026</t>
         </is>
       </c>
-      <c r="F1360" t="inlineStr"/>
-      <c r="G1360" t="inlineStr"/>
-      <c r="H1360" t="inlineStr"/>
     </row>
     <row r="1361">
       <c r="A1361" t="inlineStr">
@@ -43949,9 +43907,6 @@
           <t>[ROUTINE] Insider trade — Tang Stanley (Director) sold 84,526 shares @ $225.03 ($19.02M) on 2026-08-20</t>
         </is>
       </c>
-      <c r="F1361" t="inlineStr"/>
-      <c r="G1361" t="inlineStr"/>
-      <c r="H1361" t="inlineStr"/>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
@@ -43979,9 +43934,6 @@
           <t>[ROUTINE] Insider trade — Lee Gordon S (CHIEF ACCOUNTING OFFICER) sold 2,911 shares @ $220.62 ($642.2K) on 2026-08-20</t>
         </is>
       </c>
-      <c r="F1362" t="inlineStr"/>
-      <c r="G1362" t="inlineStr"/>
-      <c r="H1362" t="inlineStr"/>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
@@ -44009,9 +43961,6 @@
           <t>[ROUTINE] Insider trade — Adarkar Prabir (PRESIDENT AND COO) sold 17,126 shares @ $220.62 ($3.78M) on 2026-08-20</t>
         </is>
       </c>
-      <c r="F1363" t="inlineStr"/>
-      <c r="G1363" t="inlineStr"/>
-      <c r="H1363" t="inlineStr"/>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
@@ -44039,9 +43988,6 @@
           <t>[ROUTINE] Insider trade — Inukonda Ravi (CHIEF FINANCIAL OFFICER) sold 19,505 shares @ $220.62 ($4.30M) on 2026-08-20</t>
         </is>
       </c>
-      <c r="F1364" t="inlineStr"/>
-      <c r="G1364" t="inlineStr"/>
-      <c r="H1364" t="inlineStr"/>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
@@ -44069,9 +44015,6 @@
           <t>[ROUTINE] Insider trade — Sherringham Tia (GENERAL COUNSEL AND SECRETARY) sold 7,689 shares @ $220.62 ($1.70M) on 2026-08-20</t>
         </is>
       </c>
-      <c r="F1365" t="inlineStr"/>
-      <c r="G1365" t="inlineStr"/>
-      <c r="H1365" t="inlineStr"/>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
@@ -44099,9 +44042,6 @@
           <t>[ROUTINE] Insider trade — Yandell Keith (CHIEF BUSINESS OFFICER) sold 7,962 shares @ $220.62 ($1.76M) on 2026-08-20</t>
         </is>
       </c>
-      <c r="F1366" t="inlineStr"/>
-      <c r="G1366" t="inlineStr"/>
-      <c r="H1366" t="inlineStr"/>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
@@ -44129,9 +44069,6 @@
           <t>[ROUTINE] Insider trade — Fang Andy (Director) sold 1,591 shares @ $220.62 ($351.0K) on 2026-08-20</t>
         </is>
       </c>
-      <c r="F1367" t="inlineStr"/>
-      <c r="G1367" t="inlineStr"/>
-      <c r="H1367" t="inlineStr"/>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
@@ -44159,9 +44096,6 @@
           <t>9 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1368" t="inlineStr"/>
-      <c r="G1368" t="inlineStr"/>
-      <c r="H1368" t="inlineStr"/>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
@@ -44189,9 +44123,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1369" t="inlineStr"/>
-      <c r="G1369" t="inlineStr"/>
-      <c r="H1369" t="inlineStr"/>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
@@ -44219,9 +44150,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Fong Morgan (Officer) plans to sell 18,390 shares (~$918.8K) on/after 08/24/2026</t>
         </is>
       </c>
-      <c r="F1370" t="inlineStr"/>
-      <c r="G1370" t="inlineStr"/>
-      <c r="H1370" t="inlineStr"/>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
@@ -44249,9 +44177,6 @@
           <t>New senior role: VP of Product, Growth and Monetization</t>
         </is>
       </c>
-      <c r="F1371" t="inlineStr"/>
-      <c r="G1371" t="inlineStr"/>
-      <c r="H1371" t="inlineStr"/>
     </row>
     <row r="1372">
       <c r="A1372" t="inlineStr">
@@ -44279,9 +44204,6 @@
           <t>New senior role: VP of Product, Growth and Monetization</t>
         </is>
       </c>
-      <c r="F1372" t="inlineStr"/>
-      <c r="G1372" t="inlineStr"/>
-      <c r="H1372" t="inlineStr"/>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
@@ -44309,9 +44231,6 @@
           <t>12 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1373" t="inlineStr"/>
-      <c r="G1373" t="inlineStr"/>
-      <c r="H1373" t="inlineStr"/>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
@@ -44339,9 +44258,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1374" t="inlineStr"/>
-      <c r="G1374" t="inlineStr"/>
-      <c r="H1374" t="inlineStr"/>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
@@ -44369,9 +44285,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F1375" t="inlineStr"/>
-      <c r="G1375" t="inlineStr"/>
-      <c r="H1375" t="inlineStr"/>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
@@ -44399,9 +44312,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1376" t="inlineStr"/>
-      <c r="G1376" t="inlineStr"/>
-      <c r="H1376" t="inlineStr"/>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
@@ -44429,9 +44339,6 @@
           <t>[ROUTINE] Insider trade — Maurice J Duca (10%+ owner) sold 9,856 shares @ $218.87 ($2.16M) on 2026-08-20</t>
         </is>
       </c>
-      <c r="F1377" t="inlineStr"/>
-      <c r="G1377" t="inlineStr"/>
-      <c r="H1377" t="inlineStr"/>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
@@ -44459,9 +44366,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F1378" t="inlineStr"/>
-      <c r="G1378" t="inlineStr"/>
-      <c r="H1378" t="inlineStr"/>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
@@ -44489,9 +44393,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$490.9K) on/after 08/25/2026</t>
         </is>
       </c>
-      <c r="F1379" t="inlineStr"/>
-      <c r="G1379" t="inlineStr"/>
-      <c r="H1379" t="inlineStr"/>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
@@ -44519,9 +44420,6 @@
           <t>[ROUTINE] Insider trade — Eisen Anthony Mathew (Director) sold 18,000 shares @ $80.80 ($1.45M) on 2026-08-20</t>
         </is>
       </c>
-      <c r="F1380" t="inlineStr"/>
-      <c r="G1380" t="inlineStr"/>
-      <c r="H1380" t="inlineStr"/>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
@@ -44549,9 +44447,6 @@
           <t>[ROUTINE] Insider trade — Jennings Owen Britton (Business Lead) sold 1,901 shares @ $81.04 ($154.1K) on 2026-08-21</t>
         </is>
       </c>
-      <c r="F1381" t="inlineStr"/>
-      <c r="G1381" t="inlineStr"/>
-      <c r="H1381" t="inlineStr"/>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
@@ -44579,9 +44474,6 @@
           <t>[ROUTINE] Insider trade — Grassadonia Brian (Ecosystem Lead) sold 8,173 shares @ $82.42 ($673.6K) on 2026-08-24</t>
         </is>
       </c>
-      <c r="F1382" t="inlineStr"/>
-      <c r="G1382" t="inlineStr"/>
-      <c r="H1382" t="inlineStr"/>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
@@ -44609,9 +44501,6 @@
           <t>[ROUTINE] Insider trade — Ahuja Amrita (CFO &amp; COO) sold 12,612 shares @ $81.84 ($1.03M) on 2026-08-21</t>
         </is>
       </c>
-      <c r="F1383" t="inlineStr"/>
-      <c r="G1383" t="inlineStr"/>
-      <c r="H1383" t="inlineStr"/>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
@@ -44639,9 +44528,6 @@
           <t>[ROUTINE] Insider trade — Esperanza Chrysty (Chief Legal Officer) 8,376 shares withheld for taxes (vest event) on 2026-08-20</t>
         </is>
       </c>
-      <c r="F1384" t="inlineStr"/>
-      <c r="G1384" t="inlineStr"/>
-      <c r="H1384" t="inlineStr"/>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
@@ -44669,9 +44555,6 @@
           <t>[ROUTINE] Insider trade — Acosta Andrea (Chief Accounting Officer) 5,709 shares withheld for taxes (vest event) on 2026-08-20</t>
         </is>
       </c>
-      <c r="F1385" t="inlineStr"/>
-      <c r="G1385" t="inlineStr"/>
-      <c r="H1385" t="inlineStr"/>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
@@ -44699,9 +44582,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$488.9K) on/after 08/24/2026</t>
         </is>
       </c>
-      <c r="F1386" t="inlineStr"/>
-      <c r="G1386" t="inlineStr"/>
-      <c r="H1386" t="inlineStr"/>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
@@ -44729,9 +44609,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Ahuja Amrita (Officer) plans to sell 9,511 shares (~$784.0K) on/after 08/24/2026</t>
         </is>
       </c>
-      <c r="F1387" t="inlineStr"/>
-      <c r="G1387" t="inlineStr"/>
-      <c r="H1387" t="inlineStr"/>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
@@ -44759,9 +44636,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Grassadonia Brian (Officer) plans to sell 8,173 shares (~$673.6K) on/after 08/24/2026</t>
         </is>
       </c>
-      <c r="F1388" t="inlineStr"/>
-      <c r="G1388" t="inlineStr"/>
-      <c r="H1388" t="inlineStr"/>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
@@ -44789,9 +44663,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — B Jennings Owen (Officer) plans to sell 1,317 shares (~$107.3K) on/after 08/24/2026</t>
         </is>
       </c>
-      <c r="F1389" t="inlineStr"/>
-      <c r="G1389" t="inlineStr"/>
-      <c r="H1389" t="inlineStr"/>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
@@ -44819,9 +44690,6 @@
           <t>[MATERIAL] Update to 5%+ active owner disclosure</t>
         </is>
       </c>
-      <c r="F1390" t="inlineStr"/>
-      <c r="G1390" t="inlineStr"/>
-      <c r="H1390" t="inlineStr"/>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
@@ -44849,9 +44717,6 @@
           <t>New senior role: Director of Product Management, Enterprise</t>
         </is>
       </c>
-      <c r="F1391" t="inlineStr"/>
-      <c r="G1391" t="inlineStr"/>
-      <c r="H1391" t="inlineStr"/>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
@@ -44879,9 +44744,6 @@
           <t>29 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1392" t="inlineStr"/>
-      <c r="G1392" t="inlineStr"/>
-      <c r="H1392" t="inlineStr"/>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
@@ -44909,9 +44771,6 @@
           <t>[ROUTINE] Insider trade — Vassil Jonathan (Chief Revenue Officer) sold 85,280 shares @ $36.34 ($3.10M) on 2026-08-21</t>
         </is>
       </c>
-      <c r="F1393" t="inlineStr"/>
-      <c r="G1393" t="inlineStr"/>
-      <c r="H1393" t="inlineStr"/>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
@@ -44939,9 +44798,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Brehm Kyle M. (Director) plans to sell 1,000 shares (~$118.2K) on/after 08/25/2026</t>
         </is>
       </c>
-      <c r="F1394" t="inlineStr"/>
-      <c r="G1394" t="inlineStr"/>
-      <c r="H1394" t="inlineStr"/>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
@@ -44969,9 +44825,6 @@
           <t>[ROUTINE] Insider trade — Khurana Rajeev (General Counsel) BOUGHT 129 shares @ $115.88 ($15.0K) on 2026-08-20</t>
         </is>
       </c>
-      <c r="F1395" t="inlineStr"/>
-      <c r="G1395" t="inlineStr"/>
-      <c r="H1395" t="inlineStr"/>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
@@ -44999,9 +44852,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1396" t="inlineStr"/>
-      <c r="G1396" t="inlineStr"/>
-      <c r="H1396" t="inlineStr"/>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
@@ -45029,9 +44879,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1397" t="inlineStr"/>
-      <c r="G1397" t="inlineStr"/>
-      <c r="H1397" t="inlineStr"/>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
@@ -45059,9 +44906,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F1398" t="inlineStr"/>
-      <c r="G1398" t="inlineStr"/>
-      <c r="H1398" t="inlineStr"/>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
@@ -45089,9 +44933,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1399" t="inlineStr"/>
-      <c r="G1399" t="inlineStr"/>
-      <c r="H1399" t="inlineStr"/>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
@@ -45119,9 +44960,6 @@
           <t>[ROUTINE] Insider trade — Robinhood Markets, Inc. (10%+ owner) sold 10,167 shares @ $26.82 ($272.7K) on 2026-08-21</t>
         </is>
       </c>
-      <c r="F1400" t="inlineStr"/>
-      <c r="G1400" t="inlineStr"/>
-      <c r="H1400" t="inlineStr"/>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
@@ -45149,9 +44987,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1401" t="inlineStr"/>
-      <c r="G1401" t="inlineStr"/>
-      <c r="H1401" t="inlineStr"/>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
@@ -45179,9 +45014,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Mirgorodskaya Natalia (Officer) plans to sell 913 shares (~$27.4K) on/after 08/25/2026</t>
         </is>
       </c>
-      <c r="F1402" t="inlineStr"/>
-      <c r="G1402" t="inlineStr"/>
-      <c r="H1402" t="inlineStr"/>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
@@ -45209,9 +45041,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F1403" t="inlineStr"/>
-      <c r="G1403" t="inlineStr"/>
-      <c r="H1403" t="inlineStr"/>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
@@ -45239,9 +45068,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F1404" t="inlineStr"/>
-      <c r="G1404" t="inlineStr"/>
-      <c r="H1404" t="inlineStr"/>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
@@ -45269,9 +45095,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — David Fisher (Officer) plans to sell 28,500 shares (~$7.12M) on/after 08/25/2026</t>
         </is>
       </c>
-      <c r="F1405" t="inlineStr"/>
-      <c r="G1405" t="inlineStr"/>
-      <c r="H1405" t="inlineStr"/>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
@@ -45299,9 +45122,2685 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1406" t="inlineStr"/>
-      <c r="G1406" t="inlineStr"/>
-      <c r="H1406" t="inlineStr"/>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E1407" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1759509/000195004726008767/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1408" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Beggs Jill (Director) plans to sell 2,307 shares (~$40.1K) on/after 08/27/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1759509/000195004726008760/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1409" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Hope Stephen (Officer) plans to sell 5,982 shares (~$104.0K) on/after 08/27/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1759509/000195004726008753/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1410" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Lawee David (Director) plans to sell 4,613 shares (~$80.2K) on/after 08/27/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1759509/000167594826000006/xslF345X06/form4-08272026_120810.xml</t>
+        </is>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Brewer Erin (CHIEF FINANCIAL OFFICER) sold 15,000 shares @ $17.63 ($264.4K) on 2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E1412" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E1414" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000119312526369145/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Gebbia Joseph (Director) C: 960,000 shares on 2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000119312526369139/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1416" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Blecharczyk Nathan (Chief Strategy Officer) sold 353,292 shares @ $190.56 ($67.32M) on 2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000195917326006475/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Blecharczyk Nathan (Officer) plans to sell 19,659 shares (~$3.75M) on/after 08/26/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>Choice Hotels International, Inc.</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>https://media.choicehotels.com</t>
+        </is>
+      </c>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>https://blog.google</t>
+        </is>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com</t>
+        </is>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000150629326000112/xslF345X06/wk-form4_1787784460.xml</t>
+        </is>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Silbermann Benjamin (Director) sold 93,750 shares @ $23.55 ($2.21M) on 2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000192109426000960/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1422" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Silbermann Benjamin (Director) plans to sell 46,875 shares (~$1.10M) on/after 08/26/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E1424" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810806/000192109426000961/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Blum Alexander (Officer) plans to sell 1,964 shares (~$88.0K) on/after 08/27/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810806/000209316726000009/xslF345X06/wk-form4_1787790542.xml</t>
+        </is>
+      </c>
+      <c r="E1426" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Boyden Rebecca Berenice (SVP, Chief Legal Officer) sold 1,032 shares @ $45.32 ($46.8K) on 2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810806/000168097926000008/xslF345X06/wk-form4_1787790243.xml</t>
+        </is>
+      </c>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Bromberg Matthew S (President and CEO) sold 16,383 shares @ $45.31 ($742.3K) on 2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810806/000179663526000010/xslF345X06/wk-form4_1787790079.xml</t>
+        </is>
+      </c>
+      <c r="E1428" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Yahes Jarrod (SVP, Chief Financial Officer) sold 26,017 shares @ $45.31 ($1.18M) on 2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>https://newsroom.spotify.com</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>LIF</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>LIF (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1581760/000158176026000153/xslF345X06/wk-form4_1787862036.xml</t>
+        </is>
+      </c>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Synge James (Director) sold 33,299 shares @ $44.44 ($1.48M) on 2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>LIF</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>LIF (verify ticker)</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1581760/000158176026000151/xslFormDX01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form D</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>BBY</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>Best Buy Co., Inc.</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>https://www.bestbuy.com/site/help-topics/terms-and-conditions/pcmcat204400050067.c</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>BBY</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>Best Buy Co., Inc.</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/764478/000076447826000037/bby-20260827.htm</t>
+        </is>
+      </c>
+      <c r="E1435" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E1436" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/news/</t>
+        </is>
+      </c>
+      <c r="E1437" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E1438" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>https://investor.foxcorporation.com</t>
+        </is>
+      </c>
+      <c r="E1439" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E1440" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>Warner Music Group Corp.</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>https://www.wmg.com/news/</t>
+        </is>
+      </c>
+      <c r="E1441" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E1442" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1443" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E1444" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000131509826000179/xslF345X06/wk-form4_1787783273.xml</t>
+        </is>
+      </c>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Rawlings Amy Marie (Chief Accounting Officer) sold 237 shares @ $38.89 ($9.2K) on 2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>https://investors.intuit.com</t>
+        </is>
+      </c>
+      <c r="E1448" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/896878/000195004726008790/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1449" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Dale Hotz Lauren (Officer) plans to sell 908 shares (~$314.7K) on/after 08/27/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>https://mediacenter.adp.com</t>
+        </is>
+      </c>
+      <c r="E1450" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000195004726008750/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1451" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — B. Robinson Kenneth (Director) plans to sell 800 shares (~$126.7K) on/after 08/27/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000195004726008743/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1452" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Conway Craig (Director) plans to sell 3,145 shares (~$493.1K) on/after 08/27/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159787026000009/xslF345X06/wk-form4_1787774561.xml</t>
+        </is>
+      </c>
+      <c r="E1453" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sarowitz Steven I (Director) sold 441 shares @ $155.00 ($68.4K) on 2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E1454" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1454" t="inlineStr"/>
+      <c r="G1454" t="inlineStr"/>
+      <c r="H1454" t="inlineStr"/>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000195004726008762/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1455" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Hertz Jessica (Officer) plans to sell 10,394 shares (~$1.61M) on/after 08/27/2026</t>
+        </is>
+      </c>
+      <c r="F1455" t="inlineStr"/>
+      <c r="G1455" t="inlineStr"/>
+      <c r="H1455" t="inlineStr"/>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/upgrade/website</t>
+        </is>
+      </c>
+      <c r="E1456" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F1456" t="inlineStr"/>
+      <c r="G1456" t="inlineStr"/>
+      <c r="H1456" t="inlineStr"/>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000197640826000779/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1457" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Ron Gutler (Director) plans to sell 5,718 shares (~$470.5K) on/after 08/27/2026</t>
+        </is>
+      </c>
+      <c r="F1457" t="inlineStr"/>
+      <c r="G1457" t="inlineStr"/>
+      <c r="H1457" t="inlineStr"/>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000162828026059068/xslF345X06/wk-form4_1787773768.xml</t>
+        </is>
+      </c>
+      <c r="E1458" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Zohar Nir (President) sold 30,000 shares @ $85.58 ($2.57M) on 2026-08-24</t>
+        </is>
+      </c>
+      <c r="F1458" t="inlineStr"/>
+      <c r="G1458" t="inlineStr"/>
+      <c r="H1458" t="inlineStr"/>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>GoDaddy Inc.</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>https://investors.godaddy.net</t>
+        </is>
+      </c>
+      <c r="E1459" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F1459" t="inlineStr"/>
+      <c r="G1459" t="inlineStr"/>
+      <c r="H1459" t="inlineStr"/>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E1460" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F1460" t="inlineStr"/>
+      <c r="G1460" t="inlineStr"/>
+      <c r="H1460" t="inlineStr"/>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>https://www.ebayinc.com/stories/news/</t>
+        </is>
+      </c>
+      <c r="E1461" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1461" t="inlineStr"/>
+      <c r="G1461" t="inlineStr"/>
+      <c r="H1461" t="inlineStr"/>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1370637/000196922326000958/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1462" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — C. Andrew Ballard (Director) plans to sell 4,500 shares (~$373.5K) on/after 08/26/2026</t>
+        </is>
+      </c>
+      <c r="F1462" t="inlineStr"/>
+      <c r="G1462" t="inlineStr"/>
+      <c r="H1462" t="inlineStr"/>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E1463" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1463" t="inlineStr"/>
+      <c r="G1463" t="inlineStr"/>
+      <c r="H1463" t="inlineStr"/>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183261226000018/xslF345X06/form4-08272026_040801.xml</t>
+        </is>
+      </c>
+      <c r="E1464" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Adarkar Prabir (PRESIDENT AND COO) sold 55,289 shares @ $231.76 ($12.81M) on 2026-08-25</t>
+        </is>
+      </c>
+      <c r="F1464" t="inlineStr"/>
+      <c r="G1464" t="inlineStr"/>
+      <c r="H1464" t="inlineStr"/>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000114036126034688/ny20079824x2_def14c.htm</t>
+        </is>
+      </c>
+      <c r="E1465" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form DEF 14C</t>
+        </is>
+      </c>
+      <c r="F1465" t="inlineStr"/>
+      <c r="G1465" t="inlineStr"/>
+      <c r="H1465" t="inlineStr"/>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183261726000009/xslF345X06/form4-08262026_040808.xml</t>
+        </is>
+      </c>
+      <c r="E1466" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Xu Tony (CHIEF EXECUTIVE OFFICER) sold 33,334 shares @ $230.00 ($7.67M) on 2026-08-24</t>
+        </is>
+      </c>
+      <c r="F1466" t="inlineStr"/>
+      <c r="G1466" t="inlineStr"/>
+      <c r="H1466" t="inlineStr"/>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000163564826000014/xslF345X06/form4-08262026_040806.xml</t>
+        </is>
+      </c>
+      <c r="E1467" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lee Gordon S (CHIEF ACCOUNTING OFFICER) sold 2,204 shares @ $222.03 ($489.4K) on 2026-08-24</t>
+        </is>
+      </c>
+      <c r="F1467" t="inlineStr"/>
+      <c r="G1467" t="inlineStr"/>
+      <c r="H1467" t="inlineStr"/>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000189968826000016/xslF345X06/form4-08262026_040804.xml</t>
+        </is>
+      </c>
+      <c r="E1468" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sherringham Tia (GENERAL COUNSEL AND SECRETARY) sold 2,265 shares @ $227.64 ($515.6K) on 2026-08-24</t>
+        </is>
+      </c>
+      <c r="F1468" t="inlineStr"/>
+      <c r="G1468" t="inlineStr"/>
+      <c r="H1468" t="inlineStr"/>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000183261426000030/xslF345X06/form4-08262026_040801.xml</t>
+        </is>
+      </c>
+      <c r="E1469" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Tang Stanley (Director) sold 10,134 shares @ $225.00 ($2.28M) on 2026-08-24</t>
+        </is>
+      </c>
+      <c r="F1469" t="inlineStr"/>
+      <c r="G1469" t="inlineStr"/>
+      <c r="H1469" t="inlineStr"/>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>7 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1470" t="inlineStr"/>
+      <c r="G1470" t="inlineStr"/>
+      <c r="H1470" t="inlineStr"/>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/company/newsroom</t>
+        </is>
+      </c>
+      <c r="E1471" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1471" t="inlineStr"/>
+      <c r="G1471" t="inlineStr"/>
+      <c r="H1471" t="inlineStr"/>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000192109426000962/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1472" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Laughton Mary Beth (Director) plans to sell 10,236 shares (~$515.1K) on/after 08/27/2026</t>
+        </is>
+      </c>
+      <c r="F1472" t="inlineStr"/>
+      <c r="G1472" t="inlineStr"/>
+      <c r="H1472" t="inlineStr"/>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000199010626000021/xslF345X06/wk-form4_1787774684.xml</t>
+        </is>
+      </c>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Fong Morgan (Chief Legal Officer) sold 18,390 shares @ $49.96 ($918.8K) on 2026-08-24</t>
+        </is>
+      </c>
+      <c r="F1473" t="inlineStr"/>
+      <c r="G1473" t="inlineStr"/>
+      <c r="H1473" t="inlineStr"/>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/duolingo</t>
+        </is>
+      </c>
+      <c r="E1474" t="inlineStr">
+        <is>
+          <t>5 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1474" t="inlineStr"/>
+      <c r="G1474" t="inlineStr"/>
+      <c r="H1474" t="inlineStr"/>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>https://blog.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="E1475" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1475" t="inlineStr"/>
+      <c r="G1475" t="inlineStr"/>
+      <c r="H1475" t="inlineStr"/>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>https://ir.mtch.com/leadership/default.aspx</t>
+        </is>
+      </c>
+      <c r="E1476" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F1476" t="inlineStr"/>
+      <c r="G1476" t="inlineStr"/>
+      <c r="H1476" t="inlineStr"/>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>https://mtch.com/news</t>
+        </is>
+      </c>
+      <c r="E1477" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1477" t="inlineStr"/>
+      <c r="G1477" t="inlineStr"/>
+      <c r="H1477" t="inlineStr"/>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>https://mtch.com/careers</t>
+        </is>
+      </c>
+      <c r="E1478" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1478" t="inlineStr"/>
+      <c r="G1478" t="inlineStr"/>
+      <c r="H1478" t="inlineStr"/>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/891103/000195779926000167/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1479" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Bailey Stephen (Director) plans to sell 4,760 shares (~$201.2K) on/after 08/26/2026</t>
+        </is>
+      </c>
+      <c r="F1479" t="inlineStr"/>
+      <c r="G1479" t="inlineStr"/>
+      <c r="H1479" t="inlineStr"/>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1480" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1480" t="inlineStr"/>
+      <c r="G1480" t="inlineStr"/>
+      <c r="H1480" t="inlineStr"/>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726008786/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1481" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$504.0K) on/after 08/27/2026</t>
+        </is>
+      </c>
+      <c r="F1481" t="inlineStr"/>
+      <c r="G1481" t="inlineStr"/>
+      <c r="H1481" t="inlineStr"/>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726008725/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1482" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$492.0K) on/after 08/26/2026</t>
+        </is>
+      </c>
+      <c r="F1482" t="inlineStr"/>
+      <c r="G1482" t="inlineStr"/>
+      <c r="H1482" t="inlineStr"/>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>https://careers.toasttab.com/jobs?gh_jid=8147296</t>
+        </is>
+      </c>
+      <c r="E1483" t="inlineStr">
+        <is>
+          <t>New senior role: Senior Director of Product, International</t>
+        </is>
+      </c>
+      <c r="F1483" t="inlineStr"/>
+      <c r="G1483" t="inlineStr"/>
+      <c r="H1483" t="inlineStr"/>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>16 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1484" t="inlineStr"/>
+      <c r="G1484" t="inlineStr"/>
+      <c r="H1484" t="inlineStr"/>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>https://pos.toasttab.com/pricing</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F1485" t="inlineStr"/>
+      <c r="G1485" t="inlineStr"/>
+      <c r="H1485" t="inlineStr"/>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>https://dave.com/careers</t>
+        </is>
+      </c>
+      <c r="E1486" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1486" t="inlineStr"/>
+      <c r="G1486" t="inlineStr"/>
+      <c r="H1486" t="inlineStr"/>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E1487" t="inlineStr">
+        <is>
+          <t>6 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1487" t="inlineStr"/>
+      <c r="G1487" t="inlineStr"/>
+      <c r="H1487" t="inlineStr"/>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1820953/000162828026059281/afrm-sx82026.htm</t>
+        </is>
+      </c>
+      <c r="E1488" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Employee stock plan registration</t>
+        </is>
+      </c>
+      <c r="F1488" t="inlineStr"/>
+      <c r="G1488" t="inlineStr"/>
+      <c r="H1488" t="inlineStr"/>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1820953/000162828026059279/afrm-20260630.htm</t>
+        </is>
+      </c>
+      <c r="E1489" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Annual report</t>
+        </is>
+      </c>
+      <c r="F1489" t="inlineStr"/>
+      <c r="G1489" t="inlineStr"/>
+      <c r="H1489" t="inlineStr"/>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1820953/000162828026059271/afrm-20260825.htm</t>
+        </is>
+      </c>
+      <c r="E1490" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F1490" t="inlineStr"/>
+      <c r="G1490" t="inlineStr"/>
+      <c r="H1490" t="inlineStr"/>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E1491" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1491" t="inlineStr"/>
+      <c r="G1491" t="inlineStr"/>
+      <c r="H1491" t="inlineStr"/>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E1492" t="inlineStr">
+        <is>
+          <t>6 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1492" t="inlineStr"/>
+      <c r="G1492" t="inlineStr"/>
+      <c r="H1492" t="inlineStr"/>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>SGI</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>Somnigroup International Inc. (fmr. Tempur Sealy)</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>https://www.somnigroup.com/terms</t>
+        </is>
+      </c>
+      <c r="E1493" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F1493" t="inlineStr"/>
+      <c r="G1493" t="inlineStr"/>
+      <c r="H1493" t="inlineStr"/>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>SGI</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>Somnigroup International Inc. (fmr. Tempur Sealy)</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>https://somnigroup.com/about/executive-management/default.aspx</t>
+        </is>
+      </c>
+      <c r="E1494" t="inlineStr">
+        <is>
+          <t>management_team: change detected</t>
+        </is>
+      </c>
+      <c r="F1494" t="inlineStr"/>
+      <c r="G1494" t="inlineStr"/>
+      <c r="H1494" t="inlineStr"/>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>SGI</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>Somnigroup International Inc. (fmr. Tempur Sealy)</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>https://www.somnigroup.com/news</t>
+        </is>
+      </c>
+      <c r="E1495" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1495" t="inlineStr"/>
+      <c r="G1495" t="inlineStr"/>
+      <c r="H1495" t="inlineStr"/>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>SGI</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>Somnigroup International Inc. (fmr. Tempur Sealy)</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>https://investor.somnigroup.com/investor-resources/investor-overview/default.aspx</t>
+        </is>
+      </c>
+      <c r="E1496" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F1496" t="inlineStr"/>
+      <c r="G1496" t="inlineStr"/>
+      <c r="H1496" t="inlineStr"/>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>SGI</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>Somnigroup International Inc. (fmr. Tempur Sealy)</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>https://somnigroup.com/careers/default.aspx</t>
+        </is>
+      </c>
+      <c r="E1497" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1497" t="inlineStr"/>
+      <c r="G1497" t="inlineStr"/>
+      <c r="H1497" t="inlineStr"/>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>SGI</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>Somnigroup International Inc. (fmr. Tempur Sealy)</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1206264/000120626426000121/sgi-20260826.htm</t>
+        </is>
+      </c>
+      <c r="E1498" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F1498" t="inlineStr"/>
+      <c r="G1498" t="inlineStr"/>
+      <c r="H1498" t="inlineStr"/>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>ENVA</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>Enova International Inc.</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1529864/000119312526371385/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1499" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Fisher David (Executive Chairman) sold 18,569 shares @ $241.64 ($4.49M) on 2026-08-25</t>
+        </is>
+      </c>
+      <c r="F1499" t="inlineStr"/>
+      <c r="G1499" t="inlineStr"/>
+      <c r="H1499" t="inlineStr"/>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E1500" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1500" t="inlineStr"/>
+      <c r="G1500" t="inlineStr"/>
+      <c r="H1500" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1500"/>
+  <dimension ref="A1:H1575"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -46418,9 +46418,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1454" t="inlineStr"/>
-      <c r="G1454" t="inlineStr"/>
-      <c r="H1454" t="inlineStr"/>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
@@ -46448,9 +46445,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Hertz Jessica (Officer) plans to sell 10,394 shares (~$1.61M) on/after 08/27/2026</t>
         </is>
       </c>
-      <c r="F1455" t="inlineStr"/>
-      <c r="G1455" t="inlineStr"/>
-      <c r="H1455" t="inlineStr"/>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
@@ -46478,9 +46472,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F1456" t="inlineStr"/>
-      <c r="G1456" t="inlineStr"/>
-      <c r="H1456" t="inlineStr"/>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
@@ -46508,9 +46499,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Ron Gutler (Director) plans to sell 5,718 shares (~$470.5K) on/after 08/27/2026</t>
         </is>
       </c>
-      <c r="F1457" t="inlineStr"/>
-      <c r="G1457" t="inlineStr"/>
-      <c r="H1457" t="inlineStr"/>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
@@ -46538,9 +46526,6 @@
           <t>[ROUTINE] Insider trade — Zohar Nir (President) sold 30,000 shares @ $85.58 ($2.57M) on 2026-08-24</t>
         </is>
       </c>
-      <c r="F1458" t="inlineStr"/>
-      <c r="G1458" t="inlineStr"/>
-      <c r="H1458" t="inlineStr"/>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
@@ -46568,9 +46553,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F1459" t="inlineStr"/>
-      <c r="G1459" t="inlineStr"/>
-      <c r="H1459" t="inlineStr"/>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
@@ -46598,9 +46580,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F1460" t="inlineStr"/>
-      <c r="G1460" t="inlineStr"/>
-      <c r="H1460" t="inlineStr"/>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
@@ -46628,9 +46607,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1461" t="inlineStr"/>
-      <c r="G1461" t="inlineStr"/>
-      <c r="H1461" t="inlineStr"/>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
@@ -46658,9 +46634,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — C. Andrew Ballard (Director) plans to sell 4,500 shares (~$373.5K) on/after 08/26/2026</t>
         </is>
       </c>
-      <c r="F1462" t="inlineStr"/>
-      <c r="G1462" t="inlineStr"/>
-      <c r="H1462" t="inlineStr"/>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
@@ -46688,9 +46661,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1463" t="inlineStr"/>
-      <c r="G1463" t="inlineStr"/>
-      <c r="H1463" t="inlineStr"/>
     </row>
     <row r="1464">
       <c r="A1464" t="inlineStr">
@@ -46718,9 +46688,6 @@
           <t>[ROUTINE] Insider trade — Adarkar Prabir (PRESIDENT AND COO) sold 55,289 shares @ $231.76 ($12.81M) on 2026-08-25</t>
         </is>
       </c>
-      <c r="F1464" t="inlineStr"/>
-      <c r="G1464" t="inlineStr"/>
-      <c r="H1464" t="inlineStr"/>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
@@ -46748,9 +46715,6 @@
           <t>[UNKNOWN] Form DEF 14C</t>
         </is>
       </c>
-      <c r="F1465" t="inlineStr"/>
-      <c r="G1465" t="inlineStr"/>
-      <c r="H1465" t="inlineStr"/>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
@@ -46778,9 +46742,6 @@
           <t>[ROUTINE] Insider trade — Xu Tony (CHIEF EXECUTIVE OFFICER) sold 33,334 shares @ $230.00 ($7.67M) on 2026-08-24</t>
         </is>
       </c>
-      <c r="F1466" t="inlineStr"/>
-      <c r="G1466" t="inlineStr"/>
-      <c r="H1466" t="inlineStr"/>
     </row>
     <row r="1467">
       <c r="A1467" t="inlineStr">
@@ -46808,9 +46769,6 @@
           <t>[ROUTINE] Insider trade — Lee Gordon S (CHIEF ACCOUNTING OFFICER) sold 2,204 shares @ $222.03 ($489.4K) on 2026-08-24</t>
         </is>
       </c>
-      <c r="F1467" t="inlineStr"/>
-      <c r="G1467" t="inlineStr"/>
-      <c r="H1467" t="inlineStr"/>
     </row>
     <row r="1468">
       <c r="A1468" t="inlineStr">
@@ -46838,9 +46796,6 @@
           <t>[ROUTINE] Insider trade — Sherringham Tia (GENERAL COUNSEL AND SECRETARY) sold 2,265 shares @ $227.64 ($515.6K) on 2026-08-24</t>
         </is>
       </c>
-      <c r="F1468" t="inlineStr"/>
-      <c r="G1468" t="inlineStr"/>
-      <c r="H1468" t="inlineStr"/>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
@@ -46868,9 +46823,6 @@
           <t>[ROUTINE] Insider trade — Tang Stanley (Director) sold 10,134 shares @ $225.00 ($2.28M) on 2026-08-24</t>
         </is>
       </c>
-      <c r="F1469" t="inlineStr"/>
-      <c r="G1469" t="inlineStr"/>
-      <c r="H1469" t="inlineStr"/>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
@@ -46898,9 +46850,6 @@
           <t>7 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1470" t="inlineStr"/>
-      <c r="G1470" t="inlineStr"/>
-      <c r="H1470" t="inlineStr"/>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
@@ -46928,9 +46877,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1471" t="inlineStr"/>
-      <c r="G1471" t="inlineStr"/>
-      <c r="H1471" t="inlineStr"/>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
@@ -46958,9 +46904,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Laughton Mary Beth (Director) plans to sell 10,236 shares (~$515.1K) on/after 08/27/2026</t>
         </is>
       </c>
-      <c r="F1472" t="inlineStr"/>
-      <c r="G1472" t="inlineStr"/>
-      <c r="H1472" t="inlineStr"/>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
@@ -46988,9 +46931,6 @@
           <t>[ROUTINE] Insider trade — Fong Morgan (Chief Legal Officer) sold 18,390 shares @ $49.96 ($918.8K) on 2026-08-24</t>
         </is>
       </c>
-      <c r="F1473" t="inlineStr"/>
-      <c r="G1473" t="inlineStr"/>
-      <c r="H1473" t="inlineStr"/>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
@@ -47018,9 +46958,6 @@
           <t>5 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1474" t="inlineStr"/>
-      <c r="G1474" t="inlineStr"/>
-      <c r="H1474" t="inlineStr"/>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
@@ -47048,9 +46985,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1475" t="inlineStr"/>
-      <c r="G1475" t="inlineStr"/>
-      <c r="H1475" t="inlineStr"/>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
@@ -47078,9 +47012,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F1476" t="inlineStr"/>
-      <c r="G1476" t="inlineStr"/>
-      <c r="H1476" t="inlineStr"/>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
@@ -47108,9 +47039,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1477" t="inlineStr"/>
-      <c r="G1477" t="inlineStr"/>
-      <c r="H1477" t="inlineStr"/>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
@@ -47138,9 +47066,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1478" t="inlineStr"/>
-      <c r="G1478" t="inlineStr"/>
-      <c r="H1478" t="inlineStr"/>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
@@ -47168,9 +47093,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Bailey Stephen (Director) plans to sell 4,760 shares (~$201.2K) on/after 08/26/2026</t>
         </is>
       </c>
-      <c r="F1479" t="inlineStr"/>
-      <c r="G1479" t="inlineStr"/>
-      <c r="H1479" t="inlineStr"/>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
@@ -47198,9 +47120,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1480" t="inlineStr"/>
-      <c r="G1480" t="inlineStr"/>
-      <c r="H1480" t="inlineStr"/>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
@@ -47228,9 +47147,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$504.0K) on/after 08/27/2026</t>
         </is>
       </c>
-      <c r="F1481" t="inlineStr"/>
-      <c r="G1481" t="inlineStr"/>
-      <c r="H1481" t="inlineStr"/>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
@@ -47258,9 +47174,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$492.0K) on/after 08/26/2026</t>
         </is>
       </c>
-      <c r="F1482" t="inlineStr"/>
-      <c r="G1482" t="inlineStr"/>
-      <c r="H1482" t="inlineStr"/>
     </row>
     <row r="1483">
       <c r="A1483" t="inlineStr">
@@ -47288,9 +47201,6 @@
           <t>New senior role: Senior Director of Product, International</t>
         </is>
       </c>
-      <c r="F1483" t="inlineStr"/>
-      <c r="G1483" t="inlineStr"/>
-      <c r="H1483" t="inlineStr"/>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
@@ -47318,9 +47228,6 @@
           <t>16 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1484" t="inlineStr"/>
-      <c r="G1484" t="inlineStr"/>
-      <c r="H1484" t="inlineStr"/>
     </row>
     <row r="1485">
       <c r="A1485" t="inlineStr">
@@ -47348,9 +47255,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F1485" t="inlineStr"/>
-      <c r="G1485" t="inlineStr"/>
-      <c r="H1485" t="inlineStr"/>
     </row>
     <row r="1486">
       <c r="A1486" t="inlineStr">
@@ -47378,9 +47282,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1486" t="inlineStr"/>
-      <c r="G1486" t="inlineStr"/>
-      <c r="H1486" t="inlineStr"/>
     </row>
     <row r="1487">
       <c r="A1487" t="inlineStr">
@@ -47408,9 +47309,6 @@
           <t>6 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1487" t="inlineStr"/>
-      <c r="G1487" t="inlineStr"/>
-      <c r="H1487" t="inlineStr"/>
     </row>
     <row r="1488">
       <c r="A1488" t="inlineStr">
@@ -47438,9 +47336,6 @@
           <t>[ROUTINE] Employee stock plan registration</t>
         </is>
       </c>
-      <c r="F1488" t="inlineStr"/>
-      <c r="G1488" t="inlineStr"/>
-      <c r="H1488" t="inlineStr"/>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
@@ -47468,9 +47363,6 @@
           <t>[MATERIAL] Annual report</t>
         </is>
       </c>
-      <c r="F1489" t="inlineStr"/>
-      <c r="G1489" t="inlineStr"/>
-      <c r="H1489" t="inlineStr"/>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
@@ -47498,9 +47390,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F1490" t="inlineStr"/>
-      <c r="G1490" t="inlineStr"/>
-      <c r="H1490" t="inlineStr"/>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
@@ -47528,9 +47417,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1491" t="inlineStr"/>
-      <c r="G1491" t="inlineStr"/>
-      <c r="H1491" t="inlineStr"/>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
@@ -47558,9 +47444,6 @@
           <t>6 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1492" t="inlineStr"/>
-      <c r="G1492" t="inlineStr"/>
-      <c r="H1492" t="inlineStr"/>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
@@ -47588,9 +47471,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F1493" t="inlineStr"/>
-      <c r="G1493" t="inlineStr"/>
-      <c r="H1493" t="inlineStr"/>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
@@ -47618,9 +47498,6 @@
           <t>management_team: change detected</t>
         </is>
       </c>
-      <c r="F1494" t="inlineStr"/>
-      <c r="G1494" t="inlineStr"/>
-      <c r="H1494" t="inlineStr"/>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
@@ -47648,9 +47525,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1495" t="inlineStr"/>
-      <c r="G1495" t="inlineStr"/>
-      <c r="H1495" t="inlineStr"/>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
@@ -47678,9 +47552,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F1496" t="inlineStr"/>
-      <c r="G1496" t="inlineStr"/>
-      <c r="H1496" t="inlineStr"/>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
@@ -47708,9 +47579,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1497" t="inlineStr"/>
-      <c r="G1497" t="inlineStr"/>
-      <c r="H1497" t="inlineStr"/>
     </row>
     <row r="1498">
       <c r="A1498" t="inlineStr">
@@ -47738,9 +47606,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F1498" t="inlineStr"/>
-      <c r="G1498" t="inlineStr"/>
-      <c r="H1498" t="inlineStr"/>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
@@ -47768,9 +47633,6 @@
           <t>[ROUTINE] Insider trade — Fisher David (Executive Chairman) sold 18,569 shares @ $241.64 ($4.49M) on 2026-08-25</t>
         </is>
       </c>
-      <c r="F1499" t="inlineStr"/>
-      <c r="G1499" t="inlineStr"/>
-      <c r="H1499" t="inlineStr"/>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
@@ -47798,9 +47660,2130 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1500" t="inlineStr"/>
-      <c r="G1500" t="inlineStr"/>
-      <c r="H1500" t="inlineStr"/>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>LOGI</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>Logitech International S.A.</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>https://jobs.logitech.com</t>
+        </is>
+      </c>
+      <c r="E1501" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E1502" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1759509/000197349526000006/xslF345X06/form4-08282026_120821.xml</t>
+        </is>
+      </c>
+      <c r="E1503" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Whiteside Janey (Director) sold 5,480 shares @ $17.68 ($96.9K) on 2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E1504" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E1505" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E1506" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000195917326006532/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1507" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Blecharczyk Nathan (Officer) plans to sell 57,160 shares (~$10.90M) on/after 08/28/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000119312526374780/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Blecharczyk Nathan (Chief Strategy Officer) sold 19,659 shares @ $190.73 ($3.75M) on 2026-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>Choice Hotels International, Inc.</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1046311/000119312526374377/d110369d8k.htm</t>
+        </is>
+      </c>
+      <c r="E1509" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com</t>
+        </is>
+      </c>
+      <c r="E1510" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000192109426000964/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1511" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Frances Arnold (Director) plans to sell 82 shares (~$27.7K) on/after 08/28/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526374341/xslN-PX_X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1512" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form N-PX</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526371799/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1513" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — John Kent Walker (President, Global Affairs, CLO) 1,639 shares withheld for taxes (vest event) on 2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526371797/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1514" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Pichai Sundar (Chief Executive Officer) 3,703 shares withheld for taxes (vest event) on 2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526371794/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1515" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Porat Ruth (President and CIO) 1,639 shares withheld for taxes (vest event) on 2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526371788/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1516" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Schindler Philipp (SVP, Chief Business Officer) 2,015 shares withheld for taxes (vest event) on 2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526371785/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1517" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Ashkenazi Anat (SVP, Chief Financial Officer) 1,781 shares withheld for taxes (vest event) on 2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526371778/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1518" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Saraci Marsida (VP, Chief Accounting Officer) 493 shares withheld for taxes (vest event) on 2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000150629326000119/xslF345X06/wk-form3_1787949866.xml</t>
+        </is>
+      </c>
+      <c r="E1519" t="inlineStr">
+        <is>
+          <t>[ROUTINE] New insider — initial ownership statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000150629326000117/pins-20260826.htm</t>
+        </is>
+      </c>
+      <c r="E1520" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E1521" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1713445/000192441226000004/xslF345X06/wk-form4_1787868043.xml</t>
+        </is>
+      </c>
+      <c r="E1522" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sauerberg Robert A. (Director) sold 5,128 shares @ $159.92 ($820.1K) on 2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E1523" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810806/000192109426000966/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1524" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Blum Alexander (Officer) plans to sell 43,556 shares (~$1.90M) on/after 08/28/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810806/000204205626000008/xslF345X06/wk-form4_1787875227.xml</t>
+        </is>
+      </c>
+      <c r="E1525" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Blum Alexander (SVP, Chief Operating Officer) sold 22,559 shares @ $45.26 ($1.02M) on 2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E1526" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com/premium</t>
+        </is>
+      </c>
+      <c r="E1527" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E1528" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E1529" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>https://thewaltdisneycompany.com/news/</t>
+        </is>
+      </c>
+      <c r="E1530" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E1531" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E1532" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>Warner Music Group Corp.</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>https://www.wmg.com/news/</t>
+        </is>
+      </c>
+      <c r="E1533" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E1534" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>https://www.livenationentertainment.com/careers</t>
+        </is>
+      </c>
+      <c r="E1535" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1536" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1337634/000162828026059299/xslF345X06/wk-form4_1787868570.xml</t>
+        </is>
+      </c>
+      <c r="E1537" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Islam Nayaab (See Remarks) sold 305,709 shares @ $6.81 ($2.08M) on 2026-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E1538" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E1539" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E1540" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>https://quickbooks.intuit.com/pricing/</t>
+        </is>
+      </c>
+      <c r="E1541" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/896878/000162828026059416/xslF345X06/wk-form4_1787948566.xml</t>
+        </is>
+      </c>
+      <c r="E1542" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hotz Lauren D (SVP, Chief Accounting Officer) sold 907 shares @ $346.54 ($314.3K) on 2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D1543" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E1543" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1543" t="inlineStr"/>
+      <c r="G1543" t="inlineStr"/>
+      <c r="H1543" t="inlineStr"/>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>GoDaddy Inc.</t>
+        </is>
+      </c>
+      <c r="D1544" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1609711/000195004726008804/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1544" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Sweet Leah (Director) plans to sell 325 shares (~$31.6K) on/after 08/28/2026</t>
+        </is>
+      </c>
+      <c r="F1544" t="inlineStr"/>
+      <c r="G1544" t="inlineStr"/>
+      <c r="H1544" t="inlineStr"/>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1545" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E1545" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F1545" t="inlineStr"/>
+      <c r="G1545" t="inlineStr"/>
+      <c r="H1545" t="inlineStr"/>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1370637/000164781426000006/xslF345X06/form4-08282026_040801.xml</t>
+        </is>
+      </c>
+      <c r="E1546" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Charles Andrew Ballard (Director) sold 4,500 shares @ $81.85 ($368.3K) on 2026-08-26</t>
+        </is>
+      </c>
+      <c r="F1546" t="inlineStr"/>
+      <c r="G1546" t="inlineStr"/>
+      <c r="H1546" t="inlineStr"/>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E1547" t="inlineStr">
+        <is>
+          <t>5 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1547" t="inlineStr"/>
+      <c r="G1547" t="inlineStr"/>
+      <c r="H1547" t="inlineStr"/>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>https://careers.duolingo.com/jobs/8761234002?gh_jid=8761234002</t>
+        </is>
+      </c>
+      <c r="E1548" t="inlineStr">
+        <is>
+          <t>New senior role: Director of Ad Sales - West</t>
+        </is>
+      </c>
+      <c r="F1548" t="inlineStr"/>
+      <c r="G1548" t="inlineStr"/>
+      <c r="H1548" t="inlineStr"/>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/duolingo</t>
+        </is>
+      </c>
+      <c r="E1549" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1549" t="inlineStr"/>
+      <c r="G1549" t="inlineStr"/>
+      <c r="H1549" t="inlineStr"/>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D1550" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/891103/000195004726008825/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1550" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Eigenmann Philip (Officer) plans to sell 15,000 shares (~$625.5K) on/after 08/28/2026</t>
+        </is>
+      </c>
+      <c r="F1550" t="inlineStr"/>
+      <c r="G1550" t="inlineStr"/>
+      <c r="H1550" t="inlineStr"/>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/891103/000089110326000133/xslF345X06/wk-form4_1787950970.xml</t>
+        </is>
+      </c>
+      <c r="E1551" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Eigenmann Philip D (Chief Accounting Officer) sold 15,000 shares @ $41.70 ($625.5K) on 2026-08-28</t>
+        </is>
+      </c>
+      <c r="F1551" t="inlineStr"/>
+      <c r="G1551" t="inlineStr"/>
+      <c r="H1551" t="inlineStr"/>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>Match Group Inc.</t>
+        </is>
+      </c>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/891103/000089110326000132/xslF345X06/wk-form4_1787950964.xml</t>
+        </is>
+      </c>
+      <c r="E1552" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Bailey Stephen (Director) sold 4,760 shares @ $42.26 ($201.2K) on 2026-08-26</t>
+        </is>
+      </c>
+      <c r="F1552" t="inlineStr"/>
+      <c r="G1552" t="inlineStr"/>
+      <c r="H1552" t="inlineStr"/>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1553" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1553" t="inlineStr"/>
+      <c r="G1553" t="inlineStr"/>
+      <c r="H1553" t="inlineStr"/>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>https://investors.block.xyz</t>
+        </is>
+      </c>
+      <c r="E1554" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F1554" t="inlineStr"/>
+      <c r="G1554" t="inlineStr"/>
+      <c r="H1554" t="inlineStr"/>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726008828/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1555" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$510.7K) on/after 08/28/2026</t>
+        </is>
+      </c>
+      <c r="F1555" t="inlineStr"/>
+      <c r="G1555" t="inlineStr"/>
+      <c r="H1555" t="inlineStr"/>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000162828026059300/xslF345X06/wk-form4_1787868896.xml</t>
+        </is>
+      </c>
+      <c r="E1556" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Eisen Anthony Mathew (Director) sold 18,000 shares @ $82.60 ($1.49M) on 2026-08-25</t>
+        </is>
+      </c>
+      <c r="F1556" t="inlineStr"/>
+      <c r="G1556" t="inlineStr"/>
+      <c r="H1556" t="inlineStr"/>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E1557" t="inlineStr">
+        <is>
+          <t>13 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1557" t="inlineStr"/>
+      <c r="G1557" t="inlineStr"/>
+      <c r="H1557" t="inlineStr"/>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>Sezzle Inc.</t>
+        </is>
+      </c>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1662991/000166299126000150/xslF345X06/wk-form4_1787951304.xml</t>
+        </is>
+      </c>
+      <c r="E1558" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Brehm Kyle M. (Director) sold 1,000 shares @ $125.92 ($125.9K) on 2026-08-27</t>
+        </is>
+      </c>
+      <c r="F1558" t="inlineStr"/>
+      <c r="G1558" t="inlineStr"/>
+      <c r="H1558" t="inlineStr"/>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>SEZL</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>Sezzle Inc.</t>
+        </is>
+      </c>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1662991/000166299126000148/sezl-20260828.htm</t>
+        </is>
+      </c>
+      <c r="E1559" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+      <c r="F1559" t="inlineStr"/>
+      <c r="G1559" t="inlineStr"/>
+      <c r="H1559" t="inlineStr"/>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>https://dave.com/careers</t>
+        </is>
+      </c>
+      <c r="E1560" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1560" t="inlineStr"/>
+      <c r="G1560" t="inlineStr"/>
+      <c r="H1560" t="inlineStr"/>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E1561" t="inlineStr">
+        <is>
+          <t>9 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1561" t="inlineStr"/>
+      <c r="G1561" t="inlineStr"/>
+      <c r="H1561" t="inlineStr"/>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1820953/000195004726008819/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1562" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Linford Michael (Officer) plans to sell 79,219 shares (~$6.14M) on/after 08/28/2026</t>
+        </is>
+      </c>
+      <c r="F1562" t="inlineStr"/>
+      <c r="G1562" t="inlineStr"/>
+      <c r="H1562" t="inlineStr"/>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>KLAR</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>Klarna Group plc</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/2003292/000209710726000004/xslF345X06/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1563" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Siemiatkowski Sebastian (Chief Executive Officer) BOUGHT 692,506 shares @ $14.37 ($9.95M) on 2026-08-26</t>
+        </is>
+      </c>
+      <c r="F1563" t="inlineStr"/>
+      <c r="G1563" t="inlineStr"/>
+      <c r="H1563" t="inlineStr"/>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E1564" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1564" t="inlineStr"/>
+      <c r="G1564" t="inlineStr"/>
+      <c r="H1564" t="inlineStr"/>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000178387926000136/xslF345X06/wk-form4_1787867097.xml</t>
+        </is>
+      </c>
+      <c r="E1565" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Robinhood Markets, Inc. (10%+ owner) sold 9,225 shares @ $26.61 ($245.5K) on 2026-08-25</t>
+        </is>
+      </c>
+      <c r="F1565" t="inlineStr"/>
+      <c r="G1565" t="inlineStr"/>
+      <c r="H1565" t="inlineStr"/>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E1566" t="inlineStr">
+        <is>
+          <t>3 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1566" t="inlineStr"/>
+      <c r="G1566" t="inlineStr"/>
+      <c r="H1566" t="inlineStr"/>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1647639/000183385126000020/xslF345X06/wk-form4_1787868021.xml</t>
+        </is>
+      </c>
+      <c r="E1567" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Mirgorodskaya Natalia (See Remarks) sold 913 shares @ $30.03 ($27.4K) on 2026-08-25</t>
+        </is>
+      </c>
+      <c r="F1567" t="inlineStr"/>
+      <c r="G1567" t="inlineStr"/>
+      <c r="H1567" t="inlineStr"/>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>WSM</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>Williams-Sonoma Inc.</t>
+        </is>
+      </c>
+      <c r="D1568" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/719955/000194984626000554/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1568" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — King David Randolph (Officer) plans to sell 21,024 shares (~$4.92M) on/after 08/28/2026</t>
+        </is>
+      </c>
+      <c r="F1568" t="inlineStr"/>
+      <c r="G1568" t="inlineStr"/>
+      <c r="H1568" t="inlineStr"/>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>WSM</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>Williams-Sonoma Inc.</t>
+        </is>
+      </c>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/719955/000071995526000208/wsm-20260802.htm</t>
+        </is>
+      </c>
+      <c r="E1569" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Quarterly report</t>
+        </is>
+      </c>
+      <c r="F1569" t="inlineStr"/>
+      <c r="G1569" t="inlineStr"/>
+      <c r="H1569" t="inlineStr"/>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>SGI</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>Somnigroup International Inc. (fmr. Tempur Sealy)</t>
+        </is>
+      </c>
+      <c r="D1570" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1206264/000187646326000008/xslF345X06/wk-form4_1787947458.xml</t>
+        </is>
+      </c>
+      <c r="E1570" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — James Tyson Hagale (President - Leggett &amp; Platt) granted 71,123 shares on 2026-08-26</t>
+        </is>
+      </c>
+      <c r="F1570" t="inlineStr"/>
+      <c r="G1570" t="inlineStr"/>
+      <c r="H1570" t="inlineStr"/>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>SGI</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>Somnigroup International Inc. (fmr. Tempur Sealy)</t>
+        </is>
+      </c>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1206264/000187646326000006/xslF345X06/wk-form3_1787947416.xml</t>
+        </is>
+      </c>
+      <c r="E1571" t="inlineStr">
+        <is>
+          <t>[ROUTINE] New insider — initial ownership statement</t>
+        </is>
+      </c>
+      <c r="F1571" t="inlineStr"/>
+      <c r="G1571" t="inlineStr"/>
+      <c r="H1571" t="inlineStr"/>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>SGI</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>Somnigroup International Inc. (fmr. Tempur Sealy)</t>
+        </is>
+      </c>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1206264/000116633426000008/xslF345X06/wk-form4_1787947378.xml</t>
+        </is>
+      </c>
+      <c r="E1572" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Karl G Glassman (CEO - Leggett &amp; Platt) granted 549,004 shares on 2026-08-26</t>
+        </is>
+      </c>
+      <c r="F1572" t="inlineStr"/>
+      <c r="G1572" t="inlineStr"/>
+      <c r="H1572" t="inlineStr"/>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>SGI</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>Somnigroup International Inc. (fmr. Tempur Sealy)</t>
+        </is>
+      </c>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1206264/000116633426000007/xslF345X06/wk-form3_1787947351.xml</t>
+        </is>
+      </c>
+      <c r="E1573" t="inlineStr">
+        <is>
+          <t>[ROUTINE] New insider — initial ownership statement</t>
+        </is>
+      </c>
+      <c r="F1573" t="inlineStr"/>
+      <c r="G1573" t="inlineStr"/>
+      <c r="H1573" t="inlineStr"/>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>SGI</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>Somnigroup International Inc. (fmr. Tempur Sealy)</t>
+        </is>
+      </c>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1206264/000120639926000007/xslF345X06/wk-form4_1787868378.xml</t>
+        </is>
+      </c>
+      <c r="E1574" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Scott L Thompson (CEO &amp; PRESIDENT) BOUGHT 30,000 shares @ $62.84 ($1.89M) on 2026-08-27</t>
+        </is>
+      </c>
+      <c r="F1574" t="inlineStr"/>
+      <c r="G1574" t="inlineStr"/>
+      <c r="H1574" t="inlineStr"/>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D1575" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E1575" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1575" t="inlineStr"/>
+      <c r="G1575" t="inlineStr"/>
+      <c r="H1575" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1575"/>
+  <dimension ref="A1:H1617"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -48821,9 +48821,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1543" t="inlineStr"/>
-      <c r="G1543" t="inlineStr"/>
-      <c r="H1543" t="inlineStr"/>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
@@ -48851,9 +48848,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Sweet Leah (Director) plans to sell 325 shares (~$31.6K) on/after 08/28/2026</t>
         </is>
       </c>
-      <c r="F1544" t="inlineStr"/>
-      <c r="G1544" t="inlineStr"/>
-      <c r="H1544" t="inlineStr"/>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
@@ -48881,9 +48875,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F1545" t="inlineStr"/>
-      <c r="G1545" t="inlineStr"/>
-      <c r="H1545" t="inlineStr"/>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
@@ -48911,9 +48902,6 @@
           <t>[ROUTINE] Insider trade — Charles Andrew Ballard (Director) sold 4,500 shares @ $81.85 ($368.3K) on 2026-08-26</t>
         </is>
       </c>
-      <c r="F1546" t="inlineStr"/>
-      <c r="G1546" t="inlineStr"/>
-      <c r="H1546" t="inlineStr"/>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
@@ -48941,9 +48929,6 @@
           <t>5 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1547" t="inlineStr"/>
-      <c r="G1547" t="inlineStr"/>
-      <c r="H1547" t="inlineStr"/>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
@@ -48971,9 +48956,6 @@
           <t>New senior role: Director of Ad Sales - West</t>
         </is>
       </c>
-      <c r="F1548" t="inlineStr"/>
-      <c r="G1548" t="inlineStr"/>
-      <c r="H1548" t="inlineStr"/>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
@@ -49001,9 +48983,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1549" t="inlineStr"/>
-      <c r="G1549" t="inlineStr"/>
-      <c r="H1549" t="inlineStr"/>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
@@ -49031,9 +49010,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Eigenmann Philip (Officer) plans to sell 15,000 shares (~$625.5K) on/after 08/28/2026</t>
         </is>
       </c>
-      <c r="F1550" t="inlineStr"/>
-      <c r="G1550" t="inlineStr"/>
-      <c r="H1550" t="inlineStr"/>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
@@ -49061,9 +49037,6 @@
           <t>[ROUTINE] Insider trade — Eigenmann Philip D (Chief Accounting Officer) sold 15,000 shares @ $41.70 ($625.5K) on 2026-08-28</t>
         </is>
       </c>
-      <c r="F1551" t="inlineStr"/>
-      <c r="G1551" t="inlineStr"/>
-      <c r="H1551" t="inlineStr"/>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
@@ -49091,9 +49064,6 @@
           <t>[ROUTINE] Insider trade — Bailey Stephen (Director) sold 4,760 shares @ $42.26 ($201.2K) on 2026-08-26</t>
         </is>
       </c>
-      <c r="F1552" t="inlineStr"/>
-      <c r="G1552" t="inlineStr"/>
-      <c r="H1552" t="inlineStr"/>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
@@ -49121,9 +49091,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1553" t="inlineStr"/>
-      <c r="G1553" t="inlineStr"/>
-      <c r="H1553" t="inlineStr"/>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
@@ -49151,9 +49118,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F1554" t="inlineStr"/>
-      <c r="G1554" t="inlineStr"/>
-      <c r="H1554" t="inlineStr"/>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
@@ -49181,9 +49145,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$510.7K) on/after 08/28/2026</t>
         </is>
       </c>
-      <c r="F1555" t="inlineStr"/>
-      <c r="G1555" t="inlineStr"/>
-      <c r="H1555" t="inlineStr"/>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
@@ -49211,9 +49172,6 @@
           <t>[ROUTINE] Insider trade — Eisen Anthony Mathew (Director) sold 18,000 shares @ $82.60 ($1.49M) on 2026-08-25</t>
         </is>
       </c>
-      <c r="F1556" t="inlineStr"/>
-      <c r="G1556" t="inlineStr"/>
-      <c r="H1556" t="inlineStr"/>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
@@ -49241,9 +49199,6 @@
           <t>13 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1557" t="inlineStr"/>
-      <c r="G1557" t="inlineStr"/>
-      <c r="H1557" t="inlineStr"/>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
@@ -49271,9 +49226,6 @@
           <t>[ROUTINE] Insider trade — Brehm Kyle M. (Director) sold 1,000 shares @ $125.92 ($125.9K) on 2026-08-27</t>
         </is>
       </c>
-      <c r="F1558" t="inlineStr"/>
-      <c r="G1558" t="inlineStr"/>
-      <c r="H1558" t="inlineStr"/>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
@@ -49301,9 +49253,6 @@
           <t>[MATERIAL] Material event disclosure</t>
         </is>
       </c>
-      <c r="F1559" t="inlineStr"/>
-      <c r="G1559" t="inlineStr"/>
-      <c r="H1559" t="inlineStr"/>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
@@ -49331,9 +49280,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1560" t="inlineStr"/>
-      <c r="G1560" t="inlineStr"/>
-      <c r="H1560" t="inlineStr"/>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
@@ -49361,9 +49307,6 @@
           <t>9 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1561" t="inlineStr"/>
-      <c r="G1561" t="inlineStr"/>
-      <c r="H1561" t="inlineStr"/>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
@@ -49391,9 +49334,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Linford Michael (Officer) plans to sell 79,219 shares (~$6.14M) on/after 08/28/2026</t>
         </is>
       </c>
-      <c r="F1562" t="inlineStr"/>
-      <c r="G1562" t="inlineStr"/>
-      <c r="H1562" t="inlineStr"/>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
@@ -49421,9 +49361,6 @@
           <t>[ROUTINE] Insider trade — Siemiatkowski Sebastian (Chief Executive Officer) BOUGHT 692,506 shares @ $14.37 ($9.95M) on 2026-08-26</t>
         </is>
       </c>
-      <c r="F1563" t="inlineStr"/>
-      <c r="G1563" t="inlineStr"/>
-      <c r="H1563" t="inlineStr"/>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
@@ -49451,9 +49388,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1564" t="inlineStr"/>
-      <c r="G1564" t="inlineStr"/>
-      <c r="H1564" t="inlineStr"/>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
@@ -49481,9 +49415,6 @@
           <t>[ROUTINE] Insider trade — Robinhood Markets, Inc. (10%+ owner) sold 9,225 shares @ $26.61 ($245.5K) on 2026-08-25</t>
         </is>
       </c>
-      <c r="F1565" t="inlineStr"/>
-      <c r="G1565" t="inlineStr"/>
-      <c r="H1565" t="inlineStr"/>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
@@ -49511,9 +49442,6 @@
           <t>3 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1566" t="inlineStr"/>
-      <c r="G1566" t="inlineStr"/>
-      <c r="H1566" t="inlineStr"/>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
@@ -49541,9 +49469,6 @@
           <t>[ROUTINE] Insider trade — Mirgorodskaya Natalia (See Remarks) sold 913 shares @ $30.03 ($27.4K) on 2026-08-25</t>
         </is>
       </c>
-      <c r="F1567" t="inlineStr"/>
-      <c r="G1567" t="inlineStr"/>
-      <c r="H1567" t="inlineStr"/>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
@@ -49571,9 +49496,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — King David Randolph (Officer) plans to sell 21,024 shares (~$4.92M) on/after 08/28/2026</t>
         </is>
       </c>
-      <c r="F1568" t="inlineStr"/>
-      <c r="G1568" t="inlineStr"/>
-      <c r="H1568" t="inlineStr"/>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
@@ -49601,9 +49523,6 @@
           <t>[MATERIAL] Quarterly report</t>
         </is>
       </c>
-      <c r="F1569" t="inlineStr"/>
-      <c r="G1569" t="inlineStr"/>
-      <c r="H1569" t="inlineStr"/>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
@@ -49631,9 +49550,6 @@
           <t>[ROUTINE] Insider trade — James Tyson Hagale (President - Leggett &amp; Platt) granted 71,123 shares on 2026-08-26</t>
         </is>
       </c>
-      <c r="F1570" t="inlineStr"/>
-      <c r="G1570" t="inlineStr"/>
-      <c r="H1570" t="inlineStr"/>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
@@ -49661,9 +49577,6 @@
           <t>[ROUTINE] New insider — initial ownership statement</t>
         </is>
       </c>
-      <c r="F1571" t="inlineStr"/>
-      <c r="G1571" t="inlineStr"/>
-      <c r="H1571" t="inlineStr"/>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
@@ -49691,9 +49604,6 @@
           <t>[ROUTINE] Insider trade — Karl G Glassman (CEO - Leggett &amp; Platt) granted 549,004 shares on 2026-08-26</t>
         </is>
       </c>
-      <c r="F1572" t="inlineStr"/>
-      <c r="G1572" t="inlineStr"/>
-      <c r="H1572" t="inlineStr"/>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
@@ -49721,9 +49631,6 @@
           <t>[ROUTINE] New insider — initial ownership statement</t>
         </is>
       </c>
-      <c r="F1573" t="inlineStr"/>
-      <c r="G1573" t="inlineStr"/>
-      <c r="H1573" t="inlineStr"/>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
@@ -49751,9 +49658,6 @@
           <t>[ROUTINE] Insider trade — Scott L Thompson (CEO &amp; PRESIDENT) BOUGHT 30,000 shares @ $62.84 ($1.89M) on 2026-08-27</t>
         </is>
       </c>
-      <c r="F1574" t="inlineStr"/>
-      <c r="G1574" t="inlineStr"/>
-      <c r="H1574" t="inlineStr"/>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
@@ -49781,9 +49685,1185 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1575" t="inlineStr"/>
-      <c r="G1575" t="inlineStr"/>
-      <c r="H1575" t="inlineStr"/>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E1576" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E1577" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/content/terms.html</t>
+        </is>
+      </c>
+      <c r="E1578" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>https://www.bookingholdings.com/careers</t>
+        </is>
+      </c>
+      <c r="E1579" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>https://news.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E1580" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E1581" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>YOU</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>Clear Secure, Inc.</t>
+        </is>
+      </c>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>https://ir.clearme.com/news-events</t>
+        </is>
+      </c>
+      <c r="E1582" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>YOU</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>Clear Secure, Inc.</t>
+        </is>
+      </c>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>https://ir.clearme.com</t>
+        </is>
+      </c>
+      <c r="E1583" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>Choice Hotels International, Inc.</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>https://media.choicehotels.com</t>
+        </is>
+      </c>
+      <c r="E1584" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>Choice Hotels International, Inc.</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1046311/000119312526375580/d767448d8k.htm</t>
+        </is>
+      </c>
+      <c r="E1585" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com</t>
+        </is>
+      </c>
+      <c r="E1586" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E1587" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E1588" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E1589" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E1590" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E1591" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E1592" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E1593" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E1594" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>https://www.livenationentertainment.com/careers</t>
+        </is>
+      </c>
+      <c r="E1595" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1596" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E1597" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E1598" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E1599" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000195917326006543/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1600" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Wong Andrea L (Director) plans to sell 562 shares (~$22.8K) on/after 08/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>https://mediacenter.adp.com</t>
+        </is>
+      </c>
+      <c r="E1601" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>Paychex, Inc.</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>https://www.paychex.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E1602" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E1603" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1603" t="inlineStr"/>
+      <c r="G1603" t="inlineStr"/>
+      <c r="H1603" t="inlineStr"/>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/upgrade/website</t>
+        </is>
+      </c>
+      <c r="E1604" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F1604" t="inlineStr"/>
+      <c r="G1604" t="inlineStr"/>
+      <c r="H1604" t="inlineStr"/>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000162828026059480/xslF345X06/wk-form4_1788181980.xml</t>
+        </is>
+      </c>
+      <c r="E1605" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Gutler Ron (Director) sold 5,718 shares @ $85.42 ($488.4K) on 2026-08-27</t>
+        </is>
+      </c>
+      <c r="F1605" t="inlineStr"/>
+      <c r="G1605" t="inlineStr"/>
+      <c r="H1605" t="inlineStr"/>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E1606" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F1606" t="inlineStr"/>
+      <c r="G1606" t="inlineStr"/>
+      <c r="H1606" t="inlineStr"/>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E1607" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1607" t="inlineStr"/>
+      <c r="G1607" t="inlineStr"/>
+      <c r="H1607" t="inlineStr"/>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/duolingo</t>
+        </is>
+      </c>
+      <c r="E1608" t="inlineStr">
+        <is>
+          <t>4 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1608" t="inlineStr"/>
+      <c r="G1608" t="inlineStr"/>
+      <c r="H1608" t="inlineStr"/>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>Zillow Group Inc.</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>https://zillow.mediaroom.com</t>
+        </is>
+      </c>
+      <c r="E1609" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1609" t="inlineStr"/>
+      <c r="G1609" t="inlineStr"/>
+      <c r="H1609" t="inlineStr"/>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1610" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1610" t="inlineStr"/>
+      <c r="G1610" t="inlineStr"/>
+      <c r="H1610" t="inlineStr"/>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>https://investors.block.xyz</t>
+        </is>
+      </c>
+      <c r="E1611" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F1611" t="inlineStr"/>
+      <c r="G1611" t="inlineStr"/>
+      <c r="H1611" t="inlineStr"/>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>https://www.bill.com/careers</t>
+        </is>
+      </c>
+      <c r="E1612" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1612" t="inlineStr"/>
+      <c r="G1612" t="inlineStr"/>
+      <c r="H1612" t="inlineStr"/>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E1613" t="inlineStr">
+        <is>
+          <t>12 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1613" t="inlineStr"/>
+      <c r="G1613" t="inlineStr"/>
+      <c r="H1613" t="inlineStr"/>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>DAVE</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>Dave Inc.</t>
+        </is>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>https://dave.com/careers</t>
+        </is>
+      </c>
+      <c r="E1614" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1614" t="inlineStr"/>
+      <c r="G1614" t="inlineStr"/>
+      <c r="H1614" t="inlineStr"/>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/upstart</t>
+        </is>
+      </c>
+      <c r="E1615" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1615" t="inlineStr"/>
+      <c r="G1615" t="inlineStr"/>
+      <c r="H1615" t="inlineStr"/>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>https://www.upstart.com/blog</t>
+        </is>
+      </c>
+      <c r="E1616" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1616" t="inlineStr"/>
+      <c r="G1616" t="inlineStr"/>
+      <c r="H1616" t="inlineStr"/>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E1617" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1617" t="inlineStr"/>
+      <c r="G1617" t="inlineStr"/>
+      <c r="H1617" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1617"/>
+  <dimension ref="A1:H1677"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -50441,9 +50441,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1603" t="inlineStr"/>
-      <c r="G1603" t="inlineStr"/>
-      <c r="H1603" t="inlineStr"/>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
@@ -50471,9 +50468,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F1604" t="inlineStr"/>
-      <c r="G1604" t="inlineStr"/>
-      <c r="H1604" t="inlineStr"/>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
@@ -50501,9 +50495,6 @@
           <t>[ROUTINE] Insider trade — Gutler Ron (Director) sold 5,718 shares @ $85.42 ($488.4K) on 2026-08-27</t>
         </is>
       </c>
-      <c r="F1605" t="inlineStr"/>
-      <c r="G1605" t="inlineStr"/>
-      <c r="H1605" t="inlineStr"/>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
@@ -50531,9 +50522,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F1606" t="inlineStr"/>
-      <c r="G1606" t="inlineStr"/>
-      <c r="H1606" t="inlineStr"/>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
@@ -50561,9 +50549,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1607" t="inlineStr"/>
-      <c r="G1607" t="inlineStr"/>
-      <c r="H1607" t="inlineStr"/>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
@@ -50591,9 +50576,6 @@
           <t>4 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1608" t="inlineStr"/>
-      <c r="G1608" t="inlineStr"/>
-      <c r="H1608" t="inlineStr"/>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
@@ -50621,9 +50603,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1609" t="inlineStr"/>
-      <c r="G1609" t="inlineStr"/>
-      <c r="H1609" t="inlineStr"/>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
@@ -50651,9 +50630,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1610" t="inlineStr"/>
-      <c r="G1610" t="inlineStr"/>
-      <c r="H1610" t="inlineStr"/>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
@@ -50681,9 +50657,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F1611" t="inlineStr"/>
-      <c r="G1611" t="inlineStr"/>
-      <c r="H1611" t="inlineStr"/>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
@@ -50711,9 +50684,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1612" t="inlineStr"/>
-      <c r="G1612" t="inlineStr"/>
-      <c r="H1612" t="inlineStr"/>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
@@ -50741,9 +50711,6 @@
           <t>12 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1613" t="inlineStr"/>
-      <c r="G1613" t="inlineStr"/>
-      <c r="H1613" t="inlineStr"/>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
@@ -50771,9 +50738,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1614" t="inlineStr"/>
-      <c r="G1614" t="inlineStr"/>
-      <c r="H1614" t="inlineStr"/>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
@@ -50801,9 +50765,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1615" t="inlineStr"/>
-      <c r="G1615" t="inlineStr"/>
-      <c r="H1615" t="inlineStr"/>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
@@ -50831,9 +50792,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1616" t="inlineStr"/>
-      <c r="G1616" t="inlineStr"/>
-      <c r="H1616" t="inlineStr"/>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
@@ -50861,9 +50819,1701 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1617" t="inlineStr"/>
-      <c r="G1617" t="inlineStr"/>
-      <c r="H1617" t="inlineStr"/>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>Garmin Ltd.</t>
+        </is>
+      </c>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>https://newsroom.garmin.com</t>
+        </is>
+      </c>
+      <c r="E1618" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E1619" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1759509/000176086426000003/xslF345X06/form4-09012026_120910.xml</t>
+        </is>
+      </c>
+      <c r="E1620" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Lawee David (Director) sold 4,613 shares @ $17.33 ($80.0K) on 2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1759509/000178022726000006/xslF345X06/form4-09012026_120933.xml</t>
+        </is>
+      </c>
+      <c r="E1621" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hope Stephen W. (CHIEF ACCOUNTING OFFICER) sold 5,982 shares @ $17.34 ($103.7K) on 2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1759509/000200627826000004/xslF345X06/form4-09012026_120934.xml</t>
+        </is>
+      </c>
+      <c r="E1622" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Beggs Jill (Director) sold 2,307 shares @ $17.34 ($40.0K) on 2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E1623" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>https://www.bookingholdings.com/careers</t>
+        </is>
+      </c>
+      <c r="E1624" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E1625" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000195917326006546/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1626" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Blecharczyk Nathan (Officer) plans to sell 13,615 shares (~$2.55M) on/after 08/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>YOU</t>
+        </is>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>Clear Secure, Inc.</t>
+        </is>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>https://www.clearme.com/terms</t>
+        </is>
+      </c>
+      <c r="E1627" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>YOU</t>
+        </is>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>Clear Secure, Inc.</t>
+        </is>
+      </c>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>https://www.clearme.com/careers</t>
+        </is>
+      </c>
+      <c r="E1628" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com</t>
+        </is>
+      </c>
+      <c r="E1629" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1652044/000119312526377149/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1630" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Frances Arnold (Director) sold 82 shares @ $337.71 ($27.7K) on 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E1631" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1713445/000195004726008862/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1632" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Xyz Revocable Trust The (Director) plans to sell 18,000 shares (~$2.75M) on/after 08/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E1633" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810806/000192109426000971/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1634" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Barrysmith Mark (Former Affiliate) plans to sell 113,081 shares (~$4.74M) on/after 08/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E1635" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com/premium</t>
+        </is>
+      </c>
+      <c r="E1636" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1639920/000114036126035068/xslF345X06/form3.xml</t>
+        </is>
+      </c>
+      <c r="E1637" t="inlineStr">
+        <is>
+          <t>[ROUTINE] New insider — initial ownership statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>BBY</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>Best Buy Co., Inc.</t>
+        </is>
+      </c>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>https://www.bestbuy.com/site/help-topics/terms-and-conditions/pcmcat204400050067.c</t>
+        </is>
+      </c>
+      <c r="E1638" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E1639" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E1640" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E1641" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/000119312526377686/d94663d424b3.htm</t>
+        </is>
+      </c>
+      <c r="E1642" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 424B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>Warner Music Group Corp.</t>
+        </is>
+      </c>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>https://www.wmg.com/news/</t>
+        </is>
+      </c>
+      <c r="E1643" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E1644" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E1645" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E1646" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>https://quickbooks.intuit.com/pricing/</t>
+        </is>
+      </c>
+      <c r="E1647" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>Paychex, Inc.</t>
+        </is>
+      </c>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>https://www.paychex.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E1648" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>PAYC</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>Paycom Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1590955/000119312526376762/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1649" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Hadlock Terrell Shane (President/Chief Client Officer) sold 2,818 shares @ $237.82 ($670.2K) on 2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000134092226000004/xslF345X06/wk-form4_1788206548.xml</t>
+        </is>
+      </c>
+      <c r="E1650" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Conway Craig (Director) sold 3,145 shares @ $156.80 ($493.1K) on 2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000184537226000002/xslF345X06/wk-form4_1788206543.xml</t>
+        </is>
+      </c>
+      <c r="E1651" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Robinson Kenneth B. (Director) sold 800 shares @ $158.41 ($126.7K) on 2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159787026000011/xslF345X06/wk-form4_1788206535.xml</t>
+        </is>
+      </c>
+      <c r="E1652" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sarowitz Steven I (Director) sold 19,459 shares @ $157.78 ($3.07M) on 2026-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E1653" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1653" t="inlineStr"/>
+      <c r="G1653" t="inlineStr"/>
+      <c r="H1653" t="inlineStr"/>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000119312526377123/xslSCHEDULE_13D_X02/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1654" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Update to 5%+ active owner disclosure</t>
+        </is>
+      </c>
+      <c r="F1654" t="inlineStr"/>
+      <c r="G1654" t="inlineStr"/>
+      <c r="H1654" t="inlineStr"/>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D1655" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1594805/000119312526377117/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1655" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Shopify Strategic Holdings 3 LLC (10%+ owner) expiration: 344,383 Warrants to Purchase Series B Common Stock (Right to Buy) on 2026-08-31</t>
+        </is>
+      </c>
+      <c r="F1655" t="inlineStr"/>
+      <c r="G1655" t="inlineStr"/>
+      <c r="H1655" t="inlineStr"/>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D1656" t="inlineStr">
+        <is>
+          <t>https://www.wix.com/upgrade/website</t>
+        </is>
+      </c>
+      <c r="E1656" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F1656" t="inlineStr"/>
+      <c r="G1656" t="inlineStr"/>
+      <c r="H1656" t="inlineStr"/>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1657" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E1657" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F1657" t="inlineStr"/>
+      <c r="G1657" t="inlineStr"/>
+      <c r="H1657" t="inlineStr"/>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E1658" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1658" t="inlineStr"/>
+      <c r="G1658" t="inlineStr"/>
+      <c r="H1658" t="inlineStr"/>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E1659" t="inlineStr">
+        <is>
+          <t>5 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1659" t="inlineStr"/>
+      <c r="G1659" t="inlineStr"/>
+      <c r="H1659" t="inlineStr"/>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1579091/000189467426000004/xslF345X06/wk-form4_1788207154.xml</t>
+        </is>
+      </c>
+      <c r="E1660" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Laughton Mary Beth (Director) sold 10,236 shares @ $50.33 ($515.2K) on 2026-08-27</t>
+        </is>
+      </c>
+      <c r="F1660" t="inlineStr"/>
+      <c r="G1660" t="inlineStr"/>
+      <c r="H1660" t="inlineStr"/>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>Duolingo Inc.</t>
+        </is>
+      </c>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>https://blog.duolingo.com/</t>
+        </is>
+      </c>
+      <c r="E1661" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1661" t="inlineStr"/>
+      <c r="G1661" t="inlineStr"/>
+      <c r="H1661" t="inlineStr"/>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>https://investors.compass.com</t>
+        </is>
+      </c>
+      <c r="E1662" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F1662" t="inlineStr"/>
+      <c r="G1662" t="inlineStr"/>
+      <c r="H1662" t="inlineStr"/>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>COMP</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>Compass Inc.</t>
+        </is>
+      </c>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>https://www.compass.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1663" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1663" t="inlineStr"/>
+      <c r="G1663" t="inlineStr"/>
+      <c r="H1663" t="inlineStr"/>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>Block Inc. (fmr. Square)</t>
+        </is>
+      </c>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1512673/000195004726008854/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1664" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$495.5K) on/after 08/31/2026</t>
+        </is>
+      </c>
+      <c r="F1664" t="inlineStr"/>
+      <c r="G1664" t="inlineStr"/>
+      <c r="H1664" t="inlineStr"/>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1665" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000092189526002438/xslF345X06/form306297001b_08312026.xml</t>
+        </is>
+      </c>
+      <c r="E1665" t="inlineStr">
+        <is>
+          <t>[ROUTINE] New insider — initial ownership statement</t>
+        </is>
+      </c>
+      <c r="F1665" t="inlineStr"/>
+      <c r="G1665" t="inlineStr"/>
+      <c r="H1665" t="inlineStr"/>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1666" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000092189526002437/xslF345X06/form306297001a_08312026.xml</t>
+        </is>
+      </c>
+      <c r="E1666" t="inlineStr">
+        <is>
+          <t>[ROUTINE] New insider — initial ownership statement</t>
+        </is>
+      </c>
+      <c r="F1666" t="inlineStr"/>
+      <c r="G1666" t="inlineStr"/>
+      <c r="H1666" t="inlineStr"/>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>BILL Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1786352/000195004726008868/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1667" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Cieri Michael (Officer) plans to sell 10,754 shares (~$541.0K) on/after 08/31/2026</t>
+        </is>
+      </c>
+      <c r="F1667" t="inlineStr"/>
+      <c r="G1667" t="inlineStr"/>
+      <c r="H1667" t="inlineStr"/>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/toast</t>
+        </is>
+      </c>
+      <c r="E1668" t="inlineStr">
+        <is>
+          <t>8 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1668" t="inlineStr"/>
+      <c r="G1668" t="inlineStr"/>
+      <c r="H1668" t="inlineStr"/>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>TOST</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>Toast Inc.</t>
+        </is>
+      </c>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>https://investors.toasttab.com</t>
+        </is>
+      </c>
+      <c r="E1669" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+      <c r="F1669" t="inlineStr"/>
+      <c r="G1669" t="inlineStr"/>
+      <c r="H1669" t="inlineStr"/>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>Affirm Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="E1670" t="inlineStr">
+        <is>
+          <t>1 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1670" t="inlineStr"/>
+      <c r="G1670" t="inlineStr"/>
+      <c r="H1670" t="inlineStr"/>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood</t>
+        </is>
+      </c>
+      <c r="E1671" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1671" t="inlineStr"/>
+      <c r="G1671" t="inlineStr"/>
+      <c r="H1671" t="inlineStr"/>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>https://cdn.robinhood.com/assets/robinhood/legal/Robinhood-Customer-Agreement.pdf</t>
+        </is>
+      </c>
+      <c r="E1672" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F1672" t="inlineStr"/>
+      <c r="G1672" t="inlineStr"/>
+      <c r="H1672" t="inlineStr"/>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>https://robinhood.com/us/en/support/articles/trading-fees-on-robinhood/</t>
+        </is>
+      </c>
+      <c r="E1673" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F1673" t="inlineStr"/>
+      <c r="G1673" t="inlineStr"/>
+      <c r="H1673" t="inlineStr"/>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000095010326013297/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1674" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Robinhood Markets, Inc. (Parent Company / 10% Stockholder) plans to sell 1,003,737 shares (~$26.75M) on/after 09/01/2026</t>
+        </is>
+      </c>
+      <c r="F1674" t="inlineStr"/>
+      <c r="G1674" t="inlineStr"/>
+      <c r="H1674" t="inlineStr"/>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>Robinhood Markets Inc.</t>
+        </is>
+      </c>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000178387926000138/xslF345X06/wk-form4_1788208207.xml</t>
+        </is>
+      </c>
+      <c r="E1675" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Robinhood Markets, Inc. (10%+ owner) sold 13,778 shares @ $27.07 ($372.9K) on 2026-08-27</t>
+        </is>
+      </c>
+      <c r="F1675" t="inlineStr"/>
+      <c r="G1675" t="inlineStr"/>
+      <c r="H1675" t="inlineStr"/>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>Upstart Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>https://www.upstart.com/blog</t>
+        </is>
+      </c>
+      <c r="E1676" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1676" t="inlineStr"/>
+      <c r="G1676" t="inlineStr"/>
+      <c r="H1676" t="inlineStr"/>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>https://www.on-running.com/en-us/articles/</t>
+        </is>
+      </c>
+      <c r="E1677" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1677" t="inlineStr"/>
+      <c r="G1677" t="inlineStr"/>
+      <c r="H1677" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/company_urls_jc.xlsx
+++ b/config/company_urls_jc.xlsx
@@ -7203,7 +7203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1677"/>
+  <dimension ref="A1:H1767"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -51791,9 +51791,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1653" t="inlineStr"/>
-      <c r="G1653" t="inlineStr"/>
-      <c r="H1653" t="inlineStr"/>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
@@ -51821,9 +51818,6 @@
           <t>[MATERIAL] Update to 5%+ active owner disclosure</t>
         </is>
       </c>
-      <c r="F1654" t="inlineStr"/>
-      <c r="G1654" t="inlineStr"/>
-      <c r="H1654" t="inlineStr"/>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
@@ -51851,9 +51845,6 @@
           <t>[ROUTINE] Insider trade — Shopify Strategic Holdings 3 LLC (10%+ owner) expiration: 344,383 Warrants to Purchase Series B Common Stock (Right to Buy) on 2026-08-31</t>
         </is>
       </c>
-      <c r="F1655" t="inlineStr"/>
-      <c r="G1655" t="inlineStr"/>
-      <c r="H1655" t="inlineStr"/>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
@@ -51881,9 +51872,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F1656" t="inlineStr"/>
-      <c r="G1656" t="inlineStr"/>
-      <c r="H1656" t="inlineStr"/>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
@@ -51911,9 +51899,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F1657" t="inlineStr"/>
-      <c r="G1657" t="inlineStr"/>
-      <c r="H1657" t="inlineStr"/>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
@@ -51941,9 +51926,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1658" t="inlineStr"/>
-      <c r="G1658" t="inlineStr"/>
-      <c r="H1658" t="inlineStr"/>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
@@ -51971,9 +51953,6 @@
           <t>5 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1659" t="inlineStr"/>
-      <c r="G1659" t="inlineStr"/>
-      <c r="H1659" t="inlineStr"/>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
@@ -52001,9 +51980,6 @@
           <t>[ROUTINE] Insider trade — Laughton Mary Beth (Director) sold 10,236 shares @ $50.33 ($515.2K) on 2026-08-27</t>
         </is>
       </c>
-      <c r="F1660" t="inlineStr"/>
-      <c r="G1660" t="inlineStr"/>
-      <c r="H1660" t="inlineStr"/>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
@@ -52031,9 +52007,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1661" t="inlineStr"/>
-      <c r="G1661" t="inlineStr"/>
-      <c r="H1661" t="inlineStr"/>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
@@ -52061,9 +52034,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F1662" t="inlineStr"/>
-      <c r="G1662" t="inlineStr"/>
-      <c r="H1662" t="inlineStr"/>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
@@ -52091,9 +52061,6 @@
           <t>careers: change detected</t>
         </is>
       </c>
-      <c r="F1663" t="inlineStr"/>
-      <c r="G1663" t="inlineStr"/>
-      <c r="H1663" t="inlineStr"/>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
@@ -52121,9 +52088,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — M Eisen Anthony (Director) plans to sell 6,000 shares (~$495.5K) on/after 08/31/2026</t>
         </is>
       </c>
-      <c r="F1664" t="inlineStr"/>
-      <c r="G1664" t="inlineStr"/>
-      <c r="H1664" t="inlineStr"/>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
@@ -52151,9 +52115,6 @@
           <t>[ROUTINE] New insider — initial ownership statement</t>
         </is>
       </c>
-      <c r="F1665" t="inlineStr"/>
-      <c r="G1665" t="inlineStr"/>
-      <c r="H1665" t="inlineStr"/>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
@@ -52181,9 +52142,6 @@
           <t>[ROUTINE] New insider — initial ownership statement</t>
         </is>
       </c>
-      <c r="F1666" t="inlineStr"/>
-      <c r="G1666" t="inlineStr"/>
-      <c r="H1666" t="inlineStr"/>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
@@ -52211,9 +52169,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Cieri Michael (Officer) plans to sell 10,754 shares (~$541.0K) on/after 08/31/2026</t>
         </is>
       </c>
-      <c r="F1667" t="inlineStr"/>
-      <c r="G1667" t="inlineStr"/>
-      <c r="H1667" t="inlineStr"/>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
@@ -52241,9 +52196,6 @@
           <t>8 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1668" t="inlineStr"/>
-      <c r="G1668" t="inlineStr"/>
-      <c r="H1668" t="inlineStr"/>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
@@ -52271,9 +52223,6 @@
           <t>investor_relations: change detected</t>
         </is>
       </c>
-      <c r="F1669" t="inlineStr"/>
-      <c r="G1669" t="inlineStr"/>
-      <c r="H1669" t="inlineStr"/>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
@@ -52301,9 +52250,6 @@
           <t>1 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1670" t="inlineStr"/>
-      <c r="G1670" t="inlineStr"/>
-      <c r="H1670" t="inlineStr"/>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
@@ -52331,9 +52277,6 @@
           <t>2 new non-senior roles posted</t>
         </is>
       </c>
-      <c r="F1671" t="inlineStr"/>
-      <c r="G1671" t="inlineStr"/>
-      <c r="H1671" t="inlineStr"/>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
@@ -52361,9 +52304,6 @@
           <t>terms: change detected</t>
         </is>
       </c>
-      <c r="F1672" t="inlineStr"/>
-      <c r="G1672" t="inlineStr"/>
-      <c r="H1672" t="inlineStr"/>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
@@ -52391,9 +52331,6 @@
           <t>pricing: change detected</t>
         </is>
       </c>
-      <c r="F1673" t="inlineStr"/>
-      <c r="G1673" t="inlineStr"/>
-      <c r="H1673" t="inlineStr"/>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
@@ -52421,9 +52358,6 @@
           <t>[ROUTINE] Notice of proposed insider sale — Robinhood Markets, Inc. (Parent Company / 10% Stockholder) plans to sell 1,003,737 shares (~$26.75M) on/after 09/01/2026</t>
         </is>
       </c>
-      <c r="F1674" t="inlineStr"/>
-      <c r="G1674" t="inlineStr"/>
-      <c r="H1674" t="inlineStr"/>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
@@ -52451,9 +52385,6 @@
           <t>[ROUTINE] Insider trade — Robinhood Markets, Inc. (10%+ owner) sold 13,778 shares @ $27.07 ($372.9K) on 2026-08-27</t>
         </is>
       </c>
-      <c r="F1675" t="inlineStr"/>
-      <c r="G1675" t="inlineStr"/>
-      <c r="H1675" t="inlineStr"/>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
@@ -52481,9 +52412,6 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1676" t="inlineStr"/>
-      <c r="G1676" t="inlineStr"/>
-      <c r="H1676" t="inlineStr"/>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
@@ -52511,9 +52439,2571 @@
           <t>newsroom: change detected</t>
         </is>
       </c>
-      <c r="F1677" t="inlineStr"/>
-      <c r="G1677" t="inlineStr"/>
-      <c r="H1677" t="inlineStr"/>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>https://www.lyft.com/blog</t>
+        </is>
+      </c>
+      <c r="E1678" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>Lyft, Inc.</t>
+        </is>
+      </c>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1759509/000192109426000979/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1679" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Llewellyn Lindsay Catherine (Officer) plans to sell 13,204 shares (~$219.7K) on/after 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>EXPE</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>Expedia Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>https://careers.expediagroup.com</t>
+        </is>
+      </c>
+      <c r="E1680" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1681" t="inlineStr">
+        <is>
+          <t>https://www.bookingholdings.com/careers</t>
+        </is>
+      </c>
+      <c r="E1681" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1075531/000187574126000006/xslF345X06/form4-09012026_040901.xml</t>
+        </is>
+      </c>
+      <c r="E1682" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Pisano Paulo (CHIEF HUMAN RESOURCES OFFICER) sold 3,000 shares @ $203.48 ($610.4K) on 2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>BKNG</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>Booking Holdings Inc.</t>
+        </is>
+      </c>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1075531/000196922326000976/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1683" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Robert J Jr Mylod (Chairman) plans to sell 1,000 shares (~$198.4K) on/after 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>https://news.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E1684" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com</t>
+        </is>
+      </c>
+      <c r="E1685" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1686" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000119312526379365/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1686" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form 4/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1687" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000119312526379115/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1687" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Chesky Brian (CEO and Chairman) gift: 76,500 shares on 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1688" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000119312526379003/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1688" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Blecharczyk Nathan (Chief Strategy Officer) sold 70,775 shares @ $190.05 ($13.45M) on 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>Airbnb, Inc.</t>
+        </is>
+      </c>
+      <c r="D1689" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1559720/000195917326006591/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1689" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Bernstein David C (Officer) plans to sell 5,224 shares (~$953.3K) on/after 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>Choice Hotels International, Inc.</t>
+        </is>
+      </c>
+      <c r="D1690" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1046311/000119312526378502/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1690" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Dragisich Dominic (President &amp; CEO) granted 9,675 shares on 2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>Choice Hotels International, Inc.</t>
+        </is>
+      </c>
+      <c r="D1691" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1046311/000119312526378054/xslF345X06/ownership.xml</t>
+        </is>
+      </c>
+      <c r="E1691" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Pacious Patrick (Director) 46,122 shares withheld for taxes (vest event) on 2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="D1692" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com</t>
+        </is>
+      </c>
+      <c r="E1692" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>GOOG</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="D1693" t="inlineStr">
+        <is>
+          <t>https://blog.google</t>
+        </is>
+      </c>
+      <c r="E1693" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>SNAP</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>Snap Inc.</t>
+        </is>
+      </c>
+      <c r="D1694" t="inlineStr">
+        <is>
+          <t>https://newsroom.snap.com</t>
+        </is>
+      </c>
+      <c r="E1694" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D1695" t="inlineStr">
+        <is>
+          <t>https://policy.pinterest.com/en/terms-of-service</t>
+        </is>
+      </c>
+      <c r="E1695" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D1696" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000150629326000121/xslF345X06/wk-form4_1788310788.xml</t>
+        </is>
+      </c>
+      <c r="E1696" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Jewell Renee Marie-Bentley (Chief Accounting Officer) granted 108,604 shares on 2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>Pinterest, Inc.</t>
+        </is>
+      </c>
+      <c r="D1697" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1506293/000192109426000980/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1697" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Silbermann Benjamin (Director) plans to sell 46,875 shares (~$1.01M) on/after 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>Reddit, Inc.</t>
+        </is>
+      </c>
+      <c r="D1698" t="inlineStr">
+        <is>
+          <t>https://redditinc.com/careers</t>
+        </is>
+      </c>
+      <c r="E1698" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1699" t="inlineStr">
+        <is>
+          <t>https://careers.unity.com</t>
+        </is>
+      </c>
+      <c r="E1699" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>Unity Software Inc.</t>
+        </is>
+      </c>
+      <c r="D1700" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1810806/000204205626000010/xslF345X06/wk-form4_1788296564.xml</t>
+        </is>
+      </c>
+      <c r="E1700" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Blum Alexander (SVP, Chief Operating Officer) sold 43,556 shares @ $43.51 ($1.90M) on 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D1701" t="inlineStr">
+        <is>
+          <t>https://about.netflix.com/newsroom</t>
+        </is>
+      </c>
+      <c r="E1701" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D1702" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1065280/000162828026059826/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1702" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Reed Hastings (Director) plans to sell 311,300 shares (~$25.20M) on/after 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1703" t="inlineStr">
+        <is>
+          <t>https://www.spotify.com/premium</t>
+        </is>
+      </c>
+      <c r="E1703" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>SPOT</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>Spotify Technology S.A.</t>
+        </is>
+      </c>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>https://www.lifeatspotify.com</t>
+        </is>
+      </c>
+      <c r="E1704" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1705" t="inlineStr">
+        <is>
+          <t>https://www.disneyplus.com/welcome</t>
+        </is>
+      </c>
+      <c r="E1705" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>The Walt Disney Company</t>
+        </is>
+      </c>
+      <c r="D1706" t="inlineStr">
+        <is>
+          <t>https://jobs.disneycareers.com</t>
+        </is>
+      </c>
+      <c r="E1706" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D1707" t="inlineStr">
+        <is>
+          <t>https://foxcareers.com</t>
+        </is>
+      </c>
+      <c r="E1707" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1754301/999999999526002857/xslEFFECTX01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1708" t="inlineStr">
+        <is>
+          <t>[UNKNOWN] Form EFFECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>WMG</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>Warner Music Group Corp.</t>
+        </is>
+      </c>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>https://www.wmg.com/news/</t>
+        </is>
+      </c>
+      <c r="E1709" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>LYV</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>Live Nation Entertainment, Inc.</t>
+        </is>
+      </c>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>https://investors.livenationentertainment.com</t>
+        </is>
+      </c>
+      <c r="E1710" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>STUB</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>StubHub Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>https://www.stubhub.com/careers/</t>
+        </is>
+      </c>
+      <c r="E1711" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>LAMR</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>Lamar Advertising Company</t>
+        </is>
+      </c>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1090425/000119312526378592/d81164d8k.htm</t>
+        </is>
+      </c>
+      <c r="E1712" t="inlineStr">
+        <is>
+          <t>[MATERIAL] Material event disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>TTWO</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>Take-Two Interactive Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D1713" t="inlineStr">
+        <is>
+          <t>https://ir.take2games.com</t>
+        </is>
+      </c>
+      <c r="E1713" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>https://www.ea.com/news</t>
+        </is>
+      </c>
+      <c r="E1714" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>Electronic Arts Inc.</t>
+        </is>
+      </c>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>https://ir.ea.com</t>
+        </is>
+      </c>
+      <c r="E1715" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000149075426000004/xslF345X06/wk-form4_1788299541.xml</t>
+        </is>
+      </c>
+      <c r="E1716" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Wong Andrea L (Director) sold 562 shares @ $40.89 ($23.0K) on 2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1717" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000195004726008956/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1717" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — And Christina Baszucki Liv Tr Greg (Director) plans to sell 8,333 shares (~$344.1K) on/after 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>RBLX</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>Roblox Corporation</t>
+        </is>
+      </c>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1315098/000195004726008943/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1718" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Greg Baszucki (Director) plans to sell 8,333 shares (~$344.1K) on/after 09/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="D1719" t="inlineStr">
+        <is>
+          <t>https://investors.intuit.com</t>
+        </is>
+      </c>
+      <c r="E1719" t="inlineStr">
+        <is>
+          <t>investor_relations: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D1720" t="inlineStr">
+        <is>
+          <t>https://mediacenter.adp.com</t>
+        </is>
+      </c>
+      <c r="E1720" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>Automatic Data Processing, Inc.</t>
+        </is>
+      </c>
+      <c r="D1721" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/8670/000195917326006620/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1721" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — DeSilva Joseph (Officer) plans to sell 6,512 shares (~$1.84M) on/after 09/02/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="D1722" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1591698/000159787026000013/xslF345X06/wk-form4_1788292976.xml</t>
+        </is>
+      </c>
+      <c r="E1722" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sarowitz Steven I (Director) sold 5,100 shares @ $158.56 ($808.6K) on 2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="D1723" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="E1723" t="inlineStr">
+        <is>
+          <t>careers: change detected</t>
+        </is>
+      </c>
+      <c r="F1723" t="inlineStr"/>
+      <c r="G1723" t="inlineStr"/>
+      <c r="H1723" t="inlineStr"/>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D1724" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000162828026059988/xslF345X06/wk-form4_1788359347.xml</t>
+        </is>
+      </c>
+      <c r="E1724" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Meyer Shelly B (Chief People Officer) sold 479 shares @ $95.00 ($45.5K) on 2026-09-01; BOUGHT 479 shares @ $59.89 ($28.7K) on 2026-08-31</t>
+        </is>
+      </c>
+      <c r="F1724" t="inlineStr"/>
+      <c r="G1724" t="inlineStr"/>
+      <c r="H1724" t="inlineStr"/>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D1725" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000162828026059986/xslF345X06/wk-form4_1788359303.xml</t>
+        </is>
+      </c>
+      <c r="E1725" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Even-Haim Yaniv (CTO) sold 320 shares @ $95.00 ($30.4K) on 2026-09-01; BOUGHT 320 shares @ $59.89 ($19.2K) on 2026-08-31</t>
+        </is>
+      </c>
+      <c r="F1725" t="inlineStr"/>
+      <c r="G1725" t="inlineStr"/>
+      <c r="H1725" t="inlineStr"/>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D1726" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000162828026059984/xslF345X06/wk-form4_1788359211.xml</t>
+        </is>
+      </c>
+      <c r="E1726" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Shai Omer (CMO) sold 490 shares @ $95.00 ($46.5K) on 2026-09-01; BOUGHT 490 shares @ $59.89 ($29.3K) on 2026-08-31</t>
+        </is>
+      </c>
+      <c r="F1726" t="inlineStr"/>
+      <c r="G1726" t="inlineStr"/>
+      <c r="H1726" t="inlineStr"/>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D1727" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000162828026059982/xslF345X06/wk-form4_1788359133.xml</t>
+        </is>
+      </c>
+      <c r="E1727" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Shemesh Lior (CFO) sold 456 shares @ $95.00 ($43.3K) on 2026-09-01; BOUGHT 456 shares @ $59.89 ($27.3K) on 2026-08-31</t>
+        </is>
+      </c>
+      <c r="F1727" t="inlineStr"/>
+      <c r="G1727" t="inlineStr"/>
+      <c r="H1727" t="inlineStr"/>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D1728" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000162828026059979/xslF345X06/wk-form4_1788358946.xml</t>
+        </is>
+      </c>
+      <c r="E1728" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Zohar Nir (President) sold 647 shares @ $95.00 ($61.5K) on 2026-09-01; BOUGHT 647 shares @ $59.89 ($38.7K) on 2026-08-31</t>
+        </is>
+      </c>
+      <c r="F1728" t="inlineStr"/>
+      <c r="G1728" t="inlineStr"/>
+      <c r="H1728" t="inlineStr"/>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D1729" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000162828026059977/xslF345X06/wk-form4_1788358722.xml</t>
+        </is>
+      </c>
+      <c r="E1729" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Abrahami Avishai (Chief Executive Officer) sold 709 shares @ $95.00 ($67.4K) on 2026-09-01; BOUGHT 709 shares @ $59.89 ($42.5K) on 2026-08-31</t>
+        </is>
+      </c>
+      <c r="F1729" t="inlineStr"/>
+      <c r="G1729" t="inlineStr"/>
+      <c r="H1729" t="inlineStr"/>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D1730" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000197640826000795/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1730" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Nir Zohar (Officer) plans to sell 376 shares (~$33.2K) on/after 09/01/2026</t>
+        </is>
+      </c>
+      <c r="F1730" t="inlineStr"/>
+      <c r="G1730" t="inlineStr"/>
+      <c r="H1730" t="inlineStr"/>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>WIX</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>Wix.com Ltd.</t>
+        </is>
+      </c>
+      <c r="D1731" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1576789/000197640826000794/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1731" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Avishai Abrahami (Officer) plans to sell 654 shares (~$57.7K) on/after 09/01/2026</t>
+        </is>
+      </c>
+      <c r="F1731" t="inlineStr"/>
+      <c r="G1731" t="inlineStr"/>
+      <c r="H1731" t="inlineStr"/>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>GoDaddy Inc.</t>
+        </is>
+      </c>
+      <c r="D1732" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1609711/000160971126000098/xslF345X06/wk-form4_1788307453.xml</t>
+        </is>
+      </c>
+      <c r="E1732" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Insider trade — Sweet Leah (Director) sold 650 shares @ $97.41 ($63.3K) on 2026-08-28</t>
+        </is>
+      </c>
+      <c r="F1732" t="inlineStr"/>
+      <c r="G1732" t="inlineStr"/>
+      <c r="H1732" t="inlineStr"/>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>GoDaddy Inc.</t>
+        </is>
+      </c>
+      <c r="D1733" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1609711/000195004726008904/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1733" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Franklin Sine Jared (Officer) plans to sell 3,000 shares (~$305.8K) on/after 09/01/2026</t>
+        </is>
+      </c>
+      <c r="F1733" t="inlineStr"/>
+      <c r="G1733" t="inlineStr"/>
+      <c r="H1733" t="inlineStr"/>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>GoDaddy Inc.</t>
+        </is>
+      </c>
+      <c r="D1734" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1609711/000195004726008886/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1734" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Zarmi Sigal (Director) plans to sell 350 shares (~$34.1K) on/after 09/01/2026</t>
+        </is>
+      </c>
+      <c r="F1734" t="inlineStr"/>
+      <c r="G1734" t="inlineStr"/>
+      <c r="H1734" t="inlineStr"/>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>GoDaddy Inc.</t>
+        </is>
+      </c>
+      <c r="D1735" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1609711/000195004726008884/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1735" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Bhutani Amanpal (Officer) plans to sell 4,500 shares (~$438.5K) on/after 09/01/2026</t>
+        </is>
+      </c>
+      <c r="F1735" t="inlineStr"/>
+      <c r="G1735" t="inlineStr"/>
+      <c r="H1735" t="inlineStr"/>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>GoDaddy Inc.</t>
+        </is>
+      </c>
+      <c r="D1736" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1609711/000195004726008883/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1736" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — M Sweet Leah (Director) plans to sell 325 shares (~$31.7K) on/after 09/01/2026</t>
+        </is>
+      </c>
+      <c r="F1736" t="inlineStr"/>
+      <c r="G1736" t="inlineStr"/>
+      <c r="H1736" t="inlineStr"/>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1737" t="inlineStr">
+        <is>
+          <t>https://www.ebay.com/help/policies/member-behaviour-policies/user-agreement?id=4259</t>
+        </is>
+      </c>
+      <c r="E1737" t="inlineStr">
+        <is>
+          <t>terms: change detected</t>
+        </is>
+      </c>
+      <c r="F1737" t="inlineStr"/>
+      <c r="G1737" t="inlineStr"/>
+      <c r="H1737" t="inlineStr"/>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>EBAY</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>eBay Inc.</t>
+        </is>
+      </c>
+      <c r="D1738" t="inlineStr">
+        <is>
+          <t>https://www.ebayinc.com/stories/news/</t>
+        </is>
+      </c>
+      <c r="E1738" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1738" t="inlineStr"/>
+      <c r="G1738" t="inlineStr"/>
+      <c r="H1738" t="inlineStr"/>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D1739" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1370637/000195004726008921/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1739" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Fred Wilson (Director) plans to sell 20,000 shares (~$1.63M) on/after 09/01/2026</t>
+        </is>
+      </c>
+      <c r="F1739" t="inlineStr"/>
+      <c r="G1739" t="inlineStr"/>
+      <c r="H1739" t="inlineStr"/>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>ETSY</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>Etsy Inc.</t>
+        </is>
+      </c>
+      <c r="D1740" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1370637/000196922326000977/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1740" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Silverman Josh (Officer) plans to sell 11,696 shares (~$947.4K) on/after 09/01/2026</t>
+        </is>
+      </c>
+      <c r="F1740" t="inlineStr"/>
+      <c r="G1740" t="inlineStr"/>
+      <c r="H1740" t="inlineStr"/>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1741" t="inlineStr">
+        <is>
+          <t>https://about.doordash.com/en-us/news</t>
+        </is>
+      </c>
+      <c r="E1741" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1741" t="inlineStr"/>
+      <c r="G1741" t="inlineStr"/>
+      <c r="H1741" t="inlineStr"/>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1742" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726008968/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1742" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Ravi Inukonda (Officer) plans to sell 17,061 shares (~$3.95M) on/after 09/01/2026</t>
+        </is>
+      </c>
+      <c r="F1742" t="inlineStr"/>
+      <c r="G1742" t="inlineStr"/>
+      <c r="H1742" t="inlineStr"/>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>DoorDash Inc.</t>
+        </is>
+      </c>
+      <c r="D1743" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1792789/000195004726008938/xsl144X01/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="E1743" t="inlineStr">
+        <is>
+          <t>[ROUTINE] Notice of proposed insider sale — Xu Tony (Director) plans to sell 16,667 shares (~$3.86M) on/after 09/01/2026</t>
+        </is>
+      </c>
+      <c r="F1743" t="inlineStr"/>
+      <c r="G1743" t="inlineStr"/>
+      <c r="H1743" t="inlineStr"/>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1744" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="E1744" t="inlineStr">
+        <is>
+          <t>2 new non-senior roles posted</t>
+        </is>
+      </c>
+      <c r="F1744" t="inlineStr"/>
+      <c r="G1744" t="inlineStr"/>
+      <c r="H1744" t="inlineStr"/>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1745" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/instacart-plus</t>
+        </is>
+      </c>
+      <c r="E1745" t="inlineStr">
+        <is>
+          <t>pricing: change detected</t>
+        </is>
+      </c>
+      <c r="F1745" t="inlineStr"/>
+      <c r="G1745" t="inlineStr"/>
+      <c r="H1745" t="inlineStr"/>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>Maplebear Inc. (Instacart)</t>
+        </is>
+      </c>
+      <c r="D1746" t="inlineStr">
+        <is>
+          <t>https://www.instacart.com/company/newsroom</t>
+        </is>
+      </c>
+      <c r="E1746" t="inlineStr">
+        <is>
+          <t>newsroom: change detected</t>
+        </is>
+      </c>
+      <c r="F1746" t="inlineStr"/>
+      <c r="G1746" t="inlineStr"/>
+      <c r="H1746" t="inlineStr"/>
+    </row>
+    <